--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -70,7 +70,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +90,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -158,7 +163,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -550,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 16-Apr-2026  16:23:37    |    Closing Price Date: 16-Apr-2026</t>
+          <t>Scan Run: 17-Apr-2026  16:35:34    |    Closing Price Date: 17-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -589,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>82</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>35.6</v>
+        <v>40.4</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>16-Apr-2026  16:23:37</t>
+          <t>17-Apr-2026  16:35:34</t>
         </is>
       </c>
     </row>
@@ -620,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 96.8% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 98.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 82.0% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 86.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 35.6% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.4% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -648,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 242 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 245 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 205 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 216 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 89 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 101 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -756,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>574.35</v>
+        <v>584.95</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>527.61</v>
+        <v>533.0700000000001</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>557.99</v>
+        <v>559.05</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>704.33</v>
+        <v>701.91</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -800,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>435.2</v>
+        <v>436.8</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>430.64</v>
+        <v>431.23</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>432.21</v>
+        <v>432.39</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>457.16</v>
+        <v>457.04</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -844,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>368.4</v>
+        <v>373.2</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>353.24</v>
+        <v>355.14</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>361.26</v>
+        <v>361.73</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>407.2</v>
+        <v>406.47</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -888,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>700</v>
+        <v>697.75</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>669.89</v>
+        <v>672.54</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>687.5599999999999</v>
+        <v>687.96</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>745.46</v>
+        <v>744.51</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -932,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2340.4</v>
+        <v>2361.7</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2303.99</v>
+        <v>2309.48</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2179.65</v>
+        <v>2186.79</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1768</v>
+        <v>1773.91</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -976,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>306.15</v>
+        <v>307.4</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>287.34</v>
+        <v>289.25</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>288.7</v>
+        <v>289.43</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>302.38</v>
+        <v>302.46</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1020,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1187.4</v>
+        <v>1179.8</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1120.9</v>
+        <v>1126.51</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1055.61</v>
+        <v>1060.48</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>921.64</v>
+        <v>924.01</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1064,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>826.9</v>
+        <v>834.05</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>755.1799999999999</v>
+        <v>762.6900000000001</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>782.55</v>
+        <v>784.5700000000001</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>874.03</v>
+        <v>872.5</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1108,29 +1113,29 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>485.15</v>
+        <v>489.55</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>466.51</v>
+        <v>468.7</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>485.99</v>
+        <v>486.13</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>562.76</v>
+        <v>562.03</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
@@ -1152,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1071.2</v>
+        <v>1069.65</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1005.47</v>
+        <v>1011.58</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>963.88</v>
+        <v>968.02</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>950.5599999999999</v>
+        <v>951.74</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1196,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>8.31</v>
+        <v>8.43</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.01</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>18.59</v>
+        <v>18.48</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1240,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>539.5</v>
+        <v>573.8</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>462.78</v>
+        <v>473.35</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>472.38</v>
+        <v>476.36</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>497.76</v>
+        <v>498.56</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1284,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1266.4</v>
+        <v>1288</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1263.69</v>
+        <v>1266.01</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1263.53</v>
+        <v>1264.49</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1172.67</v>
+        <v>1173.51</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1328,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>121.09</v>
+        <v>121.66</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>113.47</v>
+        <v>114.25</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>117.31</v>
+        <v>117.48</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>135.81</v>
+        <v>136.07</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1372,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>610.5</v>
+        <v>606.65</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>593.73</v>
+        <v>594.96</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>580.26</v>
+        <v>581.3</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>590.71</v>
+        <v>590.77</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1416,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>473.8</v>
+        <v>472.65</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>441.6</v>
+        <v>444.56</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>442.7</v>
+        <v>443.87</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>472.35</v>
+        <v>472.36</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1460,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>385.15</v>
+        <v>386.75</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>369.51</v>
+        <v>371.15</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>356.43</v>
+        <v>357.62</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>341.84</v>
+        <v>341.51</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1504,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>137.74</v>
+        <v>138.82</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>121.61</v>
+        <v>123.25</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>129.73</v>
+        <v>130.08</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>166.57</v>
+        <v>166.21</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1548,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1074.7</v>
+        <v>1093.45</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>980.1900000000001</v>
+        <v>990.98</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>963.6799999999999</v>
+        <v>968.77</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>957.13</v>
+        <v>958.53</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1592,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>922.8</v>
+        <v>922.6</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>842.46</v>
+        <v>850.09</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>880.0700000000001</v>
+        <v>881.74</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1096.78</v>
+        <v>1092.34</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1636,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1101.95</v>
+        <v>1119.3</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>996.34</v>
+        <v>1008.05</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>971.78</v>
+        <v>977.5700000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>945.08</v>
+        <v>946.42</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1680,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1392.1</v>
+        <v>1473.3</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1290.53</v>
+        <v>1307.94</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1196.75</v>
+        <v>1207.59</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>943.6900000000001</v>
+        <v>948.22</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1724,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>15.36</v>
+        <v>15.21</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.9</v>
+        <v>14.93</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.36</v>
+        <v>15.35</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -1768,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>363.78</v>
+        <v>362.36</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>298.72</v>
+        <v>304.78</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>320.3</v>
+        <v>321.95</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>464.24</v>
+        <v>463.51</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1812,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1861.3</v>
+        <v>1904.3</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1633.44</v>
+        <v>1659.24</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1600.66</v>
+        <v>1612.57</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1606.2</v>
+        <v>1607.53</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1856,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>387.6</v>
+        <v>391.4</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>365.29</v>
+        <v>367.78</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>379.04</v>
+        <v>379.52</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>479.63</v>
+        <v>478.16</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1900,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1146.65</v>
+        <v>1139.3</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1067.78</v>
+        <v>1074.59</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1081.35</v>
+        <v>1083.63</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1247.27</v>
+        <v>1245.11</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1944,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>485.25</v>
+        <v>486.05</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>453.91</v>
+        <v>456.97</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>464.52</v>
+        <v>465.36</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>548.49</v>
+        <v>547.15</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1988,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>621</v>
+        <v>624.95</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>569.16</v>
+        <v>574.47</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>586.51</v>
+        <v>588.02</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>608.1</v>
+        <v>608.4</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2032,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>208.9</v>
+        <v>214.1</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>195.29</v>
+        <v>197.09</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>187.65</v>
+        <v>188.69</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>161</v>
+        <v>161.53</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2076,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2616</v>
+        <v>2753.2</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2395.73</v>
+        <v>2429.78</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2441.47</v>
+        <v>2453.69</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2741.05</v>
+        <v>2739.98</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2101,9 +2106,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
@@ -2120,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>970.45</v>
+        <v>976.15</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>908.22</v>
+        <v>914.6900000000001</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>938.35</v>
+        <v>939.84</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1079.05</v>
+        <v>1077.98</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2164,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>601.95</v>
+        <v>623.4</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>581.0599999999999</v>
+        <v>585.09</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>591.33</v>
+        <v>592.58</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>580.83</v>
+        <v>581.09</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2208,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>485.1</v>
+        <v>497.7</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>441.48</v>
+        <v>446.83</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>455.45</v>
+        <v>457.11</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>518.64</v>
+        <v>519.6</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2252,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1328.9</v>
+        <v>1347</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1268.01</v>
+        <v>1275.53</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1304.89</v>
+        <v>1306.54</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2296,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>482.85</v>
+        <v>490.2</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>467.75</v>
+        <v>469.89</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>456.06</v>
+        <v>457.4</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>435.38</v>
+        <v>435.59</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2340,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>317.6</v>
+        <v>318</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>294.26</v>
+        <v>296.52</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>301.8</v>
+        <v>302.43</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>356.54</v>
+        <v>355.77</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2384,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>402.7</v>
+        <v>399.85</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>383.92</v>
+        <v>385.43</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>390.45</v>
+        <v>390.82</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>395.09</v>
+        <v>395.03</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2428,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1797.9</v>
+        <v>1858</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1782.38</v>
+        <v>1789.58</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1936.07</v>
+        <v>1933.01</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2190.15</v>
+        <v>2186.26</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2472,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>300.2</v>
+        <v>306.95</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>284.84</v>
+        <v>286.95</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>279.27</v>
+        <v>280.35</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>271.55</v>
+        <v>271.73</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2516,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>427.55</v>
+        <v>431.55</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>415.38</v>
+        <v>416.92</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>437.69</v>
+        <v>437.45</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>525.75</v>
+        <v>524.3</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2560,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>648.3</v>
+        <v>648.25</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>584.4299999999999</v>
+        <v>590.51</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>600.09</v>
+        <v>601.97</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>705.02</v>
+        <v>704.45</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2604,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1289.7</v>
+        <v>1296.3</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1197.44</v>
+        <v>1206.85</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1271.37</v>
+        <v>1272.34</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1498.05</v>
+        <v>1495.76</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2648,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>336.1</v>
+        <v>341.25</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>306.5</v>
+        <v>309.81</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>323.07</v>
+        <v>323.78</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>397.72</v>
+        <v>397.39</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2692,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>188.02</v>
+        <v>189.83</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>178.49</v>
+        <v>179.57</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>178.54</v>
+        <v>178.98</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>163.43</v>
+        <v>163.67</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2736,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>731.55</v>
+        <v>747.8</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>705.92</v>
+        <v>709.91</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>722.3</v>
+        <v>723.3</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>763.39</v>
+        <v>762.62</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2780,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1000</v>
+        <v>1009.65</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>992.89</v>
+        <v>994.48</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1029.21</v>
+        <v>1028.44</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1230.67</v>
+        <v>1227.38</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2824,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>148.28</v>
+        <v>149.61</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>132.88</v>
+        <v>134.47</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>132.47</v>
+        <v>133.14</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.33</v>
+        <v>135.44</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2868,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>455.25</v>
+        <v>457</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>427.03</v>
+        <v>429.89</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>433.74</v>
+        <v>434.65</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>456.25</v>
+        <v>456.3</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2893,9 +2898,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
@@ -2912,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>170.52</v>
+        <v>168.62</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>159.41</v>
+        <v>160.29</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>175.67</v>
+        <v>175.39</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>221.58</v>
+        <v>221.3</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2956,29 +2961,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1066.2</v>
+        <v>1091.55</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1046.26</v>
+        <v>1050.57</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1087.18</v>
+        <v>1087.35</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1188.36</v>
+        <v>1187.11</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
@@ -3000,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>10340.5</v>
+        <v>10327.5</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>9861.629999999999</v>
+        <v>9906</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>9643.99</v>
+        <v>9670.790000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8665.24</v>
+        <v>8672.77</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3044,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>230.32</v>
+        <v>233.55</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>216.42</v>
+        <v>218.05</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>210.12</v>
+        <v>211.03</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>212.6</v>
+        <v>212.4</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3088,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.98</v>
+        <v>7.82</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.32</v>
+        <v>7.37</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.32</v>
+        <v>7.34</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.449999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3132,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>117.36</v>
+        <v>119.06</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>111.22</v>
+        <v>111.97</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>110.72</v>
+        <v>111.05</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.58</v>
+        <v>109.57</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3176,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>103.6</v>
+        <v>105.16</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>97.09999999999999</v>
+        <v>97.87</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>97.53</v>
+        <v>97.83</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.81</v>
+        <v>114.66</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3220,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>84.67</v>
+        <v>80.75</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>78.70999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>75.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>85.42</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3277,7 +3282,7 @@
         <v>54.8</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>78.13</v>
+        <v>78.12</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3308,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1249.7</v>
+        <v>1278.1</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1183.71</v>
+        <v>1192.7</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1142.16</v>
+        <v>1147.49</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1151.32</v>
+        <v>1153.36</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3352,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>217.13</v>
+        <v>213.04</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>172.25</v>
+        <v>176.14</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>169.02</v>
+        <v>170.75</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>203.02</v>
+        <v>202.92</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3396,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1208.55</v>
+        <v>1201.05</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>992.3</v>
+        <v>1012.18</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>996.78</v>
+        <v>1004.79</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1329.78</v>
+        <v>1327.82</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3440,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>64.98999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>59.48</v>
+        <v>60.07</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>60.63</v>
+        <v>60.83</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>61.9</v>
+        <v>61.84</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3484,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2433.2</v>
+        <v>2397.5</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2335.45</v>
+        <v>2341.36</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2387.35</v>
+        <v>2387.74</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2600.33</v>
+        <v>2596.34</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3528,29 +3533,29 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>495.1</v>
+        <v>481.6</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>472.83</v>
+        <v>473.66</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>487.21</v>
+        <v>486.99</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>539.71</v>
+        <v>538.9</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I65" s="13" t="inlineStr">
@@ -3572,29 +3577,29 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>355.8</v>
+        <v>358.45</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>346.02</v>
+        <v>347.2</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>357.57</v>
+        <v>357.6</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>402.27</v>
+        <v>401.5</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H66" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
@@ -3616,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2233.4</v>
+        <v>2259.1</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2113.41</v>
+        <v>2127.29</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2136.16</v>
+        <v>2140.98</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2060.71</v>
+        <v>2062</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3660,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4901.2</v>
+        <v>4907.5</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4444.48</v>
+        <v>4488.58</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4389.1</v>
+        <v>4409.43</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4446.52</v>
+        <v>4450.91</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3704,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>891.95</v>
+        <v>903.55</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>864.1</v>
+        <v>867.86</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>904.87</v>
+        <v>904.8099999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1048.5</v>
+        <v>1046.19</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3748,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>513.55</v>
+        <v>513.85</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>469.09</v>
+        <v>473.36</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>481.86</v>
+        <v>483.12</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>549.35</v>
+        <v>547.76</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3792,29 +3797,29 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>918.25</v>
+        <v>929.9</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>886.95</v>
+        <v>891.04</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>918.8200000000001</v>
+        <v>919.25</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1046.2</v>
+        <v>1044.64</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H71" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I71" s="13" t="inlineStr">
@@ -3836,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>108.72</v>
+        <v>109.98</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>103.33</v>
+        <v>103.96</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>105.23</v>
+        <v>105.41</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>111.08</v>
+        <v>111.02</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3880,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>996.95</v>
+        <v>1014.35</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>908.61</v>
+        <v>918.6799999999999</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>922.2</v>
+        <v>925.8099999999999</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>940.5700000000001</v>
+        <v>941.24</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3924,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>927.1</v>
+        <v>853.45</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>643.59</v>
+        <v>663.5700000000001</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>595.86</v>
+        <v>605.97</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>561.49</v>
+        <v>564.34</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3968,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>651.6</v>
+        <v>640.4</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>596.67</v>
+        <v>600.83</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>639.52</v>
+        <v>639.55</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>757.46</v>
+        <v>756.3</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4012,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1074.3</v>
+        <v>1053.65</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>963.84</v>
+        <v>972.39</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>883.61</v>
+        <v>890.28</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1050.05</v>
+        <v>1047.8</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4056,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>3967.3</v>
+        <v>3985.6</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3762.49</v>
+        <v>3783.74</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3745.86</v>
+        <v>3755.26</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3665.03</v>
+        <v>3664.6</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4100,20 +4105,20 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>636.05</v>
+        <v>646.35</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>616.13</v>
+        <v>619.01</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>631.9299999999999</v>
+        <v>632.5</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>708.78</v>
+        <v>707.04</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4144,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>58.31</v>
+        <v>59.31</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>55.47</v>
+        <v>55.83</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>55.94</v>
+        <v>56.07</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.15</v>
+        <v>59.17</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4169,9 +4174,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J79" s="14" t="inlineStr">
@@ -4188,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>703.8</v>
+        <v>726.55</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>643.1799999999999</v>
+        <v>651.12</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>657.1900000000001</v>
+        <v>659.91</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>760.5</v>
+        <v>759.04</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4232,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>158.14</v>
+        <v>161.36</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>144.26</v>
+        <v>145.88</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>150.87</v>
+        <v>151.28</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>182.99</v>
+        <v>182.95</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4276,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>219.34</v>
+        <v>214.58</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>197.77</v>
+        <v>199.37</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>203.89</v>
+        <v>204.31</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>241.78</v>
+        <v>241.39</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4320,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>152.42</v>
+        <v>148.22</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>143.89</v>
+        <v>144.3</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>138.62</v>
+        <v>139</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>125.61</v>
+        <v>125.79</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4364,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>463.05</v>
+        <v>489.7</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>423.53</v>
+        <v>429.83</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>434.78</v>
+        <v>436.94</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>474.04</v>
+        <v>474.31</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4389,9 +4394,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I84" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
@@ -4408,29 +4413,29 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>157.1</v>
+        <v>160.92</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>152.65</v>
+        <v>153.44</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>159.7</v>
+        <v>159.75</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.67</v>
+        <v>162.53</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H85" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
@@ -4452,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>171.05</v>
+        <v>174.07</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>159.58</v>
+        <v>160.96</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>163.3</v>
+        <v>163.73</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178.77</v>
+        <v>178.61</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4496,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>951.7</v>
+        <v>970.9</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>931.29</v>
+        <v>935.0599999999999</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>991.92</v>
+        <v>991.1</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1093.5</v>
+        <v>1091.73</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4540,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>621.95</v>
+        <v>621.05</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>529.72</v>
+        <v>538.41</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>562.63</v>
+        <v>564.92</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>786.95</v>
+        <v>784.59</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4584,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>567.9</v>
+        <v>565.35</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>550.37</v>
+        <v>551.8</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>570.29</v>
+        <v>570.1</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>609.34</v>
+        <v>608.8200000000001</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4628,29 +4633,29 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>130.18</v>
+        <v>132.33</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>126.57</v>
+        <v>127.12</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.63</v>
+        <v>130.69</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>137.87</v>
+        <v>137.68</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H90" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I90" s="13" t="inlineStr">
@@ -4672,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>355.4</v>
+        <v>359.75</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>326.18</v>
+        <v>329.38</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>341.36</v>
+        <v>342.09</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>407.48</v>
+        <v>406.6</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4716,20 +4721,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>188.39</v>
+        <v>191.9</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>174.74</v>
+        <v>176.37</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>183.81</v>
+        <v>184.13</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>239.4</v>
+        <v>238.55</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4760,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>18.87</v>
+        <v>19.09</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>16.54</v>
+        <v>16.78</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>17.16</v>
+        <v>17.24</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>22.14</v>
+        <v>22.08</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4804,29 +4809,29 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1090.95</v>
+        <v>1116.2</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1028.69</v>
+        <v>1037.03</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1102.09</v>
+        <v>1102.64</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1368.72</v>
+        <v>1370.29</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H94" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I94" s="13" t="inlineStr">
@@ -4848,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>296.82</v>
+        <v>313.44</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>280.05</v>
+        <v>283.23</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>293.61</v>
+        <v>294.38</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>306.44</v>
+        <v>306.27</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4873,9 +4878,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J95" s="14" t="inlineStr">
@@ -4892,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>48.54</v>
+        <v>49.61</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>43.89</v>
+        <v>44.44</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>44.39</v>
+        <v>44.59</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.49</v>
+        <v>51.52</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4936,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>964.25</v>
+        <v>974.1</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>901.63</v>
+        <v>908.53</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>903.1</v>
+        <v>905.89</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>898.67</v>
+        <v>897.99</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4980,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>809.95</v>
+        <v>803.25</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>756.4400000000001</v>
+        <v>760.9</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>752.92</v>
+        <v>754.9</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>799.15</v>
+        <v>799.37</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5024,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1551.8</v>
+        <v>1565.4</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1325.26</v>
+        <v>1348.13</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1290.51</v>
+        <v>1301.29</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1156.42</v>
+        <v>1159.66</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5068,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>836.95</v>
+        <v>838</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>801.1900000000001</v>
+        <v>804.6900000000001</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>874.21</v>
+        <v>872.79</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1040.93</v>
+        <v>1037.65</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5112,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>269.56</v>
+        <v>275.85</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>251.79</v>
+        <v>254.08</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>257.87</v>
+        <v>258.57</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>273.9</v>
+        <v>273.52</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5137,9 +5142,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
@@ -5156,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4087.1</v>
+        <v>4099.6</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3794.55</v>
+        <v>3823.6</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3712.96</v>
+        <v>3728.12</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3685.07</v>
+        <v>3688.23</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5200,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>727.3</v>
+        <v>742.3</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>697.53</v>
+        <v>701.8</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>695.64</v>
+        <v>697.47</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>770.9299999999999</v>
+        <v>768.42</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5244,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>164.17</v>
+        <v>163.03</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>152.58</v>
+        <v>153.57</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>160.12</v>
+        <v>160.23</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>177.28</v>
+        <v>176.98</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5288,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>396.75</v>
+        <v>400.75</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>362.18</v>
+        <v>365.85</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>359.91</v>
+        <v>361.51</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>404.68</v>
+        <v>404.35</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5332,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1035.4</v>
+        <v>1042.05</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>942.21</v>
+        <v>951.72</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>900.45</v>
+        <v>906.01</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>939.09</v>
+        <v>939.9</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5376,29 +5381,29 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>497.25</v>
+        <v>519.25</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>478.44</v>
+        <v>482.33</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>504.21</v>
+        <v>504.8</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>583.77</v>
+        <v>583.33</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H107" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H107" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr">
@@ -5420,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>657.55</v>
+        <v>673.7</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>621.08</v>
+        <v>626.09</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>656.58</v>
+        <v>657.25</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>758.08</v>
+        <v>757.37</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5464,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>378.6</v>
+        <v>374.75</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>344.99</v>
+        <v>347.83</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>341.79</v>
+        <v>343.08</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.64</v>
+        <v>355.63</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5508,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>68.73999999999999</v>
+        <v>72.48</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>62.34</v>
+        <v>63.31</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>64.23999999999999</v>
+        <v>64.56</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>83.90000000000001</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5552,29 +5557,29 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>34.25</v>
+        <v>33.01</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>31.77</v>
+        <v>31.89</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.59</v>
+        <v>33.56</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>43.62</v>
+        <v>43.55</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H111" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I111" s="13" t="inlineStr">
@@ -5596,20 +5601,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>128.08</v>
+        <v>128.56</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>122.26</v>
+        <v>122.86</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.48</v>
+        <v>124.64</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.03</v>
+        <v>114.12</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5640,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>395.6</v>
+        <v>391.45</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>379.68</v>
+        <v>380.8</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>379.19</v>
+        <v>379.67</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>415.82</v>
+        <v>415.84</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5684,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>25.79</v>
+        <v>26.63</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>22.84</v>
+        <v>23.2</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>23.86</v>
+        <v>23.97</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>35.03</v>
+        <v>34.93</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5728,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>544.4</v>
+        <v>549.7</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>542.76</v>
+        <v>543.4299999999999</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>575.36</v>
+        <v>574.36</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>715.1900000000001</v>
+        <v>713.4400000000001</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5772,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>124.06</v>
+        <v>123.92</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>120.42</v>
+        <v>120.75</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>128.25</v>
+        <v>128.08</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>168.5</v>
+        <v>168.1</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5816,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>440.9</v>
+        <v>448.25</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>398.41</v>
+        <v>403.16</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>397.87</v>
+        <v>399.85</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>434.02</v>
+        <v>433.59</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5860,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>353.6</v>
+        <v>351.05</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>318.98</v>
+        <v>322.03</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>328.3</v>
+        <v>329.19</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>352.74</v>
+        <v>352.59</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5885,9 +5890,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I118" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
@@ -5904,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1205.4</v>
+        <v>1269.9</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>962.23</v>
+        <v>991.54</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>888.2</v>
+        <v>903.17</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>825.17</v>
+        <v>828.95</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5948,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>721</v>
+        <v>746.6</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>664.72</v>
+        <v>672.52</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>686.36</v>
+        <v>688.72</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>763.79</v>
+        <v>762.04</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5992,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>200.16</v>
+        <v>203.09</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>184.83</v>
+        <v>186.57</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>193.07</v>
+        <v>193.46</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>221.14</v>
+        <v>220.82</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6036,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>246.34</v>
+        <v>246.23</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>232.11</v>
+        <v>233.45</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>219.6</v>
+        <v>220.65</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>199.52</v>
+        <v>199.89</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6080,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>920.25</v>
+        <v>923.35</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>861.65</v>
+        <v>867.53</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>852.8200000000001</v>
+        <v>855.59</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>962.59</v>
+        <v>961.37</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6124,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1250.2</v>
+        <v>1263.4</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1151.76</v>
+        <v>1162.39</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1126.6</v>
+        <v>1131.97</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1158.13</v>
+        <v>1158.23</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6168,29 +6173,29 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>169.51</v>
+        <v>171.96</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>164.19</v>
+        <v>164.93</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>169.93</v>
+        <v>170.01</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.97</v>
+        <v>191.68</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H125" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I125" s="13" t="inlineStr">
@@ -6212,29 +6217,29 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>13846</v>
+        <v>14349</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>13530.64</v>
+        <v>13608.58</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14048.16</v>
+        <v>14059.95</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14899.28</v>
+        <v>14890.96</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H126" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I126" s="13" t="inlineStr">
@@ -6256,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>142.65</v>
+        <v>142.1</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>125.05</v>
+        <v>126.68</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>130.65</v>
+        <v>131.1</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>164.17</v>
+        <v>164.06</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6300,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>178.08</v>
+        <v>178.86</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>172.96</v>
+        <v>173.52</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>184.52</v>
+        <v>184.29</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>213.34</v>
+        <v>212.64</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6344,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>53.26</v>
+        <v>55.86</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>46.31</v>
+        <v>47.22</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>46.81</v>
+        <v>47.16</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55.03</v>
+        <v>55.12</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6369,9 +6374,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I129" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J129" s="14" t="inlineStr">
@@ -6388,17 +6393,17 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>64.20999999999999</v>
+        <v>63.44</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>53.1</v>
+        <v>54.08</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>53</v>
+        <v>53.41</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>59.22</v>
@@ -6432,20 +6437,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1798.6</v>
+        <v>1794.9</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1672.72</v>
+        <v>1684.35</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1606.16</v>
+        <v>1613.56</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1354.1</v>
+        <v>1357.65</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6476,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1429.55</v>
+        <v>1485.75</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1131.82</v>
+        <v>1165.53</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1038.77</v>
+        <v>1056.3</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1166.79</v>
+        <v>1168.6</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6520,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>326.6</v>
+        <v>327.95</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>298.91</v>
+        <v>301.67</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>303.26</v>
+        <v>304.23</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.08</v>
+        <v>325.88</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6564,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>475.35</v>
+        <v>471.6</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>421.48</v>
+        <v>426.25</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>433.28</v>
+        <v>434.78</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>476.13</v>
+        <v>476.87</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6608,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>4824.2</v>
+        <v>4857.8</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>3992.99</v>
+        <v>4075.35</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>3616.82</v>
+        <v>3665.49</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2702.38</v>
+        <v>2722.38</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6652,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>328.1</v>
+        <v>325.15</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>337.5</v>
+        <v>336.32</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>348.82</v>
+        <v>347.89</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>367.41</v>
+        <v>366.67</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6696,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>97.28</v>
+        <v>96.78</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>92.91</v>
+        <v>93.28</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>99.91</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>130.56</v>
+        <v>130.29</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6740,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1390.2</v>
+        <v>1417.7</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1292.9</v>
+        <v>1304.79</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1311.08</v>
+        <v>1315.26</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1320.74</v>
+        <v>1322.75</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6784,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>180.18</v>
+        <v>179.23</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>172.02</v>
+        <v>172.71</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>172.7</v>
+        <v>172.95</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>189.97</v>
+        <v>189.59</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6828,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1697.7</v>
+        <v>1746</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1556.86</v>
+        <v>1574.88</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1652.94</v>
+        <v>1656.59</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2032.25</v>
+        <v>2027.34</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6872,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>387.05</v>
+        <v>388.6</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>365.79</v>
+        <v>367.96</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>380.4</v>
+        <v>380.72</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>432.58</v>
+        <v>432.1</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6916,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>869.4</v>
+        <v>877.8</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>847.84</v>
+        <v>850.7</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>838.28</v>
+        <v>839.83</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>825.96</v>
+        <v>826.53</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6960,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>365.4</v>
+        <v>369.6</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>323.23</v>
+        <v>327.65</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>329.16</v>
+        <v>330.74</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>347.13</v>
+        <v>347.05</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7004,24 +7009,24 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>188.75</v>
+        <v>192.22</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>190.1</v>
+        <v>190.3</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>200</v>
+        <v>199.7</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>239.38</v>
-      </c>
-      <c r="G144" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>238.83</v>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
@@ -7048,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1502.5</v>
+        <v>1511.6</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1325.64</v>
+        <v>1343.35</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1308.48</v>
+        <v>1316.45</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1389.23</v>
+        <v>1390.86</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7092,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1171.2</v>
+        <v>1208.4</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1100.42</v>
+        <v>1110.7</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1113.75</v>
+        <v>1117.46</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1170.55</v>
+        <v>1171.1</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7136,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>76.33</v>
+        <v>77.41</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>72.66</v>
+        <v>73.11</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>74.93000000000001</v>
+        <v>75.03</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>85.11</v>
+        <v>84.97</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7180,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>260.18</v>
+        <v>273.34</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>246.15</v>
+        <v>248.74</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>251.17</v>
+        <v>252.04</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>265.41</v>
+        <v>265.2</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7205,9 +7210,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I148" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I148" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J148" s="14" t="inlineStr">
@@ -7224,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>35.64</v>
+        <v>36.36</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>32.28</v>
+        <v>32.67</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>33.98</v>
+        <v>34.07</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>42.98</v>
+        <v>42.89</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7268,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>406.25</v>
+        <v>413.75</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>356.9</v>
+        <v>362.32</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>380.07</v>
+        <v>381.39</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>489.88</v>
+        <v>490.34</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7312,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>565.7</v>
+        <v>569.4</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>543.23</v>
+        <v>545.72</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>586.05</v>
+        <v>585.4</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>750.76</v>
+        <v>748.87</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7356,20 +7361,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>144.96</v>
+        <v>144.89</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>138.23</v>
+        <v>138.87</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.81</v>
+        <v>145.77</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>194.37</v>
+        <v>193.72</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7400,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>408.55</v>
+        <v>432.55</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>345.21</v>
+        <v>353.53</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>358.88</v>
+        <v>361.77</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>510.52</v>
+        <v>509.74</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7444,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>662.2</v>
+        <v>667.65</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>597.99</v>
+        <v>604.62</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>581.22</v>
+        <v>584.61</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>592.4</v>
+        <v>592.38</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7488,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.529999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>8.859999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>11</v>
+        <v>10.97</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7532,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>202.24</v>
+        <v>203.11</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>186.23</v>
+        <v>187.83</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>199.08</v>
+        <v>199.24</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>244.2</v>
+        <v>243.65</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7576,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>183.05</v>
+        <v>184.75</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>167.14</v>
+        <v>168.82</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>165.22</v>
+        <v>165.98</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>162.82</v>
+        <v>162.99</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7620,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>121.78</v>
+        <v>124.33</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>116.97</v>
+        <v>117.67</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>121.08</v>
+        <v>121.21</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>142.73</v>
+        <v>142.47</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7664,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>776.7</v>
+        <v>809.15</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>675.09</v>
+        <v>687.86</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>665.53</v>
+        <v>671.17</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>668.87</v>
+        <v>671.22</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7708,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>28.3</v>
+        <v>28.49</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>25.9</v>
+        <v>26.15</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>26.62</v>
+        <v>26.69</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.52</v>
+        <v>32.44</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7752,20 +7757,20 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1618.4</v>
+        <v>1642.9</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1512.78</v>
+        <v>1525.17</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1520.88</v>
+        <v>1525.66</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1488.87</v>
+        <v>1490.5</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7796,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>889.7</v>
+        <v>883.7</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>838.38</v>
+        <v>842.7</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>835.91</v>
+        <v>837.78</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>937.78</v>
+        <v>938.25</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7840,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2317.3</v>
+        <v>2376</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2063.98</v>
+        <v>2093.69</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2073.74</v>
+        <v>2085.59</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2378.04</v>
+        <v>2378.14</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7884,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>580.45</v>
+        <v>586.8</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>557.42</v>
+        <v>560.21</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>566.63</v>
+        <v>567.42</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>554.01</v>
+        <v>554.48</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7928,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>255.57</v>
+        <v>254.95</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>238.18</v>
+        <v>239.78</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>243.5</v>
+        <v>243.95</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>278.74</v>
+        <v>278.53</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7972,24 +7977,24 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>124.15</v>
+        <v>125.24</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>124.76</v>
+        <v>124.8</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>125.95</v>
+        <v>125.92</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>135.72</v>
-      </c>
-      <c r="G166" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>135.48</v>
+      </c>
+      <c r="G166" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H166" s="13" t="inlineStr">
@@ -8016,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>2944.1</v>
+        <v>3133.1</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>2927.36</v>
+        <v>2946.95</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>2907.93</v>
+        <v>2916.76</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2712.43</v>
+        <v>2716.3</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8060,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2650.6</v>
+        <v>2752</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2381.22</v>
+        <v>2416.53</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2388.9</v>
+        <v>2403.14</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2510.06</v>
+        <v>2512.11</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8104,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>224.91</v>
+        <v>225.18</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>194.89</v>
+        <v>197.77</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>203.09</v>
+        <v>203.95</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>241.59</v>
+        <v>241.31</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8148,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>196.14</v>
+        <v>197.36</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>186.31</v>
+        <v>187.36</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>190.87</v>
+        <v>191.13</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>249.98</v>
+        <v>249.05</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8192,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>131.97</v>
+        <v>132.4</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>120.09</v>
+        <v>121.26</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>126.26</v>
+        <v>126.5</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>134.74</v>
+        <v>134.59</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8236,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>263.6</v>
+        <v>268</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>250.44</v>
+        <v>252.12</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>254.58</v>
+        <v>255.1</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>273.89</v>
+        <v>273.53</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8280,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>582.1</v>
+        <v>583.65</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>525.89</v>
+        <v>531.39</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>539</v>
+        <v>540.75</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>581.16</v>
+        <v>580.74</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8324,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2349</v>
+        <v>2461.3</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2300.38</v>
+        <v>2315.7</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2292.37</v>
+        <v>2298.99</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2405.27</v>
+        <v>2403.72</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8349,9 +8354,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I174" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J174" s="14" t="inlineStr">
@@ -8368,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>34.7</v>
+        <v>34.72</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>30.38</v>
+        <v>30.8</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>31.42</v>
+        <v>31.55</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>41.34</v>
+        <v>41.24</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8412,17 +8417,17 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>9.68</v>
+        <v>9.77</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>8.640000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>8.609999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="F176" s="11" t="n">
         <v>9.93</v>
@@ -8456,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>804.95</v>
+        <v>803.4</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>800.95</v>
+        <v>801.1799999999999</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>852.88</v>
+        <v>850.9400000000001</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1051.08</v>
+        <v>1048.47</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8500,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>244.04</v>
+        <v>244.76</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>218.24</v>
+        <v>220.77</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>224.6</v>
+        <v>225.39</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>300.74</v>
+        <v>300.73</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8544,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>304.47</v>
+        <v>309.03</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>287.21</v>
+        <v>289.29</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>313.4</v>
+        <v>313.23</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>391.61</v>
+        <v>390.54</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8588,24 +8593,24 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>220.24</v>
+        <v>223.4</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>220.66</v>
+        <v>220.92</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>224.23</v>
+        <v>224.19</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>238.46</v>
-      </c>
-      <c r="G180" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>238.24</v>
+      </c>
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -8632,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>62.91</v>
+        <v>63.27</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>61.59</v>
+        <v>61.75</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>62.39</v>
+        <v>62.42</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>68.14</v>
+        <v>67.97</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8676,29 +8681,29 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>507.05</v>
+        <v>513.25</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>478.39</v>
+        <v>481.71</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>509.71</v>
+        <v>509.85</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>694.42</v>
+        <v>691.92</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H182" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H182" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I182" s="13" t="inlineStr">
@@ -8720,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>429.7</v>
+        <v>423.35</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>368.91</v>
+        <v>374.09</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>352.87</v>
+        <v>355.64</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>338.53</v>
+        <v>339.58</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8764,24 +8769,24 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1550.4</v>
+        <v>1577.5</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1557.59</v>
+        <v>1559.48</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1693.73</v>
+        <v>1689.17</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>2002.25</v>
-      </c>
-      <c r="G184" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1996.17</v>
+      </c>
+      <c r="G184" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
@@ -8808,20 +8813,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>163.95</v>
+        <v>163.1</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>151.21</v>
+        <v>152.34</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>156.52</v>
+        <v>156.77</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>177.79</v>
+        <v>177.64</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8852,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>217.54</v>
+        <v>218.47</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>194.9</v>
+        <v>197.15</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>199.02</v>
+        <v>199.78</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>192.92</v>
+        <v>193.03</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8896,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4728.8</v>
+        <v>4720</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4476.54</v>
+        <v>4499.72</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4390.01</v>
+        <v>4402.95</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4580.54</v>
+        <v>4582.11</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8940,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3560.8</v>
+        <v>3559.8</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3464.43</v>
+        <v>3473.52</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3658.95</v>
+        <v>3655.06</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4391.35</v>
+        <v>4385.35</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8984,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2397</v>
+        <v>2378.3</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2221.92</v>
+        <v>2236.82</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2120.18</v>
+        <v>2130.3</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1766.75</v>
+        <v>1771.11</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9028,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>324.55</v>
+        <v>326.3</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>311.69</v>
+        <v>313.08</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>312.37</v>
+        <v>312.91</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>337.23</v>
+        <v>336.43</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9072,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>1901.1</v>
+        <v>1885</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>2035.77</v>
+        <v>2021.41</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2071.3</v>
+        <v>2063.99</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2073.05</v>
+        <v>2073.89</v>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
@@ -9116,29 +9121,29 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>534.55</v>
+        <v>573.75</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>510.12</v>
+        <v>516.1799999999999</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>543.41</v>
+        <v>544.6</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>708.0599999999999</v>
+        <v>709.46</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H192" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H192" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I192" s="13" t="inlineStr">
@@ -9160,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1100.8</v>
+        <v>1107.85</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1012.37</v>
+        <v>1021.47</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1009</v>
+        <v>1012.88</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>917.39</v>
+        <v>918.21</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9204,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>862.6</v>
+        <v>869</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>806.86</v>
+        <v>812.78</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>838.72</v>
+        <v>839.91</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>916.87</v>
+        <v>917.15</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9248,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>147.53</v>
+        <v>146.8</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>135.21</v>
+        <v>136.32</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>137.26</v>
+        <v>137.63</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>159.37</v>
+        <v>159.12</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9292,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>548.05</v>
+        <v>547.85</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>519.27</v>
+        <v>521.99</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>533.65</v>
+        <v>534.21</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>617.63</v>
+        <v>615.83</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9336,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>412</v>
+        <v>410.55</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>378.44</v>
+        <v>381.5</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>351.37</v>
+        <v>353.69</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>356.63</v>
+        <v>356.99</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9380,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>27.9</v>
+        <v>28.17</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>26.7</v>
+        <v>26.84</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>25.84</v>
+        <v>25.93</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.74</v>
+        <v>27.75</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9424,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3606.2</v>
+        <v>3735.8</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3223.79</v>
+        <v>3272.55</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3094.53</v>
+        <v>3119.68</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2800.84</v>
+        <v>2809.96</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9468,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>407.3</v>
+        <v>433.35</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>368.92</v>
+        <v>375.05</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>371.42</v>
+        <v>373.85</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>428.29</v>
+        <v>427.43</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9493,9 +9498,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I200" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I200" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J200" s="14" t="inlineStr">
@@ -9512,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>38.75</v>
+        <v>38.93</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>37.76</v>
+        <v>37.87</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>38.5</v>
+        <v>38.52</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>35.94</v>
+        <v>35.99</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9556,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>221.94</v>
+        <v>222.36</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>212.39</v>
+        <v>213.34</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>213.01</v>
+        <v>213.37</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>224.31</v>
+        <v>223.99</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9600,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>193.46</v>
+        <v>193.97</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>176.12</v>
+        <v>177.82</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>183.24</v>
+        <v>183.66</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>228.9</v>
+        <v>228.42</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9644,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>256.35</v>
+        <v>263.08</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>206.16</v>
+        <v>211.58</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>177.54</v>
+        <v>180.89</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>133.92</v>
+        <v>135.24</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9688,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>993.9</v>
+        <v>1000.25</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>956.9400000000001</v>
+        <v>961.0599999999999</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>921.05</v>
+        <v>924.16</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>867.27</v>
+        <v>868.02</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9732,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2170.6</v>
+        <v>2221.5</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>1984.21</v>
+        <v>2006.81</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>1962.5</v>
+        <v>1972.66</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2212.94</v>
+        <v>2215.35</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9757,9 +9762,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I206" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I206" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J206" s="14" t="inlineStr">
@@ -9776,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>778.25</v>
+        <v>788.5</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>719.2</v>
+        <v>725.8</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>742.35</v>
+        <v>744.16</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>808.9299999999999</v>
+        <v>809.0599999999999</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9820,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>878.6</v>
+        <v>873.75</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>808.78</v>
+        <v>814.97</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>845.58</v>
+        <v>846.6900000000001</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>1008.02</v>
+        <v>1005.46</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9864,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>152.5</v>
+        <v>148.01</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>132.93</v>
+        <v>134.37</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>129.88</v>
+        <v>130.59</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>138.3</v>
+        <v>138.28</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9908,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>270.94</v>
+        <v>272.97</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>235.77</v>
+        <v>239.32</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>236.3</v>
+        <v>237.74</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>253.24</v>
+        <v>253.58</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9952,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>337.75</v>
+        <v>333.65</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>319.85</v>
+        <v>321.16</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>346.05</v>
+        <v>345.57</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>395.07</v>
+        <v>394.38</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -9996,29 +10001,29 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>628.3</v>
+        <v>638.5</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>616.03</v>
+        <v>618.17</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>635.25</v>
+        <v>635.38</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>685.29</v>
+        <v>684.04</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H212" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H212" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I212" s="13" t="inlineStr">
@@ -10040,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>238.36</v>
+        <v>239.49</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>217.51</v>
+        <v>219.6</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>223.79</v>
+        <v>224.4</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>254.38</v>
+        <v>253.95</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10084,20 +10089,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>811.85</v>
+        <v>813.3</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>762.0599999999999</v>
+        <v>766.9400000000001</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>795.95</v>
+        <v>796.63</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>914.11</v>
+        <v>910.9299999999999</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10128,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>135.7</v>
+        <v>135.5</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>125.99</v>
+        <v>126.89</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>134.93</v>
+        <v>134.95</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>150.38</v>
+        <v>150.27</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10172,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>970.75</v>
+        <v>996.9</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>884.9299999999999</v>
+        <v>895.6</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>842.67</v>
+        <v>848.72</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>701.78</v>
+        <v>704.22</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10216,29 +10221,29 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>387.25</v>
+        <v>405.4</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>374.1</v>
+        <v>377.08</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>392.06</v>
+        <v>392.58</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>487.43</v>
+        <v>486.62</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H217" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H217" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I217" s="13" t="inlineStr">
@@ -10260,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>112.43</v>
+        <v>115.69</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>105.42</v>
+        <v>106.4</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>106.54</v>
+        <v>106.9</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>117.21</v>
+        <v>117.13</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10304,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>487.6</v>
+        <v>491.1</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>445.37</v>
+        <v>449.73</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>454.88</v>
+        <v>456.3</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>531.27</v>
+        <v>530.99</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10348,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1222.7</v>
+        <v>1238.7</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1189.54</v>
+        <v>1194.22</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1254.06</v>
+        <v>1253.46</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1591.35</v>
+        <v>1586.88</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10392,20 +10397,20 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1754.1</v>
+        <v>1738</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1710.92</v>
+        <v>1713.5</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1734.56</v>
+        <v>1734.7</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1770.34</v>
+        <v>1770.87</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10436,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>103.8</v>
+        <v>106.01</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>95.25</v>
+        <v>96.27</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>101.72</v>
+        <v>101.89</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>125.98</v>
+        <v>125.68</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10480,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>4278.4</v>
+        <v>4210.6</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3835.96</v>
+        <v>3871.64</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3660.67</v>
+        <v>3682.23</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3030.38</v>
+        <v>3040.24</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10524,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2050</v>
+        <v>2022.3</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1787.88</v>
+        <v>1810.21</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1785.13</v>
+        <v>1794.43</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2174.44</v>
+        <v>2170.11</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10568,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>109.28</v>
+        <v>110.91</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>100.72</v>
+        <v>101.69</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>106.06</v>
+        <v>106.25</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>133.91</v>
+        <v>133.59</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10612,29 +10617,29 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>394.35</v>
+        <v>389.05</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>382.4</v>
+        <v>383.04</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>391.56</v>
+        <v>391.46</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>398.15</v>
+        <v>397.83</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H226" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H226" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I226" s="13" t="inlineStr">
@@ -10656,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>446.35</v>
+        <v>470</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>432.01</v>
+        <v>435.63</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>436.91</v>
+        <v>438.21</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>435.34</v>
+        <v>435.11</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10700,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>195.52</v>
+        <v>195.39</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>176.67</v>
+        <v>178.46</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>178.07</v>
+        <v>178.75</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>194.3</v>
+        <v>194.03</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10744,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>574.5</v>
+        <v>585.55</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>533.04</v>
+        <v>538.04</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>530.96</v>
+        <v>533.1</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>555.9299999999999</v>
+        <v>554.95</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10788,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>559.1</v>
+        <v>581.5</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>520.89</v>
+        <v>526.66</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>526.01</v>
+        <v>528.1900000000001</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>589.72</v>
+        <v>589.4299999999999</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10832,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>59.24</v>
+        <v>58.73</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>56.72</v>
+        <v>56.91</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>56.78</v>
+        <v>56.85</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.45</v>
+        <v>52.57</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10876,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>919.4</v>
+        <v>968.85</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>820.51</v>
+        <v>834.64</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>844.3099999999999</v>
+        <v>849.2</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>963.22</v>
+        <v>961.92</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10901,9 +10906,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I232" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I232" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J232" s="14" t="inlineStr">
@@ -10920,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>611.15</v>
+        <v>614.25</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>573.89</v>
+        <v>577.74</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>580.8099999999999</v>
+        <v>582.12</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>689.0599999999999</v>
+        <v>687.04</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10964,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>322</v>
+        <v>320.3</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>325.81</v>
+        <v>325.28</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>342.1</v>
+        <v>341.24</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>376.1</v>
+        <v>375.33</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11008,24 +11013,24 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>194.43</v>
+        <v>193.44</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>194.08</v>
+        <v>194.02</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>197.6</v>
+        <v>197.44</v>
       </c>
       <c r="F235" s="11" t="n">
         <v>200.91</v>
       </c>
-      <c r="G235" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="G235" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H235" s="13" t="inlineStr">
@@ -11052,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>241.53</v>
+        <v>264.83</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>223.13</v>
+        <v>227.1</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>226.99</v>
+        <v>228.47</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.85</v>
+        <v>249.94</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11077,9 +11082,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I236" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I236" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J236" s="14" t="inlineStr">
@@ -11096,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1440.4</v>
+        <v>1389.5</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1292.06</v>
+        <v>1301.34</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1262.72</v>
+        <v>1267.69</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1336.62</v>
+        <v>1334.4</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11140,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>220.03</v>
+        <v>223.7</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>207.09</v>
+        <v>208.67</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>214.12</v>
+        <v>214.5</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>228.6</v>
+        <v>228.37</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11184,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>533.45</v>
+        <v>539.2</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>506.85</v>
+        <v>509.93</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>523.72</v>
+        <v>524.33</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>560.55</v>
+        <v>559.53</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11228,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>498.8</v>
+        <v>499.6</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>471.43</v>
+        <v>474.11</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>479.26</v>
+        <v>480.06</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>487.07</v>
+        <v>486.91</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11272,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1274</v>
+        <v>1291.5</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1314.81</v>
+        <v>1312.59</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1395.84</v>
+        <v>1391.75</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1562.93</v>
+        <v>1560.01</v>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
@@ -11316,17 +11321,17 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>208.24</v>
+        <v>208.25</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>200.21</v>
+        <v>200.98</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>200.23</v>
+        <v>200.55</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
@@ -11360,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>9850</v>
+        <v>10145</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>9023.52</v>
+        <v>9130.33</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>8603.77</v>
+        <v>8664.209999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8178.66</v>
+        <v>8191.55</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11404,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1060.3</v>
+        <v>1116.1</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>899.7</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>888.66</v>
+        <v>897.58</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>954.53</v>
+        <v>956.14</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11448,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>87.81999999999999</v>
+        <v>91.37</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>74.81999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>72.88</v>
+        <v>73.61</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>97.76000000000001</v>
+        <v>97.78</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11492,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>466</v>
+        <v>483.8</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>449.05</v>
+        <v>452.36</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>463.47</v>
+        <v>464.26</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>497.72</v>
+        <v>497.39</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11536,20 +11541,20 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>466.8</v>
+        <v>464.35</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>459.94</v>
+        <v>460.36</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>476.79</v>
+        <v>476.3</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>572.45</v>
+        <v>571.36</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11580,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>771.05</v>
+        <v>755.75</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>700.8</v>
+        <v>706.03</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>681.85</v>
+        <v>684.75</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>665.0599999999999</v>
+        <v>665.47</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11624,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>264.13</v>
+        <v>260.88</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>236.12</v>
+        <v>238.48</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>247.68</v>
+        <v>248.2</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>322.39</v>
+        <v>321.21</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11668,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>502.3</v>
+        <v>499.25</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>465.06</v>
+        <v>468.32</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>440.09</v>
+        <v>442.41</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>426.65</v>
+        <v>427.19</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11712,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>499.2</v>
+        <v>500.25</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>448.38</v>
+        <v>453.32</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>460.9</v>
+        <v>462.44</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>589.27</v>
+        <v>588.52</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 17-Apr-2026  16:35:34    |    Closing Price Date: 17-Apr-2026</t>
+          <t>Scan Run: 18-Apr-2026  15:26:07    |    Closing Price Date: 17-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>86.40000000000001</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>40.4</v>
+        <v>40.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>17-Apr-2026  16:35:34</t>
+          <t>18-Apr-2026  15:26:07</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.4% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.8% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 101 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 102 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>559.05</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>701.91</v>
+        <v>701.48</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>432.39</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>457.04</v>
+        <v>456.91</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>361.73</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>406.47</v>
+        <v>406.23</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>687.96</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>744.51</v>
+        <v>744.65</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>289.43</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>302.46</v>
+        <v>302.48</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>1060.48</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>924.01</v>
+        <v>924.3200000000001</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>784.5700000000001</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>872.5</v>
+        <v>871.45</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>476.36</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>498.56</v>
+        <v>498.37</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1264.49</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1173.51</v>
+        <v>1174.18</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>117.48</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>136.07</v>
+        <v>135.84</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>581.3</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>590.77</v>
+        <v>590.6</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>443.87</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>472.36</v>
+        <v>472.3</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>357.62</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>341.51</v>
+        <v>341.01</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>130.08</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>166.21</v>
+        <v>165.59</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>968.77</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>958.53</v>
+        <v>958.37</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>881.74</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1092.34</v>
+        <v>1091.83</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>977.5700000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>946.42</v>
+        <v>946.09</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1207.59</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>948.22</v>
+        <v>947.38</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>321.95</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>463.51</v>
+        <v>462.64</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>1612.57</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1607.53</v>
+        <v>1605.41</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>379.52</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>478.16</v>
+        <v>478.11</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1083.63</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1245.11</v>
+        <v>1252.34</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>465.36</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>547.15</v>
+        <v>547.23</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>588.02</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>608.4</v>
+        <v>608.51</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>2453.69</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2739.98</v>
+        <v>2733.18</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>939.84</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1077.98</v>
+        <v>1078.41</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>592.58</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>581.09</v>
+        <v>580.53</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>457.11</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>519.6</v>
+        <v>520.5700000000001</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>457.4</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>435.59</v>
+        <v>435.58</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>302.43</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>355.77</v>
+        <v>355.31</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>390.82</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>395.03</v>
+        <v>394.92</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>1933.01</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2186.26</v>
+        <v>2189.57</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>280.35</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>271.73</v>
+        <v>271.37</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>437.45</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>524.3</v>
+        <v>524.08</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1272.34</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1495.76</v>
+        <v>1492.97</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>323.78</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>397.39</v>
+        <v>396.59</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>178.98</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>163.67</v>
+        <v>163.62</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>723.3</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>762.62</v>
+        <v>761.74</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>1028.44</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1227.38</v>
+        <v>1227.74</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>133.14</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.44</v>
+        <v>135.4</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>434.65</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>456.3</v>
+        <v>455.95</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>175.39</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>221.3</v>
+        <v>220.61</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>1087.35</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1187.11</v>
+        <v>1186.94</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>9670.790000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8672.77</v>
+        <v>8676.610000000001</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>211.03</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>212.4</v>
+        <v>211.88</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>7.34</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.42</v>
+        <v>8.41</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>111.05</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.57</v>
+        <v>109.38</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>97.83</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.66</v>
+        <v>114.6</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>75.90000000000001</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>85.26000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>54.8</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>78.12</v>
+        <v>77.75</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>1147.49</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1153.36</v>
+        <v>1153.29</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>170.75</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>202.92</v>
+        <v>202.4</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>1004.79</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1327.82</v>
+        <v>1327.31</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>60.83</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>61.84</v>
+        <v>61.9</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>2387.74</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2596.34</v>
+        <v>2596.19</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>486.99</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>538.9</v>
+        <v>538.58</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>357.6</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>401.5</v>
+        <v>401.1</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>2140.98</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2062</v>
+        <v>2061.56</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>4409.43</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4450.91</v>
+        <v>4454.92</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>904.8099999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1046.19</v>
+        <v>1045.44</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>483.12</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>547.76</v>
+        <v>547.24</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>919.25</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1044.64</v>
+        <v>1045.74</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>105.41</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>111.02</v>
+        <v>110.77</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>925.8099999999999</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>941.24</v>
+        <v>940.72</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>605.97</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>564.34</v>
+        <v>564.4400000000001</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>890.28</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1047.8</v>
+        <v>1046.01</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>3755.26</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3664.6</v>
+        <v>3657.59</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>632.5</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>707.04</v>
+        <v>706.09</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>56.07</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.17</v>
+        <v>59.12</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>659.91</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>759.04</v>
+        <v>757.49</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>151.28</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>182.95</v>
+        <v>182.5</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>204.31</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>241.39</v>
+        <v>241.2</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>139</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>125.79</v>
+        <v>125.67</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>436.94</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>474.31</v>
+        <v>474.84</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>159.75</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.53</v>
+        <v>162.41</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>163.73</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178.61</v>
+        <v>178.75</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>991.1</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1091.73</v>
+        <v>1091.08</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>564.92</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>784.59</v>
+        <v>783.5599999999999</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>570.1</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>608.8200000000001</v>
+        <v>608.66</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>130.69</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>137.68</v>
+        <v>137.6</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>342.09</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>406.6</v>
+        <v>406.51</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>184.13</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>238.55</v>
+        <v>238.09</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>17.24</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>22.08</v>
+        <v>22.01</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>1102.64</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1370.29</v>
+        <v>1369.53</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>294.38</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>306.27</v>
+        <v>306.07</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44.59</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.52</v>
+        <v>51.53</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>905.89</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>897.99</v>
+        <v>897.88</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>754.9</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>799.37</v>
+        <v>799.21</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>1301.29</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1159.66</v>
+        <v>1159.32</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>872.79</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1037.65</v>
+        <v>1037.63</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>258.57</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>273.52</v>
+        <v>273.5</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>3728.12</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3688.23</v>
+        <v>3687.18</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>697.47</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>768.42</v>
+        <v>765.51</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>160.23</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.98</v>
+        <v>176.93</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>361.51</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>404.35</v>
+        <v>404.41</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>906.01</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>939.9</v>
+        <v>936.65</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>504.8</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>583.33</v>
+        <v>582.65</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>657.25</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>757.37</v>
+        <v>757.23</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>343.08</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.63</v>
+        <v>355.45</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>64.56</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>83.56999999999999</v>
+        <v>83.63</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>33.56</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>43.55</v>
+        <v>43.41</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>124.64</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.12</v>
+        <v>114.13</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>379.67</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>415.84</v>
+        <v>415.67</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>23.97</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>34.93</v>
+        <v>34.87</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>574.36</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>713.4400000000001</v>
+        <v>713.12</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>128.08</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>168.1</v>
+        <v>168.05</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>399.85</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>433.59</v>
+        <v>433.23</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>329.19</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>352.59</v>
+        <v>352.43</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>903.17</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>828.95</v>
+        <v>827.6900000000001</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>688.72</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>762.04</v>
+        <v>759.5599999999999</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>193.46</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>220.82</v>
+        <v>220.81</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>220.65</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>199.89</v>
+        <v>199.82</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>855.59</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>961.37</v>
+        <v>961.62</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>1131.97</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1158.23</v>
+        <v>1159.53</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>170.01</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.68</v>
+        <v>191.64</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>14059.95</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14890.96</v>
+        <v>14887.22</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>131.1</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>164.06</v>
+        <v>164.04</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>184.29</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>212.64</v>
+        <v>212.49</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>47.16</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55.12</v>
+        <v>55.04</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>53.41</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.22</v>
+        <v>59.18</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>1613.56</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1357.65</v>
+        <v>1356.87</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1056.3</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1168.6</v>
+        <v>1165.28</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>304.23</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>325.88</v>
+        <v>325.86</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>434.78</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>476.87</v>
+        <v>475.72</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>3665.49</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2722.38</v>
+        <v>2723.34</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>347.89</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>366.67</v>
+        <v>366.37</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>99.79000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>130.29</v>
+        <v>130.15</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>1315.26</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1322.75</v>
+        <v>1321.89</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>172.95</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>189.59</v>
+        <v>189.24</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>1656.59</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2027.34</v>
+        <v>2024.94</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>380.72</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>432.1</v>
+        <v>431.53</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>839.83</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>826.53</v>
+        <v>826.22</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>330.74</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>347.05</v>
+        <v>346.91</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>199.7</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>238.83</v>
+        <v>238.85</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>1316.45</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1390.86</v>
+        <v>1392.91</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>1117.46</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1171.1</v>
+        <v>1170.32</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>75.03</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.97</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>252.04</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>265.2</v>
+        <v>265.26</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>34.07</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>42.89</v>
+        <v>42.81</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>381.39</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>490.34</v>
+        <v>489.05</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>585.4</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>748.87</v>
+        <v>749.2</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>145.77</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>193.72</v>
+        <v>193.65</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>584.61</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>592.38</v>
+        <v>591.85</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.97</v>
+        <v>10.99</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>199.24</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>243.65</v>
+        <v>243.57</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>165.98</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>162.99</v>
+        <v>162.76</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>121.21</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>142.47</v>
+        <v>142.2</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>671.17</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>671.22</v>
+        <v>670.33</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>26.69</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.44</v>
+        <v>32.41</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>1525.66</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1490.5</v>
+        <v>1490.76</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>837.78</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>938.25</v>
+        <v>935.97</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>2085.59</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2378.14</v>
+        <v>2373.37</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7870,9 +7870,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I163" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I163" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J163" s="14" t="inlineStr">
@@ -7902,7 +7902,7 @@
         <v>567.42</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>554.48</v>
+        <v>554.46</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>243.95</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>278.53</v>
+        <v>278.41</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>125.92</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>135.48</v>
+        <v>135.33</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>2916.76</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2716.3</v>
+        <v>2715.76</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>2403.14</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2512.11</v>
+        <v>2515.27</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>203.95</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>241.31</v>
+        <v>240.91</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>191.13</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>249.05</v>
+        <v>248.75</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>126.5</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>134.59</v>
+        <v>134.51</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>255.1</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>273.53</v>
+        <v>273.49</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>540.75</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>580.74</v>
+        <v>580.46</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>2298.99</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2403.72</v>
+        <v>2404.1</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>31.55</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>41.24</v>
+        <v>41.17</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>8.65</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>850.9400000000001</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1048.47</v>
+        <v>1047.38</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>225.39</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>300.73</v>
+        <v>300.69</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>313.23</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>390.54</v>
+        <v>390.27</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>224.19</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>238.24</v>
+        <v>238.82</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>62.42</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.97</v>
+        <v>67.95</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>509.85</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>691.92</v>
+        <v>691.95</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>355.64</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>339.58</v>
+        <v>339.21</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>1689.17</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1996.17</v>
+        <v>1995.47</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>156.77</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>177.64</v>
+        <v>178</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>199.78</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>193.03</v>
+        <v>192.92</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>4402.95</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4582.11</v>
+        <v>4582.09</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>3655.06</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4385.35</v>
+        <v>4382.38</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>2130.3</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1771.11</v>
+        <v>1770.7</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>312.91</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>336.43</v>
+        <v>336.62</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>2063.99</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2073.89</v>
+        <v>2076.38</v>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>544.6</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>709.46</v>
+        <v>706.8099999999999</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>1012.88</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>918.21</v>
+        <v>917.33</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>839.91</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>917.15</v>
+        <v>915.14</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>137.63</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>159.12</v>
+        <v>158.73</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>534.21</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>615.83</v>
+        <v>615.6799999999999</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>353.69</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>356.99</v>
+        <v>356.43</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>25.93</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.75</v>
+        <v>27.72</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>3119.68</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2809.96</v>
+        <v>2811.2</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>373.85</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>427.43</v>
+        <v>426.66</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>213.37</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.99</v>
+        <v>223.92</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>183.66</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>228.42</v>
+        <v>228.03</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>180.89</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>135.24</v>
+        <v>135.17</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>924.16</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>868.02</v>
+        <v>867.59</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>1972.66</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2215.35</v>
+        <v>2214.24</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>744.16</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>809.0599999999999</v>
+        <v>808.83</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>846.6900000000001</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>1005.46</v>
+        <v>1006</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>130.59</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>138.28</v>
+        <v>138.15</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>237.74</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>253.58</v>
+        <v>253.32</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>345.57</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>394.38</v>
+        <v>394.39</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>635.38</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>684.04</v>
+        <v>682.65</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>224.4</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.95</v>
+        <v>253.91</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>796.63</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>910.9299999999999</v>
+        <v>909.75</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>134.95</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>150.27</v>
+        <v>150.23</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>848.72</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>704.22</v>
+        <v>703.63</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>106.9</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>117.13</v>
+        <v>117.09</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>456.3</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>530.99</v>
+        <v>530.37</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>1253.46</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1586.88</v>
+        <v>1584.15</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>1734.7</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1770.87</v>
+        <v>1770.03</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>101.89</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>125.68</v>
+        <v>125.52</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>3682.23</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3040.24</v>
+        <v>3038.19</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>1794.43</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2170.11</v>
+        <v>2164.39</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>106.25</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>133.59</v>
+        <v>133.29</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>391.46</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>397.83</v>
+        <v>397.53</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>438.21</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>435.11</v>
+        <v>434.5</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>178.75</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>194.03</v>
+        <v>193.5</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>533.1</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>554.95</v>
+        <v>554.6799999999999</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>528.1900000000001</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>589.4299999999999</v>
+        <v>589.97</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>849.2</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>961.92</v>
+        <v>959.65</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>582.12</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>687.04</v>
+        <v>687.09</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>341.24</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>375.33</v>
+        <v>374.72</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>197.44</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>200.91</v>
+        <v>200.92</v>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>228.47</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.94</v>
+        <v>249.76</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>1267.69</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1334.4</v>
+        <v>1332.91</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>214.5</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>228.37</v>
+        <v>228.8</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>524.33</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>559.53</v>
+        <v>559.95</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>480.06</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>486.91</v>
+        <v>486.93</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>1391.75</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1560.01</v>
+        <v>1561.64</v>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>8664.209999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8191.55</v>
+        <v>8171.82</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>73.61</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>97.78</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>464.26</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>497.39</v>
+        <v>497.04</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>476.3</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>571.36</v>
+        <v>570.58</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>684.75</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>665.47</v>
+        <v>664.97</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>248.2</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>321.21</v>
+        <v>320.49</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>442.41</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>427.19</v>
+        <v>427.21</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>462.44</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>588.52</v>
+        <v>587.63</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 18-Apr-2026  15:26:07    |    Closing Price Date: 17-Apr-2026</t>
+          <t>Scan Run: 19-Apr-2026  15:26:11    |    Closing Price Date: 17-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>18-Apr-2026  15:26:07</t>
+          <t>19-Apr-2026  15:26:11</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>559.05</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>701.48</v>
+        <v>701.29</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>432.39</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>456.91</v>
+        <v>456.43</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>361.73</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>406.23</v>
+        <v>405.7</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>687.96</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>744.65</v>
+        <v>745.0599999999999</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>289.43</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>302.48</v>
+        <v>302.2</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>1060.48</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>924.3200000000001</v>
+        <v>922.64</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>784.5700000000001</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>871.45</v>
+        <v>870.5</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>18.43</v>
+        <v>18.35</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>476.36</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>498.37</v>
+        <v>497.74</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1264.49</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1174.18</v>
+        <v>1173.01</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>117.48</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>135.84</v>
+        <v>135.37</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>581.3</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>590.6</v>
+        <v>589.5700000000001</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>443.87</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>472.3</v>
+        <v>471.62</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>357.62</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>341.01</v>
+        <v>340.44</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>130.08</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>165.59</v>
+        <v>165.35</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>968.77</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>958.37</v>
+        <v>957.17</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>881.74</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1091.83</v>
+        <v>1087.74</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>977.5700000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>946.09</v>
+        <v>945.34</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1207.59</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>947.38</v>
+        <v>946.7</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>321.95</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>462.64</v>
+        <v>461.42</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>1612.57</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1605.41</v>
+        <v>1601.83</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>379.52</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>478.11</v>
+        <v>477.84</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1083.63</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1252.34</v>
+        <v>1247.52</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>465.36</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>547.23</v>
+        <v>545.4400000000001</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>588.02</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>608.51</v>
+        <v>607.92</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>2453.69</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2733.18</v>
+        <v>2724.86</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>939.84</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1078.41</v>
+        <v>1076.61</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>592.58</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>580.53</v>
+        <v>580.29</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>457.11</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>520.5700000000001</v>
+        <v>519.89</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>457.4</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>435.58</v>
+        <v>435.45</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>302.43</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>355.31</v>
+        <v>354.94</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>390.82</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>394.92</v>
+        <v>395.1</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>1933.01</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2189.57</v>
+        <v>2186.48</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>280.35</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>271.37</v>
+        <v>271.05</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>437.45</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>524.08</v>
+        <v>523.6799999999999</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1272.34</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1492.97</v>
+        <v>1493.55</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>323.78</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>396.59</v>
+        <v>396.23</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>178.98</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>163.62</v>
+        <v>163.56</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>723.3</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>761.74</v>
+        <v>761.05</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>1028.44</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1227.74</v>
+        <v>1226.23</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>133.14</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.4</v>
+        <v>135.18</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>434.65</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>455.95</v>
+        <v>455.45</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>175.39</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>220.61</v>
+        <v>220.18</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>1087.35</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1186.94</v>
+        <v>1185.11</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>9670.790000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8676.610000000001</v>
+        <v>8667.879999999999</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>211.03</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>211.88</v>
+        <v>211.96</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>7.34</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.41</v>
+        <v>8.4</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>111.05</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.38</v>
+        <v>109.19</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>97.83</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.6</v>
+        <v>114.48</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>75.90000000000001</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>85.09999999999999</v>
+        <v>84.88</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>54.8</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>77.75</v>
+        <v>77.61</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>1147.49</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1153.29</v>
+        <v>1151.66</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>170.75</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>202.4</v>
+        <v>202.02</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>1004.79</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1327.31</v>
+        <v>1324.15</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>60.83</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>61.9</v>
+        <v>61.86</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>2387.74</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2596.19</v>
+        <v>2592.84</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>486.99</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>538.58</v>
+        <v>538.02</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>357.6</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>401.1</v>
+        <v>401.09</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>2140.98</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2061.56</v>
+        <v>2060.84</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>4409.43</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4454.92</v>
+        <v>4449.91</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>904.8099999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1045.44</v>
+        <v>1043.55</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>483.12</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>547.24</v>
+        <v>546.11</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>919.25</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1045.74</v>
+        <v>1045.67</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>105.41</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.77</v>
+        <v>110.5</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>925.8099999999999</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>940.72</v>
+        <v>940.26</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>605.97</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>564.4400000000001</v>
+        <v>564.0599999999999</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>890.28</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1046.01</v>
+        <v>1044.91</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4071,10 +4071,10 @@
         <v>3783.74</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3755.26</v>
+        <v>3755.25</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3657.59</v>
+        <v>3636.51</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>632.5</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>706.09</v>
+        <v>704.4</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>56.07</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.12</v>
+        <v>59.14</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>659.91</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>757.49</v>
+        <v>756.12</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>151.28</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>182.5</v>
+        <v>181.82</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>204.31</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>241.2</v>
+        <v>240.86</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>139</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>125.67</v>
+        <v>125.59</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>436.94</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>474.84</v>
+        <v>473.85</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>159.75</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.41</v>
+        <v>162.3</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>163.73</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178.75</v>
+        <v>178.37</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>991.1</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1091.08</v>
+        <v>1090.07</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>564.92</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>783.5599999999999</v>
+        <v>782.01</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>570.1</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>608.66</v>
+        <v>608.1900000000001</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>130.69</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>137.6</v>
+        <v>137.33</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>342.09</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>406.51</v>
+        <v>406.2</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>184.13</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>238.09</v>
+        <v>237.5</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>17.24</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>22.01</v>
+        <v>21.96</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>1102.64</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1369.53</v>
+        <v>1364.37</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>294.38</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>306.07</v>
+        <v>305.2</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44.59</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.53</v>
+        <v>51.38</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>905.89</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>897.88</v>
+        <v>898.87</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>754.9</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>799.21</v>
+        <v>798.53</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>1301.29</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1159.32</v>
+        <v>1157.98</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>872.79</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1037.63</v>
+        <v>1035.93</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>258.57</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>273.5</v>
+        <v>272.95</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>3728.12</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3687.18</v>
+        <v>3683.69</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>697.47</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>765.51</v>
+        <v>763.8200000000001</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>160.23</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.93</v>
+        <v>176.62</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>361.51</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>404.41</v>
+        <v>403.74</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5347,10 +5347,10 @@
         <v>951.72</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>906.01</v>
+        <v>906</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>936.65</v>
+        <v>934.4</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>504.8</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>582.65</v>
+        <v>582.4299999999999</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>657.25</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>757.23</v>
+        <v>756.47</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>343.08</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.45</v>
+        <v>355.36</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>64.56</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>83.63</v>
+        <v>83.83</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>33.56</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>43.41</v>
+        <v>43.38</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>124.64</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.13</v>
+        <v>114.01</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>379.67</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>415.67</v>
+        <v>415.07</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>23.97</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>34.87</v>
+        <v>34.72</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>574.36</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>713.12</v>
+        <v>711.37</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>128.08</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>168.05</v>
+        <v>167.47</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>399.85</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>433.23</v>
+        <v>432.18</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>329.19</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>352.43</v>
+        <v>352.1</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>903.17</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>827.6900000000001</v>
+        <v>826.63</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>688.72</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>759.5599999999999</v>
+        <v>757.6799999999999</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>193.46</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>220.81</v>
+        <v>220.67</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>220.65</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>199.82</v>
+        <v>199.68</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>855.59</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>961.62</v>
+        <v>960.8200000000001</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>1131.97</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1159.53</v>
+        <v>1156.76</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>170.01</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.64</v>
+        <v>191.78</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>14059.95</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14887.22</v>
+        <v>14881.12</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>131.1</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>164.04</v>
+        <v>163.77</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>184.29</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>212.49</v>
+        <v>212.29</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>47.16</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55.04</v>
+        <v>54.92</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>53.41</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.18</v>
+        <v>59.17</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>1613.56</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1356.87</v>
+        <v>1356.65</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1056.3</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1165.28</v>
+        <v>1162.28</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>304.23</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>325.86</v>
+        <v>326.5</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>434.78</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>475.72</v>
+        <v>474.85</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>3665.49</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2723.34</v>
+        <v>2721.26</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>347.89</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>366.37</v>
+        <v>365.69</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>99.79000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>130.15</v>
+        <v>129.93</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>1315.26</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1321.89</v>
+        <v>1321.12</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>172.95</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>189.24</v>
+        <v>188.61</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>1656.59</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2024.94</v>
+        <v>2024.07</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>380.72</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>431.53</v>
+        <v>430.44</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>839.83</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>826.22</v>
+        <v>825.87</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>330.74</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>346.91</v>
+        <v>346.48</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>199.7</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>238.85</v>
+        <v>238.49</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>1316.45</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1392.91</v>
+        <v>1389.73</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>1117.46</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1170.32</v>
+        <v>1169.09</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>75.03</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.93000000000001</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>252.04</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>265.26</v>
+        <v>264.91</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>34.07</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>42.81</v>
+        <v>42.66</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>381.39</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>489.05</v>
+        <v>487.43</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>585.4</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>749.2</v>
+        <v>747.4299999999999</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>145.77</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>193.65</v>
+        <v>193.59</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>584.61</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>591.85</v>
+        <v>590.77</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.99</v>
+        <v>10.98</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>199.24</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>243.57</v>
+        <v>243.13</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>165.98</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>162.76</v>
+        <v>162.63</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>121.21</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>142.2</v>
+        <v>141.94</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>671.17</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>670.33</v>
+        <v>669.1900000000001</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>26.69</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.41</v>
+        <v>32.39</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>1525.66</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1490.76</v>
+        <v>1490.67</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>837.78</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>935.97</v>
+        <v>934.28</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>2085.59</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2373.37</v>
+        <v>2367.07</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>243.95</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>278.41</v>
+        <v>278.2</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>125.92</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>135.33</v>
+        <v>135.09</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>2916.76</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2715.76</v>
+        <v>2714.42</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>2403.14</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2515.27</v>
+        <v>2512.08</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>203.95</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>240.91</v>
+        <v>240.41</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>191.13</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>248.75</v>
+        <v>248.2</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>126.5</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>134.51</v>
+        <v>134.13</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>255.1</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>273.49</v>
+        <v>273.15</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>540.75</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>580.46</v>
+        <v>579.8</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>2298.99</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2404.1</v>
+        <v>2401.59</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>31.55</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>41.17</v>
+        <v>41.06</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>8.65</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>850.9400000000001</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1047.38</v>
+        <v>1044.69</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>225.39</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>300.69</v>
+        <v>299.91</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>313.23</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>390.27</v>
+        <v>389.83</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>224.19</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>238.82</v>
+        <v>238.3</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>62.42</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.95</v>
+        <v>67.8</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>509.85</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>691.95</v>
+        <v>690.46</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>355.64</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>339.21</v>
+        <v>338.37</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>1689.17</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1995.47</v>
+        <v>1993.28</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>156.77</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>178</v>
+        <v>177.53</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>199.78</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>192.92</v>
+        <v>192.71</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>4402.95</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4582.09</v>
+        <v>4581.19</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>3655.06</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4382.38</v>
+        <v>4379.04</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>2130.3</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1770.7</v>
+        <v>1768.99</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>312.91</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>336.62</v>
+        <v>335.48</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>2063.99</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2076.38</v>
+        <v>2073.51</v>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>544.6</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>706.8099999999999</v>
+        <v>706.5599999999999</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>1012.88</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>917.33</v>
+        <v>915.21</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>839.91</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>915.14</v>
+        <v>915.4400000000001</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>137.63</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>158.73</v>
+        <v>158.32</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>534.21</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>615.6799999999999</v>
+        <v>614.46</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>353.69</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>356.43</v>
+        <v>355.74</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>25.93</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.72</v>
+        <v>27.66</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>3119.68</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2811.2</v>
+        <v>2810.79</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>373.85</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>426.66</v>
+        <v>425.88</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>38.52</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>35.99</v>
+        <v>35.97</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>213.37</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.92</v>
+        <v>223.85</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>183.66</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>228.03</v>
+        <v>228.42</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>180.89</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>135.17</v>
+        <v>135.19</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>924.16</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>867.59</v>
+        <v>867.08</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>1972.66</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2214.24</v>
+        <v>2210.14</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>744.16</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>808.83</v>
+        <v>808.47</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>846.6900000000001</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>1006</v>
+        <v>1005.29</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>130.59</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>138.15</v>
+        <v>137.9</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>237.74</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>253.32</v>
+        <v>253.09</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>345.57</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>394.39</v>
+        <v>393.76</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>635.38</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>682.65</v>
+        <v>680.96</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>224.4</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.91</v>
+        <v>253.73</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>796.63</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>909.75</v>
+        <v>910.02</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>134.95</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>150.23</v>
+        <v>149.82</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>848.72</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>703.63</v>
+        <v>703.28</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>106.9</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>117.09</v>
+        <v>116.83</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>456.3</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>530.37</v>
+        <v>529.83</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>1253.46</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1584.15</v>
+        <v>1582.45</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>1734.7</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1770.03</v>
+        <v>1770.99</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>101.89</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>125.52</v>
+        <v>125.23</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>3682.23</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3038.19</v>
+        <v>3035.34</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>1794.43</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2164.39</v>
+        <v>2155.66</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>106.25</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>133.29</v>
+        <v>132.93</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>391.46</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>397.53</v>
+        <v>396.8</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>438.21</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>434.5</v>
+        <v>433.88</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>178.75</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>193.5</v>
+        <v>193.2</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>533.1</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>554.6799999999999</v>
+        <v>554.54</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>528.1900000000001</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>589.97</v>
+        <v>588.67</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>56.85</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.57</v>
+        <v>52.53</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>849.2</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>959.65</v>
+        <v>958.37</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>582.12</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>687.09</v>
+        <v>686.4299999999999</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>341.24</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>374.72</v>
+        <v>374.29</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>197.44</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>200.92</v>
+        <v>200.81</v>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>228.47</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.76</v>
+        <v>249.41</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>1267.69</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1332.91</v>
+        <v>1333.36</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>214.5</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>228.8</v>
+        <v>228.89</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>524.33</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>559.95</v>
+        <v>559.5599999999999</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>480.06</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>486.93</v>
+        <v>485.91</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>1391.75</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1561.64</v>
+        <v>1559.74</v>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>8664.209999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8171.82</v>
+        <v>8150.39</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>73.61</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>97.43000000000001</v>
+        <v>97.36</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>464.26</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>497.04</v>
+        <v>495.54</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>476.3</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>570.58</v>
+        <v>569.95</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>684.75</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>664.97</v>
+        <v>664.26</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>248.2</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>320.49</v>
+        <v>320.65</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>442.41</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>427.21</v>
+        <v>426.75</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>462.44</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>587.63</v>
+        <v>587.72</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -70,7 +70,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -90,11 +90,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -163,7 +158,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -555,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 19-Apr-2026  15:26:11    |    Closing Price Date: 17-Apr-2026</t>
+          <t>Scan Run: 20-Apr-2026  16:50:40    |    Closing Price Date: 20-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +589,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>98</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>40.8</v>
+        <v>36.4</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>19-Apr-2026  15:26:11</t>
+          <t>20-Apr-2026  16:50:40</t>
         </is>
       </c>
     </row>
@@ -625,21 +620,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 98.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 94.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 86.4% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 82.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.8% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 36.4% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +648,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 245 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 236 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 216 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 206 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 102 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 91 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +756,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>584.95</v>
+        <v>570.4</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>533.0700000000001</v>
+        <v>536.63</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>559.05</v>
+        <v>559.5</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>701.29</v>
+        <v>696.17</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +800,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>436.8</v>
+        <v>438.25</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>431.23</v>
+        <v>431.9</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>432.39</v>
+        <v>432.62</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>456.43</v>
+        <v>454.91</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +844,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>373.2</v>
+        <v>365.2</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>355.14</v>
+        <v>356.1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>361.73</v>
+        <v>361.87</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>405.7</v>
+        <v>404.98</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,29 +888,29 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>697.75</v>
+        <v>676.15</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>672.54</v>
+        <v>672.88</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>687.96</v>
+        <v>687.5</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>745.0599999999999</v>
+        <v>743.97</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -937,20 +932,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2361.7</v>
+        <v>2410.7</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2309.48</v>
+        <v>2319.12</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2186.79</v>
+        <v>2195.57</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1773.91</v>
+        <v>1780.25</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +976,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>307.4</v>
+        <v>298.85</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>289.25</v>
+        <v>290.16</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>289.43</v>
+        <v>289.8</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>302.2</v>
+        <v>301.98</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1006,9 +1001,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J7" s="14" t="inlineStr">
@@ -1025,20 +1020,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1179.8</v>
+        <v>1185.4</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1126.51</v>
+        <v>1132.12</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1060.48</v>
+        <v>1065.38</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>922.64</v>
+        <v>923.46</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1064,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>834.05</v>
+        <v>833.3</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>762.6900000000001</v>
+        <v>769.41</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>784.5700000000001</v>
+        <v>786.48</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>870.5</v>
+        <v>867.8</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1108,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>489.55</v>
+        <v>497.5</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>468.7</v>
+        <v>471.45</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>486.13</v>
+        <v>486.58</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>562.03</v>
+        <v>561.39</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1152,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1069.65</v>
+        <v>1068.05</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1011.58</v>
+        <v>1016.96</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>968.02</v>
+        <v>971.95</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>951.74</v>
+        <v>952.9</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1196,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.56</v>
+        <v>9.57</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>8.43</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.029999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>18.35</v>
+        <v>18.17</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1240,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>573.8</v>
+        <v>573.4</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>473.35</v>
+        <v>482.88</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>476.36</v>
+        <v>480.17</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>497.74</v>
+        <v>497.22</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1284,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1288</v>
+        <v>1309</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1266.01</v>
+        <v>1270.1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1264.49</v>
+        <v>1266.23</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1173.01</v>
+        <v>1174.13</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1328,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>121.66</v>
+        <v>120.08</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>114.25</v>
+        <v>114.81</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>117.48</v>
+        <v>117.59</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>135.37</v>
+        <v>134.86</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1372,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>606.65</v>
+        <v>599.55</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>594.96</v>
+        <v>595.4</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>581.3</v>
+        <v>582.01</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>589.5700000000001</v>
+        <v>588.96</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,20 +1416,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>472.65</v>
+        <v>466.3</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>444.56</v>
+        <v>446.63</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>443.87</v>
+        <v>444.75</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>471.62</v>
+        <v>470.72</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1446,9 +1441,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J17" s="14" t="inlineStr">
@@ -1465,20 +1460,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>386.75</v>
+        <v>385.2</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>371.15</v>
+        <v>372.49</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>357.62</v>
+        <v>358.7</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>340.44</v>
+        <v>340.67</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1504,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>138.82</v>
+        <v>134.16</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>123.25</v>
+        <v>124.29</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>130.08</v>
+        <v>130.24</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>165.35</v>
+        <v>164.99</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1548,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1093.45</v>
+        <v>1064.55</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>990.98</v>
+        <v>997.99</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>968.77</v>
+        <v>972.53</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>957.17</v>
+        <v>957.0599999999999</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1592,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>922.6</v>
+        <v>899.15</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>850.09</v>
+        <v>854.76</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>881.74</v>
+        <v>882.42</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1087.74</v>
+        <v>1081.03</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1641,20 +1636,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1119.3</v>
+        <v>1076.9</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1008.05</v>
+        <v>1014.61</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>977.5700000000001</v>
+        <v>981.46</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>945.34</v>
+        <v>943.71</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1680,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1473.3</v>
+        <v>1503.4</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1307.94</v>
+        <v>1326.56</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1207.59</v>
+        <v>1219.19</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>946.7</v>
+        <v>951.48</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,24 +1724,24 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>15.21</v>
+        <v>14.78</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.93</v>
+        <v>14.91</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.35</v>
+        <v>15.33</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
       </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -1773,20 +1768,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>362.36</v>
+        <v>347.12</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>304.78</v>
+        <v>308.82</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>321.95</v>
+        <v>322.94</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>461.42</v>
+        <v>458.95</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1812,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1904.3</v>
+        <v>1893.3</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1659.24</v>
+        <v>1681.53</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1612.57</v>
+        <v>1623.58</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1601.83</v>
+        <v>1600.93</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1856,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>391.4</v>
+        <v>397.35</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>367.78</v>
+        <v>370.59</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>379.52</v>
+        <v>380.22</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>477.84</v>
+        <v>475.85</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1900,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1139.3</v>
+        <v>1149.75</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1074.59</v>
+        <v>1081.75</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1083.63</v>
+        <v>1086.22</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1247.52</v>
+        <v>1242.66</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1944,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>486.05</v>
+        <v>471.15</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>456.97</v>
+        <v>458.32</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>465.36</v>
+        <v>465.59</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>545.4400000000001</v>
+        <v>542.04</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1988,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>624.95</v>
+        <v>613.35</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>574.47</v>
+        <v>578.17</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>588.02</v>
+        <v>589.01</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>607.92</v>
+        <v>606.75</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2032,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>214.1</v>
+        <v>222.18</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>197.09</v>
+        <v>199.48</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>188.69</v>
+        <v>190</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>161.53</v>
+        <v>162.13</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2076,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2753.2</v>
+        <v>2827.1</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2429.78</v>
+        <v>2467.62</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2453.69</v>
+        <v>2468.34</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2724.86</v>
+        <v>2722.94</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2120,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>976.15</v>
+        <v>959.85</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>914.6900000000001</v>
+        <v>918.99</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>939.84</v>
+        <v>940.62</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1076.61</v>
+        <v>1074.89</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2164,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>623.4</v>
+        <v>617.9</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>585.09</v>
+        <v>588.21</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>592.58</v>
+        <v>593.58</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>580.29</v>
+        <v>579.77</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2208,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>497.7</v>
+        <v>492.4</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>446.83</v>
+        <v>451.17</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>457.11</v>
+        <v>458.49</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>519.89</v>
+        <v>518.47</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,17 +2252,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1347</v>
+        <v>1346.1</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1275.53</v>
+        <v>1282.25</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1306.54</v>
+        <v>1308.09</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2301,20 +2296,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>490.2</v>
+        <v>486.1</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>469.89</v>
+        <v>471.43</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>457.4</v>
+        <v>458.52</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>435.45</v>
+        <v>435.93</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2340,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>318</v>
+        <v>317.9</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>296.52</v>
+        <v>298.56</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>302.43</v>
+        <v>303.04</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>354.94</v>
+        <v>353.78</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,34 +2384,34 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>399.85</v>
+        <v>390.4</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>385.43</v>
+        <v>385.91</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>390.82</v>
+        <v>390.8</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>395.1</v>
+        <v>394.46</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -2433,24 +2428,24 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1858</v>
+        <v>1770.4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1789.58</v>
+        <v>1787.76</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1933.01</v>
+        <v>1926.63</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2186.48</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2176.61</v>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -2477,20 +2472,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>306.95</v>
+        <v>308.35</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>286.95</v>
+        <v>288.99</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>280.35</v>
+        <v>281.45</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>271.05</v>
+        <v>270.8</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2516,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>431.55</v>
+        <v>424.25</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>416.92</v>
+        <v>417.61</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>437.45</v>
+        <v>436.93</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>523.6799999999999</v>
+        <v>522.16</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2560,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>648.25</v>
+        <v>637.55</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>590.51</v>
+        <v>594.99</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>601.97</v>
+        <v>603.37</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>704.45</v>
+        <v>703.79</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,29 +2604,29 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1296.3</v>
+        <v>1263.3</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1206.85</v>
+        <v>1212.23</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1272.34</v>
+        <v>1271.99</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1493.55</v>
+        <v>1485.54</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
@@ -2653,20 +2648,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>341.25</v>
+        <v>345.8</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>309.81</v>
+        <v>313.23</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>323.78</v>
+        <v>324.65</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>396.23</v>
+        <v>394.57</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2692,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>189.83</v>
+        <v>193.48</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>179.57</v>
+        <v>180.89</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>178.98</v>
+        <v>179.55</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>163.56</v>
+        <v>163.66</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2736,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>747.8</v>
+        <v>727.45</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>709.91</v>
+        <v>711.58</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723.3</v>
+        <v>723.46</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>761.05</v>
+        <v>759.1</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2780,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1009.65</v>
+        <v>1016.6</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>994.48</v>
+        <v>996.59</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1028.44</v>
+        <v>1027.97</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1226.23</v>
+        <v>1221.51</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2824,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>149.61</v>
+        <v>160.76</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>134.47</v>
+        <v>136.98</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>133.14</v>
+        <v>134.23</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.18</v>
+        <v>135.12</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2868,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>457</v>
+        <v>449.45</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>429.89</v>
+        <v>431.75</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>434.65</v>
+        <v>435.23</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>455.45</v>
+        <v>454.74</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2898,9 +2893,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
@@ -2917,20 +2912,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>168.62</v>
+        <v>167.48</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>160.29</v>
+        <v>160.97</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>175.39</v>
+        <v>175.08</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>220.18</v>
+        <v>219.15</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,29 +2956,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1091.55</v>
+        <v>1069.25</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1050.57</v>
+        <v>1052.35</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1087.35</v>
+        <v>1086.64</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1185.11</v>
+        <v>1181.75</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
@@ -3005,20 +3000,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>10327.5</v>
+        <v>10140</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>9906</v>
+        <v>9928.290000000001</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>9670.790000000001</v>
+        <v>9689.190000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8667.879999999999</v>
+        <v>8662.280000000001</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3049,20 +3044,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>233.55</v>
+        <v>236.24</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>218.05</v>
+        <v>219.79</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>211.03</v>
+        <v>212.02</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>211.96</v>
+        <v>211.37</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3093,20 +3088,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.82</v>
+        <v>7.74</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.37</v>
+        <v>7.4</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.34</v>
+        <v>7.36</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3137,20 +3132,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>119.06</v>
+        <v>117.35</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>111.97</v>
+        <v>112.48</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>111.05</v>
+        <v>111.3</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.19</v>
+        <v>108.99</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3181,20 +3176,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>105.16</v>
+        <v>105.26</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>97.87</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>97.83</v>
+        <v>98.12</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.48</v>
+        <v>114.05</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,24 +3220,24 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>80.75</v>
+        <v>78.36</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>78.90000000000001</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>75.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.88</v>
-      </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>84.56</v>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -3269,24 +3264,24 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>13-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>50.21</v>
+        <v>47.7</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>49.03</v>
+        <v>48.91</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>54.8</v>
+        <v>54.52</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>77.61</v>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>77.06999999999999</v>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -3313,20 +3308,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1278.1</v>
+        <v>1271.9</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1192.7</v>
+        <v>1200.24</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1147.49</v>
+        <v>1152.37</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1151.66</v>
+        <v>1151.04</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3352,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>213.04</v>
+        <v>206.24</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>176.14</v>
+        <v>179</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>170.75</v>
+        <v>172.14</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>202.02</v>
+        <v>201.22</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3396,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1201.05</v>
+        <v>1167.4</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1012.18</v>
+        <v>1026.96</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1004.79</v>
+        <v>1011.17</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1324.15</v>
+        <v>1314.53</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3440,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>65.59999999999999</v>
+        <v>63.92</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>60.07</v>
+        <v>60.43</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>60.83</v>
+        <v>60.95</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>61.86</v>
+        <v>61.85</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,29 +3484,29 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2397.5</v>
+        <v>2345.2</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2341.36</v>
+        <v>2341.72</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2387.74</v>
+        <v>2386.08</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2592.84</v>
+        <v>2582.87</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I64" s="13" t="inlineStr">
@@ -3533,29 +3528,29 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>481.6</v>
+        <v>502.7</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>473.66</v>
+        <v>476.43</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>486.99</v>
+        <v>487.6</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>538.02</v>
+        <v>536.61</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H65" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I65" s="13" t="inlineStr">
@@ -3577,20 +3572,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>358.45</v>
+        <v>359.95</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>347.2</v>
+        <v>348.41</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>357.6</v>
+        <v>357.69</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>401.09</v>
+        <v>400.04</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,20 +3616,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2259.1</v>
+        <v>2250.5</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2127.29</v>
+        <v>2139.02</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2140.98</v>
+        <v>2145.28</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2060.84</v>
+        <v>2060.45</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3660,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4907.5</v>
+        <v>4995.2</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4488.58</v>
+        <v>4536.83</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4409.43</v>
+        <v>4432.4</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4449.91</v>
+        <v>4451.02</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3709,20 +3704,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>903.55</v>
+        <v>890.75</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>867.86</v>
+        <v>870.04</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>904.8099999999999</v>
+        <v>904.26</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1043.55</v>
+        <v>1040.09</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,20 +3748,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>513.85</v>
+        <v>499.95</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>473.36</v>
+        <v>475.89</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>483.12</v>
+        <v>483.78</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>546.11</v>
+        <v>545.15</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,29 +3792,29 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>929.9</v>
+        <v>910.7</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>891.04</v>
+        <v>892.91</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>919.25</v>
+        <v>918.92</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1045.67</v>
+        <v>1043.51</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H71" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I71" s="13" t="inlineStr">
@@ -3841,20 +3836,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>109.98</v>
+        <v>107.3</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>103.96</v>
+        <v>104.28</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>105.41</v>
+        <v>105.49</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.5</v>
+        <v>110.22</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3885,20 +3880,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>1014.35</v>
+        <v>1017.85</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>918.6799999999999</v>
+        <v>928.13</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>925.8099999999999</v>
+        <v>929.42</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>940.26</v>
+        <v>940.1799999999999</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3924,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>853.45</v>
+        <v>869.05</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>663.5700000000001</v>
+        <v>683.14</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>605.97</v>
+        <v>616.28</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>564.0599999999999</v>
+        <v>566.37</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,29 +3968,29 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>640.4</v>
+        <v>635.55</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>600.83</v>
+        <v>604.14</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>639.55</v>
+        <v>639.39</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>756.3</v>
+        <v>755.1</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H75" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H75" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
@@ -4017,20 +4012,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1053.65</v>
+        <v>1035.15</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>972.39</v>
+        <v>978.37</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>890.28</v>
+        <v>895.96</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1044.91</v>
+        <v>1037.08</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4042,9 +4037,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
@@ -4061,20 +4056,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>3985.6</v>
+        <v>3977.5</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3783.74</v>
+        <v>3802.19</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3755.25</v>
+        <v>3763.97</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3636.51</v>
+        <v>3628</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,20 +4100,20 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>646.35</v>
+        <v>652.7</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>619.01</v>
+        <v>622.22</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>632.5</v>
+        <v>633.29</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>704.4</v>
+        <v>702.71</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4149,20 +4144,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>59.31</v>
+        <v>58.25</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>55.83</v>
+        <v>56.06</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>56.07</v>
+        <v>56.15</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.14</v>
+        <v>58.99</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4174,9 +4169,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I79" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J79" s="14" t="inlineStr">
@@ -4193,20 +4188,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>726.55</v>
+        <v>720.8</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>651.12</v>
+        <v>657.76</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>659.91</v>
+        <v>662.29</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>756.12</v>
+        <v>754.47</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,20 +4232,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>161.36</v>
+        <v>157.88</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>145.88</v>
+        <v>147.03</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>151.28</v>
+        <v>151.54</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>181.82</v>
+        <v>181.09</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4281,20 +4276,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>214.58</v>
+        <v>212.22</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>199.37</v>
+        <v>200.6</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>204.31</v>
+        <v>204.62</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>240.86</v>
+        <v>239.76</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4320,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>148.22</v>
+        <v>146.73</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>144.3</v>
+        <v>144.53</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>139</v>
+        <v>139.3</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>125.59</v>
+        <v>125.47</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4364,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>489.7</v>
+        <v>481.25</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>429.83</v>
+        <v>434.73</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>436.94</v>
+        <v>438.68</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>473.85</v>
+        <v>472.86</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4413,29 +4408,29 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>160.92</v>
+        <v>157.8</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>153.44</v>
+        <v>153.85</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>159.75</v>
+        <v>159.67</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.3</v>
+        <v>162.19</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H85" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
@@ -4457,20 +4452,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>174.07</v>
+        <v>171.54</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>160.96</v>
+        <v>161.97</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>163.73</v>
+        <v>164.03</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178.37</v>
+        <v>177.94</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4496,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>970.9</v>
+        <v>964</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>935.0599999999999</v>
+        <v>937.8200000000001</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>991.1</v>
+        <v>990.04</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1090.07</v>
+        <v>1085.86</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4545,20 +4540,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>621.05</v>
+        <v>624.6</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>538.41</v>
+        <v>546.62</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>564.92</v>
+        <v>567.26</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>782.01</v>
+        <v>776.88</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4589,29 +4584,29 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>565.35</v>
+        <v>570.15</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>551.8</v>
+        <v>553.54</v>
       </c>
       <c r="E89" s="11" t="n">
         <v>570.1</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>608.1900000000001</v>
+        <v>608.55</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H89" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
@@ -4633,29 +4628,29 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>132.33</v>
+        <v>129.6</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>127.12</v>
+        <v>127.36</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.69</v>
+        <v>130.65</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>137.33</v>
+        <v>136.87</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H90" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I90" s="13" t="inlineStr">
@@ -4677,20 +4672,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>359.75</v>
+        <v>355.3</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>329.38</v>
+        <v>331.85</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>342.09</v>
+        <v>342.6</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>406.2</v>
+        <v>404.49</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,20 +4716,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>191.9</v>
+        <v>188.39</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>176.37</v>
+        <v>177.52</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>184.13</v>
+        <v>184.3</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>237.5</v>
+        <v>236.54</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4765,20 +4760,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>19.09</v>
+        <v>19.24</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>16.78</v>
+        <v>17.01</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>17.24</v>
+        <v>17.31</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.96</v>
+        <v>21.82</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,29 +4804,29 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1116.2</v>
+        <v>1098</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1037.03</v>
+        <v>1042.83</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1102.64</v>
+        <v>1102.46</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1364.37</v>
+        <v>1355.84</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H94" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I94" s="13" t="inlineStr">
@@ -4853,20 +4848,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>313.44</v>
+        <v>310.75</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>283.23</v>
+        <v>285.85</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>294.38</v>
+        <v>295.03</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>305.2</v>
+        <v>304.44</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4892,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>49.61</v>
+        <v>48.72</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>44.44</v>
+        <v>44.85</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>44.59</v>
+        <v>44.75</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.38</v>
+        <v>51.15</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,20 +4936,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>974.1</v>
+        <v>959</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>908.53</v>
+        <v>913.34</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>905.89</v>
+        <v>907.97</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>898.87</v>
+        <v>897.5599999999999</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4985,20 +4980,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>803.25</v>
+        <v>803.5</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>760.9</v>
+        <v>764.96</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>754.9</v>
+        <v>756.8</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>798.53</v>
+        <v>797.4400000000001</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5024,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1565.4</v>
+        <v>1532</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1348.13</v>
+        <v>1365.64</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1301.29</v>
+        <v>1310.33</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1157.98</v>
+        <v>1161.58</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5073,20 +5068,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>838</v>
+        <v>835.85</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>804.6900000000001</v>
+        <v>807.66</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>872.79</v>
+        <v>871.34</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1035.93</v>
+        <v>1032.36</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5117,20 +5112,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>275.85</v>
+        <v>268.21</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>254.08</v>
+        <v>255.43</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>258.57</v>
+        <v>258.95</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>272.95</v>
+        <v>272.65</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5142,9 +5137,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I101" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
@@ -5161,20 +5156,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4099.6</v>
+        <v>4148.6</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3823.6</v>
+        <v>3854.55</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3728.12</v>
+        <v>3744.61</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3683.69</v>
+        <v>3683.18</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5200,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>742.3</v>
+        <v>731.2</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>701.8</v>
+        <v>704.6</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>697.47</v>
+        <v>698.79</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>763.8200000000001</v>
+        <v>760.62</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5244,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>163.03</v>
+        <v>160.96</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>153.57</v>
+        <v>154.28</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>160.23</v>
+        <v>160.26</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.62</v>
+        <v>176.51</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5288,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>400.75</v>
+        <v>396.55</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>365.85</v>
+        <v>368.78</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>361.51</v>
+        <v>362.88</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>403.74</v>
+        <v>402.7</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,20 +5332,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1042.05</v>
+        <v>1046.45</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>951.72</v>
+        <v>960.74</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>906</v>
+        <v>911.51</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>934.4</v>
+        <v>930.9299999999999</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,20 +5376,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>519.25</v>
+        <v>511.45</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>482.33</v>
+        <v>485.1</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>504.8</v>
+        <v>505.06</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>582.4299999999999</v>
+        <v>580.16</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5425,20 +5420,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>673.7</v>
+        <v>662.8</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>626.09</v>
+        <v>629.59</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>657.25</v>
+        <v>657.47</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>756.47</v>
+        <v>754.5599999999999</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5469,20 +5464,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>374.75</v>
+        <v>367.5</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>347.83</v>
+        <v>349.7</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>343.08</v>
+        <v>344.04</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.36</v>
+        <v>354.9</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5513,20 +5508,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>72.48</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>63.31</v>
+        <v>64.27</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>64.56</v>
+        <v>64.91</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>83.83</v>
+        <v>83.23</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,20 +5552,20 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>33.01</v>
+        <v>33.2</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>31.89</v>
+        <v>32.01</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.56</v>
+        <v>33.55</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>43.38</v>
+        <v>43.13</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5601,20 +5596,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>128.56</v>
+        <v>126.11</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>122.86</v>
+        <v>123.17</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.64</v>
+        <v>124.7</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.01</v>
+        <v>113.86</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5645,20 +5640,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>391.45</v>
+        <v>383.35</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>380.8</v>
+        <v>381.04</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>379.67</v>
+        <v>379.82</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>415.07</v>
+        <v>414.35</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5689,20 +5684,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>26.63</v>
+        <v>25.76</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>23.2</v>
+        <v>23.44</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>23.97</v>
+        <v>24.04</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>34.72</v>
+        <v>34.45</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5728,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>549.7</v>
+        <v>546.45</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>543.4299999999999</v>
+        <v>543.71</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>574.36</v>
+        <v>573.26</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>711.37</v>
+        <v>703.79</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5777,20 +5772,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>123.92</v>
+        <v>120.96</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>120.75</v>
+        <v>120.77</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>128.08</v>
+        <v>127.8</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>167.47</v>
+        <v>166.7</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5816,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>448.25</v>
+        <v>440.55</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>403.16</v>
+        <v>406.72</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>399.85</v>
+        <v>401.45</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>432.18</v>
+        <v>431.26</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5865,20 +5860,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>351.05</v>
+        <v>345.6</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>322.03</v>
+        <v>324.28</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>329.19</v>
+        <v>329.84</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>352.1</v>
+        <v>351.64</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5904,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1269.9</v>
+        <v>1245.8</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>991.54</v>
+        <v>1015.75</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>903.17</v>
+        <v>916.6</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>826.63</v>
+        <v>831</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5953,20 +5948,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>746.6</v>
+        <v>755.15</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>672.52</v>
+        <v>680.39</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>688.72</v>
+        <v>691.33</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>757.6799999999999</v>
+        <v>755.75</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5992,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>203.09</v>
+        <v>204.07</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>186.57</v>
+        <v>188.24</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>193.46</v>
+        <v>193.88</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>220.67</v>
+        <v>220.14</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6041,20 +6036,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>246.23</v>
+        <v>245.67</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>233.45</v>
+        <v>234.62</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>220.65</v>
+        <v>221.63</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>199.68</v>
+        <v>199.79</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6080,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>923.35</v>
+        <v>933.6</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>867.53</v>
+        <v>873.8200000000001</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>855.59</v>
+        <v>858.64</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>960.8200000000001</v>
+        <v>959.53</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6129,20 +6124,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1263.4</v>
+        <v>1363.8</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1162.39</v>
+        <v>1181.57</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1131.97</v>
+        <v>1141.06</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1156.76</v>
+        <v>1153.41</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,29 +6168,29 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>171.96</v>
+        <v>167.24</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>164.93</v>
+        <v>165.15</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>170.01</v>
+        <v>169.9</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.78</v>
+        <v>191.79</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H125" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I125" s="13" t="inlineStr">
@@ -6217,20 +6212,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14349</v>
+        <v>14142</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>13608.58</v>
+        <v>13659.38</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14059.95</v>
+        <v>14063.17</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14881.12</v>
+        <v>14872.13</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6261,20 +6256,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>142.1</v>
+        <v>141.58</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>126.68</v>
+        <v>128.1</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>131.1</v>
+        <v>131.51</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>163.77</v>
+        <v>163.01</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,20 +6300,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>178.86</v>
+        <v>177.36</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>173.52</v>
+        <v>173.89</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>184.29</v>
+        <v>184.02</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>212.29</v>
+        <v>211.48</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6349,20 +6344,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>55.86</v>
+        <v>55.53</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>47.22</v>
+        <v>48.01</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>47.16</v>
+        <v>47.49</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>54.92</v>
+        <v>54.74</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6393,20 +6388,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>63.44</v>
+        <v>65.88</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>54.08</v>
+        <v>55.21</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>53.41</v>
+        <v>53.9</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.17</v>
+        <v>59.06</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6437,20 +6432,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1794.9</v>
+        <v>1795.4</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1684.35</v>
+        <v>1694.93</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1613.56</v>
+        <v>1620.69</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1356.65</v>
+        <v>1359.58</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6481,20 +6476,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1485.75</v>
+        <v>1490</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1165.53</v>
+        <v>1196.43</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1056.3</v>
+        <v>1073.31</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1162.28</v>
+        <v>1160.92</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6520,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>327.95</v>
+        <v>321.2</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>301.67</v>
+        <v>303.53</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>304.23</v>
+        <v>304.9</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.5</v>
+        <v>326.19</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6550,9 +6545,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I133" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J133" s="14" t="inlineStr">
@@ -6569,20 +6564,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>471.6</v>
+        <v>456.2</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>426.25</v>
+        <v>429.1</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>434.78</v>
+        <v>435.62</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>474.85</v>
+        <v>473.18</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6608,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>4857.8</v>
+        <v>4942</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>4075.35</v>
+        <v>4157.89</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>3665.49</v>
+        <v>3715.55</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2721.26</v>
+        <v>2739.13</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6652,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>325.15</v>
+        <v>320.75</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>336.32</v>
+        <v>334.84</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>347.89</v>
+        <v>346.83</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>365.69</v>
+        <v>364.26</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6701,20 +6696,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>96.78</v>
+        <v>96.08</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>93.28</v>
+        <v>93.55</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>99.79000000000001</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>129.93</v>
+        <v>129.25</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6745,20 +6740,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1417.7</v>
+        <v>1384.1</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1304.79</v>
+        <v>1312.34</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1315.26</v>
+        <v>1317.96</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1321.12</v>
+        <v>1321.74</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6784,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>179.23</v>
+        <v>176.9</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>172.71</v>
+        <v>173.11</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>172.95</v>
+        <v>173.11</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>188.61</v>
+        <v>187.97</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6833,20 +6828,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1746</v>
+        <v>1682.9</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1574.88</v>
+        <v>1585.16</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1656.59</v>
+        <v>1657.62</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2024.07</v>
+        <v>2015.42</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6872,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>388.6</v>
+        <v>389.2</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>367.96</v>
+        <v>369.99</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>380.72</v>
+        <v>381.05</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>430.44</v>
+        <v>428.29</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,20 +6916,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>877.8</v>
+        <v>869.8</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>850.7</v>
+        <v>852.52</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>839.83</v>
+        <v>841</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>825.87</v>
+        <v>825.48</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6965,20 +6960,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>369.6</v>
+        <v>378.55</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>327.65</v>
+        <v>332.5</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>330.74</v>
+        <v>332.62</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>346.48</v>
+        <v>346.01</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7009,20 +7004,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>192.22</v>
+        <v>192.75</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>190.3</v>
+        <v>190.53</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>199.7</v>
+        <v>199.42</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>238.49</v>
+        <v>237.58</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7048,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1511.6</v>
+        <v>1494.4</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1343.35</v>
+        <v>1357.74</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1316.45</v>
+        <v>1323.43</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1389.73</v>
+        <v>1383.74</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7092,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1208.4</v>
+        <v>1185.4</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1110.7</v>
+        <v>1117.82</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1117.46</v>
+        <v>1120.13</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1169.09</v>
+        <v>1167.68</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7136,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>77.41</v>
+        <v>76.31</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>73.11</v>
+        <v>73.41</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.03</v>
+        <v>75.08</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.73999999999999</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7180,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>273.34</v>
+        <v>270.08</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>248.74</v>
+        <v>250.77</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>252.04</v>
+        <v>252.75</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>264.91</v>
+        <v>264.22</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7229,20 +7224,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>36.36</v>
+        <v>35.89</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>32.67</v>
+        <v>32.97</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>34.07</v>
+        <v>34.14</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>42.66</v>
+        <v>42.45</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7273,20 +7268,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>413.75</v>
+        <v>400.95</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>362.32</v>
+        <v>366</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>381.39</v>
+        <v>382.15</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>487.43</v>
+        <v>485.03</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,24 +7312,24 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>569.4</v>
+        <v>545.3</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>545.72</v>
+        <v>545.6799999999999</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>585.4</v>
+        <v>583.8200000000001</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>747.4299999999999</v>
-      </c>
-      <c r="G151" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>738.04</v>
+      </c>
+      <c r="G151" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -7361,20 +7356,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>144.89</v>
+        <v>144.07</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>138.87</v>
+        <v>139.36</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.77</v>
+        <v>145.71</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>193.59</v>
+        <v>193.12</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7405,20 +7400,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>432.55</v>
+        <v>414.85</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>353.53</v>
+        <v>359.37</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>361.77</v>
+        <v>363.85</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>509.74</v>
+        <v>508.8</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7444,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>667.65</v>
+        <v>670.05</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>604.62</v>
+        <v>610.85</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>584.61</v>
+        <v>587.96</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>590.77</v>
+        <v>590.24</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7493,20 +7488,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.58</v>
+        <v>9.69</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>8.93</v>
+        <v>9</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>9.210000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.98</v>
+        <v>10.93</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7532,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>203.11</v>
+        <v>201.96</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>187.83</v>
+        <v>189.18</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>199.24</v>
+        <v>199.35</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>243.13</v>
+        <v>242.07</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7581,20 +7576,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>184.75</v>
+        <v>192.16</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>168.82</v>
+        <v>171.04</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>165.98</v>
+        <v>167.01</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>162.63</v>
+        <v>162.68</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,20 +7620,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>124.33</v>
+        <v>126.93</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>117.67</v>
+        <v>118.55</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>121.21</v>
+        <v>121.43</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.94</v>
+        <v>141.58</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7669,20 +7664,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>809.15</v>
+        <v>781.5</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>687.86</v>
+        <v>696.78</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>671.17</v>
+        <v>675.49</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>669.1900000000001</v>
+        <v>669.4</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7708,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>28.49</v>
+        <v>27.83</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>26.15</v>
+        <v>26.31</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>26.69</v>
+        <v>26.74</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,20 +7752,20 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1642.9</v>
+        <v>1635.5</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1525.17</v>
+        <v>1535.68</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1525.66</v>
+        <v>1529.97</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1490.67</v>
+        <v>1489.41</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7801,20 +7796,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>883.7</v>
+        <v>866.05</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>842.7</v>
+        <v>844.92</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>837.78</v>
+        <v>838.89</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>934.28</v>
+        <v>929.54</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7840,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2376</v>
+        <v>2432.7</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2093.69</v>
+        <v>2125.98</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2085.59</v>
+        <v>2099.2</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2367.07</v>
+        <v>2361.36</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7884,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>586.8</v>
+        <v>588.45</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>560.21</v>
+        <v>562.9</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>567.42</v>
+        <v>568.24</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>554.46</v>
+        <v>553.5</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,20 +7928,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>254.95</v>
+        <v>257.02</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>239.78</v>
+        <v>241.42</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>243.95</v>
+        <v>244.46</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>278.2</v>
+        <v>277.83</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,29 +7972,29 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>125.24</v>
+        <v>130.88</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>124.8</v>
+        <v>125.38</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>125.92</v>
+        <v>126.12</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>135.09</v>
+        <v>135.53</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H166" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H166" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I166" s="13" t="inlineStr">
@@ -8021,20 +8016,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3133.1</v>
+        <v>3086.9</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>2946.95</v>
+        <v>2960.28</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>2916.76</v>
+        <v>2923.43</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2714.42</v>
+        <v>2713.52</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8060,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2752</v>
+        <v>2711.3</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2416.53</v>
+        <v>2444.61</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2403.14</v>
+        <v>2415.23</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2512.08</v>
+        <v>2511.71</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8104,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>225.18</v>
+        <v>217.39</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>197.77</v>
+        <v>199.64</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>203.95</v>
+        <v>204.48</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>240.41</v>
+        <v>239.13</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8153,20 +8148,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>197.36</v>
+        <v>193.28</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>187.36</v>
+        <v>187.93</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>191.13</v>
+        <v>191.21</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>248.2</v>
+        <v>246.78</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8197,20 +8192,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>132.4</v>
+        <v>133.14</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>121.26</v>
+        <v>122.39</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>126.5</v>
+        <v>126.76</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>134.13</v>
+        <v>133.81</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,20 +8236,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>268</v>
+        <v>261.37</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>252.12</v>
+        <v>253</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>255.1</v>
+        <v>255.35</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>273.15</v>
+        <v>272.53</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8280,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>583.65</v>
+        <v>569.6</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>531.39</v>
+        <v>535.03</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>540.75</v>
+        <v>541.88</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>579.8</v>
+        <v>579.05</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8310,9 +8305,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I173" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J173" s="14" t="inlineStr">
@@ -8329,20 +8324,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2461.3</v>
+        <v>2427.2</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2315.7</v>
+        <v>2326.32</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2298.99</v>
+        <v>2304.02</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2401.59</v>
+        <v>2398.41</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8368,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>34.72</v>
+        <v>34.4</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>30.8</v>
+        <v>31.14</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>31.55</v>
+        <v>31.66</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>41.06</v>
+        <v>40.87</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8417,20 +8412,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>9.77</v>
+        <v>9.51</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>8.75</v>
+        <v>8.82</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>8.65</v>
+        <v>8.68</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.890000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8461,24 +8456,24 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>803.4</v>
+        <v>797.85</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>801.1799999999999</v>
+        <v>800.87</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>850.9400000000001</v>
+        <v>848.86</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1044.69</v>
-      </c>
-      <c r="G177" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1037.06</v>
+      </c>
+      <c r="G177" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
@@ -8505,20 +8500,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>244.76</v>
+        <v>250.39</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>220.77</v>
+        <v>223.59</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>225.39</v>
+        <v>226.37</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>299.91</v>
+        <v>298.38</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8549,20 +8544,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>309.03</v>
+        <v>305.32</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>289.29</v>
+        <v>290.82</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>313.23</v>
+        <v>312.92</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>389.83</v>
+        <v>388.09</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8593,29 +8588,29 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>223.4</v>
+        <v>224.31</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>220.92</v>
+        <v>221.24</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>224.19</v>
+        <v>224.2</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>238.3</v>
+        <v>237.65</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H180" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H180" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I180" s="13" t="inlineStr">
@@ -8637,20 +8632,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>63.27</v>
+        <v>62.91</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>61.75</v>
+        <v>61.86</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>62.42</v>
+        <v>62.44</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.8</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,29 +8676,29 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>513.25</v>
+        <v>502.35</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>481.71</v>
+        <v>483.68</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>509.85</v>
+        <v>509.55</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>690.46</v>
+        <v>686.95</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H182" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H182" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I182" s="13" t="inlineStr">
@@ -8725,20 +8720,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>423.35</v>
+        <v>411.5</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>374.09</v>
+        <v>377.66</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>355.64</v>
+        <v>357.83</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>338.37</v>
+        <v>338.3</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,24 +8764,24 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1577.5</v>
+        <v>1558.6</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1559.48</v>
+        <v>1559.4</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1689.17</v>
+        <v>1684.05</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1993.28</v>
-      </c>
-      <c r="G184" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1986.25</v>
+      </c>
+      <c r="G184" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
@@ -8813,20 +8808,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>163.1</v>
+        <v>163.2</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>152.34</v>
+        <v>153.38</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>156.77</v>
+        <v>157.03</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>177.53</v>
+        <v>176.95</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8857,20 +8852,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>218.47</v>
+        <v>213.39</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>197.15</v>
+        <v>198.69</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>199.78</v>
+        <v>200.32</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>192.71</v>
+        <v>192.67</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8896,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4720</v>
+        <v>4724.1</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4499.72</v>
+        <v>4521.09</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4402.95</v>
+        <v>4415.55</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4581.19</v>
+        <v>4580.57</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8945,20 +8940,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3559.8</v>
+        <v>3578.3</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3473.52</v>
+        <v>3483.49</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3655.06</v>
+        <v>3652.05</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4379.04</v>
+        <v>4358.75</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8989,20 +8984,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2378.3</v>
+        <v>2275.5</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2236.82</v>
+        <v>2240.5</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2130.3</v>
+        <v>2135.99</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1768.99</v>
+        <v>1771.25</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,20 +9028,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>326.3</v>
+        <v>323.6</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>313.08</v>
+        <v>314.08</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>312.91</v>
+        <v>313.33</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>335.48</v>
+        <v>333.99</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9077,20 +9072,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>1885</v>
+        <v>1845.7</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>2021.41</v>
+        <v>2004.67</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2063.99</v>
+        <v>2055.43</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2073.51</v>
+        <v>2067.82</v>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
@@ -9121,20 +9116,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>573.75</v>
+        <v>554.9</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>516.1799999999999</v>
+        <v>519.86</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>544.6</v>
+        <v>545</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>706.5599999999999</v>
+        <v>702.26</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9165,20 +9160,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1107.85</v>
+        <v>1102.75</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1021.47</v>
+        <v>1029.21</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1012.88</v>
+        <v>1016.4</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>915.21</v>
+        <v>915.34</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9204,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>869</v>
+        <v>860.9</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>812.78</v>
+        <v>817.36</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>839.91</v>
+        <v>840.73</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>915.4400000000001</v>
+        <v>914.5700000000001</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,20 +9248,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>146.8</v>
+        <v>144.47</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>136.32</v>
+        <v>137.09</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>137.63</v>
+        <v>137.9</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>158.32</v>
+        <v>157.48</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9297,20 +9292,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>547.85</v>
+        <v>546.65</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>521.99</v>
+        <v>524.34</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>534.21</v>
+        <v>534.7</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>614.46</v>
+        <v>611.59</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9341,20 +9336,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>410.55</v>
+        <v>411.25</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>381.5</v>
+        <v>384.33</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>353.69</v>
+        <v>355.95</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>355.74</v>
+        <v>355.35</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9380,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>28.17</v>
+        <v>27.91</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>26.84</v>
+        <v>26.94</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>25.93</v>
+        <v>26.01</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.66</v>
+        <v>27.55</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9424,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3735.8</v>
+        <v>3627.6</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3272.55</v>
+        <v>3306.37</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3119.68</v>
+        <v>3139.6</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2810.79</v>
+        <v>2813.04</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9468,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>433.35</v>
+        <v>436.6</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>375.05</v>
+        <v>380.91</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>373.85</v>
+        <v>376.31</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>425.88</v>
+        <v>424.54</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9512,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>38.93</v>
+        <v>39.29</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>37.87</v>
+        <v>38.01</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>38.52</v>
+        <v>38.55</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>35.97</v>
+        <v>36.01</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,20 +9556,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>222.36</v>
+        <v>221.02</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>213.34</v>
+        <v>214.07</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>213.37</v>
+        <v>213.67</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.85</v>
+        <v>223.32</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9600,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>193.97</v>
+        <v>212.08</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>177.82</v>
+        <v>181.08</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>183.66</v>
+        <v>184.78</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>228.42</v>
+        <v>226.98</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9644,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>263.08</v>
+        <v>271.63</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>211.58</v>
+        <v>217.3</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>180.89</v>
+        <v>184.45</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>135.19</v>
+        <v>136.18</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9688,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>1000.25</v>
+        <v>996.5</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>961.0599999999999</v>
+        <v>964.4400000000001</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>924.16</v>
+        <v>926.99</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>867.08</v>
+        <v>867.1</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9732,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2221.5</v>
+        <v>2183.9</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2006.81</v>
+        <v>2023.67</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>1972.66</v>
+        <v>1980.94</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2210.14</v>
+        <v>2203.26</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9762,9 +9757,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I206" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I206" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J206" s="14" t="inlineStr">
@@ -9781,20 +9776,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>788.5</v>
+        <v>772.55</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>725.8</v>
+        <v>730.25</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>744.16</v>
+        <v>745.27</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>808.47</v>
+        <v>807.01</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9825,29 +9820,29 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>873.75</v>
+        <v>833.25</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>814.97</v>
+        <v>816.71</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>846.6900000000001</v>
+        <v>846.16</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>1005.29</v>
+        <v>1002.51</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H208" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H208" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I208" s="13" t="inlineStr">
@@ -9869,20 +9864,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>148.01</v>
+        <v>144.5</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>134.37</v>
+        <v>135.34</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>130.59</v>
+        <v>131.14</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.9</v>
+        <v>137.58</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9908,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>272.97</v>
+        <v>267.19</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>239.32</v>
+        <v>241.97</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>237.74</v>
+        <v>238.89</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>253.09</v>
+        <v>252.6</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9952,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>333.65</v>
+        <v>326.5</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>321.16</v>
+        <v>321.67</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>345.57</v>
+        <v>344.82</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>393.76</v>
+        <v>391.7</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,29 +9996,29 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>638.5</v>
+        <v>619.8</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>618.17</v>
+        <v>618.3200000000001</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>635.38</v>
+        <v>634.76</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>680.96</v>
+        <v>680.7</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H212" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H212" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I212" s="13" t="inlineStr">
@@ -10045,20 +10040,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>239.49</v>
+        <v>237.74</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>219.6</v>
+        <v>221.33</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>224.4</v>
+        <v>224.93</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.73</v>
+        <v>252.79</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,20 +10084,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>813.3</v>
+        <v>809.05</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>766.9400000000001</v>
+        <v>770.95</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>796.63</v>
+        <v>797.11</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>910.02</v>
+        <v>906.85</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10133,20 +10128,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>135.5</v>
+        <v>136.1</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>126.89</v>
+        <v>127.77</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>134.95</v>
+        <v>135</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>149.82</v>
+        <v>149.05</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10177,20 +10172,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>996.9</v>
+        <v>1030.7</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>895.6</v>
+        <v>908.46</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>848.72</v>
+        <v>855.86</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>703.28</v>
+        <v>705.47</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10221,20 +10216,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>405.4</v>
+        <v>416.2</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>377.08</v>
+        <v>380.81</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>392.58</v>
+        <v>393.51</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>486.62</v>
+        <v>485.92</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10260,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>115.69</v>
+        <v>114.29</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>106.4</v>
+        <v>107.15</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>106.9</v>
+        <v>107.19</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.83</v>
+        <v>116.4</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10309,20 +10304,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>491.1</v>
+        <v>482.65</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>449.73</v>
+        <v>452.86</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>456.3</v>
+        <v>457.33</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>529.83</v>
+        <v>527.84</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10353,29 +10348,29 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1238.7</v>
+        <v>1263.3</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1194.22</v>
+        <v>1200.8</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1253.46</v>
+        <v>1253.85</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1582.45</v>
+        <v>1576.39</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H220" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H220" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I220" s="13" t="inlineStr">
@@ -10397,29 +10392,29 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1738</v>
+        <v>1709.8</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1713.5</v>
+        <v>1713.15</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1734.7</v>
+        <v>1733.72</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1770.99</v>
-      </c>
-      <c r="G221" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H221" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1770.4</v>
+      </c>
+      <c r="G221" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H221" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I221" s="13" t="inlineStr">
@@ -10441,20 +10436,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>106.01</v>
+        <v>103.23</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>96.27</v>
+        <v>96.94</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>101.89</v>
+        <v>101.94</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>125.23</v>
+        <v>124.53</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,20 +10480,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>4210.6</v>
+        <v>4134.5</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3871.64</v>
+        <v>3896.67</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3682.23</v>
+        <v>3699.97</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3035.34</v>
+        <v>3041.67</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10529,20 +10524,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2022.3</v>
+        <v>2028.3</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1810.21</v>
+        <v>1830.98</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1794.43</v>
+        <v>1803.6</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2155.66</v>
+        <v>2145.69</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10573,29 +10568,29 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>110.91</v>
+        <v>104.89</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>101.69</v>
+        <v>102</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>106.25</v>
+        <v>106.19</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>132.93</v>
+        <v>132.36</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H225" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H225" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I225" s="13" t="inlineStr">
@@ -10617,29 +10612,29 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>389.05</v>
+        <v>392.65</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>383.04</v>
+        <v>383.95</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>391.46</v>
+        <v>391.5</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.8</v>
+        <v>396.2</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H226" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H226" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I226" s="13" t="inlineStr">
@@ -10661,20 +10656,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>470</v>
+        <v>472.8</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>435.63</v>
+        <v>439.17</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>438.21</v>
+        <v>439.57</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>433.88</v>
+        <v>433.72</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10700,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>195.39</v>
+        <v>196.3</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>178.46</v>
+        <v>180.16</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>178.75</v>
+        <v>179.43</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>193.2</v>
+        <v>192.78</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10749,20 +10744,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>585.55</v>
+        <v>574.15</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>538.04</v>
+        <v>541.48</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>533.1</v>
+        <v>534.71</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>554.54</v>
+        <v>553.9299999999999</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10788,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>581.5</v>
+        <v>566.05</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>526.66</v>
+        <v>530.41</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>528.1900000000001</v>
+        <v>529.67</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>588.67</v>
+        <v>585.84</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10837,20 +10832,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>58.73</v>
+        <v>57.41</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>56.91</v>
+        <v>56.96</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>56.85</v>
+        <v>56.87</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.53</v>
+        <v>52.5</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10881,20 +10876,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>968.85</v>
+        <v>953.6</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>834.64</v>
+        <v>845.97</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>849.2</v>
+        <v>853.29</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>958.37</v>
+        <v>956.9</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10906,9 +10901,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I232" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I232" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J232" s="14" t="inlineStr">
@@ -10925,20 +10920,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>614.25</v>
+        <v>640</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>577.74</v>
+        <v>583.67</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>582.12</v>
+        <v>584.39</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>686.4299999999999</v>
+        <v>684</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10964,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>320.3</v>
+        <v>320.75</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>325.28</v>
+        <v>324.85</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>341.24</v>
+        <v>340.44</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>374.29</v>
+        <v>372.46</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11013,20 +11008,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>193.44</v>
+        <v>191.61</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>194.02</v>
+        <v>193.79</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>197.44</v>
+        <v>197.21</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>200.81</v>
+        <v>200.59</v>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
@@ -11057,20 +11052,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>264.83</v>
+        <v>264.05</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>227.1</v>
+        <v>230.62</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>228.47</v>
+        <v>229.86</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.41</v>
+        <v>249.17</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,20 +11096,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1389.5</v>
+        <v>1423.3</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1301.34</v>
+        <v>1312.95</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1267.69</v>
+        <v>1273.8</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1333.36</v>
+        <v>1329.87</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11145,20 +11140,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>223.7</v>
+        <v>219.92</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>208.67</v>
+        <v>209.74</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>214.5</v>
+        <v>214.71</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>228.89</v>
+        <v>227.75</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,20 +11184,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>539.2</v>
+        <v>526.15</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>509.93</v>
+        <v>511.48</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>524.33</v>
+        <v>524.4</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>559.5599999999999</v>
+        <v>558.33</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11233,20 +11228,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>499.6</v>
+        <v>498.3</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>474.11</v>
+        <v>476.41</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>480.06</v>
+        <v>480.77</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>485.91</v>
+        <v>485.33</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,20 +11272,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1291.5</v>
+        <v>1274.5</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1312.59</v>
+        <v>1308.96</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1391.75</v>
+        <v>1387.15</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1559.74</v>
+        <v>1554.89</v>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
@@ -11321,17 +11316,17 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>208.25</v>
+        <v>207.31</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>200.98</v>
+        <v>201.58</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>200.55</v>
+        <v>200.81</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
@@ -11365,20 +11360,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>10145</v>
+        <v>10307</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>9130.33</v>
+        <v>9242.389999999999</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>8664.209999999999</v>
+        <v>8728.629999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8150.39</v>
+        <v>8150.63</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11404,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1116.1</v>
+        <v>1085.7</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>920.3099999999999</v>
+        <v>936.0599999999999</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>897.58</v>
+        <v>904.95</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>956.14</v>
+        <v>957.4299999999999</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11448,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>91.37</v>
+        <v>88.56</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>76.40000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>73.61</v>
+        <v>74.19</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>97.36</v>
+        <v>96.89</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11492,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>483.8</v>
+        <v>482</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>452.36</v>
+        <v>455.18</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>464.26</v>
+        <v>464.96</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>495.54</v>
+        <v>495.23</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,24 +11536,24 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>464.35</v>
+        <v>457.1</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>460.36</v>
+        <v>460.05</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>476.3</v>
+        <v>475.55</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>569.95</v>
-      </c>
-      <c r="G247" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>567.13</v>
+      </c>
+      <c r="G247" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H247" s="13" t="inlineStr">
@@ -11585,20 +11580,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>755.75</v>
+        <v>743.75</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>706.03</v>
+        <v>709.63</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>684.75</v>
+        <v>687.0700000000001</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>664.26</v>
+        <v>664.28</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11624,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>260.88</v>
+        <v>253.83</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>238.48</v>
+        <v>239.94</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>248.2</v>
+        <v>248.42</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>320.65</v>
+        <v>319.51</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,20 +11668,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>499.25</v>
+        <v>499.45</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>468.32</v>
+        <v>471.28</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>442.41</v>
+        <v>444.64</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>426.75</v>
+        <v>427.09</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,20 +11712,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>500.25</v>
+        <v>501.1</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>453.32</v>
+        <v>457.87</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>462.44</v>
+        <v>463.96</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>587.72</v>
+        <v>585.83</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -70,7 +70,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +90,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -158,7 +163,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -550,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 20-Apr-2026  16:50:40    |    Closing Price Date: 20-Apr-2026</t>
+          <t>Scan Run: 22-Apr-2026  04:50:31    |    Closing Price Date: 22-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -589,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>94.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>82.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>36.4</v>
+        <v>40.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>20-Apr-2026  16:50:40</t>
+          <t>22-Apr-2026  04:50:31</t>
         </is>
       </c>
     </row>
@@ -620,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 94.4% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 96.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 82.4% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 86.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 36.4% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.8% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -648,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 236 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 241 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 206 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 216 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 91 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 102 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -756,29 +761,29 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>570.4</v>
+        <v>554.3</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>536.63</v>
+        <v>541.1</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>559.5</v>
+        <v>559.65</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>696.17</v>
+        <v>693.5</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
@@ -800,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>438.25</v>
+        <v>438.35</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>431.9</v>
+        <v>433.05</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>432.62</v>
+        <v>433.05</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>454.91</v>
+        <v>454.58</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -844,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>365.2</v>
+        <v>364.1</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>356.1</v>
+        <v>357.33</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>361.87</v>
+        <v>361.94</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>404.98</v>
+        <v>404.15</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -888,29 +893,29 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>676.15</v>
+        <v>697.3</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>672.88</v>
+        <v>678.12</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>687.5</v>
+        <v>688.6</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>743.97</v>
+        <v>743.13</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -932,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2410.7</v>
+        <v>2429.6</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2319.12</v>
+        <v>2334.41</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2195.57</v>
+        <v>2211.49</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1780.25</v>
+        <v>1792.56</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -976,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>298.85</v>
+        <v>298.6</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>290.16</v>
+        <v>291.61</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>289.8</v>
+        <v>290.44</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>301.98</v>
+        <v>301.91</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1020,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1185.4</v>
+        <v>1176.4</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1132.12</v>
+        <v>1140.77</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1065.38</v>
+        <v>1074.18</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>923.46</v>
+        <v>928.54</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1064,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>833.3</v>
+        <v>872.1</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>769.41</v>
+        <v>787.6</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>786.48</v>
+        <v>792.87</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>867.8</v>
+        <v>867.84</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1089,9 +1094,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
@@ -1108,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>497.5</v>
+        <v>525</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>471.45</v>
+        <v>480.76</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>486.58</v>
+        <v>489.36</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>561.39</v>
+        <v>560.62</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1152,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1068.05</v>
+        <v>1070</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1016.96</v>
+        <v>1026.85</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>971.95</v>
+        <v>979.6</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>952.9</v>
+        <v>955.25</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1196,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.57</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>8.539999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.050000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>18.17</v>
+        <v>18</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1240,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>573.4</v>
+        <v>556.45</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>482.88</v>
+        <v>496.97</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>480.17</v>
+        <v>486.36</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>497.22</v>
+        <v>498.48</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1284,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1309</v>
+        <v>1340</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1270.1</v>
+        <v>1280.89</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1266.23</v>
+        <v>1271.08</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1174.13</v>
+        <v>1177.2</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1328,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>120.08</v>
+        <v>124.48</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>114.81</v>
+        <v>116.53</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>117.59</v>
+        <v>118.1</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>134.86</v>
+        <v>134.65</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1372,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>599.55</v>
+        <v>598.1</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>595.4</v>
+        <v>596</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>582.01</v>
+        <v>583.3</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>588.96</v>
+        <v>589.15</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1416,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>466.3</v>
+        <v>469.35</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>446.63</v>
+        <v>451.26</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>444.75</v>
+        <v>446.86</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>470.72</v>
+        <v>470.75</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1460,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>385.2</v>
+        <v>389.05</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>372.49</v>
+        <v>375.55</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>358.7</v>
+        <v>361.06</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>340.67</v>
+        <v>341.64</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1504,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>134.16</v>
+        <v>136.03</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>124.29</v>
+        <v>126.44</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>130.24</v>
+        <v>130.7</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>164.99</v>
+        <v>164.42</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1548,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1064.55</v>
+        <v>1119.5</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>997.99</v>
+        <v>1019.31</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>972.53</v>
+        <v>983.51</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>957.0599999999999</v>
+        <v>960.1900000000001</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1592,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>899.15</v>
+        <v>883</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>854.76</v>
+        <v>860.89</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>882.42</v>
+        <v>882.9</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1081.03</v>
+        <v>1077.23</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1636,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1076.9</v>
+        <v>1093.5</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1014.61</v>
+        <v>1028.12</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>981.46</v>
+        <v>989.73</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>943.71</v>
+        <v>946.58</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1680,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1503.4</v>
+        <v>1473.4</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1326.56</v>
+        <v>1352.3</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1219.19</v>
+        <v>1238.35</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>951.48</v>
+        <v>961.71</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1724,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>14.78</v>
+        <v>14.79</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.91</v>
+        <v>14.89</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.33</v>
+        <v>15.29</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -1768,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>347.12</v>
+        <v>349.99</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>308.82</v>
+        <v>316.29</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>322.94</v>
+        <v>325.02</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>458.95</v>
+        <v>456.8</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1812,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1893.3</v>
+        <v>1900</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1681.53</v>
+        <v>1717.94</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1623.58</v>
+        <v>1643.42</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1600.93</v>
+        <v>1606.48</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1856,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>397.35</v>
+        <v>399.5</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>370.59</v>
+        <v>375.76</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>380.22</v>
+        <v>381.67</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>475.85</v>
+        <v>474.33</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1900,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1149.75</v>
+        <v>1204.9</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1081.75</v>
+        <v>1103.95</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1086.22</v>
+        <v>1095.28</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1242.66</v>
+        <v>1241.9</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1944,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>471.15</v>
+        <v>476.35</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>458.32</v>
+        <v>461.46</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>465.59</v>
+        <v>466.36</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>542.04</v>
+        <v>540.73</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1988,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>613.35</v>
+        <v>621.5</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>578.17</v>
+        <v>585.27</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>589.01</v>
+        <v>591.17</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>606.75</v>
+        <v>606.95</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2032,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>222.18</v>
+        <v>221.48</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>199.48</v>
+        <v>203.26</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>190</v>
+        <v>192.33</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>162.13</v>
+        <v>163.29</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2076,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2827.1</v>
+        <v>2798</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2467.62</v>
+        <v>2529.92</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2468.34</v>
+        <v>2494.72</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2722.94</v>
+        <v>2724.7</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2120,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>959.85</v>
+        <v>945</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>918.99</v>
+        <v>924.74</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>940.62</v>
+        <v>941.41</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1074.89</v>
+        <v>1072.44</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2164,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>617.9</v>
+        <v>622.15</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>588.21</v>
+        <v>594.4400000000001</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>593.58</v>
+        <v>595.8</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>579.77</v>
+        <v>580.62</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2208,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>492.4</v>
+        <v>513.4</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>451.17</v>
+        <v>462.34</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>458.49</v>
+        <v>462.66</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>518.47</v>
+        <v>518.35</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2252,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1346.1</v>
+        <v>1360</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1282.25</v>
+        <v>1296.25</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1308.09</v>
+        <v>1312.04</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2296,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>486.1</v>
+        <v>476.7</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>471.43</v>
+        <v>467.8</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>458.52</v>
+        <v>454.31</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>435.93</v>
+        <v>430.78</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2340,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>317.9</v>
+        <v>312.15</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>298.56</v>
+        <v>301.08</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>303.04</v>
+        <v>303.76</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>353.78</v>
+        <v>352.96</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2384,34 +2389,34 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>390.4</v>
+        <v>403.2</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>385.91</v>
+        <v>388.99</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>390.8</v>
+        <v>391.73</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>394.46</v>
+        <v>394.63</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -2428,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1770.4</v>
+        <v>1768.7</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1787.76</v>
+        <v>1784.22</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1926.63</v>
+        <v>1914.45</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2176.61</v>
+        <v>2168.53</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2472,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>308.35</v>
+        <v>329.55</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>288.99</v>
+        <v>295.74</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>281.45</v>
+        <v>284.89</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>270.8</v>
+        <v>271.89</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2516,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>424.25</v>
+        <v>426.85</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>417.61</v>
+        <v>419.32</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>436.93</v>
+        <v>436.17</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>522.16</v>
+        <v>520.28</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2560,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>637.55</v>
+        <v>644.7</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>594.99</v>
+        <v>604.05</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>603.37</v>
+        <v>606.5599999999999</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>703.79</v>
+        <v>702.62</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2604,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1263.3</v>
+        <v>1223</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1212.23</v>
+        <v>1218.57</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1271.99</v>
+        <v>1270.14</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1485.54</v>
+        <v>1480.84</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2648,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>345.8</v>
+        <v>376.3</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>313.23</v>
+        <v>323.08</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>324.65</v>
+        <v>327.92</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>394.57</v>
+        <v>394.03</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2692,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>193.48</v>
+        <v>195.34</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>180.89</v>
+        <v>183.57</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>179.55</v>
+        <v>180.79</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>163.66</v>
+        <v>164.29</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2736,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>727.45</v>
+        <v>724.5</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>711.58</v>
+        <v>714.1799999999999</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723.46</v>
+        <v>723.66</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>759.1</v>
+        <v>758.45</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2780,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1016.6</v>
+        <v>1012.15</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>996.59</v>
+        <v>999.24</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1027.97</v>
+        <v>1026.68</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1221.51</v>
+        <v>1217.34</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2824,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>160.76</v>
+        <v>163.44</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>136.98</v>
+        <v>141.63</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>134.23</v>
+        <v>136.41</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.12</v>
+        <v>135.67</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2868,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>449.45</v>
+        <v>453.2</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>431.75</v>
+        <v>435.43</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>435.23</v>
+        <v>436.52</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>454.74</v>
+        <v>454.68</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2912,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>167.48</v>
+        <v>169.19</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>160.97</v>
+        <v>162.5</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>175.08</v>
+        <v>174.64</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>219.15</v>
+        <v>218.16</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2956,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1069.25</v>
+        <v>1079.1</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1052.35</v>
+        <v>1057.11</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1086.64</v>
+        <v>1086.02</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1181.75</v>
+        <v>1179.71</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3000,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>10140</v>
+        <v>10960</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>9928.290000000001</v>
+        <v>10097.09</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>9689.190000000001</v>
+        <v>9778.879999999999</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8662.280000000001</v>
+        <v>8705.68</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3044,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>236.24</v>
+        <v>228.53</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>219.79</v>
+        <v>221.57</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>212.02</v>
+        <v>213.38</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>211.37</v>
+        <v>211.74</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3088,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.74</v>
+        <v>7.73</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.4</v>
+        <v>7.46</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.36</v>
+        <v>7.38</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.359999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3132,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>117.35</v>
+        <v>117.75</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>112.48</v>
+        <v>113.48</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>111.3</v>
+        <v>111.81</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>108.99</v>
+        <v>109.17</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3176,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>105.26</v>
+        <v>107.8</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>98.56999999999999</v>
+        <v>100.31</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>98.12</v>
+        <v>98.89</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.05</v>
+        <v>113.94</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3220,24 +3225,24 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>78.36</v>
+        <v>79.11</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>78.84999999999999</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>76</v>
+        <v>76.19</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.56</v>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>84.44</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -3308,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1271.9</v>
+        <v>1264.1</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1200.24</v>
+        <v>1211.49</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1152.37</v>
+        <v>1160.81</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1151.04</v>
+        <v>1153.24</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3352,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>206.24</v>
+        <v>209.36</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>179</v>
+        <v>184.47</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>172.14</v>
+        <v>174.98</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>201.22</v>
+        <v>201.38</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3396,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1167.4</v>
+        <v>1174.05</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1026.96</v>
+        <v>1053.38</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1011.17</v>
+        <v>1023.58</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1314.53</v>
+        <v>1311.72</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3440,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>63.92</v>
+        <v>64.69</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>60.43</v>
+        <v>61.25</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>60.95</v>
+        <v>61.25</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>61.85</v>
+        <v>61.91</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3484,34 +3489,34 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2345.2</v>
+        <v>2582</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2341.72</v>
+        <v>2375.65</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2386.08</v>
+        <v>2396.92</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2582.87</v>
+        <v>2581.75</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H64" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J64" s="14" t="inlineStr">
@@ -3528,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>502.7</v>
+        <v>494.85</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>476.43</v>
+        <v>480.06</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>487.6</v>
+        <v>488.29</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>536.61</v>
+        <v>535.8200000000001</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3572,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>359.95</v>
+        <v>362.1</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>348.41</v>
+        <v>351.04</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>357.69</v>
+        <v>358.1</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>400.04</v>
+        <v>399.3</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3616,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2250.5</v>
+        <v>2273.9</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2139.02</v>
+        <v>2162.97</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2145.28</v>
+        <v>2154.94</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2060.45</v>
+        <v>2064.62</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3660,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4995.2</v>
+        <v>4980.5</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4536.83</v>
+        <v>4623.9</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4432.4</v>
+        <v>4477.43</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4451.02</v>
+        <v>4462.25</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3704,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>890.75</v>
+        <v>882.65</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>870.04</v>
+        <v>872.28</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>904.26</v>
+        <v>902.58</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1040.09</v>
+        <v>1036.97</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3748,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>499.95</v>
+        <v>504.15</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>475.89</v>
+        <v>481.2</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>483.78</v>
+        <v>485.42</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>545.15</v>
+        <v>544.35</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3792,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>910.7</v>
+        <v>916.45</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>892.91</v>
+        <v>897.27</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>918.92</v>
+        <v>918.77</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1043.51</v>
+        <v>1041.01</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3836,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>107.3</v>
+        <v>109.1</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>104.28</v>
+        <v>105.09</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>105.49</v>
+        <v>105.73</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.22</v>
+        <v>110.19</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3880,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>1017.85</v>
+        <v>1008</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>928.13</v>
+        <v>943.3099999999999</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>929.42</v>
+        <v>935.76</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>940.1799999999999</v>
+        <v>941.61</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3924,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>869.05</v>
+        <v>870</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>683.14</v>
+        <v>716.39</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>616.28</v>
+        <v>635.51</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>566.37</v>
+        <v>572.3099999999999</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3968,29 +3973,29 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>635.55</v>
+        <v>642.15</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>604.14</v>
+        <v>611.09</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>639.39</v>
+        <v>639.63</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>755.1</v>
+        <v>752.87</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H75" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
@@ -4012,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1035.15</v>
+        <v>1054.15</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>978.37</v>
+        <v>992.72</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>895.96</v>
+        <v>908.39</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1037.08</v>
+        <v>1037.49</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4037,9 +4042,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
@@ -4056,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>3977.5</v>
+        <v>4045</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3802.19</v>
+        <v>3836.09</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3763.97</v>
+        <v>3781.14</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3628</v>
+        <v>3635.1</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4100,20 +4105,20 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>652.7</v>
+        <v>656.75</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>622.22</v>
+        <v>628.36</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>633.29</v>
+        <v>635.04</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>702.71</v>
+        <v>701.78</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4144,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>58.25</v>
+        <v>58.71</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>56.06</v>
+        <v>56.51</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>56.15</v>
+        <v>56.33</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>58.99</v>
+        <v>58.98</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4188,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>720.8</v>
+        <v>759</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>657.76</v>
+        <v>676.9400000000001</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>662.29</v>
+        <v>670.09</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>754.47</v>
+        <v>754.66</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4213,9 +4218,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I80" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
@@ -4232,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>157.88</v>
+        <v>157.1</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>147.03</v>
+        <v>148.87</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>151.54</v>
+        <v>151.97</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>181.09</v>
+        <v>180.62</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4276,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>212.22</v>
+        <v>212.51</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>200.6</v>
+        <v>202.93</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>204.62</v>
+        <v>205.31</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>239.76</v>
+        <v>239.24</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4320,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>146.73</v>
+        <v>157.57</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>144.53</v>
+        <v>146.78</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>139.3</v>
+        <v>140.65</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>125.47</v>
+        <v>126.09</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4364,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>481.25</v>
+        <v>484.4</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>434.73</v>
+        <v>443.64</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>438.68</v>
+        <v>442.15</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>472.86</v>
+        <v>473.07</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4408,20 +4413,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>157.8</v>
+        <v>158.64</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>153.85</v>
+        <v>154.73</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>159.67</v>
+        <v>159.6</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.19</v>
+        <v>162.12</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4452,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>171.54</v>
+        <v>174.35</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>161.97</v>
+        <v>164.26</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>164.03</v>
+        <v>164.85</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>177.94</v>
+        <v>177.87</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4496,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>964</v>
+        <v>987.2</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>937.8200000000001</v>
+        <v>947.5</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>990.04</v>
+        <v>990.14</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1085.86</v>
+        <v>1083.99</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4540,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>624.6</v>
+        <v>624.85</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>546.62</v>
+        <v>561.1</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>567.26</v>
+        <v>571.8099999999999</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>776.88</v>
+        <v>773.91</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4584,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>570.15</v>
+        <v>579.35</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>553.54</v>
+        <v>557.83</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>570.1</v>
+        <v>570.64</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>608.55</v>
+        <v>607.92</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4628,29 +4633,29 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>129.6</v>
+        <v>131.22</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>127.36</v>
+        <v>128.04</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.65</v>
+        <v>130.69</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>136.87</v>
+        <v>136.76</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H90" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I90" s="13" t="inlineStr">
@@ -4672,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>355.3</v>
+        <v>364</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>331.85</v>
+        <v>337.45</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>342.6</v>
+        <v>344.15</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>404.49</v>
+        <v>403.67</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4716,20 +4721,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>188.39</v>
+        <v>187</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>177.52</v>
+        <v>179.29</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>184.3</v>
+        <v>184.53</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>236.54</v>
+        <v>235.56</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4760,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>19.24</v>
+        <v>19.66</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>17.01</v>
+        <v>17.49</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>17.31</v>
+        <v>17.49</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.82</v>
+        <v>21.78</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4804,29 +4809,29 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1098</v>
+        <v>1123.1</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1042.83</v>
+        <v>1058.1</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1102.46</v>
+        <v>1104.35</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1355.84</v>
+        <v>1351.31</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H94" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I94" s="13" t="inlineStr">
@@ -4848,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>310.75</v>
+        <v>320.27</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>285.85</v>
+        <v>292.94</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>295.03</v>
+        <v>297.33</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>304.44</v>
+        <v>304.85</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4892,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>48.72</v>
+        <v>47.69</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>44.85</v>
+        <v>45.33</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>44.75</v>
+        <v>44.97</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.15</v>
+        <v>51.07</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4936,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>959</v>
+        <v>978.1</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>913.34</v>
+        <v>923.6900000000001</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>907.97</v>
+        <v>912.75</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>897.5599999999999</v>
+        <v>898.99</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4980,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>803.5</v>
+        <v>815.1</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>764.96</v>
+        <v>774.59</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>756.8</v>
+        <v>761.52</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>797.4400000000001</v>
+        <v>797.85</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5024,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1532</v>
+        <v>1529.6</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1365.64</v>
+        <v>1392.77</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1310.33</v>
+        <v>1326.05</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1161.58</v>
+        <v>1168.57</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5068,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>835.85</v>
+        <v>870.35</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>807.66</v>
+        <v>819.37</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>871.34</v>
+        <v>871.42</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1032.36</v>
+        <v>1029.19</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5112,17 +5117,17 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>268.21</v>
+        <v>272.43</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>255.43</v>
+        <v>258.58</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>258.95</v>
+        <v>260.02</v>
       </c>
       <c r="F101" s="11" t="n">
         <v>272.65</v>
@@ -5156,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4148.6</v>
+        <v>4095.2</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3854.55</v>
+        <v>3896.58</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3744.61</v>
+        <v>3770.86</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3683.18</v>
+        <v>3691.16</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5200,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>731.2</v>
+        <v>715.05</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>704.6</v>
+        <v>707.23</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>698.79</v>
+        <v>700.36</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>760.62</v>
+        <v>759.8099999999999</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5244,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>160.96</v>
+        <v>173.55</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>154.28</v>
+        <v>157.72</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>160.26</v>
+        <v>161.26</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.51</v>
+        <v>176.45</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5288,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>396.55</v>
+        <v>402</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>368.78</v>
+        <v>375.21</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>362.88</v>
+        <v>366.07</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>402.7</v>
+        <v>402.73</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5332,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1046.45</v>
+        <v>1053</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>960.74</v>
+        <v>976.96</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>911.51</v>
+        <v>922.17</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>930.9299999999999</v>
+        <v>933.29</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5376,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>511.45</v>
+        <v>511.9</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>485.1</v>
+        <v>490.19</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>505.06</v>
+        <v>505.69</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>580.16</v>
+        <v>578.84</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5420,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
         <v>662.8</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>629.59</v>
+        <v>635.79</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>657.47</v>
+        <v>657.95</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>754.5599999999999</v>
+        <v>752.76</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5464,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>367.5</v>
+        <v>359.5</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>349.7</v>
+        <v>351.6</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>344.04</v>
+        <v>345.28</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>354.9</v>
+        <v>355</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5508,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>73.40000000000001</v>
+        <v>71.94</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>64.27</v>
+        <v>65.67</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>64.91</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>83.23</v>
+        <v>83</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5552,24 +5557,24 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>33.2</v>
+        <v>31.99</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>32.01</v>
+        <v>32.07</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.55</v>
+        <v>33.46</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>43.13</v>
-      </c>
-      <c r="G111" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>42.91</v>
+      </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
@@ -5596,20 +5601,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>126.11</v>
+        <v>125.32</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>123.17</v>
+        <v>123.47</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.7</v>
+        <v>124.71</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>113.86</v>
+        <v>114.08</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5640,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>383.35</v>
+        <v>449.3</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>381.04</v>
+        <v>392.03</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>379.82</v>
+        <v>384.55</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>414.35</v>
+        <v>414.89</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5665,9 +5670,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I113" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J113" s="14" t="inlineStr">
@@ -5684,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>25.76</v>
+        <v>26.04</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>23.44</v>
+        <v>23.89</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>24.04</v>
+        <v>24.19</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>34.45</v>
+        <v>34.28</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5728,24 +5733,24 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>546.45</v>
+        <v>544</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>543.71</v>
+        <v>544.36</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>573.26</v>
+        <v>571.27</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>703.79</v>
-      </c>
-      <c r="G115" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>700.6900000000001</v>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
@@ -5772,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>120.96</v>
+        <v>121.68</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>120.77</v>
+        <v>120.87</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>127.8</v>
+        <v>127.3</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>166.7</v>
+        <v>165.8</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5816,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>440.55</v>
+        <v>450.8</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>406.72</v>
+        <v>414.03</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>401.45</v>
+        <v>404.94</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>431.26</v>
+        <v>431.57</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5860,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>345.6</v>
+        <v>365.3</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>324.28</v>
+        <v>330.62</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>329.84</v>
+        <v>332.08</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>351.64</v>
+        <v>351.79</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5885,9 +5890,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
@@ -5904,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1245.8</v>
+        <v>1192.3</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1015.75</v>
+        <v>1049.55</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>916.6</v>
+        <v>938.58</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>831</v>
+        <v>838.35</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5948,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>755.15</v>
+        <v>794.4</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>680.39</v>
+        <v>700.33</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>691.33</v>
+        <v>698.9299999999999</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>755.75</v>
+        <v>756.4299999999999</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5973,9 +5978,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I120" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
@@ -5992,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>204.07</v>
+        <v>207.27</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>188.24</v>
+        <v>191.6</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>193.88</v>
+        <v>194.87</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>220.14</v>
+        <v>219.88</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6036,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>245.67</v>
+        <v>251.13</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>234.62</v>
+        <v>237.54</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>221.63</v>
+        <v>223.87</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>199.79</v>
+        <v>200.8</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6080,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>933.6</v>
+        <v>944.45</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>873.8200000000001</v>
+        <v>886.6900000000001</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>858.64</v>
+        <v>865.27</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>959.53</v>
+        <v>959.24</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6124,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1363.8</v>
+        <v>1354</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1181.57</v>
+        <v>1213.55</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1141.06</v>
+        <v>1157.74</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1153.41</v>
+        <v>1157.46</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6168,29 +6173,29 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>167.24</v>
+        <v>171.9</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>165.15</v>
+        <v>166.4</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>169.9</v>
+        <v>170.06</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.79</v>
+        <v>191.4</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H125" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I125" s="13" t="inlineStr">
@@ -6212,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14142</v>
+        <v>14470</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>13659.38</v>
+        <v>13801.61</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14063.17</v>
+        <v>14092.34</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14872.13</v>
+        <v>14863.62</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6256,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>141.58</v>
+        <v>141.63</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>128.1</v>
+        <v>130.48</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>131.51</v>
+        <v>132.26</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>163.01</v>
+        <v>162.58</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6300,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>177.36</v>
+        <v>180.86</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>173.89</v>
+        <v>175.32</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>184.02</v>
+        <v>183.85</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>211.48</v>
+        <v>210.89</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6344,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>55.53</v>
+        <v>58.27</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>48.01</v>
+        <v>49.67</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>47.49</v>
+        <v>48.23</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>54.74</v>
+        <v>54.79</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6388,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>65.88</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>55.21</v>
+        <v>57.38</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>53.9</v>
+        <v>54.92</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.06</v>
+        <v>59.22</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6432,20 +6437,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1795.4</v>
+        <v>1814.5</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1694.93</v>
+        <v>1713.2</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1620.69</v>
+        <v>1634.1</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1359.58</v>
+        <v>1368.2</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6476,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1490</v>
+        <v>1487.05</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1196.43</v>
+        <v>1247.04</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1073.31</v>
+        <v>1104.2</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1160.92</v>
+        <v>1167.14</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6520,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>321.2</v>
+        <v>324.5</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>303.53</v>
+        <v>307.14</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>304.9</v>
+        <v>306.32</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.19</v>
+        <v>326.14</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6564,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>456.2</v>
+        <v>453.5</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>429.1</v>
+        <v>433.98</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>435.62</v>
+        <v>437.19</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>473.18</v>
+        <v>472.84</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6608,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>4942</v>
+        <v>5148</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>4157.89</v>
+        <v>4330.88</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>3715.55</v>
+        <v>3822.79</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2739.13</v>
+        <v>2786.07</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6652,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>320.75</v>
+        <v>317.6</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>334.84</v>
+        <v>332.26</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>346.83</v>
+        <v>344.82</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>364.26</v>
+        <v>363.4</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6696,29 +6701,29 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>96.08</v>
+        <v>102.4</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>93.55</v>
+        <v>95</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>99.65000000000001</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>129.25</v>
+        <v>128.7</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H137" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I137" s="13" t="inlineStr">
@@ -6740,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1384.1</v>
+        <v>1462.9</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1312.34</v>
+        <v>1338.34</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1317.96</v>
+        <v>1328.53</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1321.74</v>
+        <v>1324.38</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6784,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>176.9</v>
+        <v>178.16</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>173.11</v>
+        <v>173.9</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>173.11</v>
+        <v>173.44</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>187.97</v>
+        <v>187.76</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6828,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1682.9</v>
+        <v>1755.3</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1585.16</v>
+        <v>1617.15</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1657.62</v>
+        <v>1665.62</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2015.42</v>
+        <v>2010.39</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6872,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>389.2</v>
+        <v>393.25</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>369.99</v>
+        <v>373.9</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>381.05</v>
+        <v>381.86</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>428.29</v>
+        <v>427.56</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6916,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>869.8</v>
+        <v>877</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>852.52</v>
+        <v>857.01</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>841</v>
+        <v>843.79</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>825.48</v>
+        <v>826.5</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6960,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>378.55</v>
+        <v>382.25</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>332.5</v>
+        <v>341.32</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>332.62</v>
+        <v>336.35</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>346.01</v>
+        <v>346.71</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7004,29 +7009,29 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>192.75</v>
+        <v>210.8</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>190.53</v>
+        <v>193.83</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>199.42</v>
+        <v>200.13</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>237.58</v>
+        <v>237</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H144" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I144" s="13" t="inlineStr">
@@ -7048,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1494.4</v>
+        <v>1569.9</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1357.74</v>
+        <v>1390.93</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1323.43</v>
+        <v>1340.06</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1383.74</v>
+        <v>1386.82</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7092,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1185.4</v>
+        <v>1195.7</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1117.82</v>
+        <v>1132.84</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1120.13</v>
+        <v>1126.33</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1167.68</v>
+        <v>1168.34</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7136,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>76.31</v>
+        <v>76.84</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>73.41</v>
+        <v>74.05</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.08</v>
+        <v>75.22</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.29000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7180,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>270.08</v>
+        <v>274.65</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>250.77</v>
+        <v>255.2</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>252.75</v>
+        <v>254.48</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>264.22</v>
+        <v>264.43</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7224,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>35.89</v>
+        <v>35.83</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>32.97</v>
+        <v>33.48</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>34.14</v>
+        <v>34.27</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>42.45</v>
+        <v>42.32</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7268,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>400.95</v>
+        <v>406.9</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>366</v>
+        <v>373.26</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>382.15</v>
+        <v>383.99</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>485.03</v>
+        <v>483.46</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7312,24 +7317,24 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>545.3</v>
+        <v>552.85</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>545.6799999999999</v>
+        <v>547.15</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>583.8200000000001</v>
+        <v>581.52</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>738.04</v>
-      </c>
-      <c r="G151" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>734.4</v>
+      </c>
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -7356,20 +7361,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>144.07</v>
+        <v>144.71</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>139.36</v>
+        <v>140.39</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.71</v>
+        <v>145.65</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>193.12</v>
+        <v>192.17</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7400,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>414.85</v>
+        <v>420.5</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>359.37</v>
+        <v>369.72</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>363.85</v>
+        <v>367.89</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>508.8</v>
+        <v>506.97</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7444,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>670.05</v>
+        <v>670.3</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>610.85</v>
+        <v>621.4299999999999</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>587.96</v>
+        <v>594.2</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>590.24</v>
+        <v>591.8</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7488,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.69</v>
+        <v>9.58</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>9.23</v>
+        <v>9.26</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.93</v>
+        <v>10.9</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7532,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>201.96</v>
+        <v>222.84</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>189.18</v>
+        <v>194.06</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>199.35</v>
+        <v>200.62</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>242.07</v>
+        <v>241.55</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7576,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>192.16</v>
+        <v>187.89</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>171.04</v>
+        <v>174.01</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>167.01</v>
+        <v>168.58</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>162.68</v>
+        <v>163.16</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7620,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>126.93</v>
+        <v>133.63</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>118.55</v>
+        <v>121.15</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>121.43</v>
+        <v>122.31</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.58</v>
+        <v>141.41</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7664,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>781.5</v>
+        <v>815.35</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>696.78</v>
+        <v>715.46</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>675.49</v>
+        <v>685.01</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>669.4</v>
+        <v>671.97</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7708,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>27.83</v>
+        <v>27.45</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>26.31</v>
+        <v>26.5</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>26.74</v>
+        <v>26.79</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7752,20 +7757,20 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1635.5</v>
+        <v>1631.9</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1535.68</v>
+        <v>1551.73</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1529.97</v>
+        <v>1537.19</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1489.41</v>
+        <v>1492.08</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7796,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>866.05</v>
+        <v>869.4</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>844.92</v>
+        <v>849.36</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>838.89</v>
+        <v>841.23</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>929.54</v>
+        <v>928.35</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7840,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2432.7</v>
+        <v>2459.6</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2125.98</v>
+        <v>2185.71</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2099.2</v>
+        <v>2126.57</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2361.36</v>
+        <v>2363.22</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7884,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>588.45</v>
+        <v>606.55</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>562.9</v>
+        <v>570.73</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>568.24</v>
+        <v>571.15</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>553.5</v>
+        <v>554.54</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7928,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>257.02</v>
+        <v>260</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>241.42</v>
+        <v>244.72</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>244.46</v>
+        <v>245.63</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>277.83</v>
+        <v>277.47</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7972,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>130.88</v>
+        <v>133.14</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>125.38</v>
+        <v>126.92</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>126.12</v>
+        <v>126.71</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>135.53</v>
+        <v>135.5</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8016,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3086.9</v>
+        <v>3134</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>2960.28</v>
+        <v>2992.15</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>2923.43</v>
+        <v>2939.78</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2713.52</v>
+        <v>2721.89</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8060,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2711.3</v>
+        <v>2735</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2444.61</v>
+        <v>2496.6</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2415.23</v>
+        <v>2439.51</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2511.71</v>
+        <v>2516.05</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8104,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>217.39</v>
+        <v>221.44</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>199.64</v>
+        <v>203.57</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>204.48</v>
+        <v>205.77</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>239.13</v>
+        <v>238.78</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8148,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>193.28</v>
+        <v>196.6</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>187.93</v>
+        <v>189.46</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>191.21</v>
+        <v>191.61</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>246.78</v>
+        <v>245.79</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8192,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>133.14</v>
+        <v>131.11</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>122.39</v>
+        <v>123.98</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>126.76</v>
+        <v>127.09</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>133.81</v>
+        <v>133.75</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8236,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>261.37</v>
+        <v>264.75</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>253</v>
+        <v>255.03</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>255.35</v>
+        <v>256.03</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>272.53</v>
+        <v>272.36</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8280,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>569.6</v>
+        <v>571.1</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>535.03</v>
+        <v>541.4</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>541.88</v>
+        <v>544.05</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>579.05</v>
+        <v>578.87</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8324,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2427.2</v>
+        <v>2405.4</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2326.32</v>
+        <v>2341.14</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2304.02</v>
+        <v>2312.02</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2398.41</v>
+        <v>2398.6</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8368,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>34.4</v>
+        <v>34.72</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>31.14</v>
+        <v>31.78</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>31.66</v>
+        <v>31.89</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.87</v>
+        <v>40.75</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8412,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>9.51</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>8.82</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>8.68</v>
+        <v>8.75</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8456,24 +8461,24 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>797.85</v>
+        <v>811.4</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>800.87</v>
+        <v>802.59</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>848.86</v>
+        <v>845.9</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1037.06</v>
-      </c>
-      <c r="G177" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1032.57</v>
+      </c>
+      <c r="G177" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
@@ -8500,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>250.39</v>
+        <v>258.48</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>223.59</v>
+        <v>229.77</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>226.37</v>
+        <v>228.78</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>298.38</v>
+        <v>297.57</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8544,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>305.32</v>
+        <v>304.91</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>290.82</v>
+        <v>293.48</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>312.92</v>
+        <v>312.35</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>388.09</v>
+        <v>386.45</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8588,20 +8593,20 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>224.31</v>
+        <v>226.5</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>221.24</v>
+        <v>222.2</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>224.2</v>
+        <v>224.38</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>237.65</v>
+        <v>237.43</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8632,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>62.91</v>
+        <v>63.68</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>61.86</v>
+        <v>62.17</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>62.44</v>
+        <v>62.53</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.70999999999999</v>
+        <v>67.63</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8676,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>502.35</v>
+        <v>503.95</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>483.68</v>
+        <v>487.77</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>509.55</v>
+        <v>509.3</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>686.95</v>
+        <v>683.37</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8720,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>411.5</v>
+        <v>415.4</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>377.66</v>
+        <v>384.65</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>357.83</v>
+        <v>362.32</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>338.3</v>
+        <v>339.84</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8764,24 +8769,24 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1558.6</v>
+        <v>1575.5</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1559.4</v>
+        <v>1562.4</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1684.05</v>
+        <v>1675.73</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1986.25</v>
-      </c>
-      <c r="G184" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1978.12</v>
+      </c>
+      <c r="G184" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
@@ -8808,20 +8813,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>163.2</v>
+        <v>164.35</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>153.38</v>
+        <v>155.41</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>157.03</v>
+        <v>157.61</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>176.95</v>
+        <v>176.71</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8852,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>213.39</v>
+        <v>214.45</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>198.69</v>
+        <v>201.35</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>200.32</v>
+        <v>201.32</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>192.67</v>
+        <v>193.08</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8896,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4724.1</v>
+        <v>4625</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4521.09</v>
+        <v>4545.07</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4415.55</v>
+        <v>4433.89</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4580.57</v>
+        <v>4582.03</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8940,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3578.3</v>
+        <v>3537</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3483.49</v>
+        <v>3454.92</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3652.05</v>
+        <v>3598.01</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4358.75</v>
+        <v>4285.25</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8984,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2275.5</v>
+        <v>2441.9</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2240.5</v>
+        <v>2271.24</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2135.99</v>
+        <v>2156.98</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1771.25</v>
+        <v>1783.86</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9028,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>323.6</v>
+        <v>328.4</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>314.08</v>
+        <v>317.06</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>313.33</v>
+        <v>314.66</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>333.99</v>
+        <v>333.92</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9072,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>1845.7</v>
+        <v>1912.4</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>2004.67</v>
+        <v>1981.75</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2055.43</v>
+        <v>2041.73</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2067.82</v>
+        <v>2064.04</v>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
@@ -9116,20 +9121,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>554.9</v>
+        <v>563</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>519.86</v>
+        <v>527.47</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>545</v>
+        <v>546.29</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>702.26</v>
+        <v>699.48</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9160,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1102.75</v>
+        <v>1159</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1029.21</v>
+        <v>1048.35</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1016.4</v>
+        <v>1025.44</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>915.34</v>
+        <v>919.66</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9204,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>860.9</v>
+        <v>865.95</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>817.36</v>
+        <v>826.0700000000001</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>840.73</v>
+        <v>842.62</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>914.5700000000001</v>
+        <v>913.6</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9248,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>144.47</v>
+        <v>147.88</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>137.09</v>
+        <v>138.94</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>137.9</v>
+        <v>138.62</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>157.48</v>
+        <v>157.28</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9292,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>546.65</v>
+        <v>558.05</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>524.34</v>
+        <v>529.26</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>534.7</v>
+        <v>535.97</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>611.59</v>
+        <v>610.39</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9336,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>411.25</v>
+        <v>400.55</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>384.33</v>
+        <v>387.68</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>355.95</v>
+        <v>359.55</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>355.35</v>
+        <v>356.29</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9380,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>27.91</v>
+        <v>28.38</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>26.94</v>
+        <v>27.15</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>26.01</v>
+        <v>26.17</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.55</v>
+        <v>27.56</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9424,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3627.6</v>
+        <v>3618</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3306.37</v>
+        <v>3360.21</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3139.6</v>
+        <v>3175.21</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2813.04</v>
+        <v>2828.67</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9468,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>436.6</v>
+        <v>476.85</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>380.91</v>
+        <v>397.31</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>376.31</v>
+        <v>383.6</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>424.54</v>
+        <v>425.46</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9512,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>39.29</v>
+        <v>39.62</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>38.01</v>
+        <v>38.29</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>38.55</v>
+        <v>38.63</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.01</v>
+        <v>36.08</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9556,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>221.02</v>
+        <v>227.31</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>214.07</v>
+        <v>216.39</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>213.67</v>
+        <v>214.68</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.32</v>
+        <v>223.39</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9581,9 +9586,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I202" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I202" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J202" s="14" t="inlineStr">
@@ -9600,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>212.08</v>
+        <v>212.5</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>181.08</v>
+        <v>186.53</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>184.78</v>
+        <v>186.8</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>226.98</v>
+        <v>226.67</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9644,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>271.63</v>
+        <v>285.99</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>217.3</v>
+        <v>229.11</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>184.45</v>
+        <v>191.97</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>136.18</v>
+        <v>139.08</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9688,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>996.5</v>
+        <v>1006.85</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>964.4400000000001</v>
+        <v>971.28</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>926.99</v>
+        <v>932.76</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>867.1</v>
+        <v>869.77</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9732,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2183.9</v>
+        <v>2225.9</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2023.67</v>
+        <v>2062.17</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>1980.94</v>
+        <v>2000.57</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2203.26</v>
+        <v>2203.92</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9757,9 +9762,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I206" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I206" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J206" s="14" t="inlineStr">
@@ -9776,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>772.55</v>
+        <v>792.25</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>730.25</v>
+        <v>740.9</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>745.27</v>
+        <v>748.62</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>807.01</v>
+        <v>806.65</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9820,29 +9825,29 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>833.25</v>
+        <v>872.35</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>816.71</v>
+        <v>825.01</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>846.16</v>
+        <v>847.39</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>1002.51</v>
+        <v>999.73</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H208" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H208" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I208" s="13" t="inlineStr">
@@ -9864,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>144.5</v>
+        <v>144.36</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>135.34</v>
+        <v>136.95</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>131.14</v>
+        <v>132.14</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.58</v>
+        <v>137.71</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9908,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>267.19</v>
+        <v>289.77</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>241.97</v>
+        <v>249.77</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>238.89</v>
+        <v>242.42</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>252.6</v>
+        <v>253.24</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9952,29 +9957,29 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>326.5</v>
+        <v>373.75</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>321.67</v>
+        <v>328.31</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>344.82</v>
+        <v>345.81</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>391.7</v>
+        <v>391.03</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H211" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H211" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I211" s="13" t="inlineStr">
@@ -9996,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>619.8</v>
+        <v>624.55</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>618.3200000000001</v>
+        <v>619.13</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>634.76</v>
+        <v>633.84</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>680.7</v>
+        <v>679.55</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10040,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>237.74</v>
+        <v>239.21</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>221.33</v>
+        <v>224.42</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>224.93</v>
+        <v>225.96</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>252.79</v>
+        <v>252.51</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10084,20 +10089,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>809.05</v>
+        <v>803.15</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>770.95</v>
+        <v>776.7</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>797.11</v>
+        <v>797.54</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>906.85</v>
+        <v>904.79</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10128,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>136.1</v>
+        <v>137.55</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>127.77</v>
+        <v>129.55</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>135</v>
+        <v>135.2</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>149.05</v>
+        <v>148.82</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10172,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1030.7</v>
+        <v>1040.15</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>908.46</v>
+        <v>930.4</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>855.86</v>
+        <v>869.17</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>705.47</v>
+        <v>711.87</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10216,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>416.2</v>
+        <v>416.9</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>380.81</v>
+        <v>387.53</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>393.51</v>
+        <v>395.38</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>485.92</v>
+        <v>484.57</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10260,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>114.29</v>
+        <v>115.2</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>107.15</v>
+        <v>108.45</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>107.19</v>
+        <v>107.74</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.4</v>
+        <v>116.36</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10304,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>482.65</v>
+        <v>499.35</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>452.86</v>
+        <v>460.53</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>457.33</v>
+        <v>460.23</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>527.84</v>
+        <v>527.1900000000001</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10348,29 +10353,29 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1263.3</v>
+        <v>1235.1</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1200.8</v>
+        <v>1208.33</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1253.85</v>
+        <v>1252.98</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1576.39</v>
+        <v>1569.78</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H220" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H220" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I220" s="13" t="inlineStr">
@@ -10392,24 +10397,24 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1709.8</v>
+        <v>1723.9</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1713.15</v>
+        <v>1714.24</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1733.72</v>
+        <v>1732.59</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1770.4</v>
-      </c>
-      <c r="G221" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1769.38</v>
+      </c>
+      <c r="G221" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H221" s="13" t="inlineStr">
@@ -10436,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>103.23</v>
+        <v>103.71</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>96.94</v>
+        <v>98.17</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>101.94</v>
+        <v>102.08</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>124.53</v>
+        <v>124.12</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10480,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>4134.5</v>
+        <v>4186.2</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3896.67</v>
+        <v>3944.17</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3699.97</v>
+        <v>3735.16</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3041.67</v>
+        <v>3063.76</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10524,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2028.3</v>
+        <v>2032.5</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1830.98</v>
+        <v>1868.59</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1803.6</v>
+        <v>1821.66</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2145.69</v>
+        <v>2143.56</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10568,29 +10573,29 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>104.89</v>
+        <v>106.56</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>102</v>
+        <v>102.89</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>106.19</v>
+        <v>106.25</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>132.36</v>
+        <v>131.86</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H225" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H225" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I225" s="13" t="inlineStr">
@@ -10612,29 +10617,29 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>392.65</v>
+        <v>388</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>383.95</v>
+        <v>384.64</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>391.5</v>
+        <v>391.22</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.2</v>
+        <v>396.03</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H226" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H226" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I226" s="13" t="inlineStr">
@@ -10656,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>472.8</v>
+        <v>475.3</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>439.17</v>
+        <v>445.6</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>439.57</v>
+        <v>442.26</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>433.72</v>
+        <v>434.53</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10700,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>196.3</v>
+        <v>191.95</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>180.16</v>
+        <v>182.22</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>179.43</v>
+        <v>180.36</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>192.78</v>
+        <v>192.76</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10725,9 +10730,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I228" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I228" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J228" s="14" t="inlineStr">
@@ -10744,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>574.15</v>
+        <v>602.25</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>541.48</v>
+        <v>552.35</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>534.71</v>
+        <v>539.83</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>553.9299999999999</v>
+        <v>554.87</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10788,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>566.05</v>
+        <v>588.5</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>530.41</v>
+        <v>541.1</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>529.67</v>
+        <v>534.26</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>585.84</v>
+        <v>585.91</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10813,9 +10818,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I230" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I230" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J230" s="14" t="inlineStr">
@@ -10832,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>57.41</v>
+        <v>58.74</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>56.96</v>
+        <v>57.26</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>56.87</v>
+        <v>57.01</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.5</v>
+        <v>52.63</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10876,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>953.6</v>
+        <v>969</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>845.97</v>
+        <v>866.5</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>853.29</v>
+        <v>861.41</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>956.9</v>
+        <v>956.9299999999999</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10901,9 +10906,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I232" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I232" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J232" s="14" t="inlineStr">
@@ -10920,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>640</v>
+        <v>649.25</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>583.67</v>
+        <v>595.22</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>584.39</v>
+        <v>589.23</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>684</v>
+        <v>683.27</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10964,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>320.75</v>
+        <v>318.35</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>324.85</v>
+        <v>323.77</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>340.44</v>
+        <v>338.78</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>372.46</v>
+        <v>371.4</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11008,24 +11013,24 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>191.61</v>
+        <v>196.3</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>193.79</v>
+        <v>194.36</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>197.21</v>
+        <v>197.19</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>200.59</v>
-      </c>
-      <c r="G235" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>200.52</v>
+      </c>
+      <c r="G235" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H235" s="13" t="inlineStr">
@@ -11052,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>264.05</v>
+        <v>264.48</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>230.62</v>
+        <v>236.38</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>229.86</v>
+        <v>232.36</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.17</v>
+        <v>249.43</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11096,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1423.3</v>
+        <v>1494.6</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1312.95</v>
+        <v>1345.26</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1273.8</v>
+        <v>1290.49</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1329.87</v>
+        <v>1333.06</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11140,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>219.92</v>
+        <v>221.25</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>209.74</v>
+        <v>211.82</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>214.71</v>
+        <v>215.21</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>227.75</v>
+        <v>227.62</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11184,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>526.15</v>
+        <v>534.1</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>511.48</v>
+        <v>515.03</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>524.4</v>
+        <v>524.9</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>558.33</v>
+        <v>557.78</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11228,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>498.3</v>
+        <v>506.9</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>476.41</v>
+        <v>481.22</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>480.77</v>
+        <v>482.46</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>485.33</v>
+        <v>485.68</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11272,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1274.5</v>
+        <v>1304.8</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1308.96</v>
+        <v>1306.56</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1387.15</v>
+        <v>1380.1</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1554.89</v>
+        <v>1549.75</v>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
@@ -11316,17 +11321,17 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>207.31</v>
+        <v>209.5</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>201.58</v>
+        <v>202.89</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>200.81</v>
+        <v>201.43</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
@@ -11360,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>10307</v>
+        <v>10723.5</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>9242.389999999999</v>
+        <v>9493.92</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>8728.629999999999</v>
+        <v>8874.52</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8150.63</v>
+        <v>8199.610000000001</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11404,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1085.7</v>
+        <v>1075</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>936.0599999999999</v>
+        <v>960.09</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>904.95</v>
+        <v>917.52</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>957.4299999999999</v>
+        <v>959.62</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11448,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>88.56</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>77.56</v>
+        <v>80.06</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>74.19</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>96.89</v>
+        <v>96.78</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11492,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>482</v>
+        <v>488.8</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>455.18</v>
+        <v>461.25</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>464.96</v>
+        <v>466.78</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>495.23</v>
+        <v>495.1</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11536,29 +11541,29 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>457.1</v>
+        <v>488.5</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>460.05</v>
+        <v>464.44</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>475.55</v>
+        <v>476.2</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>567.13</v>
-      </c>
-      <c r="G247" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H247" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>565.49</v>
+      </c>
+      <c r="G247" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H247" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I247" s="13" t="inlineStr">
@@ -11580,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>743.75</v>
+        <v>753.25</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>709.63</v>
+        <v>716.88</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>687.0700000000001</v>
+        <v>691.87</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>664.28</v>
+        <v>665.96</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11624,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>253.83</v>
+        <v>259.79</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>239.94</v>
+        <v>243.7</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>248.42</v>
+        <v>249.37</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>319.51</v>
+        <v>318.34</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11668,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>499.45</v>
+        <v>507.7</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>471.28</v>
+        <v>477.8</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>444.64</v>
+        <v>449.45</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>427.09</v>
+        <v>428.68</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11712,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>501.1</v>
+        <v>504.65</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>457.87</v>
+        <v>466.01</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>463.96</v>
+        <v>466.93</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>585.83</v>
+        <v>584.1900000000001</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 22-Apr-2026  04:50:31    |    Closing Price Date: 22-Apr-2026</t>
+          <t>Scan Run: 22-Apr-2026  16:46:33    |    Closing Price Date: 22-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -598,20 +598,20 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>40.8</v>
+        <v>44.4</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>22-Apr-2026  04:50:31</t>
+          <t>22-Apr-2026  16:46:33</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 96.4% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 96.8% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 86.4% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 89.2% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.8% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 44.4% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 241 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 242 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 216 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 223 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 102 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 111 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -765,25 +765,25 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>554.3</v>
+        <v>564.55</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>541.1</v>
+        <v>542.0700000000001</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>559.65</v>
+        <v>560.05</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>693.5</v>
+        <v>693.6</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>438.35</v>
+        <v>442.8</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>433.05</v>
+        <v>433.48</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>433.05</v>
+        <v>433.22</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>454.58</v>
+        <v>454.62</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>364.1</v>
+        <v>366.95</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>357.33</v>
+        <v>357.61</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>361.94</v>
+        <v>362.06</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>404.15</v>
+        <v>404.18</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>697.3</v>
+        <v>693.95</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>678.12</v>
+        <v>677.8</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>688.6</v>
+        <v>688.47</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>743.13</v>
+        <v>743.1</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -941,16 +941,16 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2429.6</v>
+        <v>2423.2</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2334.41</v>
+        <v>2333.8</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2211.49</v>
+        <v>2211.24</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1792.56</v>
+        <v>1792.5</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>298.6</v>
+        <v>299.15</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>291.61</v>
+        <v>291.66</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>290.44</v>
+        <v>290.46</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>301.91</v>
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1176.4</v>
+        <v>1183.3</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1140.77</v>
+        <v>1141.42</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1074.18</v>
+        <v>1074.45</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>928.54</v>
+        <v>928.6</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>872.1</v>
+        <v>890.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>787.6</v>
+        <v>789.3200000000001</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>792.87</v>
+        <v>793.58</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>867.84</v>
+        <v>868.02</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>525</v>
+        <v>525.3</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>480.76</v>
+        <v>480.78</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>489.36</v>
+        <v>489.37</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>560.62</v>
+        <v>560.63</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1070</v>
+        <v>1056.85</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1026.85</v>
+        <v>1025.6</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>979.6</v>
+        <v>979.09</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>955.25</v>
+        <v>955.12</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.369999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>18</v>
@@ -1249,16 +1249,16 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>556.45</v>
+        <v>553.1</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>496.97</v>
+        <v>496.66</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>486.36</v>
+        <v>486.23</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>498.48</v>
+        <v>498.44</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1340</v>
+        <v>1343.3</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1280.89</v>
+        <v>1281.21</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1271.08</v>
+        <v>1271.21</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1177.2</v>
+        <v>1177.23</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>124.48</v>
+        <v>126.05</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>116.53</v>
+        <v>116.67</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>118.1</v>
+        <v>118.16</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>134.65</v>
+        <v>134.67</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1381,20 +1381,20 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>598.1</v>
+        <v>591.05</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>596</v>
+        <v>595.33</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>583.3</v>
+        <v>583.02</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>589.15</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>589.08</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1425,16 +1425,16 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>469.35</v>
+        <v>471.8</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>451.26</v>
+        <v>451.49</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>446.86</v>
+        <v>446.96</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>470.75</v>
+        <v>470.77</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1446,9 +1446,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J17" s="14" t="inlineStr">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>389.05</v>
+        <v>392.05</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>375.55</v>
+        <v>375.83</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>361.06</v>
+        <v>361.18</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>341.64</v>
+        <v>341.67</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>136.03</v>
+        <v>137.63</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>126.44</v>
+        <v>126.59</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>130.7</v>
+        <v>130.76</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>164.42</v>
+        <v>164.44</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1119.5</v>
+        <v>1129.75</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1019.31</v>
+        <v>1020.28</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>983.51</v>
+        <v>983.91</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>960.1900000000001</v>
+        <v>960.29</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>883</v>
+        <v>887.35</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>860.89</v>
+        <v>861.3099999999999</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>882.9</v>
+        <v>883.0700000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1077.23</v>
+        <v>1077.27</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1645,16 +1645,16 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1093.5</v>
+        <v>1079.45</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1028.12</v>
+        <v>1026.79</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>989.73</v>
+        <v>989.1799999999999</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>946.58</v>
+        <v>946.4400000000001</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1473.4</v>
+        <v>1442.7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1352.3</v>
+        <v>1349.37</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1238.35</v>
+        <v>1237.14</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>961.71</v>
+        <v>961.41</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>14.79</v>
+        <v>14.81</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>14.89</v>
@@ -1777,16 +1777,16 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>349.99</v>
+        <v>359.24</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>316.29</v>
+        <v>317.17</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>325.02</v>
+        <v>325.38</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>456.8</v>
+        <v>456.89</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1900</v>
+        <v>1950.4</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1717.94</v>
+        <v>1722.74</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1643.42</v>
+        <v>1645.4</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1606.48</v>
+        <v>1606.98</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>399.5</v>
+        <v>398.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>375.76</v>
+        <v>375.64</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>381.67</v>
+        <v>381.62</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>474.33</v>
+        <v>474.32</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1204.9</v>
+        <v>1223.5</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1103.95</v>
+        <v>1105.72</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1095.28</v>
+        <v>1096.01</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1241.9</v>
+        <v>1242.09</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>476.35</v>
+        <v>478.55</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>461.46</v>
+        <v>461.67</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>466.36</v>
+        <v>466.44</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>540.73</v>
+        <v>540.75</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>621.5</v>
+        <v>624.25</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>585.27</v>
+        <v>585.53</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>591.17</v>
+        <v>591.28</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>606.95</v>
+        <v>606.98</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>221.48</v>
+        <v>222.13</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>203.26</v>
+        <v>203.32</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>192.33</v>
+        <v>192.36</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>163.29</v>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2798</v>
+        <v>2808.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2529.92</v>
+        <v>2530.95</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2494.72</v>
+        <v>2495.15</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2724.7</v>
+        <v>2724.8</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>945</v>
+        <v>948.35</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>924.74</v>
+        <v>925.05</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>941.41</v>
+        <v>941.54</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1072.44</v>
+        <v>1072.47</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>622.15</v>
+        <v>622.05</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>594.4400000000001</v>
+        <v>594.4299999999999</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>595.8</v>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>513.4</v>
+        <v>516.75</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>462.34</v>
+        <v>462.66</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>462.66</v>
+        <v>462.79</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>518.35</v>
+        <v>518.39</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1360</v>
+        <v>1377.8</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1296.25</v>
+        <v>1297.95</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1312.04</v>
+        <v>1312.74</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2305,16 +2305,16 @@
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>476.7</v>
+        <v>471.7</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>467.8</v>
+        <v>467.32</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>454.31</v>
+        <v>454.11</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>430.78</v>
+        <v>430.73</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2349,16 +2349,16 @@
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>312.15</v>
+        <v>317.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>301.08</v>
+        <v>301.62</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>303.76</v>
+        <v>303.99</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>352.96</v>
+        <v>353.02</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>403.2</v>
+        <v>396.35</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>388.99</v>
+        <v>388.34</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>391.73</v>
+        <v>391.46</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>394.63</v>
+        <v>394.56</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1768.7</v>
+        <v>1784.6</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1784.22</v>
+        <v>1785.74</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1914.45</v>
+        <v>1915.08</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2168.53</v>
+        <v>2168.69</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>329.55</v>
+        <v>326.35</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>295.74</v>
+        <v>295.43</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>284.89</v>
+        <v>284.76</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>271.89</v>
+        <v>271.86</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>426.85</v>
+        <v>424.4</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>419.32</v>
+        <v>419.09</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>436.17</v>
+        <v>436.08</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>520.28</v>
+        <v>520.25</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>644.7</v>
+        <v>675.3</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>604.05</v>
+        <v>606.96</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>606.5599999999999</v>
+        <v>607.76</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>702.62</v>
+        <v>702.92</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2613,16 +2613,16 @@
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1223</v>
+        <v>1220.5</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1218.57</v>
+        <v>1218.33</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1270.14</v>
+        <v>1270.04</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1480.84</v>
+        <v>1480.82</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2657,16 +2657,16 @@
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>376.3</v>
+        <v>375.25</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>323.08</v>
+        <v>322.98</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>327.92</v>
+        <v>327.88</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>394.03</v>
+        <v>394.02</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>195.34</v>
+        <v>195.32</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>183.57</v>
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>724.5</v>
+        <v>723.95</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>714.1799999999999</v>
+        <v>714.13</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723.66</v>
+        <v>723.63</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>758.45</v>
+        <v>758.4400000000001</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2789,25 +2789,25 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1012.15</v>
+        <v>1046.9</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>999.24</v>
+        <v>1002.55</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1026.68</v>
+        <v>1028.05</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1217.34</v>
+        <v>1217.69</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>163.44</v>
+        <v>159.81</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>141.63</v>
+        <v>141.29</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>136.41</v>
+        <v>136.27</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.67</v>
+        <v>135.63</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>453.2</v>
+        <v>457.3</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>435.43</v>
+        <v>435.82</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>436.52</v>
+        <v>436.68</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>454.68</v>
+        <v>454.72</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2898,9 +2898,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
@@ -2921,16 +2921,16 @@
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>169.19</v>
+        <v>170.79</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>162.5</v>
+        <v>162.65</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>174.64</v>
+        <v>174.7</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>218.16</v>
+        <v>218.18</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2965,25 +2965,25 @@
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1079.1</v>
+        <v>1096.9</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1057.11</v>
+        <v>1058.81</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1086.02</v>
+        <v>1086.72</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1179.71</v>
+        <v>1179.89</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
@@ -3009,16 +3009,16 @@
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>10960</v>
+        <v>11541</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>10097.09</v>
+        <v>10152.43</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>9778.879999999999</v>
+        <v>9801.67</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8705.68</v>
+        <v>8711.459999999999</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3053,16 +3053,16 @@
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>228.53</v>
+        <v>228.22</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>221.57</v>
+        <v>221.54</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>213.38</v>
+        <v>213.36</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>211.74</v>
+        <v>211.73</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.73</v>
+        <v>7.83</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.46</v>
+        <v>7.47</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.38</v>
+        <v>7.39</v>
       </c>
       <c r="F55" s="11" t="n">
         <v>8.35</v>
@@ -3141,16 +3141,16 @@
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>117.75</v>
+        <v>121.98</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>113.48</v>
+        <v>113.88</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>111.81</v>
+        <v>111.98</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.17</v>
+        <v>109.21</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>107.8</v>
+        <v>108.99</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>100.31</v>
+        <v>100.43</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>98.89</v>
+        <v>98.94</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>113.94</v>
+        <v>113.95</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>79.11</v>
+        <v>79.83</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>78.79000000000001</v>
+        <v>78.86</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>76.19</v>
+        <v>76.22</v>
       </c>
       <c r="F58" s="11" t="n">
         <v>84.44</v>
@@ -3317,13 +3317,13 @@
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1264.1</v>
+        <v>1263.9</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1211.49</v>
+        <v>1211.47</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1160.81</v>
+        <v>1160.8</v>
       </c>
       <c r="F60" s="11" t="n">
         <v>1153.24</v>
@@ -3361,16 +3361,16 @@
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>209.36</v>
+        <v>212.19</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>184.47</v>
+        <v>184.74</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>174.98</v>
+        <v>175.09</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>201.38</v>
+        <v>201.41</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3405,16 +3405,16 @@
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1174.05</v>
+        <v>1204.45</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1053.38</v>
+        <v>1056.28</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1023.58</v>
+        <v>1024.77</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1311.72</v>
+        <v>1312.02</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3449,16 +3449,16 @@
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>64.69</v>
+        <v>65.23</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>61.25</v>
+        <v>61.3</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>61.25</v>
+        <v>61.27</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>61.91</v>
+        <v>61.92</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3493,16 +3493,16 @@
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2582</v>
+        <v>2717.9</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2375.65</v>
+        <v>2388.59</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2396.92</v>
+        <v>2402.25</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2581.75</v>
+        <v>2583.1</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3537,16 +3537,16 @@
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>494.85</v>
+        <v>496.6</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>480.06</v>
+        <v>480.22</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>488.29</v>
+        <v>488.35</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>535.8200000000001</v>
+        <v>535.84</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3581,16 +3581,16 @@
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>362.1</v>
+        <v>359</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>351.04</v>
+        <v>350.75</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>358.1</v>
+        <v>357.98</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>399.3</v>
+        <v>399.27</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3625,16 +3625,16 @@
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2273.9</v>
+        <v>2275.2</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2162.97</v>
+        <v>2163.09</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2154.94</v>
+        <v>2154.99</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2064.62</v>
+        <v>2064.63</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3669,16 +3669,16 @@
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4980.5</v>
+        <v>5086</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4623.9</v>
+        <v>4633.94</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4477.43</v>
+        <v>4481.56</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4462.25</v>
+        <v>4463.3</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3713,16 +3713,16 @@
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>882.65</v>
+        <v>888.6</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>872.28</v>
+        <v>872.84</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>902.58</v>
+        <v>902.8099999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1036.97</v>
+        <v>1037.03</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3757,16 +3757,16 @@
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>504.15</v>
+        <v>506.9</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>481.2</v>
+        <v>481.46</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>485.42</v>
+        <v>485.53</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>544.35</v>
+        <v>544.38</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3801,13 +3801,13 @@
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>916.45</v>
+        <v>916.25</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>897.27</v>
+        <v>897.25</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>918.77</v>
+        <v>918.76</v>
       </c>
       <c r="F71" s="11" t="n">
         <v>1041.01</v>
@@ -3845,16 +3845,16 @@
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>109.1</v>
+        <v>111.03</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>105.09</v>
+        <v>105.27</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>105.73</v>
+        <v>105.81</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.19</v>
+        <v>110.21</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3866,9 +3866,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J72" s="14" t="inlineStr">
@@ -3889,16 +3889,16 @@
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>1008</v>
+        <v>1031.85</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>943.3099999999999</v>
+        <v>945.58</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>935.76</v>
+        <v>936.7</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>941.61</v>
+        <v>941.84</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3933,13 +3933,13 @@
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>870</v>
+        <v>870.55</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>716.39</v>
+        <v>716.4400000000001</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>635.51</v>
+        <v>635.53</v>
       </c>
       <c r="F74" s="11" t="n">
         <v>572.3099999999999</v>
@@ -3977,16 +3977,16 @@
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>642.15</v>
+        <v>651.25</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>611.09</v>
+        <v>611.95</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>639.63</v>
+        <v>639.99</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>752.87</v>
+        <v>752.96</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4021,16 +4021,16 @@
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1054.15</v>
+        <v>1065</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>992.72</v>
+        <v>993.76</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>908.39</v>
+        <v>908.8200000000001</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1037.49</v>
+        <v>1037.6</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>4045</v>
+        <v>4051.5</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3836.09</v>
+        <v>3836.71</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3781.14</v>
+        <v>3781.4</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3635.1</v>
+        <v>3635.16</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4109,16 +4109,16 @@
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>656.75</v>
+        <v>644.7</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>628.36</v>
+        <v>627.21</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>635.04</v>
+        <v>634.5700000000001</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>701.78</v>
+        <v>701.66</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>58.71</v>
+        <v>58.69</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>56.51</v>
+        <v>56.5</v>
       </c>
       <c r="E79" s="11" t="n">
         <v>56.33</v>
@@ -4197,16 +4197,16 @@
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>759</v>
+        <v>749.7</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>676.9400000000001</v>
+        <v>676.0599999999999</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>670.09</v>
+        <v>669.72</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>754.66</v>
+        <v>754.5599999999999</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4218,9 +4218,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I80" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>157.1</v>
+        <v>161.34</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>148.87</v>
+        <v>149.27</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>151.97</v>
+        <v>152.14</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>180.62</v>
+        <v>180.66</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4285,13 +4285,13 @@
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>212.51</v>
+        <v>212.15</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>202.93</v>
+        <v>202.9</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>205.31</v>
+        <v>205.29</v>
       </c>
       <c r="F82" s="11" t="n">
         <v>239.24</v>
@@ -4329,16 +4329,16 @@
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>157.57</v>
+        <v>154.95</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>146.78</v>
+        <v>146.53</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>140.65</v>
+        <v>140.55</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>126.09</v>
+        <v>126.06</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>484.4</v>
+        <v>488.5</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>443.64</v>
+        <v>444.03</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>442.15</v>
+        <v>442.31</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>473.07</v>
+        <v>473.12</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>158.64</v>
+        <v>158.08</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>154.73</v>
+        <v>154.68</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>159.6</v>
+        <v>159.57</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>162.12</v>
@@ -4461,16 +4461,16 @@
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>174.35</v>
+        <v>175.25</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>164.26</v>
+        <v>164.34</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>164.85</v>
+        <v>164.88</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>177.87</v>
+        <v>177.88</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4505,16 +4505,16 @@
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>987.2</v>
+        <v>989.95</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>947.5</v>
+        <v>947.76</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>990.14</v>
+        <v>990.24</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1083.99</v>
+        <v>1084.02</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4549,16 +4549,16 @@
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>624.85</v>
+        <v>619.1</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>561.1</v>
+        <v>560.55</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>571.8099999999999</v>
+        <v>571.58</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>773.91</v>
+        <v>773.85</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4593,16 +4593,16 @@
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>579.35</v>
+        <v>578.3</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>557.83</v>
+        <v>557.73</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>570.64</v>
+        <v>570.59</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>607.92</v>
+        <v>607.91</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4637,25 +4637,25 @@
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>131.22</v>
+        <v>130.6</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>128.04</v>
+        <v>127.98</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.69</v>
+        <v>130.66</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>136.76</v>
+        <v>136.75</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H90" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I90" s="13" t="inlineStr">
@@ -4681,16 +4681,16 @@
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>364</v>
+        <v>366.8</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>337.45</v>
+        <v>337.72</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>344.15</v>
+        <v>344.26</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>403.67</v>
+        <v>403.69</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4725,16 +4725,16 @@
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>187</v>
+        <v>189.21</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>179.29</v>
+        <v>179.5</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>184.53</v>
+        <v>184.62</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>235.56</v>
+        <v>235.58</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4769,13 +4769,13 @@
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>19.66</v>
+        <v>20.18</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>17.49</v>
+        <v>17.54</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>17.49</v>
+        <v>17.51</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>21.78</v>
@@ -4813,13 +4813,13 @@
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1123.1</v>
+        <v>1123.5</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1058.1</v>
+        <v>1058.13</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1104.35</v>
+        <v>1104.37</v>
       </c>
       <c r="F94" s="11" t="n">
         <v>1351.31</v>
@@ -4857,16 +4857,16 @@
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>320.27</v>
+        <v>324.25</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>292.94</v>
+        <v>293.32</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>297.33</v>
+        <v>297.49</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>304.85</v>
+        <v>304.89</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4901,16 +4901,16 @@
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>47.69</v>
+        <v>47.78</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>45.33</v>
+        <v>45.34</v>
       </c>
       <c r="E96" s="11" t="n">
         <v>44.97</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.07</v>
+        <v>51.08</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4945,16 +4945,16 @@
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>978.1</v>
+        <v>977.05</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>923.6900000000001</v>
+        <v>923.59</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>912.75</v>
+        <v>912.71</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>898.99</v>
+        <v>898.98</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4989,16 +4989,16 @@
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>815.1</v>
+        <v>811.45</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>774.59</v>
+        <v>774.24</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>761.52</v>
+        <v>761.38</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>797.85</v>
+        <v>797.8099999999999</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5033,16 +5033,16 @@
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1529.6</v>
+        <v>1519.9</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1392.77</v>
+        <v>1391.84</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1326.05</v>
+        <v>1325.67</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1168.57</v>
+        <v>1168.47</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5077,25 +5077,25 @@
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>870.35</v>
+        <v>890.9</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>819.37</v>
+        <v>821.33</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>871.42</v>
+        <v>872.22</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1029.19</v>
+        <v>1029.4</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H100" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I100" s="13" t="inlineStr">
@@ -5121,16 +5121,16 @@
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>272.43</v>
+        <v>274.44</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>258.58</v>
+        <v>258.77</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>260.02</v>
+        <v>260.09</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>272.65</v>
+        <v>272.67</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5142,9 +5142,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
@@ -5165,16 +5165,16 @@
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4095.2</v>
+        <v>4190</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3896.58</v>
+        <v>3905.61</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3770.86</v>
+        <v>3774.57</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3691.16</v>
+        <v>3692.1</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5209,16 +5209,16 @@
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>715.05</v>
+        <v>710.4</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>707.23</v>
+        <v>706.79</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>700.36</v>
+        <v>700.1799999999999</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>759.8099999999999</v>
+        <v>759.76</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5253,16 +5253,16 @@
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>173.55</v>
+        <v>178.26</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>157.72</v>
+        <v>158.17</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>161.26</v>
+        <v>161.45</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.45</v>
+        <v>176.49</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5274,9 +5274,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I104" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
@@ -5297,16 +5297,16 @@
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>402</v>
+        <v>409.75</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>375.21</v>
+        <v>375.95</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>366.07</v>
+        <v>366.37</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>402.73</v>
+        <v>402.81</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5318,9 +5318,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
@@ -5341,16 +5341,16 @@
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1053</v>
+        <v>1064.4</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>976.96</v>
+        <v>978.05</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>922.17</v>
+        <v>922.61</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>933.29</v>
+        <v>933.41</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5385,16 +5385,16 @@
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>511.9</v>
+        <v>515.1</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>490.19</v>
+        <v>490.5</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>505.69</v>
+        <v>505.81</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>578.84</v>
+        <v>578.87</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>662.8</v>
+        <v>659.95</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>635.79</v>
+        <v>635.52</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>657.95</v>
+        <v>657.84</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>752.76</v>
+        <v>752.73</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5473,16 +5473,16 @@
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>359.5</v>
+        <v>384.3</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>351.6</v>
+        <v>353.96</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>345.28</v>
+        <v>346.25</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355</v>
+        <v>355.25</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5517,16 +5517,16 @@
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>71.94</v>
+        <v>72.58</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>65.67</v>
+        <v>65.73</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>65.45999999999999</v>
+        <v>65.48</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>83</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5561,20 +5561,20 @@
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>31.99</v>
+        <v>32.38</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>32.07</v>
+        <v>32.11</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.46</v>
+        <v>33.47</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.91</v>
-      </c>
-      <c r="G111" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>42.92</v>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
@@ -5605,16 +5605,16 @@
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>125.32</v>
+        <v>126.29</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>123.47</v>
+        <v>123.57</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.71</v>
+        <v>124.75</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.08</v>
+        <v>114.09</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5649,16 +5649,16 @@
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>449.3</v>
+        <v>451.45</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>392.03</v>
+        <v>392.23</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>384.55</v>
+        <v>384.64</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>414.89</v>
+        <v>414.91</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>26.04</v>
+        <v>26.13</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>23.89</v>
+        <v>23.9</v>
       </c>
       <c r="E114" s="11" t="n">
         <v>24.19</v>
@@ -5737,20 +5737,20 @@
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>544</v>
+        <v>545.35</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>544.36</v>
+        <v>544.49</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>571.27</v>
+        <v>571.3200000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>700.6900000000001</v>
-      </c>
-      <c r="G115" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>700.71</v>
+      </c>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
@@ -5781,16 +5781,16 @@
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>121.68</v>
+        <v>123.59</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>120.87</v>
+        <v>121.05</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>127.3</v>
+        <v>127.37</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>165.8</v>
+        <v>165.82</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5825,16 +5825,16 @@
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>450.8</v>
+        <v>454.1</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>414.03</v>
+        <v>414.35</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>404.94</v>
+        <v>405.07</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>431.57</v>
+        <v>431.6</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5869,16 +5869,16 @@
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>365.3</v>
+        <v>376.35</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>330.62</v>
+        <v>331.67</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>332.08</v>
+        <v>332.52</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>351.79</v>
+        <v>351.9</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5913,16 +5913,16 @@
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1192.3</v>
+        <v>1202.1</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1049.55</v>
+        <v>1050.48</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>938.58</v>
+        <v>938.96</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>838.35</v>
+        <v>838.45</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5957,16 +5957,16 @@
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>794.4</v>
+        <v>813.65</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>700.33</v>
+        <v>702.16</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>698.9299999999999</v>
+        <v>699.6900000000001</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>756.4299999999999</v>
+        <v>756.62</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -6001,16 +6001,16 @@
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>207.27</v>
+        <v>204.04</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>191.6</v>
+        <v>191.29</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>194.87</v>
+        <v>194.74</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>219.88</v>
+        <v>219.84</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6045,16 +6045,16 @@
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>251.13</v>
+        <v>250.64</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>237.54</v>
+        <v>237.5</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>223.87</v>
+        <v>223.85</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>200.8</v>
+        <v>200.79</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6089,16 +6089,16 @@
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>944.45</v>
+        <v>935.15</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>886.6900000000001</v>
+        <v>885.8099999999999</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>865.27</v>
+        <v>864.9</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>959.24</v>
+        <v>959.15</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6133,16 +6133,16 @@
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1354</v>
+        <v>1354.9</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1213.55</v>
+        <v>1213.63</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1157.74</v>
+        <v>1157.77</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1157.46</v>
+        <v>1157.47</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>171.9</v>
+        <v>172.37</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>166.4</v>
+        <v>166.45</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>170.06</v>
+        <v>170.08</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.4</v>
+        <v>191.41</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6221,16 +6221,16 @@
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14470</v>
+        <v>14591</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>13801.61</v>
+        <v>13813.13</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14092.34</v>
+        <v>14097.09</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14863.62</v>
+        <v>14864.82</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6265,16 +6265,16 @@
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>141.63</v>
+        <v>144.23</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>130.48</v>
+        <v>130.73</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>132.26</v>
+        <v>132.36</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>162.58</v>
+        <v>162.6</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6309,16 +6309,16 @@
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>180.86</v>
+        <v>178.37</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>175.32</v>
+        <v>175.09</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>183.85</v>
+        <v>183.76</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>210.89</v>
+        <v>210.87</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6353,16 +6353,16 @@
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>58.27</v>
+        <v>59.07</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>49.67</v>
+        <v>49.74</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>48.23</v>
+        <v>48.26</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>54.79</v>
+        <v>54.8</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6397,16 +6397,16 @@
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>68.40000000000001</v>
+        <v>69.16</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>57.38</v>
+        <v>57.45</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>54.92</v>
+        <v>54.95</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.22</v>
+        <v>59.23</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6441,16 +6441,16 @@
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1814.5</v>
+        <v>1794.4</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1713.2</v>
+        <v>1711.29</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1634.1</v>
+        <v>1633.31</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1368.2</v>
+        <v>1368</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6485,16 +6485,16 @@
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1487.05</v>
+        <v>1588.25</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1247.04</v>
+        <v>1256.68</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1104.2</v>
+        <v>1108.17</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1167.14</v>
+        <v>1168.14</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6529,16 +6529,16 @@
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>324.5</v>
+        <v>326.2</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>307.14</v>
+        <v>307.3</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>306.32</v>
+        <v>306.38</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.14</v>
+        <v>326.16</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6550,9 +6550,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I133" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J133" s="14" t="inlineStr">
@@ -6573,16 +6573,16 @@
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>453.5</v>
+        <v>452.2</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>433.98</v>
+        <v>433.85</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>437.19</v>
+        <v>437.14</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>472.84</v>
+        <v>472.83</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6617,16 +6617,16 @@
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>5148</v>
+        <v>5279.6</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>4330.88</v>
+        <v>4343.41</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>3822.79</v>
+        <v>3827.96</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2786.07</v>
+        <v>2787.38</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6661,16 +6661,16 @@
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>317.6</v>
+        <v>319.9</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>332.26</v>
+        <v>332.48</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>344.82</v>
+        <v>344.91</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>363.4</v>
+        <v>363.42</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6705,13 +6705,13 @@
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>102.4</v>
+        <v>102.77</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>95</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>99.79000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="F137" s="11" t="n">
         <v>128.7</v>
@@ -6749,16 +6749,16 @@
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1462.9</v>
+        <v>1455.5</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1338.34</v>
+        <v>1337.64</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1328.53</v>
+        <v>1328.24</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1324.38</v>
+        <v>1324.31</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6793,16 +6793,16 @@
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>178.16</v>
+        <v>179.56</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>173.9</v>
+        <v>174.04</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>173.44</v>
+        <v>173.5</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>187.76</v>
+        <v>187.78</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6837,16 +6837,16 @@
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1755.3</v>
+        <v>1762.9</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1617.15</v>
+        <v>1617.87</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1665.62</v>
+        <v>1665.92</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2010.39</v>
+        <v>2010.47</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6881,16 +6881,16 @@
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>393.25</v>
+        <v>389.1</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>373.9</v>
+        <v>373.5</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>381.86</v>
+        <v>381.69</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>427.56</v>
+        <v>427.52</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6925,16 +6925,16 @@
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>877</v>
+        <v>890.7</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>857.01</v>
+        <v>858.3099999999999</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>843.79</v>
+        <v>844.33</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>826.5</v>
+        <v>826.64</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6969,16 +6969,16 @@
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>382.25</v>
+        <v>385.9</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>341.32</v>
+        <v>341.67</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>336.35</v>
+        <v>336.49</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>346.71</v>
+        <v>346.74</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7013,16 +7013,16 @@
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>210.8</v>
+        <v>204.5</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>193.83</v>
+        <v>193.23</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>200.13</v>
+        <v>199.88</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>237</v>
+        <v>236.94</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7057,16 +7057,16 @@
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1569.9</v>
+        <v>1658.6</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1390.93</v>
+        <v>1399.38</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1340.06</v>
+        <v>1343.54</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1386.82</v>
+        <v>1387.7</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7101,16 +7101,16 @@
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1195.7</v>
+        <v>1200.8</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1132.84</v>
+        <v>1133.33</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1126.33</v>
+        <v>1126.53</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1168.34</v>
+        <v>1168.39</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7145,16 +7145,16 @@
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>76.84</v>
+        <v>77.88</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>74.05</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.22</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.14</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7189,16 +7189,16 @@
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>274.65</v>
+        <v>271.56</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>255.2</v>
+        <v>254.91</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>254.48</v>
+        <v>254.35</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>264.43</v>
+        <v>264.4</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7233,13 +7233,13 @@
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>35.83</v>
+        <v>36.29</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>33.48</v>
+        <v>33.53</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>34.27</v>
+        <v>34.29</v>
       </c>
       <c r="F149" s="11" t="n">
         <v>42.32</v>
@@ -7277,16 +7277,16 @@
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>406.9</v>
+        <v>427.55</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>373.26</v>
+        <v>375.23</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>383.99</v>
+        <v>384.8</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>483.46</v>
+        <v>483.67</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7321,16 +7321,16 @@
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>552.85</v>
+        <v>551.95</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>547.15</v>
+        <v>547.0700000000001</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>581.52</v>
+        <v>581.48</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>734.4</v>
+        <v>734.39</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7365,25 +7365,25 @@
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>144.71</v>
+        <v>148.21</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>140.39</v>
+        <v>140.72</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.65</v>
+        <v>145.79</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>192.17</v>
+        <v>192.2</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H152" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H152" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I152" s="13" t="inlineStr">
@@ -7409,13 +7409,13 @@
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>420.5</v>
+        <v>421.2</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>369.72</v>
+        <v>369.79</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>367.89</v>
+        <v>367.92</v>
       </c>
       <c r="F153" s="11" t="n">
         <v>506.97</v>
@@ -7453,16 +7453,16 @@
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>670.3</v>
+        <v>673.65</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>621.4299999999999</v>
+        <v>621.75</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>594.2</v>
+        <v>594.34</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>591.8</v>
+        <v>591.83</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7497,16 +7497,16 @@
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.58</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>9.109999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>9.26</v>
+        <v>9.27</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.9</v>
+        <v>10.91</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7541,13 +7541,13 @@
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>222.84</v>
+        <v>222.23</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>194.06</v>
+        <v>194</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>200.62</v>
+        <v>200.59</v>
       </c>
       <c r="F156" s="11" t="n">
         <v>241.55</v>
@@ -7585,16 +7585,16 @@
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>187.89</v>
+        <v>186.52</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>174.01</v>
+        <v>173.88</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>168.58</v>
+        <v>168.52</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>163.16</v>
+        <v>163.15</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7629,16 +7629,16 @@
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>133.63</v>
+        <v>136.27</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>121.15</v>
+        <v>121.41</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>122.31</v>
+        <v>122.41</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.41</v>
+        <v>141.43</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7673,16 +7673,16 @@
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>815.35</v>
+        <v>817</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>715.46</v>
+        <v>715.61</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>685.01</v>
+        <v>685.0700000000001</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>671.97</v>
+        <v>671.99</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7717,16 +7717,16 @@
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>27.45</v>
+        <v>28.35</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>26.5</v>
+        <v>26.58</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>26.79</v>
+        <v>26.82</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.23</v>
+        <v>32.24</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7761,16 +7761,16 @@
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1631.9</v>
+        <v>1595.9</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1551.73</v>
+        <v>1548.3</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1537.19</v>
+        <v>1535.78</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1492.08</v>
+        <v>1491.72</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7805,16 +7805,16 @@
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>869.4</v>
+        <v>881</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>849.36</v>
+        <v>850.46</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>841.23</v>
+        <v>841.6900000000001</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>928.35</v>
+        <v>928.46</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7849,16 +7849,16 @@
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2459.6</v>
+        <v>2491.4</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2185.71</v>
+        <v>2188.74</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2126.57</v>
+        <v>2127.82</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2363.22</v>
+        <v>2363.53</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7893,16 +7893,16 @@
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>606.55</v>
+        <v>612.35</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>570.73</v>
+        <v>571.28</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>571.15</v>
+        <v>571.38</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>554.54</v>
+        <v>554.6</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7937,16 +7937,16 @@
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>260</v>
+        <v>263.13</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>244.72</v>
+        <v>245.02</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>245.63</v>
+        <v>245.75</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>277.47</v>
+        <v>277.5</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7981,13 +7981,13 @@
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>133.14</v>
+        <v>133.23</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>126.92</v>
+        <v>126.93</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>126.71</v>
+        <v>126.72</v>
       </c>
       <c r="F166" s="11" t="n">
         <v>135.5</v>
@@ -8025,16 +8025,16 @@
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3134</v>
+        <v>3163.3</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>2992.15</v>
+        <v>2994.94</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>2939.78</v>
+        <v>2940.93</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2721.89</v>
+        <v>2722.18</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8069,16 +8069,16 @@
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2735</v>
+        <v>2750.7</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2496.6</v>
+        <v>2498.09</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2439.51</v>
+        <v>2440.13</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2516.05</v>
+        <v>2516.21</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8113,16 +8113,16 @@
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>221.44</v>
+        <v>218.13</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>203.57</v>
+        <v>203.25</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>205.77</v>
+        <v>205.64</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>238.78</v>
+        <v>238.75</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8157,16 +8157,16 @@
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>196.6</v>
+        <v>197.77</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>189.46</v>
+        <v>189.58</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>191.61</v>
+        <v>191.65</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>245.79</v>
+        <v>245.8</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8201,16 +8201,16 @@
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>131.11</v>
+        <v>132.69</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>123.98</v>
+        <v>124.13</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>127.09</v>
+        <v>127.15</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>133.75</v>
+        <v>133.77</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8245,16 +8245,16 @@
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>264.75</v>
+        <v>265.96</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>255.03</v>
+        <v>255.15</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>256.03</v>
+        <v>256.08</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>272.36</v>
+        <v>272.37</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8289,16 +8289,16 @@
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>571.1</v>
+        <v>574</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>541.4</v>
+        <v>541.67</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>544.05</v>
+        <v>544.17</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>578.87</v>
+        <v>578.9</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8333,16 +8333,16 @@
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2405.4</v>
+        <v>2454.3</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2341.14</v>
+        <v>2345.8</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2312.02</v>
+        <v>2313.94</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2398.6</v>
+        <v>2399.09</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8377,16 +8377,16 @@
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>34.72</v>
+        <v>36.07</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>31.78</v>
+        <v>31.91</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.75</v>
+        <v>40.76</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8421,16 +8421,16 @@
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>9.609999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>8.949999999999999</v>
+        <v>9</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>8.75</v>
+        <v>8.77</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8442,9 +8442,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I176" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J176" s="14" t="inlineStr">
@@ -8465,13 +8465,13 @@
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>811.4</v>
+        <v>811.2</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>802.59</v>
+        <v>802.5700000000001</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>845.9</v>
+        <v>845.89</v>
       </c>
       <c r="F177" s="11" t="n">
         <v>1032.57</v>
@@ -8509,16 +8509,16 @@
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>258.48</v>
+        <v>260.75</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>229.77</v>
+        <v>229.99</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>228.78</v>
+        <v>228.87</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>297.57</v>
+        <v>297.59</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8553,16 +8553,16 @@
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>304.91</v>
+        <v>311.72</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>293.48</v>
+        <v>294.12</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>312.35</v>
+        <v>312.62</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>386.45</v>
+        <v>386.52</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8597,25 +8597,25 @@
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>226.5</v>
+        <v>223.83</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>222.2</v>
+        <v>221.95</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>224.38</v>
+        <v>224.27</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>237.43</v>
+        <v>237.4</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H180" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H180" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I180" s="13" t="inlineStr">
@@ -8641,13 +8641,13 @@
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>63.68</v>
+        <v>63.82</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>62.17</v>
+        <v>62.18</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>62.53</v>
+        <v>62.54</v>
       </c>
       <c r="F181" s="11" t="n">
         <v>67.63</v>
@@ -8685,25 +8685,25 @@
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>503.95</v>
+        <v>518.75</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>487.77</v>
+        <v>489.18</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>509.3</v>
+        <v>509.89</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>683.37</v>
+        <v>683.52</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H182" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H182" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I182" s="13" t="inlineStr">
@@ -8729,16 +8729,16 @@
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>415.4</v>
+        <v>421.4</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>384.65</v>
+        <v>385.23</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>362.32</v>
+        <v>362.55</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>339.84</v>
+        <v>339.9</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8773,20 +8773,20 @@
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1575.5</v>
+        <v>1545.9</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1562.4</v>
+        <v>1559.58</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1675.73</v>
+        <v>1674.57</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1978.12</v>
-      </c>
-      <c r="G184" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1977.83</v>
+      </c>
+      <c r="G184" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
@@ -8817,16 +8817,16 @@
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>164.35</v>
+        <v>165.2</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>155.41</v>
+        <v>155.5</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>157.61</v>
+        <v>157.64</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>176.71</v>
+        <v>176.72</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8861,16 +8861,16 @@
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>214.45</v>
+        <v>214</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>201.35</v>
+        <v>201.31</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>201.32</v>
+        <v>201.3</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>193.08</v>
+        <v>193.07</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8905,16 +8905,16 @@
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4625</v>
+        <v>4580.3</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4545.07</v>
+        <v>4540.81</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4433.89</v>
+        <v>4432.14</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4582.03</v>
+        <v>4581.59</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8926,9 +8926,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I187" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J187" s="14" t="inlineStr">
@@ -8949,16 +8949,16 @@
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3537</v>
+        <v>3500</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3454.92</v>
+        <v>3451.4</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3598.01</v>
+        <v>3596.56</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4285.25</v>
+        <v>4284.88</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8993,16 +8993,16 @@
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2441.9</v>
+        <v>2547</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2271.24</v>
+        <v>2281.25</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2156.98</v>
+        <v>2161.1</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1783.86</v>
+        <v>1784.91</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9037,16 +9037,16 @@
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>328.4</v>
+        <v>329.9</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>317.06</v>
+        <v>317.21</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>314.66</v>
+        <v>314.72</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>333.92</v>
+        <v>333.94</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9081,16 +9081,16 @@
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>1912.4</v>
+        <v>1938.9</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>1981.75</v>
+        <v>1984.27</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2041.73</v>
+        <v>2042.77</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2064.04</v>
+        <v>2064.3</v>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
@@ -9125,16 +9125,16 @@
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>563</v>
+        <v>564.25</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>527.47</v>
+        <v>527.59</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>546.29</v>
+        <v>546.34</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>699.48</v>
+        <v>699.49</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9169,13 +9169,13 @@
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1159</v>
+        <v>1158.8</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1048.35</v>
+        <v>1048.33</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1025.44</v>
+        <v>1025.43</v>
       </c>
       <c r="F193" s="11" t="n">
         <v>919.66</v>
@@ -9213,16 +9213,16 @@
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>865.95</v>
+        <v>880.2</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>826.0700000000001</v>
+        <v>827.4299999999999</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>842.62</v>
+        <v>843.1799999999999</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>913.6</v>
+        <v>913.74</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9257,16 +9257,16 @@
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>147.88</v>
+        <v>150.67</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>138.94</v>
+        <v>139.2</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>138.62</v>
+        <v>138.73</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>157.28</v>
+        <v>157.31</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9301,16 +9301,16 @@
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>558.05</v>
+        <v>564.5</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>529.26</v>
+        <v>529.88</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>535.97</v>
+        <v>536.22</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>610.39</v>
+        <v>610.46</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9345,16 +9345,16 @@
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>400.55</v>
+        <v>408.35</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>387.68</v>
+        <v>388.42</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>359.55</v>
+        <v>359.86</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>356.29</v>
+        <v>356.36</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9389,13 +9389,13 @@
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>28.38</v>
+        <v>28.58</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>27.15</v>
+        <v>27.17</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>26.17</v>
+        <v>26.18</v>
       </c>
       <c r="F198" s="11" t="n">
         <v>27.56</v>
@@ -9433,16 +9433,16 @@
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3618</v>
+        <v>3591.6</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3360.21</v>
+        <v>3357.7</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3175.21</v>
+        <v>3174.17</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2828.67</v>
+        <v>2828.41</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>476.85</v>
+        <v>471.85</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>397.31</v>
+        <v>396.84</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>383.6</v>
+        <v>383.4</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>425.46</v>
+        <v>425.41</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9521,10 +9521,10 @@
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>39.62</v>
+        <v>39.85</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>38.29</v>
+        <v>38.31</v>
       </c>
       <c r="E201" s="11" t="n">
         <v>38.63</v>
@@ -9565,16 +9565,16 @@
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>227.31</v>
+        <v>229.92</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>216.39</v>
+        <v>216.64</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>214.68</v>
+        <v>214.79</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.39</v>
+        <v>223.41</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9609,16 +9609,16 @@
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>212.5</v>
+        <v>218.65</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>186.53</v>
+        <v>187.11</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>186.8</v>
+        <v>187.04</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>226.67</v>
+        <v>226.73</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9653,16 +9653,16 @@
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>285.99</v>
+        <v>290.99</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>229.11</v>
+        <v>229.59</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>191.97</v>
+        <v>192.17</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>139.08</v>
+        <v>139.13</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9697,16 +9697,16 @@
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>1006.85</v>
+        <v>1002.05</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>971.28</v>
+        <v>970.8200000000001</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>932.76</v>
+        <v>932.5700000000001</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>869.77</v>
+        <v>869.73</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9741,16 +9741,16 @@
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2225.9</v>
+        <v>2272.3</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2062.17</v>
+        <v>2066.59</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>2000.57</v>
+        <v>2002.39</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2203.92</v>
+        <v>2204.38</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9785,16 +9785,16 @@
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>792.25</v>
+        <v>788.1</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>740.9</v>
+        <v>740.5</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>748.62</v>
+        <v>748.46</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>806.65</v>
+        <v>806.61</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9829,16 +9829,16 @@
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>872.35</v>
+        <v>910.85</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>825.01</v>
+        <v>828.6799999999999</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>847.39</v>
+        <v>848.9</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>999.73</v>
+        <v>1000.11</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9873,16 +9873,16 @@
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>144.36</v>
+        <v>143.54</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>136.95</v>
+        <v>136.87</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>132.14</v>
+        <v>132.11</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.71</v>
+        <v>137.7</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9917,16 +9917,16 @@
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>289.77</v>
+        <v>297.31</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>249.77</v>
+        <v>250.48</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>242.42</v>
+        <v>242.72</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>253.24</v>
+        <v>253.32</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9961,16 +9961,16 @@
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>373.75</v>
+        <v>357.85</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>328.31</v>
+        <v>326.79</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>345.81</v>
+        <v>345.19</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>391.03</v>
+        <v>390.87</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10005,25 +10005,25 @@
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>624.55</v>
+        <v>656</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>619.13</v>
+        <v>622.12</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>633.84</v>
+        <v>635.0700000000001</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>679.55</v>
+        <v>679.86</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H212" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H212" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I212" s="13" t="inlineStr">
@@ -10049,16 +10049,16 @@
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>239.21</v>
+        <v>242.35</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>224.42</v>
+        <v>224.72</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>225.96</v>
+        <v>226.08</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>252.51</v>
+        <v>252.54</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10093,16 +10093,16 @@
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>803.15</v>
+        <v>802.65</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>776.7</v>
+        <v>776.65</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>797.54</v>
+        <v>797.52</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>904.79</v>
+        <v>904.78</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10137,16 +10137,16 @@
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>137.55</v>
+        <v>140.35</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>129.55</v>
+        <v>129.82</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>135.2</v>
+        <v>135.31</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>148.82</v>
+        <v>148.85</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10181,16 +10181,16 @@
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1040.15</v>
+        <v>1062.7</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>930.4</v>
+        <v>932.55</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>869.17</v>
+        <v>870.0599999999999</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>711.87</v>
+        <v>712.1</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10225,16 +10225,16 @@
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>416.9</v>
+        <v>418.4</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>387.53</v>
+        <v>387.68</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>395.38</v>
+        <v>395.44</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>484.57</v>
+        <v>484.59</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10269,16 +10269,16 @@
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>115.2</v>
+        <v>115.67</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>108.45</v>
+        <v>108.5</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>107.74</v>
+        <v>107.75</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.36</v>
+        <v>116.37</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10313,13 +10313,13 @@
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>499.35</v>
+        <v>500.15</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>460.53</v>
+        <v>460.61</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>460.23</v>
+        <v>460.26</v>
       </c>
       <c r="F219" s="11" t="n">
         <v>527.1900000000001</v>
@@ -10357,16 +10357,16 @@
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1235.1</v>
+        <v>1238</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1208.33</v>
+        <v>1208.61</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1252.98</v>
+        <v>1253.09</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1569.78</v>
+        <v>1569.81</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10401,16 +10401,16 @@
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1723.9</v>
+        <v>1724.5</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1714.24</v>
+        <v>1714.3</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1732.59</v>
+        <v>1732.62</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1769.38</v>
+        <v>1769.39</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10445,16 +10445,16 @@
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>103.71</v>
+        <v>106.33</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>98.17</v>
+        <v>98.42</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>102.08</v>
+        <v>102.18</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>124.12</v>
+        <v>124.15</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10489,16 +10489,16 @@
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>4186.2</v>
+        <v>4022.9</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3944.17</v>
+        <v>3928.62</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3735.16</v>
+        <v>3728.76</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3063.76</v>
+        <v>3062.14</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10533,16 +10533,16 @@
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2032.5</v>
+        <v>2052.6</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1868.59</v>
+        <v>1870.5</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1821.66</v>
+        <v>1822.45</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2143.56</v>
+        <v>2143.76</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>106.56</v>
+        <v>107.02</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>102.89</v>
+        <v>102.93</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>106.25</v>
+        <v>106.27</v>
       </c>
       <c r="F225" s="11" t="n">
         <v>131.86</v>
@@ -10621,25 +10621,25 @@
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>388</v>
+        <v>395.6</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>384.64</v>
+        <v>385.37</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>391.22</v>
+        <v>391.51</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.03</v>
+        <v>396.1</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H226" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H226" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I226" s="13" t="inlineStr">
@@ -10665,16 +10665,16 @@
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>475.3</v>
+        <v>476.55</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>445.6</v>
+        <v>445.72</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>442.26</v>
+        <v>442.31</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>434.53</v>
+        <v>434.54</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10709,13 +10709,13 @@
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>191.95</v>
+        <v>192.54</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>182.22</v>
+        <v>182.27</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>180.36</v>
+        <v>180.38</v>
       </c>
       <c r="F228" s="11" t="n">
         <v>192.76</v>
@@ -10753,16 +10753,16 @@
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>602.25</v>
+        <v>599.6</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>552.35</v>
+        <v>552.1</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>539.83</v>
+        <v>539.73</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>554.87</v>
+        <v>554.84</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10797,16 +10797,16 @@
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>588.5</v>
+        <v>587.25</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>541.1</v>
+        <v>540.98</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>534.26</v>
+        <v>534.21</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>585.91</v>
+        <v>585.9</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10841,16 +10841,16 @@
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>58.74</v>
+        <v>58.49</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>57.26</v>
+        <v>57.24</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>57.01</v>
+        <v>57</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.63</v>
+        <v>52.62</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10885,16 +10885,16 @@
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>969</v>
+        <v>998.3</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>866.5</v>
+        <v>869.29</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>861.41</v>
+        <v>862.5599999999999</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>956.9299999999999</v>
+        <v>957.23</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10929,16 +10929,16 @@
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>649.25</v>
+        <v>645.85</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>595.22</v>
+        <v>594.9</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>589.23</v>
+        <v>589.1</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>683.27</v>
+        <v>683.24</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10973,16 +10973,16 @@
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>318.35</v>
+        <v>314.35</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>323.77</v>
+        <v>323.39</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>338.78</v>
+        <v>338.63</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>371.4</v>
+        <v>371.36</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11017,30 +11017,30 @@
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>196.3</v>
+        <v>205.52</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>194.36</v>
+        <v>195.24</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>197.19</v>
+        <v>197.55</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>200.52</v>
+        <v>200.61</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H235" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I235" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H235" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I235" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J235" s="14" t="inlineStr">
@@ -11061,16 +11061,16 @@
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>264.48</v>
+        <v>263.87</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>236.38</v>
+        <v>236.32</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>232.36</v>
+        <v>232.33</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.43</v>
+        <v>249.42</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11105,16 +11105,16 @@
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1494.6</v>
+        <v>1488.4</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1345.26</v>
+        <v>1344.67</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1290.49</v>
+        <v>1290.25</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1333.06</v>
+        <v>1333</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11149,16 +11149,16 @@
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>221.25</v>
+        <v>223.57</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>211.82</v>
+        <v>212.04</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>215.21</v>
+        <v>215.3</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>227.62</v>
+        <v>227.64</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11193,13 +11193,13 @@
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>534.1</v>
+        <v>533.8</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>515.03</v>
+        <v>515</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>524.9</v>
+        <v>524.89</v>
       </c>
       <c r="F239" s="11" t="n">
         <v>557.78</v>
@@ -11237,16 +11237,16 @@
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>506.9</v>
+        <v>502.6</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>481.22</v>
+        <v>480.81</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>482.46</v>
+        <v>482.3</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>485.68</v>
+        <v>485.63</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11281,20 +11281,20 @@
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1304.8</v>
+        <v>1312.7</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1306.56</v>
+        <v>1307.31</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1380.1</v>
+        <v>1380.41</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1549.75</v>
-      </c>
-      <c r="G241" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1549.82</v>
+      </c>
+      <c r="G241" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H241" s="13" t="inlineStr">
@@ -11325,10 +11325,10 @@
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>209.5</v>
+        <v>209.61</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>202.89</v>
+        <v>202.9</v>
       </c>
       <c r="E242" s="11" t="n">
         <v>201.43</v>
@@ -11369,16 +11369,16 @@
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>10723.5</v>
+        <v>11051</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>9493.92</v>
+        <v>9525.120000000001</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>8874.52</v>
+        <v>8887.370000000001</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8199.610000000001</v>
+        <v>8202.870000000001</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1075</v>
+        <v>1093.35</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>960.09</v>
+        <v>961.84</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>917.52</v>
+        <v>918.24</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>959.62</v>
+        <v>959.8</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11457,16 +11457,16 @@
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>94.15000000000001</v>
+        <v>97.09</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>80.06</v>
+        <v>80.34</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>75.51000000000001</v>
+        <v>75.62</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>96.78</v>
+        <v>96.81</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11478,9 +11478,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I245" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I245" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J245" s="14" t="inlineStr">
@@ -11501,16 +11501,16 @@
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>488.8</v>
+        <v>510.5</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>461.25</v>
+        <v>463.32</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>466.78</v>
+        <v>467.63</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>495.1</v>
+        <v>495.31</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11522,9 +11522,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I246" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I246" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J246" s="14" t="inlineStr">
@@ -11545,16 +11545,16 @@
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>488.5</v>
+        <v>484.5</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>464.44</v>
+        <v>464.06</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>476.2</v>
+        <v>476.05</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>565.49</v>
+        <v>565.45</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11589,16 +11589,16 @@
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>753.25</v>
+        <v>740.85</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>716.88</v>
+        <v>715.7</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>691.87</v>
+        <v>691.38</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>665.96</v>
+        <v>665.84</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11633,16 +11633,16 @@
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>259.79</v>
+        <v>260.46</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>243.7</v>
+        <v>243.76</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>249.37</v>
+        <v>249.39</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>318.34</v>
+        <v>318.35</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11677,16 +11677,16 @@
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>507.7</v>
+        <v>503.25</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>477.8</v>
+        <v>477.38</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>449.45</v>
+        <v>449.28</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>428.68</v>
+        <v>428.64</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11721,16 +11721,16 @@
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>504.65</v>
+        <v>504.45</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>466.01</v>
+        <v>465.99</v>
       </c>
       <c r="E251" s="11" t="n">
         <v>466.93</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>584.1900000000001</v>
+        <v>584.1799999999999</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 22-Apr-2026  16:46:33    |    Closing Price Date: 22-Apr-2026</t>
+          <t>Scan Run: 23-Apr-2026  18:00:15    |    Closing Price Date: 23-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>96.8</v>
+        <v>92</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>89.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>22-Apr-2026  16:46:33</t>
+          <t>23-Apr-2026  18:00:15</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 96.8% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 92.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 89.2% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 85.6% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 44.4% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 242 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 230 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 223 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 214 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 111 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 110 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,29 +761,29 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>564.55</v>
+        <v>559.25</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>542.0700000000001</v>
+        <v>543.71</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>560.05</v>
+        <v>560.02</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>693.6</v>
+        <v>694.73</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>442.8</v>
+        <v>434.55</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>433.48</v>
+        <v>433.58</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>433.22</v>
+        <v>433.28</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>454.62</v>
+        <v>454.14</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>366.95</v>
+        <v>371.95</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>357.61</v>
+        <v>358.97</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>362.06</v>
+        <v>362.44</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>404.18</v>
+        <v>403.74</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>693.95</v>
+        <v>688.55</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>677.8</v>
+        <v>678.83</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>688.47</v>
+        <v>688.48</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>743.1</v>
+        <v>742.27</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2423.2</v>
+        <v>2386.7</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2333.8</v>
+        <v>2338.84</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2211.24</v>
+        <v>2218.12</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1792.5</v>
+        <v>1798.41</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>299.15</v>
+        <v>298.65</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>291.66</v>
+        <v>292.33</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>290.46</v>
+        <v>290.79</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>301.91</v>
+        <v>302.2</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1183.3</v>
+        <v>1181.4</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1141.42</v>
+        <v>1145.23</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1074.45</v>
+        <v>1078.64</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>928.6</v>
+        <v>931.45</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>890.2</v>
+        <v>886.25</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>789.3200000000001</v>
+        <v>798.55</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>793.58</v>
+        <v>797.22</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>868.02</v>
+        <v>868.51</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>525.3</v>
+        <v>531.85</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>480.78</v>
+        <v>485.65</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>489.37</v>
+        <v>491.03</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>560.63</v>
+        <v>560.34</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1056.85</v>
+        <v>1061.55</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1025.6</v>
+        <v>1029.02</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>979.09</v>
+        <v>982.3200000000001</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>955.12</v>
+        <v>957.47</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.07</v>
+        <v>9.08</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>18</v>
+        <v>17.98</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>553.1</v>
+        <v>561.15</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>496.66</v>
+        <v>502.8</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>486.23</v>
+        <v>489.17</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>498.44</v>
+        <v>499.41</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1343.3</v>
+        <v>1341</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1281.21</v>
+        <v>1286.9</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1271.21</v>
+        <v>1273.94</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1177.23</v>
+        <v>1178.75</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>126.05</v>
+        <v>122.3</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>116.67</v>
+        <v>117.21</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>118.16</v>
+        <v>118.32</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>134.67</v>
+        <v>134.64</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,24 +1377,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>591.05</v>
+        <v>596.85</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>595.33</v>
+        <v>595.48</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>583.02</v>
+        <v>583.5599999999999</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>589.08</v>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>588.79</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>471.8</v>
+        <v>456.9</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>451.49</v>
+        <v>452.01</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>446.96</v>
+        <v>447.35</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>470.77</v>
+        <v>470.62</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1446,9 +1446,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J17" s="14" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>392.05</v>
+        <v>388.8</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>375.83</v>
+        <v>377.07</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>361.18</v>
+        <v>362.26</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>341.67</v>
+        <v>342.31</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>137.63</v>
+        <v>135.87</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>126.59</v>
+        <v>127.47</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>130.76</v>
+        <v>130.96</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>164.44</v>
+        <v>164.32</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1129.75</v>
+        <v>1135.55</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1020.28</v>
+        <v>1031.26</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>983.91</v>
+        <v>989.86</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>960.29</v>
+        <v>962.99</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,29 +1597,29 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>887.35</v>
+        <v>860.8</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>861.3099999999999</v>
+        <v>861.26</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>883.0700000000001</v>
+        <v>882.2</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1077.27</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1076.51</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1079.45</v>
+        <v>1088.5</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1026.79</v>
+        <v>1032.66</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>989.1799999999999</v>
+        <v>993.0700000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>946.4400000000001</v>
+        <v>947.5</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1442.7</v>
+        <v>1460.2</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1349.37</v>
+        <v>1359.93</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1237.14</v>
+        <v>1245.89</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>961.41</v>
+        <v>967.73</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>14.81</v>
+        <v>14.57</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.89</v>
+        <v>14.86</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.29</v>
+        <v>15.26</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>359.24</v>
+        <v>351.21</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>317.17</v>
+        <v>320.41</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>325.38</v>
+        <v>326.4</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>456.89</v>
+        <v>457.03</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1950.4</v>
+        <v>2111</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1722.74</v>
+        <v>1759.72</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1645.4</v>
+        <v>1663.66</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1606.98</v>
+        <v>1612.47</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>398.2</v>
+        <v>393.5</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>375.64</v>
+        <v>377.34</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>381.62</v>
+        <v>382.09</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>474.32</v>
+        <v>474.25</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1223.5</v>
+        <v>1239.95</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1105.72</v>
+        <v>1118.5</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1096.01</v>
+        <v>1101.66</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1242.09</v>
+        <v>1242.28</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>478.55</v>
+        <v>471</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>461.67</v>
+        <v>462.55</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>466.44</v>
+        <v>466.62</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>540.75</v>
+        <v>542.24</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>624.25</v>
+        <v>614.9</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>585.53</v>
+        <v>588.33</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>591.28</v>
+        <v>592.21</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>606.98</v>
+        <v>607.91</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>222.13</v>
+        <v>217.6</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>203.32</v>
+        <v>204.68</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>192.36</v>
+        <v>193.35</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>163.29</v>
+        <v>163.83</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2808.8</v>
+        <v>2990.5</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2530.95</v>
+        <v>2574.71</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2495.15</v>
+        <v>2514.57</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2724.8</v>
+        <v>2735.86</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>948.35</v>
+        <v>942.25</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>925.05</v>
+        <v>926.6900000000001</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>941.54</v>
+        <v>941.5700000000001</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1072.47</v>
+        <v>1071.15</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>622.05</v>
+        <v>616.5</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>594.4299999999999</v>
+        <v>596.53</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>595.8</v>
+        <v>596.61</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>580.62</v>
+        <v>581.4400000000001</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>516.75</v>
+        <v>511.05</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>462.66</v>
+        <v>467.26</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>462.79</v>
+        <v>464.68</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>518.39</v>
+        <v>519.5</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1377.8</v>
+        <v>1412.8</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1297.95</v>
+        <v>1308.88</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1312.74</v>
+        <v>1316.66</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>471.7</v>
+        <v>468.6</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>467.32</v>
+        <v>467.44</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>454.11</v>
+        <v>454.68</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>430.73</v>
+        <v>431.21</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>317.8</v>
+        <v>312.75</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>301.62</v>
+        <v>302.68</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>303.99</v>
+        <v>304.33</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>353.02</v>
+        <v>352.47</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,34 +2389,34 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>396.35</v>
+        <v>384.75</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>388.34</v>
+        <v>388</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>391.46</v>
+        <v>391.2</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>394.56</v>
       </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1784.6</v>
+        <v>1691</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1785.74</v>
+        <v>1776.71</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1915.08</v>
+        <v>1906.29</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2168.69</v>
+        <v>2163.67</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>326.35</v>
+        <v>324.8</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>295.43</v>
+        <v>298.23</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>284.76</v>
+        <v>286.33</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>271.86</v>
+        <v>273.2</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>424.4</v>
+        <v>422.55</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>419.09</v>
+        <v>419.42</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>436.08</v>
+        <v>435.54</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>520.25</v>
+        <v>518.79</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>675.3</v>
+        <v>663.95</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>606.96</v>
+        <v>612.39</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>607.76</v>
+        <v>609.97</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>702.92</v>
+        <v>702.54</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,24 +2609,24 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1220.5</v>
+        <v>1200.2</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1218.33</v>
+        <v>1216.6</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1270.04</v>
+        <v>1267.3</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1480.82</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1477.08</v>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>375.25</v>
+        <v>381.55</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>322.98</v>
+        <v>328.56</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>327.88</v>
+        <v>329.98</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>394.02</v>
+        <v>393.64</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>195.32</v>
+        <v>191.89</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>183.57</v>
+        <v>184.36</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>180.79</v>
+        <v>181.22</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>164.29</v>
+        <v>164.68</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>723.95</v>
+        <v>728.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>714.13</v>
+        <v>715.51</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723.63</v>
+        <v>723.83</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>758.4400000000001</v>
+        <v>758.47</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1046.9</v>
+        <v>1071.05</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1002.55</v>
+        <v>1009.08</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1028.05</v>
+        <v>1029.73</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1217.69</v>
+        <v>1217.95</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>159.81</v>
+        <v>159.78</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>141.29</v>
+        <v>143.05</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>136.27</v>
+        <v>137.19</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.63</v>
+        <v>135.62</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>457.3</v>
+        <v>455.45</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>435.82</v>
+        <v>437.69</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>436.68</v>
+        <v>437.42</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>454.72</v>
+        <v>455.32</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>170.79</v>
+        <v>174.55</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>162.65</v>
+        <v>163.78</v>
       </c>
       <c r="E51" s="11" t="n">
         <v>174.7</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>218.18</v>
+        <v>217.97</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1096.9</v>
+        <v>1110.3</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1058.81</v>
+        <v>1063.71</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1086.72</v>
+        <v>1087.64</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1179.89</v>
+        <v>1180.4</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>11541</v>
+        <v>11677.5</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>10152.43</v>
+        <v>10297.67</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>9801.67</v>
+        <v>9875.23</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8711.459999999999</v>
+        <v>8755.49</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>228.22</v>
+        <v>223.21</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>221.54</v>
+        <v>221.7</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>213.36</v>
+        <v>213.75</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>211.73</v>
+        <v>212.29</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.83</v>
+        <v>7.72</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.47</v>
+        <v>7.49</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.39</v>
+        <v>7.4</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.35</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>121.98</v>
+        <v>120.42</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>113.88</v>
+        <v>114.5</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>111.98</v>
+        <v>112.31</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.21</v>
+        <v>109.45</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>108.99</v>
+        <v>106.69</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>100.43</v>
+        <v>101.02</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>98.94</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>113.95</v>
+        <v>113.92</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>79.83</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>78.86</v>
+        <v>78.87</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>76.22</v>
+        <v>76.33</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.44</v>
+        <v>84.64</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>54.52</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>77.06999999999999</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1263.9</v>
+        <v>1256.9</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1211.47</v>
+        <v>1215.8</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1160.8</v>
+        <v>1164.57</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1153.24</v>
+        <v>1155.68</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>212.19</v>
+        <v>212.04</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>184.74</v>
+        <v>187.34</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>175.09</v>
+        <v>176.54</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>201.41</v>
+        <v>202.1</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1204.45</v>
+        <v>1195.3</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1056.28</v>
+        <v>1069.52</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1024.77</v>
+        <v>1031.46</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1312.02</v>
+        <v>1316.44</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>65.23</v>
+        <v>65.95</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>61.3</v>
+        <v>61.74</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>61.27</v>
+        <v>61.46</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>61.92</v>
+        <v>62.02</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2717.9</v>
+        <v>2692.6</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2388.59</v>
+        <v>2417.55</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2402.25</v>
+        <v>2413.63</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2583.1</v>
+        <v>2586.57</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>496.6</v>
+        <v>505.55</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>480.22</v>
+        <v>482.64</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>488.35</v>
+        <v>489.03</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>535.84</v>
+        <v>536.59</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>359</v>
+        <v>371.95</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>350.75</v>
+        <v>352.77</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>357.98</v>
+        <v>358.52</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>399.27</v>
+        <v>399.31</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2275.2</v>
+        <v>2221.2</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2163.09</v>
+        <v>2168.62</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2154.99</v>
+        <v>2157.59</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2064.63</v>
+        <v>2067.65</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>5086</v>
+        <v>4978.7</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4633.94</v>
+        <v>4666.78</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4481.56</v>
+        <v>4501.06</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4463.3</v>
+        <v>4468.82</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>888.6</v>
+        <v>875.4</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>872.84</v>
+        <v>873.09</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>902.8099999999999</v>
+        <v>901.74</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1037.03</v>
+        <v>1036.33</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>506.9</v>
+        <v>502.35</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>481.46</v>
+        <v>483.45</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>485.53</v>
+        <v>486.19</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>544.38</v>
+        <v>544.89</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>916.25</v>
+        <v>914</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>897.25</v>
+        <v>898.85</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>918.76</v>
+        <v>918.5700000000001</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1041.01</v>
+        <v>1039.86</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>111.03</v>
+        <v>108.38</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>105.27</v>
+        <v>105.57</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>105.81</v>
+        <v>105.91</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.21</v>
+        <v>110.29</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3866,9 +3866,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I72" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J72" s="14" t="inlineStr">
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>1031.85</v>
+        <v>997.75</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>945.58</v>
+        <v>950.55</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>936.7</v>
+        <v>939.09</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>941.84</v>
+        <v>942.8200000000001</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>870.55</v>
+        <v>842.5</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>716.4400000000001</v>
+        <v>728.45</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>635.53</v>
+        <v>643.65</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>572.3099999999999</v>
+        <v>575.3099999999999</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>651.25</v>
+        <v>640.6</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>611.95</v>
+        <v>614.6799999999999</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>639.99</v>
+        <v>640.01</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>752.96</v>
+        <v>751.84</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1065</v>
+        <v>1033.65</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>993.76</v>
+        <v>997.5599999999999</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>908.8200000000001</v>
+        <v>913.71</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1037.6</v>
+        <v>1041.23</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4042,9 +4042,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>4051.5</v>
+        <v>4195.7</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3836.71</v>
+        <v>3870.9</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3781.4</v>
+        <v>3797.64</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3635.16</v>
+        <v>3646.78</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,29 +4105,29 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>644.7</v>
+        <v>632.45</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>627.21</v>
+        <v>627.71</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>634.5700000000001</v>
+        <v>634.49</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>701.66</v>
+        <v>701.37</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>58.69</v>
+        <v>57.66</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>56.5</v>
+        <v>56.61</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>56.33</v>
+        <v>56.38</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>58.98</v>
+        <v>59.03</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>749.7</v>
+        <v>725.8</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>676.0599999999999</v>
+        <v>680.8</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>669.72</v>
+        <v>671.92</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>754.5599999999999</v>
+        <v>754.47</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>161.34</v>
+        <v>159.6</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>149.27</v>
+        <v>150.26</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>152.14</v>
+        <v>152.43</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>180.66</v>
+        <v>180.64</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>212.15</v>
+        <v>208.26</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>202.9</v>
+        <v>203.41</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>205.29</v>
+        <v>205.41</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>239.24</v>
+        <v>239.35</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>154.95</v>
+        <v>154.96</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>146.53</v>
+        <v>147.33</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>140.55</v>
+        <v>141.11</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>126.06</v>
+        <v>126.52</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>488.5</v>
+        <v>481.95</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>444.03</v>
+        <v>447.64</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>442.31</v>
+        <v>443.87</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>473.12</v>
+        <v>473.78</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4413,20 +4413,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>158.08</v>
+        <v>156.92</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>154.68</v>
+        <v>154.89</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>159.57</v>
+        <v>159.47</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.12</v>
+        <v>162.09</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>175.25</v>
+        <v>174.3</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>164.34</v>
+        <v>165.29</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>164.88</v>
+        <v>165.25</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>177.88</v>
+        <v>178</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>989.95</v>
+        <v>972.05</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>947.76</v>
+        <v>950.08</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>990.24</v>
+        <v>989.53</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1084.02</v>
+        <v>1083.43</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4545,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>619.1</v>
+        <v>605.1</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>560.55</v>
+        <v>564.79</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>571.58</v>
+        <v>572.9</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>773.85</v>
+        <v>773.51</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4589,29 +4589,29 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>578.3</v>
+        <v>570.15</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>557.73</v>
+        <v>558.91</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>570.59</v>
+        <v>570.58</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>607.91</v>
+        <v>608.01</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H89" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
@@ -4633,24 +4633,24 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>130.6</v>
+        <v>127.8</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>127.98</v>
+        <v>127.96</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.66</v>
+        <v>130.55</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>136.75</v>
-      </c>
-      <c r="G90" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>136.87</v>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>366.8</v>
+        <v>361.45</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>337.72</v>
+        <v>339.98</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>344.26</v>
+        <v>344.93</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>403.69</v>
+        <v>403.91</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,20 +4721,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>189.21</v>
+        <v>187.13</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>179.5</v>
+        <v>180.23</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>184.62</v>
+        <v>184.71</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>235.58</v>
+        <v>235.82</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>20.18</v>
+        <v>20.61</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>17.54</v>
+        <v>17.83</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>17.51</v>
+        <v>17.63</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.78</v>
+        <v>21.86</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1123.5</v>
+        <v>1203.8</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1058.13</v>
+        <v>1072.01</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1104.37</v>
+        <v>1108.27</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1351.31</v>
+        <v>1350.09</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>324.25</v>
+        <v>317.02</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>293.32</v>
+        <v>295.57</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>297.49</v>
+        <v>298.26</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>304.89</v>
+        <v>305.32</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>47.78</v>
+        <v>47.99</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>45.34</v>
+        <v>45.59</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>44.97</v>
+        <v>45.09</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.08</v>
+        <v>51.15</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>977.05</v>
+        <v>971.65</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>923.59</v>
+        <v>928.16</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>912.71</v>
+        <v>915.02</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>898.98</v>
+        <v>901.27</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>811.45</v>
+        <v>805.9</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>774.24</v>
+        <v>777.26</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>761.38</v>
+        <v>763.12</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>797.8099999999999</v>
+        <v>797.72</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1519.9</v>
+        <v>1551.6</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1391.84</v>
+        <v>1407.06</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1325.67</v>
+        <v>1334.53</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1168.47</v>
+        <v>1173.95</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>890.9</v>
+        <v>877.45</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>821.33</v>
+        <v>826.67</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>872.22</v>
+        <v>872.4299999999999</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1029.4</v>
+        <v>1028.02</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>274.44</v>
+        <v>267.46</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>258.77</v>
+        <v>259.6</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>260.09</v>
+        <v>260.38</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>272.67</v>
+        <v>272.56</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5142,9 +5142,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I101" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4190</v>
+        <v>4188.2</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3905.61</v>
+        <v>3932.52</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3774.57</v>
+        <v>3790.8</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3692.1</v>
+        <v>3695.11</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>710.4</v>
+        <v>723.95</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>706.79</v>
+        <v>708.4299999999999</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>700.1799999999999</v>
+        <v>701.11</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>759.76</v>
+        <v>760.38</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>178.26</v>
+        <v>177.62</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>158.17</v>
+        <v>160.02</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>161.45</v>
+        <v>162.08</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.49</v>
+        <v>177.17</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>409.75</v>
+        <v>404.35</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>375.95</v>
+        <v>378.66</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>366.37</v>
+        <v>367.86</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>402.81</v>
+        <v>403.59</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1064.4</v>
+        <v>1069.55</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>978.05</v>
+        <v>986.76</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>922.61</v>
+        <v>928.38</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>933.41</v>
+        <v>935.4400000000001</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>515.1</v>
+        <v>521.1</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>490.5</v>
+        <v>493.41</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>505.81</v>
+        <v>506.41</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>578.87</v>
+        <v>578.36</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5425,29 +5425,29 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>659.95</v>
+        <v>650</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>635.52</v>
+        <v>636.9</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>657.84</v>
+        <v>657.54</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>752.73</v>
+        <v>752.05</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H108" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H108" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I108" s="13" t="inlineStr">
@@ -5469,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>384.3</v>
+        <v>381.2</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>353.96</v>
+        <v>356.55</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>346.25</v>
+        <v>347.62</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.25</v>
+        <v>355.72</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>72.58</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>65.73</v>
+        <v>66.27</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>65.48</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>83.01000000000001</v>
+        <v>83.17</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,20 +5557,20 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>32.38</v>
+        <v>32.26</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.47</v>
+        <v>33.42</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.92</v>
+        <v>42.93</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5601,20 +5601,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>126.29</v>
+        <v>126.25</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>123.57</v>
+        <v>123.82</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.75</v>
+        <v>124.8</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.09</v>
+        <v>114.26</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>451.45</v>
+        <v>468.9</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>392.23</v>
+        <v>399.54</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>384.64</v>
+        <v>387.94</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>414.91</v>
+        <v>415.45</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>26.13</v>
+        <v>25.69</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>23.9</v>
+        <v>24.07</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>24.19</v>
+        <v>24.25</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>34.28</v>
+        <v>34.19</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,24 +5733,24 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>545.35</v>
+        <v>544.3</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>544.49</v>
+        <v>544.47</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>571.3200000000001</v>
+        <v>570.26</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>700.71</v>
-      </c>
-      <c r="G115" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>699.24</v>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>123.59</v>
+        <v>122.26</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>121.05</v>
+        <v>121.17</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>127.37</v>
+        <v>127.17</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>165.82</v>
+        <v>165.61</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>454.1</v>
+        <v>459.25</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>414.35</v>
+        <v>418.62</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>405.07</v>
+        <v>407.19</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>431.6</v>
+        <v>431.13</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>376.35</v>
+        <v>366.3</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>331.67</v>
+        <v>334.97</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>332.52</v>
+        <v>333.84</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>351.9</v>
+        <v>352.35</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1202.1</v>
+        <v>1284.1</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1050.48</v>
+        <v>1072.73</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>938.96</v>
+        <v>952.49</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>838.45</v>
+        <v>843.9</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>813.65</v>
+        <v>791.2</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>702.16</v>
+        <v>710.64</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>699.6900000000001</v>
+        <v>703.27</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>756.62</v>
+        <v>758.38</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>204.04</v>
+        <v>200.73</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>191.29</v>
+        <v>192.19</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>194.74</v>
+        <v>194.97</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>219.84</v>
+        <v>219.57</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>250.64</v>
+        <v>244.97</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>237.5</v>
+        <v>238.21</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>223.85</v>
+        <v>224.68</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>200.79</v>
+        <v>201.32</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>935.15</v>
+        <v>946.8</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>885.8099999999999</v>
+        <v>891.62</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>864.9</v>
+        <v>868.12</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>959.15</v>
+        <v>960.49</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1354.9</v>
+        <v>1328.1</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1213.63</v>
+        <v>1224.54</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1157.77</v>
+        <v>1164.45</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1157.47</v>
+        <v>1159.77</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,29 +6173,29 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>172.37</v>
+        <v>168.85</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>166.45</v>
+        <v>166.67</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>170.08</v>
+        <v>170.03</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.41</v>
+        <v>191.44</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H125" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I125" s="13" t="inlineStr">
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14591</v>
+        <v>14493</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>13813.13</v>
+        <v>13877.88</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14097.09</v>
+        <v>14112.61</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14864.82</v>
+        <v>14859.58</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6261,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>144.23</v>
+        <v>142.73</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>130.73</v>
+        <v>131.87</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>132.36</v>
+        <v>132.77</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>162.6</v>
+        <v>162.52</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,24 +6305,24 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>178.37</v>
+        <v>172.53</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>175.09</v>
+        <v>174.84</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>183.76</v>
+        <v>183.32</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>210.87</v>
-      </c>
-      <c r="G128" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>210.63</v>
+      </c>
+      <c r="G128" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>59.07</v>
+        <v>57.41</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>49.74</v>
+        <v>50.47</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>48.26</v>
+        <v>48.62</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>54.8</v>
+        <v>54.93</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>69.16</v>
+        <v>67.11</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>57.45</v>
+        <v>58.37</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>54.95</v>
+        <v>55.42</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.23</v>
+        <v>59.33</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1794.4</v>
+        <v>1786.2</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1711.29</v>
+        <v>1718.42</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1633.31</v>
+        <v>1639.3</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1368</v>
+        <v>1371.96</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1588.25</v>
+        <v>1747.05</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1256.68</v>
+        <v>1303.38</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1108.17</v>
+        <v>1133.22</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1168.14</v>
+        <v>1176.35</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>326.2</v>
+        <v>321.9</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>307.3</v>
+        <v>308.69</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>306.38</v>
+        <v>306.99</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.16</v>
+        <v>326.38</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6550,9 +6550,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I133" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J133" s="14" t="inlineStr">
@@ -6569,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>452.2</v>
+        <v>442.3</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>433.85</v>
+        <v>434.66</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>437.14</v>
+        <v>437.34</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>472.83</v>
+        <v>473.19</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>5279.6</v>
+        <v>5347.5</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>4343.41</v>
+        <v>4439.04</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>3827.96</v>
+        <v>3887.55</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2787.38</v>
+        <v>2814.07</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>319.9</v>
+        <v>323.45</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>332.48</v>
+        <v>331.62</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>344.91</v>
+        <v>344.07</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>363.42</v>
+        <v>362.65</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>102.77</v>
+        <v>110.59</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>95.04000000000001</v>
+        <v>96.52</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>99.8</v>
+        <v>100.23</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>128.7</v>
+        <v>128.53</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1455.5</v>
+        <v>1429.9</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1337.64</v>
+        <v>1346.43</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1328.24</v>
+        <v>1332.23</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1324.31</v>
+        <v>1325.52</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>179.56</v>
+        <v>193.25</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>174.04</v>
+        <v>175.87</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>173.5</v>
+        <v>174.27</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>187.78</v>
+        <v>188.24</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6814,9 +6814,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I139" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J139" s="14" t="inlineStr">
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1762.9</v>
+        <v>1746.1</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1617.87</v>
+        <v>1630.08</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1665.92</v>
+        <v>1669.06</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2010.47</v>
+        <v>2006.19</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>389.1</v>
+        <v>401.8</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>373.5</v>
+        <v>376.2</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>381.69</v>
+        <v>382.48</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>427.52</v>
+        <v>428.61</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>890.7</v>
+        <v>906.25</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>858.3099999999999</v>
+        <v>862.88</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>844.33</v>
+        <v>846.76</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>826.64</v>
+        <v>825.6900000000001</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>385.9</v>
+        <v>385.85</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>341.67</v>
+        <v>345.88</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>336.49</v>
+        <v>338.43</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>346.74</v>
+        <v>347.56</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>204.5</v>
+        <v>199.89</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>193.23</v>
+        <v>193.86</v>
       </c>
       <c r="E144" s="11" t="n">
         <v>199.88</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>236.94</v>
+        <v>236.5</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1658.6</v>
+        <v>1660</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1399.38</v>
+        <v>1424.2</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1343.54</v>
+        <v>1355.95</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1387.7</v>
+        <v>1395.22</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1200.8</v>
+        <v>1185.8</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1133.33</v>
+        <v>1138.32</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1126.53</v>
+        <v>1128.85</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1168.39</v>
+        <v>1169.19</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>77.88</v>
+        <v>77.41</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>74.15000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.26000000000001</v>
+        <v>75.34</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.15000000000001</v>
+        <v>84.28</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>271.56</v>
+        <v>272.16</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>254.91</v>
+        <v>256.55</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>254.35</v>
+        <v>255.05</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>264.4</v>
+        <v>264.58</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7229,17 +7229,17 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>36.29</v>
+        <v>35.54</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>33.53</v>
+        <v>33.72</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>34.29</v>
+        <v>34.33</v>
       </c>
       <c r="F149" s="11" t="n">
         <v>42.32</v>
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>427.55</v>
+        <v>408.25</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>375.23</v>
+        <v>378.37</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>384.8</v>
+        <v>385.72</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>483.67</v>
+        <v>484.33</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>551.95</v>
+        <v>566.8</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>547.0700000000001</v>
+        <v>548.95</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>581.48</v>
+        <v>580.91</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>734.39</v>
+        <v>731.34</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,29 +7361,29 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>148.21</v>
+        <v>144.63</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>140.72</v>
+        <v>141.09</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.79</v>
+        <v>145.74</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>192.2</v>
+        <v>191.8</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H152" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H152" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I152" s="13" t="inlineStr">
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>421.2</v>
+        <v>414.65</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>369.79</v>
+        <v>374.06</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>367.92</v>
+        <v>369.75</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>506.97</v>
+        <v>506.05</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>673.65</v>
+        <v>671.5</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>621.75</v>
+        <v>626.49</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>594.34</v>
+        <v>597.36</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>591.83</v>
+        <v>592.51</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7493,17 +7493,17 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>9.130000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>9.27</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="F155" s="11" t="n">
         <v>10.91</v>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>222.23</v>
+        <v>220.94</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>194</v>
+        <v>196.57</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>200.59</v>
+        <v>201.39</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>241.55</v>
+        <v>242.4</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>186.52</v>
+        <v>185.91</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>173.88</v>
+        <v>175.03</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>168.52</v>
+        <v>169.2</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>163.15</v>
+        <v>163.58</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>136.27</v>
+        <v>137.06</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>121.41</v>
+        <v>122.9</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>122.41</v>
+        <v>122.99</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.43</v>
+        <v>141.48</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>817</v>
+        <v>829.6</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>715.61</v>
+        <v>726.47</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>685.0700000000001</v>
+        <v>690.74</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>671.99</v>
+        <v>674.14</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>28.35</v>
+        <v>28.46</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>26.58</v>
+        <v>26.76</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>26.82</v>
+        <v>26.89</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.24</v>
+        <v>32.26</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,20 +7757,20 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1595.9</v>
+        <v>1582.7</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1548.3</v>
+        <v>1551.58</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1535.78</v>
+        <v>1537.62</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1491.72</v>
+        <v>1494.17</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>881</v>
+        <v>864.05</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>850.46</v>
+        <v>851.76</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>841.6900000000001</v>
+        <v>842.5599999999999</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>928.46</v>
+        <v>929.13</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2491.4</v>
+        <v>2446.2</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2188.74</v>
+        <v>2213.26</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2127.82</v>
+        <v>2140.3</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2363.53</v>
+        <v>2363.69</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>612.35</v>
+        <v>619.15</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>571.28</v>
+        <v>575.84</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>571.38</v>
+        <v>573.25</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>554.6</v>
+        <v>555.76</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,17 +7933,17 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>263.13</v>
+        <v>257.33</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>245.02</v>
+        <v>246.19</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>245.75</v>
+        <v>246.2</v>
       </c>
       <c r="F165" s="11" t="n">
         <v>277.5</v>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>133.23</v>
+        <v>131.46</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>126.93</v>
+        <v>127.36</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>126.72</v>
+        <v>126.9</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>135.5</v>
+        <v>135.06</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3163.3</v>
+        <v>3250.8</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>2994.94</v>
+        <v>3019.31</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>2940.93</v>
+        <v>2953.08</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2722.18</v>
+        <v>2728.49</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2750.7</v>
+        <v>2804.2</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2498.09</v>
+        <v>2527.25</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2440.13</v>
+        <v>2454.41</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2516.21</v>
+        <v>2521.13</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>218.13</v>
+        <v>222.31</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>203.25</v>
+        <v>205.07</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>205.64</v>
+        <v>206.3</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>238.75</v>
+        <v>238.79</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8153,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>197.77</v>
+        <v>192.69</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>189.58</v>
+        <v>189.87</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>191.65</v>
+        <v>191.69</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>245.8</v>
+        <v>246.2</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8197,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>132.69</v>
+        <v>132.16</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>124.13</v>
+        <v>124.89</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>127.15</v>
+        <v>127.35</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>133.77</v>
+        <v>133.89</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>265.96</v>
+        <v>261.6</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>255.15</v>
+        <v>255.76</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>256.08</v>
+        <v>256.29</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>272.37</v>
+        <v>272.62</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>574</v>
+        <v>585.4</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>541.67</v>
+        <v>545.84</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>544.17</v>
+        <v>545.78</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>578.9</v>
+        <v>578.15</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8310,9 +8310,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I173" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J173" s="14" t="inlineStr">
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2454.3</v>
+        <v>2459.8</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2345.8</v>
+        <v>2356.66</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2313.94</v>
+        <v>2319.66</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2399.09</v>
+        <v>2399.57</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>36.07</v>
+        <v>35.7</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>31.91</v>
+        <v>32.27</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>31.94</v>
+        <v>32.09</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.76</v>
+        <v>40.8</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8417,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>10.1</v>
+        <v>9.92</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>8.77</v>
+        <v>8.82</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.859999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8461,24 +8461,24 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>811.2</v>
+        <v>802.05</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>802.5700000000001</v>
+        <v>802.52</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>845.89</v>
+        <v>844.17</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1032.57</v>
-      </c>
-      <c r="G177" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1034.22</v>
+      </c>
+      <c r="G177" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>260.75</v>
+        <v>252.07</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>229.99</v>
+        <v>232.09</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>228.87</v>
+        <v>229.78</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>297.59</v>
+        <v>297.86</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>311.72</v>
+        <v>309.56</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>294.12</v>
+        <v>295.59</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>312.62</v>
+        <v>312.5</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>386.52</v>
+        <v>385.78</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8593,24 +8593,24 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>223.83</v>
+        <v>221.79</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>221.95</v>
+        <v>221.93</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>224.27</v>
+        <v>224.18</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>237.4</v>
-      </c>
-      <c r="G180" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>237.36</v>
+      </c>
+      <c r="G180" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>63.82</v>
+        <v>63.5</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>62.18</v>
+        <v>62.31</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>62.54</v>
+        <v>62.57</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.63</v>
+        <v>67.61</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>518.75</v>
+        <v>513.75</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>489.18</v>
+        <v>491.52</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>509.89</v>
+        <v>510.04</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>683.52</v>
+        <v>683.47</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>421.4</v>
+        <v>411.65</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>385.23</v>
+        <v>387.74</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>362.55</v>
+        <v>364.48</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>339.9</v>
+        <v>341.24</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1545.9</v>
+        <v>1497.7</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1559.58</v>
+        <v>1553.69</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1674.57</v>
+        <v>1667.64</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1977.83</v>
+        <v>1968.27</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8813,20 +8813,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>165.2</v>
+        <v>163.33</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>155.5</v>
+        <v>156.24</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>157.64</v>
+        <v>157.87</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>176.72</v>
+        <v>176.74</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>214</v>
+        <v>209.92</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>201.31</v>
+        <v>202.13</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>201.3</v>
+        <v>201.64</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>193.07</v>
+        <v>193.51</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4580.3</v>
+        <v>4589.8</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4540.81</v>
+        <v>4545.48</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4432.14</v>
+        <v>4438.32</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4581.59</v>
+        <v>4582.83</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8926,9 +8926,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I187" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I187" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J187" s="14" t="inlineStr">
@@ -8945,24 +8945,24 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3500</v>
+        <v>3445.3</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3451.4</v>
+        <v>3450.82</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3596.56</v>
+        <v>3590.63</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4284.88</v>
-      </c>
-      <c r="G188" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>4275.37</v>
+      </c>
+      <c r="G188" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H188" s="13" t="inlineStr">
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2547</v>
+        <v>2525.5</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2281.25</v>
+        <v>2304.51</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2161.1</v>
+        <v>2175.39</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1784.91</v>
+        <v>1796.46</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>329.9</v>
+        <v>323.8</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>317.21</v>
+        <v>317.83</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>314.72</v>
+        <v>315.07</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>333.94</v>
+        <v>334.5</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9077,34 +9077,34 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>1938.9</v>
+        <v>2186.2</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>1984.27</v>
+        <v>2003.5</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2042.77</v>
+        <v>2048.39</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2064.3</v>
-      </c>
-      <c r="G191" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H191" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I191" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2068</v>
+      </c>
+      <c r="G191" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H191" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I191" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J191" s="14" t="inlineStr">
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>564.25</v>
+        <v>554.95</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>527.59</v>
+        <v>530.2</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>546.34</v>
+        <v>546.6799999999999</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>699.49</v>
+        <v>695.84</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9165,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1158.8</v>
+        <v>1111.05</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1048.33</v>
+        <v>1054.3</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1025.43</v>
+        <v>1028.79</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>919.66</v>
+        <v>921.8200000000001</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>880.2</v>
+        <v>855.75</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>827.4299999999999</v>
+        <v>830.12</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>843.1799999999999</v>
+        <v>843.67</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>913.74</v>
+        <v>913.35</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>150.67</v>
+        <v>148.53</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>139.2</v>
+        <v>140.09</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>138.73</v>
+        <v>139.11</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>157.31</v>
+        <v>157.67</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>564.5</v>
+        <v>553.75</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>529.88</v>
+        <v>532.15</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>536.22</v>
+        <v>536.91</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>610.46</v>
+        <v>610.6</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>408.35</v>
+        <v>427.6</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>388.42</v>
+        <v>392.15</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>359.86</v>
+        <v>362.52</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>356.36</v>
+        <v>358.04</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>28.58</v>
+        <v>28.89</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>27.17</v>
+        <v>27.33</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>26.18</v>
+        <v>26.28</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.56</v>
+        <v>27.64</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3591.6</v>
+        <v>3584.6</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3357.7</v>
+        <v>3379.31</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3174.17</v>
+        <v>3190.27</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2828.41</v>
+        <v>2838.01</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>471.85</v>
+        <v>469.65</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>396.84</v>
+        <v>403.77</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>383.4</v>
+        <v>386.79</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>425.41</v>
+        <v>426.43</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>39.85</v>
+        <v>39.15</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>38.31</v>
+        <v>38.39</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>38.63</v>
+        <v>38.65</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.08</v>
+        <v>36.11</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>229.92</v>
+        <v>235.12</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>216.64</v>
+        <v>218.4</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>214.79</v>
+        <v>215.58</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.41</v>
+        <v>223.36</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>218.65</v>
+        <v>219.65</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>187.11</v>
+        <v>190.21</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>187.04</v>
+        <v>188.32</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>226.73</v>
+        <v>226.44</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>290.99</v>
+        <v>276.45</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>229.59</v>
+        <v>234.05</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>192.17</v>
+        <v>195.48</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>139.13</v>
+        <v>140.62</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>1002.05</v>
+        <v>1069</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>970.8200000000001</v>
+        <v>980.17</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>932.5700000000001</v>
+        <v>937.92</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>869.73</v>
+        <v>871.98</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2272.3</v>
+        <v>2310</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2066.59</v>
+        <v>2089.77</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>2002.39</v>
+        <v>2014.45</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2204.38</v>
+        <v>2204.97</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>788.1</v>
+        <v>773.75</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>740.5</v>
+        <v>743.67</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>748.46</v>
+        <v>749.45</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>806.61</v>
+        <v>806.33</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>910.85</v>
+        <v>901.3</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>828.6799999999999</v>
+        <v>835.59</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>848.9</v>
+        <v>850.95</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>1000.11</v>
+        <v>999.99</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>143.54</v>
+        <v>142.88</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>136.87</v>
+        <v>137.44</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>132.11</v>
+        <v>132.53</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.7</v>
+        <v>137.97</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>297.31</v>
+        <v>291.49</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>250.48</v>
+        <v>254.39</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>242.72</v>
+        <v>244.63</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>253.32</v>
+        <v>254.08</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>357.85</v>
+        <v>355.7</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>326.79</v>
+        <v>329.54</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>345.19</v>
+        <v>345.6</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>390.87</v>
+        <v>390.26</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>656</v>
+        <v>663.1</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>622.12</v>
+        <v>626.02</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>635.0700000000001</v>
+        <v>636.17</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>679.86</v>
+        <v>679.64</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>242.35</v>
+        <v>240.72</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>224.72</v>
+        <v>226.24</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>226.08</v>
+        <v>226.65</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>252.54</v>
+        <v>254.38</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,20 +10089,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>802.65</v>
+        <v>806.75</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>776.65</v>
+        <v>779.52</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>797.52</v>
+        <v>797.88</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>904.78</v>
+        <v>904.14</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>140.35</v>
+        <v>139.37</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>129.82</v>
+        <v>130.73</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>135.31</v>
+        <v>135.47</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>148.85</v>
+        <v>148.7</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1062.7</v>
+        <v>1070.45</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>932.55</v>
+        <v>945.6799999999999</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>870.0599999999999</v>
+        <v>877.92</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>712.1</v>
+        <v>716.25</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>418.4</v>
+        <v>410.6</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>387.68</v>
+        <v>389.86</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>395.44</v>
+        <v>396.04</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>484.59</v>
+        <v>483.85</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>115.67</v>
+        <v>117.53</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>108.5</v>
+        <v>109.36</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>107.75</v>
+        <v>108.14</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.37</v>
+        <v>116.53</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10290,9 +10290,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I218" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I218" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J218" s="14" t="inlineStr">
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>500.15</v>
+        <v>500.45</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>460.61</v>
+        <v>464.4</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>460.26</v>
+        <v>461.84</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>527.1900000000001</v>
+        <v>528.35</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10353,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1238</v>
+        <v>1243.7</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1208.61</v>
+        <v>1211.95</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1253.09</v>
+        <v>1252.72</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1569.81</v>
+        <v>1568.3</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10397,24 +10397,24 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1724.5</v>
+        <v>1699.8</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1714.3</v>
+        <v>1712.92</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1732.62</v>
+        <v>1731.33</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1769.39</v>
-      </c>
-      <c r="G221" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1770.61</v>
+      </c>
+      <c r="G221" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H221" s="13" t="inlineStr">
@@ -10441,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>106.33</v>
+        <v>104.76</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>98.42</v>
+        <v>99.02</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>102.18</v>
+        <v>102.28</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>124.15</v>
+        <v>124.2</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,24 +10485,24 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>4022.9</v>
+        <v>3789.4</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3928.62</v>
+        <v>3915.36</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3728.76</v>
+        <v>3731.13</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3062.14</v>
-      </c>
-      <c r="G223" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3068.1</v>
+      </c>
+      <c r="G223" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H223" s="12" t="inlineStr">
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2052.6</v>
+        <v>2157.8</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1870.5</v>
+        <v>1897.86</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1822.45</v>
+        <v>1835.6</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2143.76</v>
+        <v>2153.55</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10554,9 +10554,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I224" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I224" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J224" s="14" t="inlineStr">
@@ -10573,29 +10573,29 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>107.02</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>102.93</v>
+        <v>102.63</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>106.27</v>
+        <v>106.01</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>131.86</v>
-      </c>
-      <c r="G225" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H225" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>131.39</v>
+      </c>
+      <c r="G225" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H225" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I225" s="13" t="inlineStr">
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>395.6</v>
+        <v>395.15</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>385.37</v>
+        <v>386.3</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>391.51</v>
+        <v>391.66</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.1</v>
+        <v>396.12</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>476.55</v>
+        <v>466.7</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>445.72</v>
+        <v>447.72</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>442.31</v>
+        <v>443.27</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>434.54</v>
+        <v>435.36</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>192.54</v>
+        <v>188.13</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>182.27</v>
+        <v>182.83</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>180.38</v>
+        <v>180.69</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>192.76</v>
+        <v>193.25</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>599.6</v>
+        <v>647.7</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>552.1</v>
+        <v>561.21</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>539.73</v>
+        <v>543.96</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>554.84</v>
+        <v>557.05</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>587.25</v>
+        <v>586.75</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>540.98</v>
+        <v>545.34</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>534.21</v>
+        <v>536.28</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>585.9</v>
+        <v>587.85</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10818,9 +10818,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I230" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I230" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J230" s="14" t="inlineStr">
@@ -10837,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>58.49</v>
+        <v>58.51</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>57.24</v>
+        <v>57.36</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>57</v>
+        <v>57.06</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.62</v>
+        <v>52.72</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>998.3</v>
+        <v>1019.65</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>869.29</v>
+        <v>883.61</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>862.5599999999999</v>
+        <v>868.72</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>957.23</v>
+        <v>958.3</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>645.85</v>
+        <v>627.75</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>594.9</v>
+        <v>598.03</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>589.1</v>
+        <v>590.61</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>683.24</v>
+        <v>682.86</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>314.35</v>
+        <v>310.8</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>323.39</v>
+        <v>322.19</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>338.63</v>
+        <v>337.54</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>371.36</v>
+        <v>371.07</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>205.52</v>
+        <v>207.43</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>195.24</v>
+        <v>196.4</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>197.55</v>
+        <v>197.94</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>200.61</v>
+        <v>200.78</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>263.87</v>
+        <v>263.3</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>236.32</v>
+        <v>238.89</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>232.33</v>
+        <v>233.55</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.42</v>
+        <v>249.65</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1488.4</v>
+        <v>1464.8</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1344.67</v>
+        <v>1356.11</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1290.25</v>
+        <v>1297.09</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1333</v>
+        <v>1335.92</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11145,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>223.57</v>
+        <v>222.7</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>212.04</v>
+        <v>213.05</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>215.3</v>
+        <v>215.59</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>227.64</v>
+        <v>227.87</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,29 +11189,29 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>533.8</v>
+        <v>514.4</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>515</v>
+        <v>514.9400000000001</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>524.89</v>
+        <v>524.48</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>557.78</v>
-      </c>
-      <c r="G239" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H239" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>557.0599999999999</v>
+      </c>
+      <c r="G239" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H239" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I239" s="13" t="inlineStr">
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>502.6</v>
+        <v>496.6</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>480.81</v>
+        <v>482.31</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>482.3</v>
+        <v>482.86</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>485.63</v>
+        <v>486.01</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,24 +11277,24 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1312.7</v>
+        <v>1299.2</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1307.31</v>
+        <v>1306.54</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1380.41</v>
+        <v>1377.22</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1549.82</v>
-      </c>
-      <c r="G241" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1546.46</v>
+      </c>
+      <c r="G241" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H241" s="13" t="inlineStr">
@@ -11321,17 +11321,17 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>209.61</v>
+        <v>211.76</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>202.9</v>
+        <v>203.75</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>201.43</v>
+        <v>201.84</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>11051</v>
+        <v>10884.5</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>9525.120000000001</v>
+        <v>9654.58</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>8887.370000000001</v>
+        <v>8965.690000000001</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8202.870000000001</v>
+        <v>8237.75</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1093.35</v>
+        <v>1066.05</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>961.84</v>
+        <v>971.77</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>918.24</v>
+        <v>924.03</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>959.8</v>
+        <v>960.86</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>97.09</v>
+        <v>106.79</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>80.34</v>
+        <v>82.86</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>75.62</v>
+        <v>76.84</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>96.81</v>
+        <v>96.62</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>510.5</v>
+        <v>508.8</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>463.32</v>
+        <v>467.65</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>467.63</v>
+        <v>469.25</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>495.31</v>
+        <v>495.68</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,20 +11541,20 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>484.5</v>
+        <v>481.3</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>464.06</v>
+        <v>465.7</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>476.05</v>
+        <v>476.25</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>565.45</v>
+        <v>563.79</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>740.85</v>
+        <v>756.65</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>715.7</v>
+        <v>719.6</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>691.38</v>
+        <v>693.9400000000001</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>665.84</v>
+        <v>666.4</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>260.46</v>
+        <v>261.67</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>243.76</v>
+        <v>245.47</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>249.39</v>
+        <v>249.87</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>318.35</v>
+        <v>317.89</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>503.25</v>
+        <v>498.85</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>477.38</v>
+        <v>479.42</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>449.28</v>
+        <v>451.22</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>428.64</v>
+        <v>429.44</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>504.45</v>
+        <v>501.55</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>465.99</v>
+        <v>469.38</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>466.93</v>
+        <v>468.28</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>584.1799999999999</v>
+        <v>583.47</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 23-Apr-2026  18:00:15    |    Closing Price Date: 23-Apr-2026</t>
+          <t>Scan Run: 24-Apr-2026  16:42:09    |    Closing Price Date: 24-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>92</v>
+        <v>83.2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>85.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>44</v>
+        <v>40.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>23-Apr-2026  18:00:15</t>
+          <t>24-Apr-2026  16:42:09</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 92.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 83.2% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 85.6% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 76.8% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.8% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 230 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 208 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 214 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 192 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 110 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 102 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>559.25</v>
+        <v>556.2</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>543.71</v>
+        <v>544.9</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>560.02</v>
+        <v>559.87</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>694.73</v>
+        <v>693.1900000000001</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,29 +805,29 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>434.55</v>
+        <v>428.65</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>433.58</v>
+        <v>433.11</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>433.28</v>
+        <v>433.09</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>454.14</v>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>455.07</v>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I3" s="13" t="inlineStr">
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>371.95</v>
+        <v>366.7</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>358.97</v>
+        <v>359.71</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>362.44</v>
+        <v>362.61</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>403.74</v>
+        <v>403.17</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>688.55</v>
+        <v>692.95</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>678.83</v>
+        <v>680.17</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>688.48</v>
+        <v>688.65</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>742.27</v>
+        <v>741.85</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2386.7</v>
+        <v>2395</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2338.84</v>
+        <v>2344.18</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2218.12</v>
+        <v>2225.06</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1798.41</v>
+        <v>1804.35</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>298.65</v>
+        <v>299.05</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>292.33</v>
+        <v>292.97</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>290.79</v>
+        <v>291.11</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>302.2</v>
+        <v>302.02</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1181.4</v>
+        <v>1113.8</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1145.23</v>
+        <v>1142.24</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1078.64</v>
+        <v>1080.02</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>931.45</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>933.8</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>886.25</v>
+        <v>884.4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>798.55</v>
+        <v>806.73</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>797.22</v>
+        <v>800.63</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>868.51</v>
+        <v>867.73</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>531.85</v>
+        <v>527.75</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>485.65</v>
+        <v>489.66</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>491.03</v>
+        <v>492.47</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>560.34</v>
+        <v>560.02</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1061.55</v>
+        <v>1050.05</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1029.02</v>
+        <v>1031.02</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>982.3200000000001</v>
+        <v>984.98</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>957.47</v>
+        <v>960.41</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,29 +1201,29 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>8.74</v>
+        <v>8.77</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>9.08</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17.98</v>
+        <v>17.88</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>561.15</v>
+        <v>558.3</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>502.8</v>
+        <v>508.08</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>489.17</v>
+        <v>491.88</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>499.41</v>
+        <v>500.56</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
         <v>1341</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1286.9</v>
+        <v>1292.06</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1273.94</v>
+        <v>1276.57</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1178.75</v>
+        <v>1180</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>122.3</v>
+        <v>119.04</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>117.21</v>
+        <v>117.38</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>118.32</v>
+        <v>118.35</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>134.64</v>
+        <v>134.82</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>596.85</v>
+        <v>603.3</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>595.48</v>
+        <v>596.22</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>583.5599999999999</v>
+        <v>584.34</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>588.79</v>
+        <v>589.15</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,24 +1421,24 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>456.9</v>
+        <v>449.75</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>452.01</v>
+        <v>451.79</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>447.35</v>
+        <v>447.44</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>470.62</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>471.09</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>388.8</v>
+        <v>382.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>377.07</v>
+        <v>377.59</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>362.26</v>
+        <v>363.06</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>342.31</v>
+        <v>343.16</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>135.87</v>
+        <v>133.05</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>127.47</v>
+        <v>128.01</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>130.96</v>
+        <v>131.04</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>164.32</v>
+        <v>164.12</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1135.55</v>
+        <v>1123.75</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1031.26</v>
+        <v>1040.07</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>989.86</v>
+        <v>995.11</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>962.99</v>
+        <v>964.14</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>860.8</v>
+        <v>831.45</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>861.26</v>
+        <v>858.42</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>882.2</v>
+        <v>880.21</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1076.51</v>
+        <v>1073.07</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1088.5</v>
+        <v>1040.65</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1032.66</v>
+        <v>1033.42</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>993.0700000000001</v>
+        <v>994.9400000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>947.5</v>
+        <v>947.11</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1460.2</v>
+        <v>1421.1</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1359.93</v>
+        <v>1365.75</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1245.89</v>
+        <v>1252.76</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>967.73</v>
+        <v>973.2</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>14.57</v>
+        <v>13.98</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.86</v>
+        <v>14.78</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.26</v>
+        <v>15.21</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>351.21</v>
+        <v>349.34</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>320.41</v>
+        <v>323.17</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>326.4</v>
+        <v>327.3</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>457.03</v>
+        <v>455.05</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>2111</v>
+        <v>2090.2</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1759.72</v>
+        <v>1791.19</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1663.66</v>
+        <v>1680.38</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1612.47</v>
+        <v>1616.81</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>393.5</v>
+        <v>388.6</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>377.34</v>
+        <v>378.41</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>382.09</v>
+        <v>382.34</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>474.25</v>
+        <v>472.97</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1239.95</v>
+        <v>1250.6</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1118.5</v>
+        <v>1131.09</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1101.66</v>
+        <v>1107.5</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1242.28</v>
+        <v>1242.42</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1930,9 +1930,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
@@ -1949,29 +1949,29 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>471</v>
+        <v>460.1</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>462.55</v>
+        <v>462.32</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>466.62</v>
+        <v>466.37</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>542.24</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>540.72</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>614.9</v>
+        <v>606.8</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>588.33</v>
+        <v>590.08</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>592.21</v>
+        <v>592.78</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>607.91</v>
+        <v>607.8</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2018,9 +2018,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>217.6</v>
+        <v>212.76</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>204.68</v>
+        <v>205.45</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>193.35</v>
+        <v>194.11</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>163.83</v>
+        <v>164.32</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2990.5</v>
+        <v>3060.7</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2574.71</v>
+        <v>2621</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2514.57</v>
+        <v>2535.99</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2735.86</v>
+        <v>2735.15</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,29 +2125,29 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>942.25</v>
+        <v>907.9</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>926.6900000000001</v>
+        <v>924.9</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>941.5700000000001</v>
+        <v>940.25</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1071.15</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1068.66</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>616.5</v>
+        <v>597.25</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>596.53</v>
+        <v>596.6</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>596.61</v>
+        <v>596.64</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>581.4400000000001</v>
+        <v>581.62</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>511.05</v>
+        <v>511.25</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>467.26</v>
+        <v>471.45</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>464.68</v>
+        <v>466.51</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>519.5</v>
+        <v>519.17</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1412.8</v>
+        <v>1366.7</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1308.88</v>
+        <v>1314.39</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1316.66</v>
+        <v>1318.62</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2301,24 +2301,24 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>468.6</v>
+        <v>457.2</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>467.44</v>
+        <v>466.47</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>454.68</v>
+        <v>454.78</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>431.21</v>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>431.62</v>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2345,29 +2345,29 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>312.75</v>
+        <v>302.15</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>302.68</v>
+        <v>302.63</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>304.33</v>
+        <v>304.24</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>352.47</v>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>351.86</v>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>384.75</v>
+        <v>382.65</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>388</v>
+        <v>387.49</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>391.2</v>
+        <v>390.86</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>394.56</v>
+        <v>395.06</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1691</v>
+        <v>1694.3</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1776.71</v>
+        <v>1768.86</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1906.29</v>
+        <v>1897.98</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2163.67</v>
+        <v>2160.26</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>324.8</v>
+        <v>326.2</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>298.23</v>
+        <v>300.89</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>286.33</v>
+        <v>287.89</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>273.2</v>
+        <v>273.52</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>422.55</v>
+        <v>427.45</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>419.42</v>
+        <v>420.19</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>435.54</v>
+        <v>435.23</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>518.79</v>
+        <v>517.3099999999999</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>663.95</v>
+        <v>648.6</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>612.39</v>
+        <v>615.84</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>609.97</v>
+        <v>611.48</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>702.54</v>
+        <v>702</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1200.2</v>
+        <v>1136.2</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1216.6</v>
+        <v>1208.95</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1267.3</v>
+        <v>1262.16</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1477.08</v>
+        <v>1474.67</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>381.55</v>
+        <v>373</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>328.56</v>
+        <v>332.79</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>329.98</v>
+        <v>331.67</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>393.64</v>
+        <v>393.63</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>191.89</v>
+        <v>193.37</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>184.36</v>
+        <v>185.22</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>181.22</v>
+        <v>181.7</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>164.68</v>
+        <v>165.04</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>728.6</v>
+        <v>707.4</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>715.51</v>
+        <v>714.74</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723.83</v>
+        <v>723.1799999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>758.47</v>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>757.39</v>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1071.05</v>
+        <v>1062.2</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1009.08</v>
+        <v>1014.14</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1029.73</v>
+        <v>1031.01</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1217.95</v>
+        <v>1218.29</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>159.78</v>
+        <v>161.72</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>143.05</v>
+        <v>144.83</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>137.19</v>
+        <v>138.15</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.62</v>
+        <v>135.61</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>455.45</v>
+        <v>455.05</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>437.69</v>
+        <v>439.34</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>437.42</v>
+        <v>438.11</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>455.32</v>
+        <v>455.4</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2898,9 +2898,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>174.55</v>
+        <v>169.01</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>163.78</v>
+        <v>164.28</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>174.7</v>
+        <v>174.48</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>217.97</v>
+        <v>217.28</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1110.3</v>
+        <v>1092.9</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1063.71</v>
+        <v>1066.49</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1087.64</v>
+        <v>1087.85</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1180.4</v>
+        <v>1179.38</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>11677.5</v>
+        <v>11829.5</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>10297.67</v>
+        <v>10443.56</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>9875.23</v>
+        <v>9951.870000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8755.49</v>
+        <v>8776.26</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>223.21</v>
+        <v>225.84</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>221.7</v>
+        <v>222.09</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>213.75</v>
+        <v>214.22</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>212.29</v>
+        <v>212.19</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.72</v>
+        <v>7.62</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.49</v>
+        <v>7.51</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.4</v>
+        <v>7.41</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.359999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>120.42</v>
+        <v>119.07</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>114.5</v>
+        <v>114.94</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>112.31</v>
+        <v>112.57</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.45</v>
+        <v>109.59</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>106.69</v>
+        <v>103.31</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>101.02</v>
+        <v>101.24</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>99.23999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>113.92</v>
+        <v>113.96</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>78.95999999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>78.87</v>
+        <v>78.91</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>76.33</v>
+        <v>76.44</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.64</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>54.52</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>77.18000000000001</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1256.9</v>
+        <v>1250.1</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1215.8</v>
+        <v>1219.06</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1164.57</v>
+        <v>1167.93</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1155.68</v>
+        <v>1154.46</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>212.04</v>
+        <v>206.61</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>187.34</v>
+        <v>189.17</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>176.54</v>
+        <v>177.72</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>202.1</v>
+        <v>202</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1195.3</v>
+        <v>1202.85</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1069.52</v>
+        <v>1082.22</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1031.46</v>
+        <v>1038.18</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1316.44</v>
+        <v>1317.82</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>65.95</v>
+        <v>65.22</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>61.74</v>
+        <v>62.07</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>61.46</v>
+        <v>61.61</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>62.02</v>
+        <v>62.14</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2692.6</v>
+        <v>2639.7</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2417.55</v>
+        <v>2438.7</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2413.63</v>
+        <v>2422.5</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2586.57</v>
+        <v>2585.73</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>505.55</v>
+        <v>510.05</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>482.64</v>
+        <v>485.25</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>489.03</v>
+        <v>489.85</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>536.59</v>
+        <v>535.9299999999999</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>371.95</v>
+        <v>366.15</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>352.77</v>
+        <v>354.04</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>358.52</v>
+        <v>358.82</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>399.31</v>
+        <v>398.73</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2221.2</v>
+        <v>2175</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2168.62</v>
+        <v>2169.23</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2157.59</v>
+        <v>2158.27</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2067.65</v>
+        <v>2067.8</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4978.7</v>
+        <v>4851.5</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4666.78</v>
+        <v>4684.37</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4501.06</v>
+        <v>4514.8</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4468.82</v>
+        <v>4474.62</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3709,24 +3709,24 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>875.4</v>
+        <v>866.45</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>873.09</v>
+        <v>872.46</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>901.74</v>
+        <v>900.35</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1036.33</v>
-      </c>
-      <c r="G69" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1035.46</v>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>502.35</v>
+        <v>495.65</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>483.45</v>
+        <v>484.61</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>486.19</v>
+        <v>486.56</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>544.89</v>
+        <v>544.02</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>914</v>
+        <v>908.6</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>898.85</v>
+        <v>899.78</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>918.5700000000001</v>
+        <v>918.1799999999999</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1039.86</v>
+        <v>1038.29</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>108.38</v>
+        <v>106</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>105.57</v>
+        <v>105.61</v>
       </c>
       <c r="E72" s="11" t="n">
         <v>105.91</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.29</v>
+        <v>110.2</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>997.75</v>
+        <v>973</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>950.55</v>
+        <v>952.6900000000001</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>939.09</v>
+        <v>940.42</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>942.8200000000001</v>
+        <v>943.38</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>842.5</v>
+        <v>828.7</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>728.45</v>
+        <v>737.99</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>643.65</v>
+        <v>650.9</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>575.3099999999999</v>
+        <v>577.61</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>640.6</v>
+        <v>644.8</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>614.6799999999999</v>
+        <v>617.55</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>640.01</v>
+        <v>640.2</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>751.84</v>
+        <v>750.77</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1033.65</v>
+        <v>1008.5</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>997.5599999999999</v>
+        <v>998.6</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>913.71</v>
+        <v>917.4299999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1041.23</v>
+        <v>1046.71</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>4195.7</v>
+        <v>4035.9</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3870.9</v>
+        <v>3886.61</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3797.64</v>
+        <v>3806.99</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3646.78</v>
+        <v>3651.87</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,24 +4105,24 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>632.45</v>
+        <v>627.1</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>627.71</v>
+        <v>627.65</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>634.49</v>
+        <v>634.2</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>701.37</v>
-      </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>701.39</v>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>57.66</v>
+        <v>57.03</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>56.61</v>
+        <v>56.65</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>56.38</v>
+        <v>56.41</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.03</v>
+        <v>59.02</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>725.8</v>
+        <v>709.05</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>680.8</v>
+        <v>683.49</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>671.92</v>
+        <v>673.38</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>754.47</v>
+        <v>756.45</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>159.6</v>
+        <v>154.81</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>150.26</v>
+        <v>150.69</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>152.43</v>
+        <v>152.53</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>180.64</v>
+        <v>180.26</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>208.26</v>
+        <v>208.87</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>203.41</v>
+        <v>203.93</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>205.41</v>
+        <v>205.54</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>239.35</v>
+        <v>238.99</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>154.96</v>
+        <v>151.37</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>147.33</v>
+        <v>147.72</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>141.11</v>
+        <v>141.52</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>126.52</v>
+        <v>126.72</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>481.95</v>
+        <v>468.45</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>447.64</v>
+        <v>449.63</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>443.87</v>
+        <v>444.83</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>473.78</v>
+        <v>473.65</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4394,9 +4394,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I84" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
@@ -4413,24 +4413,24 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>156.92</v>
+        <v>154.56</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>154.89</v>
+        <v>154.86</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>159.47</v>
+        <v>159.28</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.09</v>
-      </c>
-      <c r="G85" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>161.96</v>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>174.3</v>
+        <v>172.22</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>165.29</v>
+        <v>165.95</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>165.25</v>
+        <v>165.52</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178</v>
+        <v>177.97</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>972.05</v>
+        <v>969.5</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>950.08</v>
+        <v>951.9299999999999</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>989.53</v>
+        <v>988.74</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1083.43</v>
+        <v>1082.68</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4545,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>605.1</v>
+        <v>603.1</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>564.79</v>
+        <v>568.4400000000001</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>572.9</v>
+        <v>574.08</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>773.51</v>
+        <v>772.36</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>570.15</v>
+        <v>569.35</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>558.91</v>
+        <v>559.9</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>570.58</v>
+        <v>570.53</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>608.01</v>
+        <v>607.58</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,20 +4633,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>127.8</v>
+        <v>125.49</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>127.96</v>
+        <v>127.73</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.55</v>
+        <v>130.35</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>136.87</v>
+        <v>136.73</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>361.45</v>
+        <v>355.25</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>339.98</v>
+        <v>341.43</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>344.93</v>
+        <v>345.34</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>403.91</v>
+        <v>403.18</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,29 +4721,29 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>187.13</v>
+        <v>181.1</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>180.23</v>
+        <v>180.31</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>184.71</v>
+        <v>184.57</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>235.82</v>
+        <v>235.06</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H92" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I92" s="13" t="inlineStr">
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>20.61</v>
+        <v>20.05</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>17.83</v>
+        <v>18.04</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>17.63</v>
+        <v>17.73</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.86</v>
+        <v>21.8</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1203.8</v>
+        <v>1148.55</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1072.01</v>
+        <v>1079.3</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1108.27</v>
+        <v>1109.85</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1350.09</v>
+        <v>1344.99</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>317.02</v>
+        <v>320.06</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>295.57</v>
+        <v>297.9</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>298.26</v>
+        <v>299.11</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>305.32</v>
+        <v>305.38</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>47.99</v>
+        <v>46.92</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>45.59</v>
+        <v>45.72</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>45.09</v>
+        <v>45.16</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.15</v>
+        <v>51.12</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>971.65</v>
+        <v>963.25</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>928.16</v>
+        <v>931.5</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>915.02</v>
+        <v>916.91</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>901.27</v>
+        <v>901.34</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>805.9</v>
+        <v>809.7</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>777.26</v>
+        <v>780.35</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>763.12</v>
+        <v>764.95</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>797.72</v>
+        <v>798.28</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1551.6</v>
+        <v>1504.6</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1407.06</v>
+        <v>1416.35</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1334.53</v>
+        <v>1341.2</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1173.95</v>
+        <v>1177.77</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5073,29 +5073,29 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>877.45</v>
+        <v>860.05</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>826.67</v>
+        <v>829.85</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>872.4299999999999</v>
+        <v>871.9400000000001</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1028.02</v>
+        <v>1025.17</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H100" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H100" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I100" s="13" t="inlineStr">
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>267.46</v>
+        <v>263.29</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>259.6</v>
+        <v>259.95</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>260.38</v>
+        <v>260.5</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>272.56</v>
+        <v>273.11</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4188.2</v>
+        <v>4216</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3932.52</v>
+        <v>3959.52</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3790.8</v>
+        <v>3807.47</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3695.11</v>
+        <v>3701.31</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>723.95</v>
+        <v>721.15</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>708.4299999999999</v>
+        <v>709.64</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>701.11</v>
+        <v>701.9</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>760.38</v>
+        <v>759.04</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>177.62</v>
+        <v>176.51</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>160.02</v>
+        <v>161.59</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>162.08</v>
+        <v>162.65</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>177.17</v>
+        <v>176.91</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5274,9 +5274,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I104" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>404.35</v>
+        <v>397.35</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>378.66</v>
+        <v>380.44</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>367.86</v>
+        <v>369.02</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>403.59</v>
+        <v>403.9</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5318,9 +5318,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I105" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1069.55</v>
+        <v>1055.1</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>986.76</v>
+        <v>993.27</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>928.38</v>
+        <v>933.34</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>935.4400000000001</v>
+        <v>936.65</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>521.1</v>
+        <v>515.25</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>493.41</v>
+        <v>495.49</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>506.41</v>
+        <v>506.76</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>578.36</v>
+        <v>578.03</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5425,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>650</v>
+        <v>640.1</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>636.9</v>
+        <v>637.2</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>657.54</v>
+        <v>656.85</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>752.05</v>
+        <v>751.48</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5469,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>381.2</v>
+        <v>371.7</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>356.55</v>
+        <v>358</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>347.62</v>
+        <v>348.57</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.72</v>
+        <v>355.62</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>71.31999999999999</v>
+        <v>71.53</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>66.27</v>
+        <v>66.77</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>65.70999999999999</v>
+        <v>65.94</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>83.17</v>
+        <v>82.97</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,24 +5557,24 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>32.26</v>
+        <v>31.36</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>32.12</v>
+        <v>32.05</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.42</v>
+        <v>33.34</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="G111" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>42.78</v>
+      </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
@@ -5601,29 +5601,29 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>126.25</v>
+        <v>122.99</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>123.82</v>
+        <v>123.74</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.8</v>
+        <v>124.73</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.26</v>
-      </c>
-      <c r="G112" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H112" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>114.32</v>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H112" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I112" s="12" t="inlineStr">
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>468.9</v>
+        <v>459.35</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>399.54</v>
+        <v>405.23</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>387.94</v>
+        <v>390.74</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>415.45</v>
+        <v>415.6</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>25.69</v>
+        <v>24.64</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>24.07</v>
+        <v>24.12</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>24.25</v>
+        <v>24.26</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>34.19</v>
+        <v>34.04</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>544.3</v>
+        <v>527.4</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>544.47</v>
+        <v>542.84</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>570.26</v>
+        <v>568.58</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>699.24</v>
+        <v>697.17</v>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
@@ -5777,24 +5777,24 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>122.26</v>
+        <v>117.93</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>121.17</v>
+        <v>120.86</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>127.17</v>
+        <v>126.81</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>165.61</v>
-      </c>
-      <c r="G116" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>165.02</v>
+      </c>
+      <c r="G116" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>459.25</v>
+        <v>448.9</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>418.62</v>
+        <v>421.51</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>407.19</v>
+        <v>408.83</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>431.13</v>
+        <v>431.74</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>366.3</v>
+        <v>359.9</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>334.97</v>
+        <v>337.34</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>333.84</v>
+        <v>334.86</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>352.35</v>
+        <v>352.67</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1284.1</v>
+        <v>1247.7</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1072.73</v>
+        <v>1089.39</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>952.49</v>
+        <v>964.0700000000001</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>843.9</v>
+        <v>847.63</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>791.2</v>
+        <v>798.15</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>710.64</v>
+        <v>718.98</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>703.27</v>
+        <v>706.99</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>758.38</v>
+        <v>758.75</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>200.73</v>
+        <v>197.15</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>192.19</v>
+        <v>192.67</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>194.97</v>
+        <v>195.06</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>219.57</v>
+        <v>219.32</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>244.97</v>
+        <v>242.04</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>238.21</v>
+        <v>238.57</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>224.68</v>
+        <v>225.36</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>201.32</v>
+        <v>201.57</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>946.8</v>
+        <v>937.15</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>891.62</v>
+        <v>895.95</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>868.12</v>
+        <v>870.8200000000001</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>960.49</v>
+        <v>959.26</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1328.1</v>
+        <v>1337.4</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1224.54</v>
+        <v>1235.29</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1164.45</v>
+        <v>1171.24</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1159.77</v>
+        <v>1162.32</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,24 +6173,24 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>168.85</v>
+        <v>163.63</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>166.67</v>
+        <v>166.38</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>170.03</v>
+        <v>169.78</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.44</v>
-      </c>
-      <c r="G125" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>190.88</v>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H125" s="13" t="inlineStr">
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14493</v>
+        <v>14288</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>13877.88</v>
+        <v>13916.94</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14112.61</v>
+        <v>14119.49</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14859.58</v>
+        <v>14861.35</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6261,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>142.73</v>
+        <v>140.16</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>131.87</v>
+        <v>132.66</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>132.77</v>
+        <v>133.06</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>162.52</v>
+        <v>162.29</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>172.53</v>
+        <v>166.7</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>174.84</v>
+        <v>174.07</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>183.32</v>
+        <v>182.67</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>210.63</v>
+        <v>210.03</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>57.41</v>
+        <v>57.43</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>50.47</v>
+        <v>51.14</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>48.62</v>
+        <v>48.97</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>54.93</v>
+        <v>54.9</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>67.11</v>
+        <v>67.53</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>58.37</v>
+        <v>59.24</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>55.42</v>
+        <v>55.9</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.33</v>
+        <v>59.43</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1786.2</v>
+        <v>1727</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1718.42</v>
+        <v>1719.24</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1639.3</v>
+        <v>1642.74</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1371.96</v>
+        <v>1375.31</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1747.05</v>
+        <v>1654.1</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1303.38</v>
+        <v>1336.78</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1133.22</v>
+        <v>1153.65</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1176.35</v>
+        <v>1181</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>321.9</v>
+        <v>319.1</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>308.69</v>
+        <v>309.68</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>306.99</v>
+        <v>307.47</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.38</v>
+        <v>326.23</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6569,29 +6569,29 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>442.3</v>
+        <v>433.4</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>434.66</v>
+        <v>434.54</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>437.34</v>
+        <v>437.19</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>473.19</v>
-      </c>
-      <c r="G134" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H134" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>472.77</v>
+      </c>
+      <c r="G134" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H134" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I134" s="13" t="inlineStr">
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>5347.5</v>
+        <v>5139.2</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>4439.04</v>
+        <v>4505.72</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>3887.55</v>
+        <v>3936.63</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2814.07</v>
+        <v>2838.14</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>323.45</v>
+        <v>317.9</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>331.62</v>
+        <v>330.31</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>344.07</v>
+        <v>343.04</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>362.65</v>
+        <v>362.56</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>110.59</v>
+        <v>113.53</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>96.52</v>
+        <v>98.14</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>100.23</v>
+        <v>100.75</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>128.53</v>
+        <v>128</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1429.9</v>
+        <v>1411.1</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1346.43</v>
+        <v>1352.58</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1332.23</v>
+        <v>1335.32</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1325.52</v>
+        <v>1327.22</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>193.25</v>
+        <v>190.21</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>175.87</v>
+        <v>177.23</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>174.27</v>
+        <v>174.9</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>188.24</v>
+        <v>188.44</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1746.1</v>
+        <v>1700.1</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1630.08</v>
+        <v>1636.75</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1669.06</v>
+        <v>1670.28</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2006.19</v>
+        <v>2001.06</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>401.8</v>
+        <v>393</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>376.2</v>
+        <v>377.8</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>382.48</v>
+        <v>382.89</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>428.61</v>
+        <v>427.79</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>906.25</v>
+        <v>903.65</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>862.88</v>
+        <v>866.76</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>846.76</v>
+        <v>848.99</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>825.6900000000001</v>
+        <v>827.45</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>385.85</v>
+        <v>375.95</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>345.88</v>
+        <v>348.74</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>338.43</v>
+        <v>339.9</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>347.56</v>
+        <v>348.01</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7009,29 +7009,29 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>199.89</v>
+        <v>194.55</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>193.86</v>
+        <v>193.93</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>199.88</v>
+        <v>199.68</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>236.5</v>
+        <v>236.11</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H144" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H144" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I144" s="13" t="inlineStr">
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1660</v>
+        <v>1634.5</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1424.2</v>
+        <v>1444.23</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1355.95</v>
+        <v>1366.88</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1395.22</v>
+        <v>1394.3</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1185.8</v>
+        <v>1168.6</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1138.32</v>
+        <v>1141.21</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1128.85</v>
+        <v>1130.41</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1169.19</v>
+        <v>1169.9</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7122,9 +7122,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I146" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J146" s="14" t="inlineStr">
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>77.41</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>74.45999999999999</v>
+        <v>74.58</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.34</v>
+        <v>75.36</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.28</v>
+        <v>84.2</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>272.16</v>
+        <v>270.09</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>256.55</v>
+        <v>257.84</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>255.05</v>
+        <v>255.64</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>264.58</v>
+        <v>264.99</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7229,29 +7229,29 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>35.54</v>
+        <v>34.2</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>33.72</v>
+        <v>33.76</v>
       </c>
       <c r="E149" s="11" t="n">
         <v>34.33</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>42.32</v>
+        <v>42.06</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H149" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I149" s="13" t="inlineStr">
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>408.25</v>
+        <v>402.9</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>378.37</v>
+        <v>380.71</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>385.72</v>
+        <v>386.39</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>484.33</v>
+        <v>483.14</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>566.8</v>
+        <v>566.85</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>548.95</v>
+        <v>550.65</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>580.91</v>
+        <v>580.36</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>731.34</v>
+        <v>727.91</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,20 +7361,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>144.63</v>
+        <v>143.57</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>141.09</v>
+        <v>141.33</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.74</v>
+        <v>145.66</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>191.8</v>
+        <v>191.33</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>414.65</v>
+        <v>399.75</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>374.06</v>
+        <v>376.51</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>369.75</v>
+        <v>370.92</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>506.05</v>
+        <v>505</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>671.5</v>
+        <v>666</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>626.49</v>
+        <v>630.25</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>597.36</v>
+        <v>600.05</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>592.51</v>
+        <v>593.04</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.65</v>
+        <v>9.35</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>9.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E155" s="11" t="n">
         <v>9.279999999999999</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.91</v>
+        <v>10.9</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>220.94</v>
+        <v>217.26</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>196.57</v>
+        <v>198.54</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>201.39</v>
+        <v>202.01</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>242.4</v>
+        <v>242</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>185.91</v>
+        <v>183.65</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>175.03</v>
+        <v>175.85</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>169.2</v>
+        <v>169.77</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>163.58</v>
+        <v>163.87</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>137.06</v>
+        <v>133.67</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>122.9</v>
+        <v>123.92</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>122.99</v>
+        <v>123.41</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.48</v>
+        <v>141.58</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>829.6</v>
+        <v>800.55</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>726.47</v>
+        <v>733.52</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>690.74</v>
+        <v>695.05</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>674.14</v>
+        <v>675.16</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>28.46</v>
+        <v>27.7</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>26.76</v>
+        <v>26.85</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>26.89</v>
+        <v>26.92</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.26</v>
+        <v>32.22</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,24 +7757,24 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1582.7</v>
+        <v>1543.7</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1551.58</v>
+        <v>1550.83</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1537.62</v>
+        <v>1537.86</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1494.17</v>
-      </c>
-      <c r="G161" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1497.9</v>
+      </c>
+      <c r="G161" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>864.05</v>
+        <v>889.65</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>851.76</v>
+        <v>855.36</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>842.5599999999999</v>
+        <v>844.41</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>929.13</v>
+        <v>928.6</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2446.2</v>
+        <v>2408.5</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2213.26</v>
+        <v>2231.85</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2140.3</v>
+        <v>2150.82</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2363.69</v>
+        <v>2363.34</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>619.15</v>
+        <v>594.65</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>575.84</v>
+        <v>577.63</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>573.25</v>
+        <v>574.09</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>555.76</v>
+        <v>555.9400000000001</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>257.33</v>
+        <v>262.33</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>246.19</v>
+        <v>247.73</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>246.2</v>
+        <v>246.84</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>277.5</v>
+        <v>277.47</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>131.46</v>
+        <v>134.3</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>127.36</v>
+        <v>128.02</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>126.9</v>
+        <v>127.19</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>135.06</v>
+        <v>134.73</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3250.8</v>
+        <v>3232.6</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>3019.31</v>
+        <v>3039.62</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>2953.08</v>
+        <v>2964.04</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2728.49</v>
+        <v>2734.89</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2804.2</v>
+        <v>2804.9</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2527.25</v>
+        <v>2553.69</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2454.41</v>
+        <v>2468.15</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2521.13</v>
+        <v>2523.4</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>222.31</v>
+        <v>214.26</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>205.07</v>
+        <v>205.94</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>206.3</v>
+        <v>206.61</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>238.79</v>
+        <v>238.55</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8153,29 +8153,29 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>192.69</v>
+        <v>190.14</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>189.87</v>
+        <v>189.9</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>191.69</v>
+        <v>191.63</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>246.2</v>
+        <v>246.18</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H170" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H170" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I170" s="13" t="inlineStr">
@@ -8197,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>132.16</v>
+        <v>128.2</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>124.89</v>
+        <v>125.21</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>127.35</v>
+        <v>127.38</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>133.89</v>
+        <v>133.87</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>261.6</v>
+        <v>256.47</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>255.76</v>
+        <v>255.83</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>256.29</v>
+        <v>256.3</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>272.62</v>
+        <v>272.42</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>585.4</v>
+        <v>589.85</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>545.84</v>
+        <v>550.03</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>545.78</v>
+        <v>547.51</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>578.15</v>
+        <v>578.29</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2459.8</v>
+        <v>2605.8</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2356.66</v>
+        <v>2380.38</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2319.66</v>
+        <v>2330.88</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2399.57</v>
+        <v>2402.18</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>35.7</v>
+        <v>34.25</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>32.27</v>
+        <v>32.46</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>32.09</v>
+        <v>32.17</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.8</v>
+        <v>40.74</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8417,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>9.92</v>
+        <v>9.48</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>9.09</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8442,9 +8442,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I176" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J176" s="14" t="inlineStr">
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>802.05</v>
+        <v>779.7</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>802.52</v>
+        <v>800.35</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>844.17</v>
+        <v>841.64</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1034.22</v>
+        <v>1029.75</v>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>252.07</v>
+        <v>247.71</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>232.09</v>
+        <v>233.58</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>229.78</v>
+        <v>230.48</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>297.86</v>
+        <v>297.07</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>309.56</v>
+        <v>301.19</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>295.59</v>
+        <v>296.13</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>312.5</v>
+        <v>312.05</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>385.78</v>
+        <v>384.73</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8593,20 +8593,20 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
+        <v>220.48</v>
+      </c>
+      <c r="D180" s="11" t="n">
         <v>221.79</v>
       </c>
-      <c r="D180" s="11" t="n">
-        <v>221.93</v>
-      </c>
       <c r="E180" s="11" t="n">
-        <v>224.18</v>
+        <v>224.03</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>237.36</v>
+        <v>236.95</v>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>63.5</v>
+        <v>63.43</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>62.31</v>
+        <v>62.42</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>62.57</v>
+        <v>62.61</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.61</v>
+        <v>67.63</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,29 +8681,29 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>513.75</v>
+        <v>497.6</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>491.52</v>
+        <v>492.1</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>510.04</v>
+        <v>509.55</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>683.47</v>
+        <v>680.28</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H182" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H182" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I182" s="13" t="inlineStr">
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>411.65</v>
+        <v>412.55</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>387.74</v>
+        <v>390.1</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>364.48</v>
+        <v>366.36</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>341.24</v>
+        <v>342.59</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1497.7</v>
+        <v>1470</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1553.69</v>
+        <v>1545.72</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1667.64</v>
+        <v>1659.89</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1968.27</v>
+        <v>1964.58</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8813,20 +8813,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>163.33</v>
+        <v>162.33</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>156.24</v>
+        <v>156.82</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>157.87</v>
+        <v>158.04</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>176.74</v>
+        <v>176.72</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>209.92</v>
+        <v>209.35</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>202.13</v>
+        <v>202.82</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>201.64</v>
+        <v>201.94</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>193.51</v>
+        <v>193.64</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4589.8</v>
+        <v>4595.3</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4545.48</v>
+        <v>4550.22</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4438.32</v>
+        <v>4444.48</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4582.83</v>
+        <v>4582.65</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3445.3</v>
+        <v>3427.6</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3450.82</v>
+        <v>3448.61</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3590.63</v>
+        <v>3584.24</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4275.37</v>
+        <v>4265.37</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2525.5</v>
+        <v>2530.7</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2304.51</v>
+        <v>2326.05</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2175.39</v>
+        <v>2189.33</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1796.46</v>
+        <v>1801.81</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>323.8</v>
+        <v>318.1</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>317.83</v>
+        <v>317.86</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>315.07</v>
+        <v>315.19</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>334.5</v>
+        <v>334.36</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>2186.2</v>
+        <v>2503.1</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>2003.5</v>
+        <v>2051.08</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2048.39</v>
+        <v>2066.22</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2068</v>
+        <v>2071.17</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9121,29 +9121,29 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>554.95</v>
+        <v>545.25</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>530.2</v>
+        <v>531.63</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>546.6799999999999</v>
+        <v>546.62</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>695.84</v>
+        <v>691.86</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H192" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H192" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I192" s="13" t="inlineStr">
@@ -9165,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1111.05</v>
+        <v>1109.65</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1054.3</v>
+        <v>1059.58</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1028.79</v>
+        <v>1031.96</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>921.8200000000001</v>
+        <v>923.71</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>855.75</v>
+        <v>845</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>830.12</v>
+        <v>831.54</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>843.67</v>
+        <v>843.72</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>913.35</v>
+        <v>912.37</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>148.53</v>
+        <v>144.82</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>140.09</v>
+        <v>140.54</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>139.11</v>
+        <v>139.34</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>157.67</v>
+        <v>157.46</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9297,29 +9297,29 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>553.75</v>
+        <v>523.25</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>532.15</v>
+        <v>531.3</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>536.91</v>
+        <v>536.38</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>610.6</v>
-      </c>
-      <c r="G196" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H196" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>610.34</v>
+      </c>
+      <c r="G196" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H196" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I196" s="13" t="inlineStr">
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>427.6</v>
+        <v>413.9</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>392.15</v>
+        <v>394.22</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>362.52</v>
+        <v>364.53</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>358.04</v>
+        <v>358.54</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>28.89</v>
+        <v>27.83</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>27.33</v>
+        <v>27.38</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>26.28</v>
+        <v>26.34</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.64</v>
+        <v>27.68</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3584.6</v>
+        <v>3478.7</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3379.31</v>
+        <v>3388.77</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3190.27</v>
+        <v>3201.58</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2838.01</v>
+        <v>2842.74</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>469.65</v>
+        <v>454.15</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>403.77</v>
+        <v>408.57</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>386.79</v>
+        <v>389.43</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>426.43</v>
+        <v>426.84</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,29 +9517,29 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>39.15</v>
+        <v>38.63</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>38.39</v>
+        <v>38.42</v>
       </c>
       <c r="E201" s="11" t="n">
         <v>38.65</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.11</v>
+        <v>36.16</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H201" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H201" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I201" s="12" t="inlineStr">
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>235.12</v>
+        <v>231.75</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>218.4</v>
+        <v>219.67</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>215.58</v>
+        <v>216.22</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.36</v>
+        <v>223.62</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>219.65</v>
+        <v>213.31</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>190.21</v>
+        <v>192.41</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>188.32</v>
+        <v>189.3</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>226.44</v>
+        <v>226.78</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>276.45</v>
+        <v>266.45</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>234.05</v>
+        <v>237.14</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>195.48</v>
+        <v>198.26</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>140.62</v>
+        <v>141.9</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>1069</v>
+        <v>1066.25</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>980.17</v>
+        <v>988.37</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>937.92</v>
+        <v>942.95</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>871.98</v>
+        <v>873.5599999999999</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2310</v>
+        <v>2331.4</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2089.77</v>
+        <v>2112.78</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>2014.45</v>
+        <v>2026.88</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2204.97</v>
+        <v>2207.56</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>773.75</v>
+        <v>753.45</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>743.67</v>
+        <v>744.6</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>749.45</v>
+        <v>749.61</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>806.33</v>
+        <v>805.87</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>901.3</v>
+        <v>869.55</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>835.59</v>
+        <v>838.83</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>850.95</v>
+        <v>851.6799999999999</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>999.99</v>
+        <v>999.52</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>142.88</v>
+        <v>139.28</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>137.44</v>
+        <v>137.62</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>132.53</v>
+        <v>132.8</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.97</v>
+        <v>137.84</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>291.49</v>
+        <v>287.1</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>254.39</v>
+        <v>257.51</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>244.63</v>
+        <v>246.3</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>254.08</v>
+        <v>254.49</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>355.7</v>
+        <v>350.65</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>329.54</v>
+        <v>331.55</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>345.6</v>
+        <v>345.8</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>390.26</v>
+        <v>390.3</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>663.1</v>
+        <v>642.85</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>626.02</v>
+        <v>627.63</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>636.17</v>
+        <v>636.4299999999999</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>679.64</v>
+        <v>679.29</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>240.72</v>
+        <v>235.58</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>226.24</v>
+        <v>227.13</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>226.65</v>
+        <v>227</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>254.38</v>
+        <v>253.36</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,29 +10089,29 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>806.75</v>
+        <v>794.7</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>779.52</v>
+        <v>780.96</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>797.88</v>
+        <v>797.76</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>904.14</v>
+        <v>903.79</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H214" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H214" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I214" s="13" t="inlineStr">
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>139.37</v>
+        <v>137.41</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>130.73</v>
+        <v>131.37</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>135.47</v>
+        <v>135.55</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>148.7</v>
+        <v>148.62</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1070.45</v>
+        <v>1112.85</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>945.6799999999999</v>
+        <v>961.6</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>877.92</v>
+        <v>887.13</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>716.25</v>
+        <v>720.11</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>410.6</v>
+        <v>397.85</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>389.86</v>
+        <v>390.62</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>396.04</v>
+        <v>396.11</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>483.85</v>
+        <v>483</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>117.53</v>
+        <v>114.35</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>109.36</v>
+        <v>109.83</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>108.14</v>
+        <v>108.38</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.53</v>
+        <v>116.62</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10290,9 +10290,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I218" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I218" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J218" s="14" t="inlineStr">
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>500.45</v>
+        <v>485.8</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>464.4</v>
+        <v>466.44</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>461.84</v>
+        <v>462.78</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>528.35</v>
+        <v>527.38</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10353,24 +10353,24 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1243.7</v>
+        <v>1208.6</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1211.95</v>
+        <v>1211.63</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1252.72</v>
+        <v>1250.99</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1568.3</v>
-      </c>
-      <c r="G220" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1563.58</v>
+      </c>
+      <c r="G220" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H220" s="13" t="inlineStr">
@@ -10397,20 +10397,20 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1699.8</v>
+        <v>1680.1</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1712.92</v>
+        <v>1709.79</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1731.33</v>
+        <v>1729.32</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1770.61</v>
+        <v>1769.63</v>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
@@ -10441,29 +10441,29 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>104.76</v>
+        <v>102.28</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>99.02</v>
+        <v>99.33</v>
       </c>
       <c r="E222" s="11" t="n">
         <v>102.28</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>124.2</v>
+        <v>124.07</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H222" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H222" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I222" s="13" t="inlineStr">
@@ -10485,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>3789.4</v>
+        <v>3799.3</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3915.36</v>
+        <v>3904.31</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3731.13</v>
+        <v>3733.81</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3068.1</v>
+        <v>3075.45</v>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2157.8</v>
+        <v>2108.8</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1897.86</v>
+        <v>1917.95</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1835.6</v>
+        <v>1846.32</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2153.55</v>
+        <v>2149.94</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10554,9 +10554,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I224" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I224" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J224" s="14" t="inlineStr">
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>99.73999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>102.63</v>
+        <v>102.1</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>106.01</v>
+        <v>105.66</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>131.39</v>
+        <v>130.99</v>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
@@ -10617,17 +10617,17 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>395.15</v>
+        <v>395.1</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>386.3</v>
+        <v>387.14</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>391.66</v>
+        <v>391.79</v>
       </c>
       <c r="F226" s="11" t="n">
         <v>396.12</v>
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>466.7</v>
+        <v>455.65</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>447.72</v>
+        <v>448.48</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>443.27</v>
+        <v>443.75</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>435.36</v>
+        <v>435.42</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>188.13</v>
+        <v>184.11</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>182.83</v>
+        <v>182.95</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>180.69</v>
+        <v>180.82</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>193.25</v>
+        <v>193.06</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>647.7</v>
+        <v>665.15</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>561.21</v>
+        <v>571.11</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>543.96</v>
+        <v>548.72</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>557.05</v>
+        <v>557.6</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>586.75</v>
+        <v>576</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>545.34</v>
+        <v>548.26</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>536.28</v>
+        <v>537.83</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>587.85</v>
+        <v>586.17</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10837,29 +10837,29 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>58.51</v>
+        <v>56.79</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>57.36</v>
+        <v>57.31</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>57.06</v>
+        <v>57.05</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.72</v>
-      </c>
-      <c r="G231" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H231" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>52.76</v>
+      </c>
+      <c r="G231" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H231" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I231" s="12" t="inlineStr">
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>1019.65</v>
+        <v>994.9</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>883.61</v>
+        <v>894.21</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>868.72</v>
+        <v>873.66</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>958.3</v>
+        <v>957.58</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>627.75</v>
+        <v>617.35</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>598.03</v>
+        <v>599.87</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>590.61</v>
+        <v>591.66</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>682.86</v>
+        <v>682.45</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>310.8</v>
+        <v>299.3</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>322.19</v>
+        <v>320.01</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>337.54</v>
+        <v>336.04</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>371.07</v>
+        <v>369.1</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>207.43</v>
+        <v>203.06</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>196.4</v>
+        <v>197.03</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>197.94</v>
+        <v>198.14</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>200.78</v>
+        <v>201.11</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>263.3</v>
+        <v>256.21</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>238.89</v>
+        <v>240.54</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>233.55</v>
+        <v>234.44</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.65</v>
+        <v>249.8</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1464.8</v>
+        <v>1493.3</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1356.11</v>
+        <v>1369.17</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1297.09</v>
+        <v>1304.79</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1335.92</v>
+        <v>1340.09</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11145,29 +11145,29 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>222.7</v>
+        <v>215.03</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>213.05</v>
+        <v>213.24</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>215.59</v>
+        <v>215.57</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>227.87</v>
+        <v>227.59</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H238" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H238" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I238" s="13" t="inlineStr">
@@ -11189,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>514.4</v>
+        <v>512.25</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>514.9400000000001</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>524.48</v>
+        <v>524</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>557.0599999999999</v>
+        <v>556.65</v>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>496.6</v>
+        <v>499.95</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>482.31</v>
+        <v>483.99</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>482.86</v>
+        <v>483.53</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>486.01</v>
+        <v>486.29</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1299.2</v>
+        <v>1280.6</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1306.54</v>
+        <v>1304.07</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1377.22</v>
+        <v>1373.44</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1546.46</v>
+        <v>1544.81</v>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
@@ -11321,17 +11321,17 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>211.76</v>
+        <v>207.15</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>203.75</v>
+        <v>204.07</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>201.84</v>
+        <v>202.05</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>10884.5</v>
+        <v>10768.5</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>9654.58</v>
+        <v>9760.67</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>8965.690000000001</v>
+        <v>9036.379999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8237.75</v>
+        <v>8261.59</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1066.05</v>
+        <v>1028.15</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>971.77</v>
+        <v>977.14</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>924.03</v>
+        <v>928.12</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>960.86</v>
+        <v>961.53</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>106.79</v>
+        <v>110.85</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>82.86</v>
+        <v>85.52</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>76.84</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>96.62</v>
+        <v>96.87</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>508.8</v>
+        <v>505.35</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>467.65</v>
+        <v>471.24</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>469.25</v>
+        <v>470.66</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>495.68</v>
+        <v>495.79</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,29 +11541,29 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>481.3</v>
+        <v>462.75</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>465.7</v>
+        <v>465.42</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>476.25</v>
+        <v>475.72</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>563.79</v>
-      </c>
-      <c r="G247" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H247" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>562.84</v>
+      </c>
+      <c r="G247" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H247" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I247" s="13" t="inlineStr">
@@ -11585,24 +11585,24 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>756.65</v>
+        <v>718.3</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>719.6</v>
+        <v>719.48</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>693.9400000000001</v>
+        <v>694.9</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>666.4</v>
-      </c>
-      <c r="G248" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>666.88</v>
+      </c>
+      <c r="G248" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H248" s="12" t="inlineStr">
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>261.67</v>
+        <v>256.26</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>245.47</v>
+        <v>246.49</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>249.87</v>
+        <v>250.12</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>317.89</v>
+        <v>317.25</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>498.85</v>
+        <v>490.85</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>479.42</v>
+        <v>480.51</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>451.22</v>
+        <v>452.78</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>429.44</v>
+        <v>430.3</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>501.55</v>
+        <v>500.85</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>469.38</v>
+        <v>472.37</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>468.28</v>
+        <v>469.56</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>583.47</v>
+        <v>583.4400000000001</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 24-Apr-2026  16:42:09    |    Closing Price Date: 24-Apr-2026</t>
+          <t>Scan Run: 25-Apr-2026  15:57:41    |    Closing Price Date: 24-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>24-Apr-2026  16:42:09</t>
+          <t>25-Apr-2026  15:57:41</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>559.87</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>693.1900000000001</v>
+        <v>693.79</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>433.09</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>455.07</v>
+        <v>455.24</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>362.61</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>403.17</v>
+        <v>403.4</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>688.65</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>741.85</v>
+        <v>742.0599999999999</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>291.11</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>302.02</v>
+        <v>302.2</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>1080.02</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>933.8</v>
+        <v>934.27</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
         <v>806.73</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>800.63</v>
+        <v>800.64</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>867.73</v>
+        <v>868.28</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>984.98</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>960.41</v>
+        <v>960.95</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>9.08</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17.88</v>
+        <v>17.91</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>491.88</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>500.56</v>
+        <v>500.67</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1276.57</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1180</v>
+        <v>1180.58</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>118.35</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>134.82</v>
+        <v>135.03</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>584.34</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>589.15</v>
+        <v>589.37</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>447.44</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>471.09</v>
+        <v>471.14</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>363.06</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>343.16</v>
+        <v>343.49</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131.04</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>164.12</v>
+        <v>164.65</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>995.11</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>964.14</v>
+        <v>965.29</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>880.21</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1073.07</v>
+        <v>1075.86</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>994.9400000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>947.11</v>
+        <v>947.05</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1252.76</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>973.2</v>
+        <v>973.53</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>327.3</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>455.05</v>
+        <v>456</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
         <v>1791.19</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1680.38</v>
+        <v>1680.39</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1616.81</v>
+        <v>1621</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>382.34</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>472.97</v>
+        <v>472.59</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1107.5</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1242.42</v>
+        <v>1242.12</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>466.37</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>540.72</v>
+        <v>541.9400000000001</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>592.78</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>607.8</v>
+        <v>607.8099999999999</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>2535.99</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2735.15</v>
+        <v>2734.88</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>940.25</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1068.66</v>
+        <v>1069.81</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>596.64</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>581.62</v>
+        <v>582.0700000000001</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>466.51</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>519.17</v>
+        <v>519.8</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>454.78</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>431.62</v>
+        <v>432.16</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>304.24</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>351.86</v>
+        <v>351.76</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>390.86</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>395.06</v>
+        <v>395.34</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>1897.98</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2160.26</v>
+        <v>2161.31</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>287.89</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>273.52</v>
+        <v>273.83</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>435.23</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>517.3099999999999</v>
+        <v>517.47</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1262.16</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1474.67</v>
+        <v>1476.22</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>331.67</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>393.63</v>
+        <v>394.09</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>181.7</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>165.04</v>
+        <v>165.11</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>723.1799999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>757.39</v>
+        <v>758.38</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>1031.01</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1218.29</v>
+        <v>1218.81</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>138.15</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.61</v>
+        <v>135.35</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>174.48</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>217.28</v>
+        <v>217.18</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>1087.85</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1179.38</v>
+        <v>1178.64</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>9951.870000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8776.26</v>
+        <v>8776.43</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>214.22</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>212.19</v>
+        <v>212.28</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>7.41</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.34</v>
+        <v>8.33</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>112.57</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.59</v>
+        <v>109.69</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>99.40000000000001</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>113.96</v>
+        <v>114.14</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>76.44</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.54000000000001</v>
+        <v>84.64</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>54.52</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>77.06999999999999</v>
+        <v>77.12</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>1167.93</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1154.46</v>
+        <v>1152.53</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>177.72</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>202</v>
+        <v>202.12</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>1038.18</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1317.82</v>
+        <v>1317.36</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>61.61</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>62.14</v>
+        <v>62.26</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>2422.5</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2585.73</v>
+        <v>2586.57</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>489.85</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>535.9299999999999</v>
+        <v>535.83</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>358.82</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>398.73</v>
+        <v>399.12</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>2158.27</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2067.8</v>
+        <v>2068.05</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>4514.8</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4474.62</v>
+        <v>4473.4</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>900.35</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1035.46</v>
+        <v>1035.83</v>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>486.56</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>544.02</v>
+        <v>543.9</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>918.1799999999999</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1038.29</v>
+        <v>1038.98</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>105.91</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.2</v>
+        <v>110.44</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>940.42</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>943.38</v>
+        <v>943.55</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>650.9</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>577.61</v>
+        <v>577.8</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>917.4299999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1046.71</v>
+        <v>1043.68</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>3806.99</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3651.87</v>
+        <v>3652.03</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>634.2</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>701.39</v>
+        <v>702.13</v>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>56.41</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.02</v>
+        <v>59.04</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>673.38</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>756.45</v>
+        <v>756.59</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>152.53</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>180.26</v>
+        <v>180.84</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>205.54</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>238.99</v>
+        <v>238.81</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>141.52</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>126.72</v>
+        <v>126.86</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>444.83</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>473.65</v>
+        <v>474.4</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>159.28</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>161.96</v>
+        <v>162.05</v>
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>165.52</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>177.97</v>
+        <v>178.12</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>988.74</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1082.68</v>
+        <v>1083.16</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>574.08</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>772.36</v>
+        <v>773.9400000000001</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>570.53</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>607.58</v>
+        <v>607.64</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>130.35</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>136.73</v>
+        <v>136.88</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>345.34</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>403.18</v>
+        <v>403.41</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>184.57</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>235.06</v>
+        <v>235.69</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>17.73</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.8</v>
+        <v>21.84</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>1109.85</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1344.99</v>
+        <v>1348.73</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>299.11</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>305.38</v>
+        <v>305.67</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>916.91</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>901.34</v>
+        <v>901.53</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>764.95</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>798.28</v>
+        <v>798.45</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>1341.2</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1177.77</v>
+        <v>1176.86</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>871.9400000000001</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1025.17</v>
+        <v>1026.16</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>260.5</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>273.11</v>
+        <v>273.09</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>3807.47</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3701.31</v>
+        <v>3703.76</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>701.9</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>759.04</v>
+        <v>760.13</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>162.65</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.91</v>
+        <v>176.98</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>369.02</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>403.9</v>
+        <v>404.58</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>933.34</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>936.65</v>
+        <v>936.9</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>506.76</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>578.03</v>
+        <v>578.5700000000001</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>656.85</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>751.48</v>
+        <v>752.09</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>348.57</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.62</v>
+        <v>355.81</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>65.94</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>82.97</v>
+        <v>82.95</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>33.34</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.78</v>
+        <v>42.85</v>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>124.73</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.32</v>
+        <v>114.41</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>390.74</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>415.6</v>
+        <v>416.32</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>24.26</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>34.04</v>
+        <v>34.29</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>568.58</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>697.17</v>
+        <v>697.29</v>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>126.81</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>165.02</v>
+        <v>165.13</v>
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>408.83</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>431.74</v>
+        <v>431.65</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>334.86</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>352.67</v>
+        <v>352.79</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>964.0700000000001</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>847.63</v>
+        <v>847.79</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>706.99</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>758.75</v>
+        <v>759.39</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>195.06</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>219.32</v>
+        <v>219.33</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>225.36</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>201.57</v>
+        <v>201.68</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>870.8200000000001</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>959.26</v>
+        <v>959.47</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>1171.24</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1162.32</v>
+        <v>1163.48</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>169.78</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>190.88</v>
+        <v>190.7</v>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>14119.49</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14861.35</v>
+        <v>14872.72</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>133.06</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>162.29</v>
+        <v>162.82</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>182.67</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>210.03</v>
+        <v>210.09</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>48.97</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>54.9</v>
+        <v>55.02</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>55.9</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.43</v>
+        <v>59.46</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>1642.74</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1375.31</v>
+        <v>1374.56</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1153.65</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1181</v>
+        <v>1181.46</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>307.47</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.23</v>
+        <v>326.54</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>437.19</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>472.77</v>
+        <v>473.3</v>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>3936.63</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2838.14</v>
+        <v>2838.93</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>343.04</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>362.56</v>
+        <v>362.83</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>100.75</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>128</v>
+        <v>128.37</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>1335.32</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1327.22</v>
+        <v>1328.89</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>174.9</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>188.44</v>
+        <v>188.54</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>1670.28</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2001.06</v>
+        <v>2001.41</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>382.89</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>427.79</v>
+        <v>428.19</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>848.99</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>827.45</v>
+        <v>827.46</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>339.9</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>348.01</v>
+        <v>348.32</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>199.68</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>236.11</v>
+        <v>236.09</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>1366.88</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1394.3</v>
+        <v>1395.91</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>1130.41</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1169.9</v>
+        <v>1170.38</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>75.36</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.2</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>255.64</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>264.99</v>
+        <v>265.69</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>34.33</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>42.06</v>
+        <v>42.04</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>386.39</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>483.14</v>
+        <v>483.18</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>580.36</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>727.91</v>
+        <v>729.34</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>145.66</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>191.33</v>
+        <v>191.35</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>600.05</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>593.04</v>
+        <v>594.45</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>202.01</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>242</v>
+        <v>242.11</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>169.77</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>163.87</v>
+        <v>163.95</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>123.41</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.58</v>
+        <v>141.71</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>695.05</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>675.16</v>
+        <v>675.62</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>26.92</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.22</v>
+        <v>32.27</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>1537.86</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1497.9</v>
+        <v>1500.87</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>844.41</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>928.6</v>
+        <v>929.22</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>2150.82</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2363.34</v>
+        <v>2365.76</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>574.09</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>555.9400000000001</v>
+        <v>555.89</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>246.84</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>277.47</v>
+        <v>277.38</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>127.19</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>134.73</v>
+        <v>134.86</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>2964.04</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2734.89</v>
+        <v>2735.9</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>2468.15</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2523.4</v>
+        <v>2527.84</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>206.61</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>238.55</v>
+        <v>238.87</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>191.63</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>246.18</v>
+        <v>246.51</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>127.38</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>133.87</v>
+        <v>134.01</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>256.3</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>272.42</v>
+        <v>272.59</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>547.51</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>578.29</v>
+        <v>580.74</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>2330.88</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2402.18</v>
+        <v>2402.1</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>32.17</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.74</v>
+        <v>40.78</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>8.84</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>841.64</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1029.75</v>
+        <v>1031.53</v>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>230.48</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>297.07</v>
+        <v>297.38</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>312.05</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>384.73</v>
+        <v>384.71</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>224.03</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>236.95</v>
+        <v>237.28</v>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>62.61</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.63</v>
+        <v>67.66</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>509.55</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>680.28</v>
+        <v>680.59</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>366.36</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>342.59</v>
+        <v>342.67</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>1659.89</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1964.58</v>
+        <v>1962.25</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>158.04</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>176.72</v>
+        <v>176.75</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>201.94</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>193.64</v>
+        <v>193.77</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>4444.48</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4582.65</v>
+        <v>4582.88</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>3584.24</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4265.37</v>
+        <v>4261.86</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>2189.33</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1801.81</v>
+        <v>1803.47</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>315.19</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>334.36</v>
+        <v>334.41</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>2066.22</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2071.17</v>
+        <v>2071.14</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>546.62</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>691.86</v>
+        <v>691.8</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>1031.96</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>923.71</v>
+        <v>923.79</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>843.72</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>912.37</v>
+        <v>913.3</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>139.34</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>157.46</v>
+        <v>157.25</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>536.38</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>610.34</v>
+        <v>610.3</v>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>364.53</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>358.54</v>
+        <v>358.92</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>26.34</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.68</v>
+        <v>27.76</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>3201.58</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2842.74</v>
+        <v>2842.87</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>389.43</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>426.84</v>
+        <v>427.91</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>38.65</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.16</v>
+        <v>36.18</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>216.22</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.62</v>
+        <v>223.85</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>189.3</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>226.78</v>
+        <v>228.22</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>198.26</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>141.9</v>
+        <v>142</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>942.95</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>873.5599999999999</v>
+        <v>873.96</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>2026.88</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2207.56</v>
+        <v>2208.63</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>749.61</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>805.87</v>
+        <v>806.04</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>851.6799999999999</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>999.52</v>
+        <v>1000.05</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>132.8</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.84</v>
+        <v>137.91</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>246.3</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>254.49</v>
+        <v>254.56</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>345.8</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>390.3</v>
+        <v>390.6</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>636.4299999999999</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>679.29</v>
+        <v>679.1900000000001</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>227</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.36</v>
+        <v>253.52</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>797.76</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>903.79</v>
+        <v>903.63</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>135.55</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>148.62</v>
+        <v>148.76</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>887.13</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>720.11</v>
+        <v>720.49</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>108.38</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.62</v>
+        <v>116.92</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>462.78</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>527.38</v>
+        <v>527.5700000000001</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>1250.99</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1563.58</v>
+        <v>1564.47</v>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>1729.32</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1769.63</v>
+        <v>1770.07</v>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>102.28</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>124.07</v>
+        <v>124.91</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>3733.81</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3075.45</v>
+        <v>3075.67</v>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>1846.32</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2149.94</v>
+        <v>2152.22</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>105.66</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>130.99</v>
+        <v>131.1</v>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>391.79</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.12</v>
+        <v>395.95</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>443.75</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>435.42</v>
+        <v>435.96</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>180.82</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>193.06</v>
+        <v>193.61</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>548.72</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>557.6</v>
+        <v>558.08</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>537.83</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>586.17</v>
+        <v>586.41</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>57.05</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.76</v>
+        <v>52.79</v>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>873.66</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>957.58</v>
+        <v>959.45</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>591.66</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>682.45</v>
+        <v>682.74</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>336.04</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>369.1</v>
+        <v>369.28</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>198.14</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>201.11</v>
+        <v>201.45</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>234.44</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.8</v>
+        <v>249.91</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>1304.79</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1340.09</v>
+        <v>1340.23</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>215.57</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>227.59</v>
+        <v>227.91</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>524</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>556.65</v>
+        <v>557.33</v>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>483.53</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>486.29</v>
+        <v>486.25</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>1373.44</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1544.81</v>
+        <v>1547.23</v>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>9036.379999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8261.59</v>
+        <v>8267.639999999999</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>78.18000000000001</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>96.87</v>
+        <v>96.89</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>470.66</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>495.79</v>
+        <v>495.86</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>475.72</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>562.84</v>
+        <v>562.95</v>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>694.9</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>666.88</v>
+        <v>665.63</v>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>250.12</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>317.25</v>
+        <v>318.05</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>452.78</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>430.3</v>
+        <v>430.51</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>469.56</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>583.4400000000001</v>
+        <v>585.23</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 25-Apr-2026  15:57:41    |    Closing Price Date: 24-Apr-2026</t>
+          <t>Scan Run: 26-Apr-2026  16:00:25    |    Closing Price Date: 24-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>25-Apr-2026  15:57:41</t>
+          <t>26-Apr-2026  16:00:25</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>559.87</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>693.79</v>
+        <v>693.05</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>433.09</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>455.24</v>
+        <v>455.31</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>362.61</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>403.4</v>
+        <v>403.41</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>688.65</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>742.0599999999999</v>
+        <v>741.96</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>291.11</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>302.2</v>
+        <v>302.03</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>1080.02</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>934.27</v>
+        <v>932.84</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>800.64</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>868.28</v>
+        <v>868.16</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>984.98</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>960.95</v>
+        <v>961.22</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>9.08</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17.91</v>
+        <v>17.95</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>491.88</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>500.67</v>
+        <v>500.44</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1276.57</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1180.58</v>
+        <v>1180.7</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>118.35</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>135.03</v>
+        <v>135.11</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>584.34</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>589.37</v>
+        <v>589.08</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>447.44</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>471.14</v>
+        <v>471</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>363.06</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>343.49</v>
+        <v>343.44</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131.04</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>164.65</v>
+        <v>164.7</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>995.11</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>965.29</v>
+        <v>965.62</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>880.21</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1075.86</v>
+        <v>1076.29</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>994.9400000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>947.05</v>
+        <v>947.78</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1252.76</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>973.53</v>
+        <v>973.75</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>327.3</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>456</v>
+        <v>455.58</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>1680.39</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1621</v>
+        <v>1621.61</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>382.34</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>472.59</v>
+        <v>472.12</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1107.5</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1242.12</v>
+        <v>1242.25</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>466.37</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>541.9400000000001</v>
+        <v>542.02</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>592.78</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>607.8099999999999</v>
+        <v>607.78</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>2535.99</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2734.88</v>
+        <v>2734.89</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>940.25</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1069.81</v>
+        <v>1070</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>596.64</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>582.0700000000001</v>
+        <v>582.8200000000001</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>466.51</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>519.8</v>
+        <v>519.03</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>454.78</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>432.16</v>
+        <v>432.11</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>304.24</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>351.76</v>
+        <v>351.8</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>390.86</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>395.34</v>
+        <v>395.08</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>1897.98</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2161.31</v>
+        <v>2161.59</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>287.89</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>273.83</v>
+        <v>273.69</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>435.23</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>517.47</v>
+        <v>517.39</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1262.16</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1476.22</v>
+        <v>1475.83</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>331.67</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>394.09</v>
+        <v>393.98</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>181.7</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>165.11</v>
+        <v>165.16</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>723.1799999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>758.38</v>
+        <v>758.55</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>1031.01</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1218.81</v>
+        <v>1219.37</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>138.15</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.35</v>
+        <v>135.6</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>438.11</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>455.4</v>
+        <v>455.51</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>174.48</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>217.18</v>
+        <v>216.92</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>1087.85</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1178.64</v>
+        <v>1177.58</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>9951.870000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8776.43</v>
+        <v>8782.120000000001</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>214.22</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>212.28</v>
+        <v>211.96</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>99.40000000000001</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.14</v>
+        <v>114.17</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>76.44</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.64</v>
+        <v>84.63</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>54.52</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>77.12</v>
+        <v>77.81</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>1167.93</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1152.53</v>
+        <v>1151.9</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>177.72</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>202.12</v>
+        <v>201.96</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>1038.18</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1317.36</v>
+        <v>1317.11</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>61.61</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>62.26</v>
+        <v>62.23</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>2422.5</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2586.57</v>
+        <v>2587.4</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>489.85</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>535.83</v>
+        <v>535.25</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>358.82</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>399.12</v>
+        <v>399.01</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>2158.27</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2068.05</v>
+        <v>2067.69</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>4514.8</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4473.4</v>
+        <v>4472.22</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>900.35</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1035.83</v>
+        <v>1036.03</v>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>486.56</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>543.9</v>
+        <v>544.91</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>918.1799999999999</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1038.98</v>
+        <v>1038.9</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>105.91</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.44</v>
+        <v>110.55</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>940.42</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>943.55</v>
+        <v>944.08</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>650.9</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>577.8</v>
+        <v>577.71</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>917.4299999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1043.68</v>
+        <v>1043.51</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>3806.99</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3652.03</v>
+        <v>3651.01</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>634.2</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>702.13</v>
+        <v>702.74</v>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>56.41</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.04</v>
+        <v>59.07</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>673.38</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>756.59</v>
+        <v>756.6</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>152.53</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>180.84</v>
+        <v>180.69</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>205.54</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>238.81</v>
+        <v>239.14</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>444.83</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>474.4</v>
+        <v>474.9</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>159.28</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.05</v>
+        <v>162.01</v>
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>165.52</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178.12</v>
+        <v>178.73</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>988.74</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1083.16</v>
+        <v>1082.76</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>574.08</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>773.9400000000001</v>
+        <v>774.13</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>570.53</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>607.64</v>
+        <v>607.62</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>345.34</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>403.41</v>
+        <v>403.27</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>184.57</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>235.69</v>
+        <v>235.5</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>17.73</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.84</v>
+        <v>21.88</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>1109.85</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1348.73</v>
+        <v>1349.42</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>299.11</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>305.67</v>
+        <v>305.46</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>45.16</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.12</v>
+        <v>51.14</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>916.91</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>901.53</v>
+        <v>902.73</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>764.95</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>798.45</v>
+        <v>798.6900000000001</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>1341.2</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1176.86</v>
+        <v>1176.9</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>871.9400000000001</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1026.16</v>
+        <v>1025.21</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>260.5</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>273.09</v>
+        <v>273.82</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>3807.47</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3703.76</v>
+        <v>3702.25</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>701.9</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>760.13</v>
+        <v>759.8200000000001</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>162.65</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.98</v>
+        <v>176.83</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>369.02</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>404.58</v>
+        <v>404.55</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>933.34</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>936.9</v>
+        <v>936.3200000000001</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>506.76</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>578.5700000000001</v>
+        <v>578.12</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>656.85</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>752.09</v>
+        <v>751.64</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>348.57</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.81</v>
+        <v>355.7</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>65.94</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>82.95</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>33.34</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.85</v>
+        <v>42.95</v>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>124.73</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.41</v>
+        <v>114.4</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>24.26</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>34.29</v>
+        <v>34.12</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>568.58</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>697.29</v>
+        <v>698.0599999999999</v>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>126.81</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>165.13</v>
+        <v>165.11</v>
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>408.83</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>431.65</v>
+        <v>431.3</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>334.86</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>352.79</v>
+        <v>352.71</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>964.0700000000001</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>847.79</v>
+        <v>848.72</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>706.99</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>759.39</v>
+        <v>759.54</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>195.06</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>219.33</v>
+        <v>219.37</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>225.36</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>201.68</v>
+        <v>201.59</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>870.8200000000001</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>959.47</v>
+        <v>959.49</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>1171.24</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1163.48</v>
+        <v>1162.66</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>169.78</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>190.7</v>
+        <v>191.2</v>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>14119.49</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14872.72</v>
+        <v>14864.77</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>133.06</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>162.82</v>
+        <v>162.67</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>182.67</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>210.09</v>
+        <v>210.13</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>48.97</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55.02</v>
+        <v>55.05</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>55.9</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.46</v>
+        <v>59.51</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>1642.74</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1374.56</v>
+        <v>1374.54</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1153.65</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1181.46</v>
+        <v>1182.98</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>307.47</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.54</v>
+        <v>326.5</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>437.19</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>473.3</v>
+        <v>473.66</v>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>3936.63</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2838.93</v>
+        <v>2840.81</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>343.04</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>362.83</v>
+        <v>362.88</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>100.75</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>128.37</v>
+        <v>128.73</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>1335.32</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1328.89</v>
+        <v>1329.97</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>174.9</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>188.54</v>
+        <v>188.41</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>1670.28</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2001.41</v>
+        <v>2001.78</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>382.89</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>428.19</v>
+        <v>428.48</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>848.99</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>827.46</v>
+        <v>826.88</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>339.9</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>348.32</v>
+        <v>349.1</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>199.68</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>236.09</v>
+        <v>236</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>1366.88</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1395.91</v>
+        <v>1393.44</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>1130.41</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1170.38</v>
+        <v>1170.65</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>75.36</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.29000000000001</v>
+        <v>84.34</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>255.64</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>265.69</v>
+        <v>265.96</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>34.33</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>42.04</v>
+        <v>42.03</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>386.39</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>483.18</v>
+        <v>482.83</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>580.36</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>729.34</v>
+        <v>729.03</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>145.66</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>191.35</v>
+        <v>191.4</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>600.05</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>594.45</v>
+        <v>594.65</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>202.01</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>242.11</v>
+        <v>242.3</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>169.77</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>163.95</v>
+        <v>163.88</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>123.41</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.71</v>
+        <v>141.84</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>695.05</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>675.62</v>
+        <v>676.67</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>26.92</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.27</v>
+        <v>32.31</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>1537.86</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1500.87</v>
+        <v>1500.29</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>844.41</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>929.22</v>
+        <v>928.63</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>2150.82</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2365.76</v>
+        <v>2363.46</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>574.09</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>555.89</v>
+        <v>556.01</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>246.84</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>277.38</v>
+        <v>277.32</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>127.19</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>134.86</v>
+        <v>135.03</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>2964.04</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2735.9</v>
+        <v>2738.5</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>2468.15</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2527.84</v>
+        <v>2526.51</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>191.63</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>246.51</v>
+        <v>246.94</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>127.38</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>134.01</v>
+        <v>134.02</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>256.3</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>272.59</v>
+        <v>272.62</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>547.51</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>580.74</v>
+        <v>579.63</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>2330.88</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2402.1</v>
+        <v>2400.49</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>32.17</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.78</v>
+        <v>40.79</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>8.84</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>841.64</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1031.53</v>
+        <v>1032.06</v>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>230.48</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>297.38</v>
+        <v>297.71</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>312.05</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>384.71</v>
+        <v>384.82</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>224.03</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>237.28</v>
+        <v>237.18</v>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>62.61</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.66</v>
+        <v>67.72</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>509.55</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>680.59</v>
+        <v>680.6799999999999</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>366.36</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>342.67</v>
+        <v>342.13</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>1659.89</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1962.25</v>
+        <v>1963.14</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>201.94</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>193.77</v>
+        <v>193.76</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>4444.48</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4582.88</v>
+        <v>4583.03</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>3584.24</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4261.86</v>
+        <v>4261.64</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>2189.33</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1803.47</v>
+        <v>1802.71</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>315.19</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>334.41</v>
+        <v>333.99</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>2066.22</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2071.14</v>
+        <v>2070.22</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>546.62</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>691.8</v>
+        <v>689.4</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>1031.96</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>923.79</v>
+        <v>923.84</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>843.72</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>913.3</v>
+        <v>911.86</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>139.34</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>157.25</v>
+        <v>157.31</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>536.38</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>610.3</v>
+        <v>609.9</v>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>364.53</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>358.92</v>
+        <v>359.18</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>26.34</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.76</v>
+        <v>27.74</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>3201.58</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2842.87</v>
+        <v>2842.69</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>389.43</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>427.91</v>
+        <v>428.12</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>216.22</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.85</v>
+        <v>223.75</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>189.3</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>228.22</v>
+        <v>226.22</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>198.26</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>142</v>
+        <v>142.11</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>942.95</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>873.96</v>
+        <v>873.9</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>2026.88</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2208.63</v>
+        <v>2206.62</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>749.61</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>806.04</v>
+        <v>805.92</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>851.6799999999999</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>1000.05</v>
+        <v>999.41</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>132.8</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.91</v>
+        <v>137.94</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>246.3</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>254.56</v>
+        <v>254.68</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>345.8</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>390.6</v>
+        <v>392.04</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>636.4299999999999</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>679.1900000000001</v>
+        <v>680.34</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>227</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.52</v>
+        <v>253.58</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>797.76</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>903.63</v>
+        <v>904.96</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>135.55</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>148.76</v>
+        <v>148.63</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>887.13</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>720.49</v>
+        <v>720.3</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>108.38</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.92</v>
+        <v>116.84</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>462.78</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>527.5700000000001</v>
+        <v>527.65</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>1250.99</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1564.47</v>
+        <v>1564.39</v>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>1729.32</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1770.07</v>
+        <v>1770.28</v>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>3733.81</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3075.67</v>
+        <v>3075.86</v>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>1846.32</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2152.22</v>
+        <v>2152.35</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>105.66</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>131.1</v>
+        <v>131.26</v>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>391.79</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>395.95</v>
+        <v>396.48</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>443.75</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>435.96</v>
+        <v>435.94</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>180.82</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>193.61</v>
+        <v>193.34</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>548.72</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>558.08</v>
+        <v>557.78</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>537.83</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>586.41</v>
+        <v>586.03</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>873.66</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>959.45</v>
+        <v>961.04</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>591.66</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>682.74</v>
+        <v>682.04</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>336.04</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>369.28</v>
+        <v>369.31</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>198.14</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>201.45</v>
+        <v>201.54</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>234.44</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.91</v>
+        <v>249.86</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>1304.79</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1340.23</v>
+        <v>1341.28</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>215.57</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>227.91</v>
+        <v>227.95</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>524</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>557.33</v>
+        <v>557.09</v>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>483.53</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>486.25</v>
+        <v>486.06</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>1373.44</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1547.23</v>
+        <v>1547.86</v>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>9036.379999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8267.639999999999</v>
+        <v>8262.200000000001</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>78.18000000000001</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>96.89</v>
+        <v>96.75</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>470.66</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>495.86</v>
+        <v>496.09</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>475.72</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>562.95</v>
+        <v>562.35</v>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>694.9</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>665.63</v>
+        <v>664.9</v>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>250.12</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>318.05</v>
+        <v>317.86</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>452.78</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>430.51</v>
+        <v>430.11</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>469.56</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>585.23</v>
+        <v>585.71</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 26-Apr-2026  16:00:25    |    Closing Price Date: 24-Apr-2026</t>
+          <t>Scan Run: 27-Apr-2026  17:53:31    |    Closing Price Date: 27-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>83.2</v>
+        <v>94</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>76.8</v>
+        <v>86</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>40.8</v>
+        <v>47.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>26-Apr-2026  16:00:25</t>
+          <t>27-Apr-2026  17:53:31</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 83.2% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 94.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 76.8% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 86.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.8% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 47.6% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 208 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 235 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 192 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 215 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 102 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 119 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,29 +761,29 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>556.2</v>
+        <v>564.9</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>544.9</v>
+        <v>546.8</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>559.87</v>
+        <v>560.0700000000001</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>693.05</v>
+        <v>692.0599999999999</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
@@ -805,29 +805,29 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>428.65</v>
+        <v>435.55</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>433.11</v>
+        <v>433.34</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>433.09</v>
+        <v>433.19</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>455.31</v>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>455.26</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I3" s="13" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>366.7</v>
+        <v>381.8</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>359.71</v>
+        <v>361.81</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>362.61</v>
+        <v>363.36</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>403.41</v>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>692.95</v>
+        <v>712.75</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>680.17</v>
+        <v>683.28</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>688.65</v>
+        <v>689.6</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>741.96</v>
+        <v>742.62</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2395</v>
+        <v>2494.6</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2344.18</v>
+        <v>2358.51</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2225.06</v>
+        <v>2235.63</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1804.35</v>
+        <v>1811.21</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>299.05</v>
+        <v>330.55</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>292.97</v>
+        <v>296.55</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>291.11</v>
+        <v>292.66</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>302.03</v>
+        <v>302.33</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1006,9 +1006,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J7" s="14" t="inlineStr">
@@ -1025,24 +1025,24 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1113.8</v>
+        <v>1154.5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1142.24</v>
+        <v>1143.4</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1080.02</v>
+        <v>1082.94</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>932.84</v>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>937.8200000000001</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>884.4</v>
+        <v>871.4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>806.73</v>
+        <v>812.89</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>800.64</v>
+        <v>803.41</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>868.16</v>
+        <v>867.72</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>527.75</v>
+        <v>521.3</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>489.66</v>
+        <v>492.67</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>492.47</v>
+        <v>493.6</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>560.02</v>
+        <v>559.63</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1050.05</v>
+        <v>1044.95</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1031.02</v>
+        <v>1032.35</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>984.98</v>
+        <v>987.33</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>961.22</v>
+        <v>962.95</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,29 +1201,29 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>8.77</v>
+        <v>8.81</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.08</v>
+        <v>9.09</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17.95</v>
+        <v>17.82</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>558.3</v>
+        <v>554.55</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>508.08</v>
+        <v>512.51</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>491.88</v>
+        <v>494.34</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>500.44</v>
+        <v>501.18</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1341</v>
+        <v>1334.5</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1292.06</v>
+        <v>1296.1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1276.57</v>
+        <v>1278.85</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1180.7</v>
+        <v>1182.49</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>119.04</v>
+        <v>123.49</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>117.38</v>
+        <v>117.97</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>118.35</v>
+        <v>118.55</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>135.11</v>
+        <v>135.06</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>603.3</v>
+        <v>601.9</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>596.22</v>
+        <v>596.76</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>584.34</v>
+        <v>585.03</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>589.08</v>
+        <v>589.05</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,24 +1421,24 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>449.75</v>
+        <v>452.65</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>451.79</v>
+        <v>451.88</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>447.44</v>
+        <v>447.65</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>471</v>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>470.98</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>382.5</v>
+        <v>390.7</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>377.59</v>
+        <v>378.83</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>363.06</v>
+        <v>364.14</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>343.44</v>
+        <v>343.8</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>133.05</v>
+        <v>136.79</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>128.01</v>
+        <v>128.84</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>131.04</v>
+        <v>131.27</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>164.7</v>
+        <v>164.2</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1123.75</v>
+        <v>1138.35</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1040.07</v>
+        <v>1049.43</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>995.11</v>
+        <v>1000.73</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>965.62</v>
+        <v>967.61</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,24 +1597,24 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>831.45</v>
+        <v>879.05</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>858.42</v>
+        <v>860.38</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>880.21</v>
+        <v>880.17</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1076.29</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1074.34</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1040.65</v>
+        <v>1083.35</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1033.42</v>
+        <v>1038.18</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>994.9400000000001</v>
+        <v>998.4</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>947.78</v>
+        <v>949.5700000000001</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1421.1</v>
+        <v>1426.2</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1365.75</v>
+        <v>1371.51</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1252.76</v>
+        <v>1259.56</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>973.75</v>
+        <v>978.38</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>13.98</v>
+        <v>14.05</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.78</v>
+        <v>14.71</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.21</v>
+        <v>15.17</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>349.34</v>
+        <v>350.05</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>323.17</v>
+        <v>325.73</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>327.3</v>
+        <v>328.19</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>455.58</v>
+        <v>454.76</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>2090.2</v>
+        <v>2237.1</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1791.19</v>
+        <v>1833.66</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1680.39</v>
+        <v>1702.22</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1621.61</v>
+        <v>1627.43</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>388.6</v>
+        <v>397.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>378.41</v>
+        <v>380.2</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>382.34</v>
+        <v>382.93</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>472.12</v>
+        <v>470.66</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1250.6</v>
+        <v>1306.9</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1131.09</v>
+        <v>1147.83</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1107.5</v>
+        <v>1115.32</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1242.25</v>
+        <v>1244.59</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,29 +1949,29 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>460.1</v>
+        <v>483.25</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>462.32</v>
+        <v>464.31</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>466.37</v>
+        <v>467.03</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>542.02</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>541.34</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>606.8</v>
+        <v>624.55</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>590.08</v>
+        <v>593.37</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>592.78</v>
+        <v>594.02</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>607.78</v>
+        <v>608.36</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2018,9 +2018,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>212.76</v>
+        <v>216.78</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>205.45</v>
+        <v>206.53</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>194.11</v>
+        <v>195</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>164.32</v>
+        <v>164.84</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3060.7</v>
+        <v>3216.4</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2621</v>
+        <v>2677.7</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2535.99</v>
+        <v>2562.67</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2734.89</v>
+        <v>2739.32</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,29 +2125,29 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>907.9</v>
+        <v>942.1</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>924.9</v>
+        <v>926.54</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>940.25</v>
+        <v>940.3200000000001</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1070</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1068.4</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>597.25</v>
+        <v>618.75</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>596.6</v>
+        <v>598.71</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>596.64</v>
+        <v>597.5</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>582.8200000000001</v>
+        <v>583.48</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>511.25</v>
+        <v>516.8</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>471.45</v>
+        <v>475.77</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>466.51</v>
+        <v>468.48</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>519.03</v>
+        <v>518.59</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1366.7</v>
+        <v>1420.7</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1314.39</v>
+        <v>1324.52</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1318.62</v>
+        <v>1322.63</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2301,24 +2301,24 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>457.2</v>
+        <v>483.8</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>466.47</v>
+        <v>468.12</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>454.78</v>
+        <v>455.92</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>432.11</v>
-      </c>
-      <c r="G37" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>432.48</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>302.15</v>
+        <v>304.2</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>302.63</v>
+        <v>302.78</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>304.24</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>351.8</v>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>351.05</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -2389,34 +2389,34 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>382.65</v>
+        <v>396.6</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>387.49</v>
+        <v>388.36</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>390.86</v>
+        <v>391.09</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>395.08</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>395.12</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1694.3</v>
+        <v>1718.2</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1768.86</v>
+        <v>1764.04</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1897.98</v>
+        <v>1890.93</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2161.59</v>
+        <v>2158.09</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>326.2</v>
+        <v>337.35</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>300.89</v>
+        <v>304.37</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>287.89</v>
+        <v>289.83</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>273.69</v>
+        <v>274.37</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>427.45</v>
+        <v>428</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>420.19</v>
+        <v>420.93</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>435.23</v>
+        <v>434.94</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>517.39</v>
+        <v>516.72</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>648.6</v>
+        <v>662.5</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>615.84</v>
+        <v>620.28</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>611.48</v>
+        <v>613.48</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>702</v>
+        <v>701.61</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1136.2</v>
+        <v>1187.8</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1208.95</v>
+        <v>1206.93</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1262.16</v>
+        <v>1259.25</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1475.83</v>
+        <v>1473.11</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>373</v>
+        <v>400.1</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>332.79</v>
+        <v>339.2</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>331.67</v>
+        <v>334.35</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>393.98</v>
+        <v>394.11</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2678,9 +2678,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>193.37</v>
+        <v>190.92</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>185.22</v>
+        <v>185.76</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>181.7</v>
+        <v>182.06</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>165.16</v>
+        <v>165.42</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,24 +2741,24 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>707.4</v>
+        <v>722.65</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>714.74</v>
+        <v>715.49</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723.1799999999999</v>
+        <v>723.16</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>758.55</v>
-      </c>
-      <c r="G47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>759.5599999999999</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1062.2</v>
+        <v>1071.95</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1014.14</v>
+        <v>1019.64</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1031.01</v>
+        <v>1032.61</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1219.37</v>
+        <v>1219.41</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>161.72</v>
+        <v>165.59</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>144.83</v>
+        <v>146.8</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>138.15</v>
+        <v>139.23</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>135.6</v>
+        <v>136.16</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>455.05</v>
+        <v>467.25</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>439.34</v>
+        <v>442</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>438.11</v>
+        <v>439.25</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>455.51</v>
+        <v>455.88</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2898,9 +2898,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
@@ -2917,29 +2917,29 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>169.01</v>
+        <v>174.8</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>164.28</v>
+        <v>165.28</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>174.48</v>
+        <v>174.49</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>216.92</v>
+        <v>217.04</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I51" s="13" t="inlineStr">
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1092.9</v>
+        <v>1103.6</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1066.49</v>
+        <v>1070.03</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1087.85</v>
+        <v>1088.47</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1177.58</v>
+        <v>1176.73</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>11829.5</v>
+        <v>12417</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>10443.56</v>
+        <v>10631.51</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>9951.870000000001</v>
+        <v>10048.54</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8782.120000000001</v>
+        <v>8823.34</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>225.84</v>
+        <v>229.34</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>222.09</v>
+        <v>222.78</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>214.22</v>
+        <v>214.82</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>211.96</v>
+        <v>212.15</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3093,17 +3093,17 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.62</v>
+        <v>7.92</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.51</v>
+        <v>7.55</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.41</v>
+        <v>7.43</v>
       </c>
       <c r="F55" s="11" t="n">
         <v>8.33</v>
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>119.07</v>
+        <v>123.07</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>114.94</v>
+        <v>115.71</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>112.57</v>
+        <v>112.98</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.69</v>
+        <v>109.98</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>103.31</v>
+        <v>110.51</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>101.24</v>
+        <v>102.12</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>99.40000000000001</v>
+        <v>99.84</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.17</v>
+        <v>114.19</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>79.29000000000001</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>78.91</v>
+        <v>79.56</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>76.44</v>
+        <v>76.81</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.63</v>
+        <v>84.69</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3250,9 +3250,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
@@ -3269,20 +3269,20 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>47.7</v>
+        <v>46.28</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>48.91</v>
+        <v>48.66</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>54.52</v>
+        <v>54.2</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>77.81</v>
+        <v>78.09</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1250.1</v>
+        <v>1242.6</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1219.06</v>
+        <v>1221.3</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1167.93</v>
+        <v>1170.85</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1151.9</v>
+        <v>1154.63</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>206.61</v>
+        <v>209.46</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>189.17</v>
+        <v>191.11</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>177.72</v>
+        <v>178.97</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>201.96</v>
+        <v>202.03</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1202.85</v>
+        <v>1231.9</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1082.22</v>
+        <v>1096.47</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1038.18</v>
+        <v>1045.78</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1317.11</v>
+        <v>1317.76</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>65.22</v>
+        <v>67.34</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>62.07</v>
+        <v>62.58</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>61.61</v>
+        <v>61.83</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>62.23</v>
+        <v>62.26</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2639.7</v>
+        <v>2625.8</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2438.7</v>
+        <v>2456.52</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2422.5</v>
+        <v>2430.47</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2587.4</v>
+        <v>2591.16</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>510.05</v>
+        <v>507.9</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>485.25</v>
+        <v>487.4</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>489.85</v>
+        <v>490.56</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>535.25</v>
+        <v>535.11</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>366.15</v>
+        <v>367.05</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>354.04</v>
+        <v>355.28</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>358.82</v>
+        <v>359.15</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>399.01</v>
+        <v>398.57</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2175</v>
+        <v>2211.4</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2169.23</v>
+        <v>2173.25</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2158.27</v>
+        <v>2160.35</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2067.69</v>
+        <v>2069.95</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4851.5</v>
+        <v>4883.7</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4684.37</v>
+        <v>4703.35</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4514.8</v>
+        <v>4529.27</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4472.22</v>
+        <v>4480.48</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3709,24 +3709,24 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>866.45</v>
+        <v>881.4</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>872.46</v>
+        <v>873.3099999999999</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>900.35</v>
+        <v>899.61</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1036.03</v>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1034.66</v>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>495.65</v>
+        <v>513.35</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>484.61</v>
+        <v>487.35</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>486.56</v>
+        <v>487.61</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>544.91</v>
+        <v>545.75</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>908.6</v>
+        <v>915.15</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>899.78</v>
+        <v>901.24</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>918.1799999999999</v>
+        <v>918.0599999999999</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1038.9</v>
+        <v>1037.39</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>106</v>
+        <v>109.14</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>105.61</v>
+        <v>105.94</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>105.91</v>
+        <v>106.04</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.55</v>
+        <v>110.58</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>973</v>
+        <v>1013.5</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>952.6900000000001</v>
+        <v>958.48</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>940.42</v>
+        <v>943.29</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>944.08</v>
+        <v>944.99</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>828.7</v>
+        <v>872.55</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>737.99</v>
+        <v>750.8099999999999</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>650.9</v>
+        <v>659.59</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>577.71</v>
+        <v>581.12</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>644.8</v>
+        <v>662.65</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>617.55</v>
+        <v>621.84</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>640.2</v>
+        <v>641.08</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>750.77</v>
+        <v>749.9</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1008.5</v>
+        <v>1059.15</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>998.6</v>
+        <v>1004.37</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>917.4299999999999</v>
+        <v>922.99</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1043.51</v>
+        <v>1041.53</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4042,9 +4042,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>4035.9</v>
+        <v>4038</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3886.61</v>
+        <v>3901.03</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3806.99</v>
+        <v>3816.05</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3651.01</v>
+        <v>3656.5</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,24 +4105,24 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>627.1</v>
+        <v>631.4</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>627.65</v>
+        <v>628.01</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>634.2</v>
+        <v>634.09</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>702.74</v>
-      </c>
-      <c r="G78" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>701.62</v>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>57.03</v>
+        <v>57.9</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>56.65</v>
+        <v>56.77</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>56.41</v>
+        <v>56.47</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.07</v>
+        <v>59.13</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>709.05</v>
+        <v>724.55</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>683.49</v>
+        <v>687.4</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>673.38</v>
+        <v>675.39</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>756.6</v>
+        <v>756.95</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>154.81</v>
+        <v>164.17</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>150.69</v>
+        <v>151.97</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>152.53</v>
+        <v>152.98</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>180.69</v>
+        <v>181.25</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>208.87</v>
+        <v>211.23</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>203.93</v>
+        <v>204.62</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>205.54</v>
+        <v>205.77</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>239.14</v>
+        <v>238.84</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>151.37</v>
+        <v>152.81</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>147.72</v>
+        <v>148.2</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>141.52</v>
+        <v>141.96</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>126.86</v>
+        <v>127.55</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>468.45</v>
+        <v>474.85</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>449.63</v>
+        <v>452.03</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>444.83</v>
+        <v>446.01</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>474.9</v>
+        <v>474.82</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4394,9 +4394,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I84" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
@@ -4413,24 +4413,24 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>154.56</v>
+        <v>157.61</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>154.86</v>
+        <v>155.12</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>159.28</v>
+        <v>159.21</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.01</v>
-      </c>
-      <c r="G85" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>162.08</v>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>172.22</v>
+        <v>174.9</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>165.95</v>
+        <v>166.8</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>165.52</v>
+        <v>165.89</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178.73</v>
+        <v>178.8</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,29 +4501,29 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>969.5</v>
+        <v>993</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>951.9299999999999</v>
+        <v>955.84</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>988.74</v>
+        <v>988.91</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1082.76</v>
+        <v>1083.58</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H87" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr">
@@ -4545,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>603.1</v>
+        <v>613.85</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>568.4400000000001</v>
+        <v>572.77</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>574.08</v>
+        <v>575.64</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>774.13</v>
+        <v>771.66</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4589,29 +4589,29 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>569.35</v>
+        <v>577.45</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>559.9</v>
+        <v>561.5700000000001</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>570.53</v>
+        <v>570.8</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>607.62</v>
+        <v>607.96</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H89" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
@@ -4633,24 +4633,24 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>125.49</v>
+        <v>129.02</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>127.73</v>
+        <v>127.85</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.35</v>
+        <v>130.3</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>136.88</v>
-      </c>
-      <c r="G90" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>137.03</v>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>355.25</v>
+        <v>360.2</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>341.43</v>
+        <v>343.22</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>345.34</v>
+        <v>345.92</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>403.27</v>
+        <v>403.83</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,29 +4721,29 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>181.1</v>
+        <v>189.15</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>180.31</v>
+        <v>181.15</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>184.57</v>
+        <v>184.75</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>235.5</v>
+        <v>235.64</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H92" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I92" s="13" t="inlineStr">
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>20.05</v>
+        <v>20.71</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>18.04</v>
+        <v>18.3</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>17.73</v>
+        <v>17.85</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1148.55</v>
+        <v>1189.4</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1079.3</v>
+        <v>1089.78</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1109.85</v>
+        <v>1112.97</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1349.42</v>
+        <v>1348.86</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>320.06</v>
+        <v>320.08</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>297.9</v>
+        <v>300.02</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>299.11</v>
+        <v>299.93</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>305.46</v>
+        <v>305.83</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>46.92</v>
+        <v>47.7</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>45.72</v>
+        <v>45.9</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>45.16</v>
+        <v>45.26</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.14</v>
+        <v>51.19</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>963.25</v>
+        <v>970.05</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>931.5</v>
+        <v>935.1799999999999</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>916.91</v>
+        <v>919</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>902.73</v>
+        <v>905.17</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>809.7</v>
+        <v>819.8</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>780.35</v>
+        <v>784.11</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>764.95</v>
+        <v>767.1</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>798.6900000000001</v>
+        <v>798.83</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1504.6</v>
+        <v>1521.9</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1416.35</v>
+        <v>1426.4</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1341.2</v>
+        <v>1348.28</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1176.9</v>
+        <v>1179.49</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>860.05</v>
+        <v>869.7</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>829.85</v>
+        <v>833.65</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>871.9400000000001</v>
+        <v>871.85</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1025.21</v>
+        <v>1024.69</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>263.29</v>
+        <v>267.94</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>259.95</v>
+        <v>260.71</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>260.5</v>
+        <v>260.79</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>273.82</v>
+        <v>273.39</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4216</v>
+        <v>4234.2</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3959.52</v>
+        <v>3985.68</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3807.47</v>
+        <v>3824.2</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3702.25</v>
+        <v>3709.17</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>721.15</v>
+        <v>718.05</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>709.64</v>
+        <v>710.4400000000001</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>701.9</v>
+        <v>702.53</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>759.8200000000001</v>
+        <v>758.77</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>176.51</v>
+        <v>182.11</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>161.59</v>
+        <v>163.55</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>162.65</v>
+        <v>163.41</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.83</v>
+        <v>177.27</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5274,9 +5274,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I104" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>397.35</v>
+        <v>408.4</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>380.44</v>
+        <v>383.1</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>369.02</v>
+        <v>370.56</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>404.55</v>
+        <v>404.63</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5318,9 +5318,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1055.1</v>
+        <v>1094.65</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>993.27</v>
+        <v>1002.92</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>933.34</v>
+        <v>939.67</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>936.3200000000001</v>
+        <v>940.22</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>515.25</v>
+        <v>516.6</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>495.49</v>
+        <v>497.5</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>506.76</v>
+        <v>507.15</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>578.12</v>
+        <v>578.3</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5425,29 +5425,29 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>640.1</v>
+        <v>657.6</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>637.2</v>
+        <v>639.14</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>656.85</v>
+        <v>656.88</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>751.64</v>
+        <v>751.15</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H108" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H108" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I108" s="13" t="inlineStr">
@@ -5469,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>371.7</v>
+        <v>374.15</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>358</v>
+        <v>359.54</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>348.57</v>
+        <v>349.57</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.7</v>
+        <v>356.97</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>71.53</v>
+        <v>78.16</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>66.77</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>65.94</v>
+        <v>66.42</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>83.01000000000001</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,24 +5557,24 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>31.36</v>
+        <v>33.06</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.34</v>
+        <v>33.33</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.95</v>
-      </c>
-      <c r="G111" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>43.07</v>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
@@ -5601,24 +5601,24 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>122.99</v>
+        <v>124.51</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>123.74</v>
+        <v>123.82</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.73</v>
+        <v>124.72</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="G112" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>114.55</v>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H112" s="13" t="inlineStr">
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>459.35</v>
+        <v>477.1</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>405.23</v>
+        <v>412.08</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>390.74</v>
+        <v>394.13</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>416.32</v>
+        <v>416.81</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>24.64</v>
+        <v>26.33</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>24.12</v>
+        <v>24.33</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>24.26</v>
+        <v>24.34</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>34.12</v>
+        <v>33.99</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>527.4</v>
+        <v>536.65</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>542.84</v>
+        <v>542.25</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>568.58</v>
+        <v>567.33</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>698.0599999999999</v>
+        <v>697.6799999999999</v>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
@@ -5777,24 +5777,24 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>117.93</v>
+        <v>122.29</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>120.86</v>
+        <v>120.99</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>126.81</v>
+        <v>126.63</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>165.11</v>
-      </c>
-      <c r="G116" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>164.69</v>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>448.9</v>
+        <v>461.15</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>421.51</v>
+        <v>425.28</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>408.83</v>
+        <v>410.88</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>431.3</v>
+        <v>431.65</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>359.9</v>
+        <v>376.6</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>337.34</v>
+        <v>341.08</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>334.86</v>
+        <v>336.5</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>352.71</v>
+        <v>353.07</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1247.7</v>
+        <v>1328.35</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1089.39</v>
+        <v>1112.15</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>964.0700000000001</v>
+        <v>978.36</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>848.72</v>
+        <v>856.78</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>798.15</v>
+        <v>799.8</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>718.98</v>
+        <v>726.67</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>706.99</v>
+        <v>710.63</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>759.54</v>
+        <v>760.28</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>197.15</v>
+        <v>201.29</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>192.67</v>
+        <v>193.49</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>195.06</v>
+        <v>195.3</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>219.37</v>
+        <v>219.21</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>242.04</v>
+        <v>254.32</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>238.57</v>
+        <v>240.07</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>225.36</v>
+        <v>226.49</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>201.59</v>
+        <v>202.29</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>937.15</v>
+        <v>927.05</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>895.95</v>
+        <v>898.91</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>870.8200000000001</v>
+        <v>873.03</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>959.49</v>
+        <v>959.27</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1337.4</v>
+        <v>1448.3</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1235.29</v>
+        <v>1255.57</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1171.24</v>
+        <v>1182.1</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1162.66</v>
+        <v>1162.76</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>163.63</v>
+        <v>165.91</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>166.38</v>
+        <v>166.34</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>169.78</v>
+        <v>169.63</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.2</v>
+        <v>191.48</v>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14288</v>
+        <v>14509</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>13916.94</v>
+        <v>13973.33</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14119.49</v>
+        <v>14134.77</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14864.77</v>
+        <v>14872.33</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6261,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>140.16</v>
+        <v>148.79</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>132.66</v>
+        <v>134.2</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>133.06</v>
+        <v>133.67</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>162.67</v>
+        <v>162.81</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>166.7</v>
+        <v>169.59</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>174.07</v>
+        <v>173.64</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>182.67</v>
+        <v>182.15</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>210.13</v>
+        <v>209.71</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>57.43</v>
+        <v>58.95</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>51.14</v>
+        <v>51.88</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>48.97</v>
+        <v>49.36</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55.05</v>
+        <v>55.21</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>67.53</v>
+        <v>69.31</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>59.24</v>
+        <v>60.2</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>55.9</v>
+        <v>56.42</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.51</v>
+        <v>59.7</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1727</v>
+        <v>1747.6</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1719.24</v>
+        <v>1721.94</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1642.74</v>
+        <v>1646.86</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1374.54</v>
+        <v>1378.43</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1654.1</v>
+        <v>1657.2</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1336.78</v>
+        <v>1367.3</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1153.65</v>
+        <v>1173.4</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1182.98</v>
+        <v>1190.48</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>319.1</v>
+        <v>324.15</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>309.68</v>
+        <v>311.06</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>307.47</v>
+        <v>308.12</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.5</v>
+        <v>326.36</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6569,29 +6569,29 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>433.4</v>
+        <v>447.15</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>434.54</v>
+        <v>435.74</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>437.19</v>
+        <v>437.58</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>473.66</v>
-      </c>
-      <c r="G134" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H134" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>473.54</v>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I134" s="13" t="inlineStr">
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>5139.2</v>
+        <v>5303</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>4505.72</v>
+        <v>4581.65</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>3936.63</v>
+        <v>3990.21</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2840.81</v>
+        <v>2866.24</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>317.9</v>
+        <v>327.15</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>330.31</v>
+        <v>330.01</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>343.04</v>
+        <v>342.42</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>362.88</v>
+        <v>362.47</v>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>113.53</v>
+        <v>116.47</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>98.14</v>
+        <v>99.88</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>100.75</v>
+        <v>101.37</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>128.73</v>
+        <v>128.24</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1411.1</v>
+        <v>1440.5</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1352.58</v>
+        <v>1360.96</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1335.32</v>
+        <v>1339.45</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1329.97</v>
+        <v>1332.08</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>190.21</v>
+        <v>192.12</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>177.23</v>
+        <v>178.65</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>174.9</v>
+        <v>175.57</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>188.41</v>
+        <v>188.57</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1700.1</v>
+        <v>1735.7</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1636.75</v>
+        <v>1646.18</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1670.28</v>
+        <v>1672.84</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2001.78</v>
+        <v>1996.89</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>393</v>
+        <v>401.3</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>377.8</v>
+        <v>380.04</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>382.89</v>
+        <v>383.62</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>428.48</v>
+        <v>428.83</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>903.65</v>
+        <v>899.95</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>866.76</v>
+        <v>869.92</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>848.99</v>
+        <v>850.99</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>826.88</v>
+        <v>826.39</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>375.95</v>
+        <v>382.15</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>348.74</v>
+        <v>351.93</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>339.9</v>
+        <v>341.55</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>349.1</v>
+        <v>349.53</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>194.55</v>
+        <v>199.29</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>193.93</v>
+        <v>194.44</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>199.68</v>
+        <v>199.66</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>236</v>
+        <v>235.73</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1634.5</v>
+        <v>1654</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1444.23</v>
+        <v>1464.21</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1366.88</v>
+        <v>1378.14</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1393.44</v>
+        <v>1401.07</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1168.6</v>
+        <v>1216.5</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1141.21</v>
+        <v>1148.38</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1130.41</v>
+        <v>1133.79</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1170.65</v>
+        <v>1171.2</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7122,9 +7122,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I146" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I146" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J146" s="14" t="inlineStr">
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>75.76000000000001</v>
+        <v>76.91</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>74.58</v>
+        <v>74.8</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.36</v>
+        <v>75.42</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.34</v>
+        <v>84.25</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>270.09</v>
+        <v>270.67</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>257.84</v>
+        <v>259.06</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>255.64</v>
+        <v>256.23</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>265.96</v>
+        <v>266.47</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7229,29 +7229,29 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>34.2</v>
+        <v>35.37</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>33.76</v>
+        <v>33.92</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>34.33</v>
+        <v>34.37</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>42.03</v>
+        <v>41.99</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H149" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H149" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I149" s="13" t="inlineStr">
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>402.9</v>
+        <v>413.75</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>380.71</v>
+        <v>383.86</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>386.39</v>
+        <v>387.47</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>482.83</v>
+        <v>483.12</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,29 +7317,29 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>566.85</v>
+        <v>585.25</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>550.65</v>
+        <v>553.95</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>580.36</v>
+        <v>580.55</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>729.03</v>
+        <v>728.5599999999999</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H151" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H151" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I151" s="13" t="inlineStr">
@@ -7361,29 +7361,29 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>143.57</v>
+        <v>148.01</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>141.33</v>
+        <v>141.96</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.66</v>
+        <v>145.75</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>191.4</v>
+        <v>190.99</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H152" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H152" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I152" s="13" t="inlineStr">
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>399.75</v>
+        <v>414</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>376.51</v>
+        <v>380.08</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>370.92</v>
+        <v>372.61</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>505</v>
+        <v>504.09</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>666</v>
+        <v>674.85</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>630.25</v>
+        <v>634.5</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>600.05</v>
+        <v>602.99</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>594.65</v>
+        <v>594.34</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.35</v>
+        <v>9.51</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>9.279999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>217.26</v>
+        <v>217.99</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>198.54</v>
+        <v>200.39</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>202.01</v>
+        <v>202.64</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>242.3</v>
+        <v>242.16</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>183.65</v>
+        <v>195.2</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>175.85</v>
+        <v>177.69</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>169.77</v>
+        <v>170.77</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>163.88</v>
+        <v>164.43</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>133.67</v>
+        <v>135.91</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>123.92</v>
+        <v>125.06</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>123.41</v>
+        <v>123.9</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.84</v>
+        <v>141.7</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>800.55</v>
+        <v>808.1</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>733.52</v>
+        <v>740.63</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>695.05</v>
+        <v>699.48</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>676.67</v>
+        <v>678.8099999999999</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>27.7</v>
+        <v>27.96</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>26.85</v>
+        <v>26.96</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>26.92</v>
+        <v>26.96</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,24 +7757,24 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1543.7</v>
+        <v>1572.3</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1550.83</v>
+        <v>1552.87</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1537.86</v>
+        <v>1539.21</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1500.29</v>
-      </c>
-      <c r="G161" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1488.22</v>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>889.65</v>
+        <v>915.95</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>855.36</v>
+        <v>861.13</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>844.41</v>
+        <v>847.22</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>928.63</v>
+        <v>929.51</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2408.5</v>
+        <v>2497.8</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2231.85</v>
+        <v>2257.18</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2150.82</v>
+        <v>2164.43</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2363.46</v>
+        <v>2363.09</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>594.65</v>
+        <v>600</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>577.63</v>
+        <v>579.76</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>574.09</v>
+        <v>575.1</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>556.01</v>
+        <v>556.33</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>262.33</v>
+        <v>274.18</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>247.73</v>
+        <v>250.25</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>246.84</v>
+        <v>247.91</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>277.32</v>
+        <v>277.25</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>134.3</v>
+        <v>133.9</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>128.02</v>
+        <v>128.58</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>127.19</v>
+        <v>127.46</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>135.03</v>
+        <v>134.91</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3232.6</v>
+        <v>3261.4</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>3039.62</v>
+        <v>3060.74</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>2964.04</v>
+        <v>2975.7</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2738.5</v>
+        <v>2744.7</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2804.9</v>
+        <v>2857.4</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2553.69</v>
+        <v>2582.61</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2468.15</v>
+        <v>2483.42</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2526.51</v>
+        <v>2533.42</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>214.26</v>
+        <v>218.32</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>205.94</v>
+        <v>207.12</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>206.61</v>
+        <v>207.07</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>238.87</v>
+        <v>238.76</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8153,29 +8153,29 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>190.14</v>
+        <v>198.76</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>189.9</v>
+        <v>190.74</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>191.63</v>
+        <v>191.91</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>246.94</v>
+        <v>246.2</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H170" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H170" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I170" s="13" t="inlineStr">
@@ -8197,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>128.2</v>
+        <v>131.04</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>125.21</v>
+        <v>125.76</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>127.38</v>
+        <v>127.53</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>134.02</v>
+        <v>134.06</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>256.47</v>
+        <v>261.27</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>255.83</v>
+        <v>256.35</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>256.3</v>
+        <v>256.5</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>272.62</v>
+        <v>271.65</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>589.85</v>
+        <v>592.5</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>550.03</v>
+        <v>554.0700000000001</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>547.51</v>
+        <v>549.28</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>579.63</v>
+        <v>580.35</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2605.8</v>
+        <v>2693.9</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2380.38</v>
+        <v>2410.24</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2330.88</v>
+        <v>2345.12</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2400.49</v>
+        <v>2404.08</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>34.25</v>
+        <v>36.13</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>32.46</v>
+        <v>32.81</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>32.17</v>
+        <v>32.33</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.79</v>
+        <v>40.8</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8417,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>9.48</v>
+        <v>10.15</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>9.130000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>8.84</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.880000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8442,9 +8442,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I176" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J176" s="14" t="inlineStr">
@@ -8461,24 +8461,24 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>779.7</v>
+        <v>812</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>800.35</v>
+        <v>801.46</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>841.64</v>
+        <v>840.48</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1032.06</v>
-      </c>
-      <c r="G177" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1032.98</v>
+      </c>
+      <c r="G177" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>247.71</v>
+        <v>256.32</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>233.58</v>
+        <v>235.75</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>230.48</v>
+        <v>231.49</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>297.71</v>
+        <v>296.27</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>301.19</v>
+        <v>308.29</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>296.13</v>
+        <v>297.29</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>312.05</v>
+        <v>311.91</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>384.82</v>
+        <v>384.02</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8593,24 +8593,24 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>220.48</v>
+        <v>223.01</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>221.79</v>
+        <v>221.91</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>224.03</v>
+        <v>223.99</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>237.18</v>
-      </c>
-      <c r="G180" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>237.05</v>
+      </c>
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>63.43</v>
+        <v>64.14</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>62.42</v>
+        <v>62.58</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>62.61</v>
+        <v>62.67</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.72</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,29 +8681,29 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>497.6</v>
+        <v>531.6</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>492.1</v>
+        <v>495.86</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>509.55</v>
+        <v>510.41</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>680.6799999999999</v>
+        <v>679.13</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H182" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H182" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I182" s="13" t="inlineStr">
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>412.55</v>
+        <v>422.4</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>390.1</v>
+        <v>393.18</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>366.36</v>
+        <v>368.56</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>342.13</v>
+        <v>342.86</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1470</v>
+        <v>1472.1</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1545.72</v>
+        <v>1538.71</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1659.89</v>
+        <v>1652.52</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1963.14</v>
+        <v>1958.39</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8813,20 +8813,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>162.33</v>
+        <v>163.93</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>156.82</v>
+        <v>157.5</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>158.04</v>
+        <v>158.27</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>176.75</v>
+        <v>177.02</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>209.35</v>
+        <v>216.26</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>202.82</v>
+        <v>204.1</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>201.94</v>
+        <v>202.5</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>193.76</v>
+        <v>194.04</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4595.3</v>
+        <v>4646.1</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4550.22</v>
+        <v>4559.35</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4444.48</v>
+        <v>4452.39</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4583.03</v>
+        <v>4582.92</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3427.6</v>
+        <v>3431.2</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3448.61</v>
+        <v>3446.95</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3584.24</v>
+        <v>3578.23</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4261.64</v>
+        <v>4251.91</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2530.7</v>
+        <v>2602.4</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2326.05</v>
+        <v>2352.37</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2189.33</v>
+        <v>2205.52</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1802.71</v>
+        <v>1809.51</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>318.1</v>
+        <v>323.05</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>317.86</v>
+        <v>318.35</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>315.19</v>
+        <v>315.5</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>333.99</v>
+        <v>333.75</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>2503.1</v>
+        <v>2422.6</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>2051.08</v>
+        <v>2086.47</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2066.22</v>
+        <v>2080.2</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2070.22</v>
+        <v>2075.44</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9121,29 +9121,29 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>545.25</v>
+        <v>565.05</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>531.63</v>
+        <v>534.8099999999999</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>546.62</v>
+        <v>547.35</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>689.4</v>
+        <v>690.4400000000001</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H192" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H192" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I192" s="13" t="inlineStr">
@@ -9165,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1109.65</v>
+        <v>1124.7</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1059.58</v>
+        <v>1065.78</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1031.96</v>
+        <v>1035.6</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>923.84</v>
+        <v>922.78</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>845</v>
+        <v>872.45</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>831.54</v>
+        <v>835.4400000000001</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>843.72</v>
+        <v>844.85</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>911.86</v>
+        <v>911.29</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>144.82</v>
+        <v>146.61</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>140.54</v>
+        <v>141.12</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>139.34</v>
+        <v>139.62</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>157.31</v>
+        <v>157.26</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>523.25</v>
+        <v>525.35</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>531.3</v>
+        <v>530.74</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>536.38</v>
+        <v>535.9400000000001</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>609.9</v>
+        <v>608.4</v>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>413.9</v>
+        <v>415.2</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>394.22</v>
+        <v>396.22</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>364.53</v>
+        <v>366.52</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>359.18</v>
+        <v>360.38</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>27.83</v>
+        <v>28.03</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>27.38</v>
+        <v>27.44</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>26.34</v>
+        <v>26.41</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.74</v>
+        <v>27.78</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3478.7</v>
+        <v>3569.2</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3388.77</v>
+        <v>3405.96</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3201.58</v>
+        <v>3215.99</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2842.69</v>
+        <v>2849.62</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>454.15</v>
+        <v>477.75</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>408.57</v>
+        <v>415.16</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>389.43</v>
+        <v>392.89</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>428.12</v>
+        <v>429.26</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,29 +9517,29 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>38.63</v>
+        <v>39.91</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>38.42</v>
+        <v>38.56</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>38.65</v>
+        <v>38.7</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.18</v>
+        <v>36.24</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H201" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H201" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I201" s="12" t="inlineStr">
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>231.75</v>
+        <v>235.18</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>219.67</v>
+        <v>221.14</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>216.22</v>
+        <v>216.96</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>223.75</v>
+        <v>224.02</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>213.31</v>
+        <v>216.01</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>192.41</v>
+        <v>194.66</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>189.3</v>
+        <v>190.34</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>226.22</v>
+        <v>224.98</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>266.45</v>
+        <v>279.77</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>237.14</v>
+        <v>241.2</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>198.26</v>
+        <v>201.46</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>142.11</v>
+        <v>143.44</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>1066.25</v>
+        <v>1098.55</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>988.37</v>
+        <v>998.86</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>942.95</v>
+        <v>949.0599999999999</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>873.9</v>
+        <v>875.55</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2331.4</v>
+        <v>2333.3</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2112.78</v>
+        <v>2133.78</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>2026.88</v>
+        <v>2038.9</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2206.62</v>
+        <v>2208.78</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>753.45</v>
+        <v>779.1</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>744.6</v>
+        <v>747.89</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>749.61</v>
+        <v>750.77</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>805.92</v>
+        <v>805.4299999999999</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>869.55</v>
+        <v>884.4</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>838.83</v>
+        <v>843.17</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>851.6799999999999</v>
+        <v>852.97</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>999.41</v>
+        <v>998.6</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>139.28</v>
+        <v>146.72</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>137.62</v>
+        <v>138.48</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>132.8</v>
+        <v>133.34</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.94</v>
+        <v>138.08</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>287.1</v>
+        <v>296.05</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>257.51</v>
+        <v>261.18</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>246.3</v>
+        <v>248.25</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>254.68</v>
+        <v>254.94</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>350.65</v>
+        <v>355.35</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>331.55</v>
+        <v>333.82</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>345.8</v>
+        <v>346.17</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>392.04</v>
+        <v>391.71</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>642.85</v>
+        <v>704.45</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>627.63</v>
+        <v>634.9400000000001</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>636.4299999999999</v>
+        <v>639.1</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>680.34</v>
+        <v>682.15</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10026,9 +10026,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I212" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I212" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J212" s="14" t="inlineStr">
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>235.58</v>
+        <v>238.86</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>227.13</v>
+        <v>228.25</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>227</v>
+        <v>227.47</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.58</v>
+        <v>253.47</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,29 +10089,29 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>794.7</v>
+        <v>854.1</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>780.96</v>
+        <v>787.9299999999999</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>797.76</v>
+        <v>799.97</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>904.96</v>
+        <v>904.83</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H214" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H214" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I214" s="13" t="inlineStr">
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>137.41</v>
+        <v>137.81</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>131.37</v>
+        <v>131.98</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>135.55</v>
+        <v>135.63</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>148.63</v>
+        <v>148.66</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1112.85</v>
+        <v>1089.8</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>961.6</v>
+        <v>973.8099999999999</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>887.13</v>
+        <v>895.08</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>720.3</v>
+        <v>724.1900000000001</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>397.85</v>
+        <v>412.9</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>390.62</v>
+        <v>392.74</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>396.11</v>
+        <v>396.77</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>483</v>
+        <v>482.3</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>114.35</v>
+        <v>114.86</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>109.83</v>
+        <v>110.31</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>108.38</v>
+        <v>108.64</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.84</v>
+        <v>116.87</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>485.8</v>
+        <v>582.95</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>466.44</v>
+        <v>477.54</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>462.78</v>
+        <v>467.49</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>527.65</v>
+        <v>527.96</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10334,9 +10334,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I219" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I219" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J219" s="14" t="inlineStr">
@@ -10353,24 +10353,24 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1208.6</v>
+        <v>1250</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1211.63</v>
+        <v>1215.29</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1250.99</v>
+        <v>1250.95</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1564.39</v>
-      </c>
-      <c r="G220" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1562.5</v>
+      </c>
+      <c r="G220" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H220" s="13" t="inlineStr">
@@ -10397,20 +10397,20 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1680.1</v>
+        <v>1699.7</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1709.79</v>
+        <v>1708.83</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1729.32</v>
+        <v>1728.16</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1770.28</v>
+        <v>1769.53</v>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
@@ -10441,29 +10441,29 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>102.28</v>
+        <v>107.15</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>99.33</v>
+        <v>100.08</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>102.28</v>
+        <v>102.47</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>124.91</v>
+        <v>124.79</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H222" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H222" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I222" s="13" t="inlineStr">
@@ -10485,24 +10485,24 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>3799.3</v>
+        <v>3946.5</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3904.31</v>
+        <v>3908.32</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3733.81</v>
+        <v>3742.15</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3075.86</v>
-      </c>
-      <c r="G223" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3084.61</v>
+      </c>
+      <c r="G223" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H223" s="12" t="inlineStr">
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2108.8</v>
+        <v>2215.5</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1917.95</v>
+        <v>1946.29</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1846.32</v>
+        <v>1860.8</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2152.35</v>
+        <v>2153.57</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10554,9 +10554,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I224" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I224" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J224" s="14" t="inlineStr">
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>97.13</v>
+        <v>99.2</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>102.1</v>
+        <v>101.83</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>105.66</v>
+        <v>105.41</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>131.26</v>
+        <v>130.77</v>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>395.1</v>
+        <v>412.45</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>387.14</v>
+        <v>389.55</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>391.79</v>
+        <v>392.6</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.48</v>
+        <v>396.47</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10642,9 +10642,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I226" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I226" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J226" s="14" t="inlineStr">
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>455.65</v>
+        <v>462.35</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>448.48</v>
+        <v>449.8</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>443.75</v>
+        <v>444.48</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>435.94</v>
+        <v>436.5</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>184.11</v>
+        <v>186.68</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>182.95</v>
+        <v>183.31</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>180.82</v>
+        <v>181.05</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>193.34</v>
+        <v>193.1</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>665.15</v>
+        <v>680.75</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>571.11</v>
+        <v>581.55</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>548.72</v>
+        <v>553.89</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>557.78</v>
+        <v>559.3</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>576</v>
+        <v>598.35</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>548.26</v>
+        <v>553.03</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>537.83</v>
+        <v>540.21</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>586.03</v>
+        <v>586.02</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10818,9 +10818,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I230" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I230" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J230" s="14" t="inlineStr">
@@ -10837,29 +10837,29 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>56.79</v>
+        <v>57.52</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>57.31</v>
+        <v>57.33</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>57.05</v>
+        <v>57.07</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.79</v>
-      </c>
-      <c r="G231" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H231" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>52.85</v>
+      </c>
+      <c r="G231" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H231" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I231" s="12" t="inlineStr">
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>994.9</v>
+        <v>1023.95</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>894.21</v>
+        <v>906.5599999999999</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>873.66</v>
+        <v>879.5599999999999</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>961.04</v>
+        <v>960.6799999999999</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>617.35</v>
+        <v>637.7</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>599.87</v>
+        <v>603.47</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>591.66</v>
+        <v>593.47</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>682.04</v>
+        <v>680.1</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>299.3</v>
+        <v>300</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>320.01</v>
+        <v>318.11</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>336.04</v>
+        <v>334.62</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>369.31</v>
+        <v>368.65</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>203.06</v>
+        <v>205.75</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>197.03</v>
+        <v>197.86</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>198.14</v>
+        <v>198.44</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>201.54</v>
+        <v>201.4</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>256.21</v>
+        <v>258.9</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>240.54</v>
+        <v>242.29</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>234.44</v>
+        <v>235.4</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>249.86</v>
+        <v>250.86</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1493.3</v>
+        <v>1500</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1369.17</v>
+        <v>1381.63</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1304.79</v>
+        <v>1312.44</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1341.28</v>
+        <v>1342</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11145,29 +11145,29 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>215.03</v>
+        <v>220.67</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>213.24</v>
+        <v>213.95</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>215.57</v>
+        <v>215.77</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>227.95</v>
+        <v>228.06</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H238" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H238" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I238" s="13" t="inlineStr">
@@ -11189,24 +11189,24 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>512.25</v>
+        <v>521.35</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>514.6799999999999</v>
+        <v>515.3200000000001</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>524</v>
+        <v>523.9</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>557.09</v>
-      </c>
-      <c r="G239" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>556.78</v>
+      </c>
+      <c r="G239" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H239" s="13" t="inlineStr">
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>499.95</v>
+        <v>525.8</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>483.99</v>
+        <v>487.98</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>483.53</v>
+        <v>485.18</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>486.06</v>
+        <v>486.69</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1280.6</v>
+        <v>1293.5</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1304.07</v>
+        <v>1303.06</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1373.44</v>
+        <v>1370.3</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1547.86</v>
+        <v>1544.42</v>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
@@ -11321,17 +11321,17 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>207.15</v>
+        <v>208.82</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>204.07</v>
+        <v>204.52</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>202.05</v>
+        <v>202.31</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>10768.5</v>
+        <v>11204</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>9760.67</v>
+        <v>9898.129999999999</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>9036.379999999999</v>
+        <v>9121.389999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8262.200000000001</v>
+        <v>8290.549999999999</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1028.15</v>
+        <v>1055.45</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>977.14</v>
+        <v>984.59</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>928.12</v>
+        <v>933.11</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>961.53</v>
+        <v>962.46</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>110.85</v>
+        <v>116.39</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>85.52</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>78.18000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>96.75</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>505.35</v>
+        <v>523.35</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>471.24</v>
+        <v>476.2</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>470.66</v>
+        <v>472.73</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>496.09</v>
+        <v>496.14</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,24 +11541,24 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>462.75</v>
+        <v>469.3</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>465.42</v>
+        <v>465.79</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>475.72</v>
+        <v>475.47</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>562.35</v>
-      </c>
-      <c r="G247" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>562.8200000000001</v>
+      </c>
+      <c r="G247" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H247" s="13" t="inlineStr">
@@ -11585,24 +11585,24 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>718.3</v>
+        <v>750.6</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>719.48</v>
+        <v>722.4400000000001</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>694.9</v>
+        <v>697.08</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>664.9</v>
-      </c>
-      <c r="G248" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>665.66</v>
+      </c>
+      <c r="G248" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H248" s="12" t="inlineStr">
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>256.26</v>
+        <v>260.47</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>246.49</v>
+        <v>247.83</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>250.12</v>
+        <v>250.53</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>317.86</v>
+        <v>317.79</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>490.85</v>
+        <v>492.75</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>480.51</v>
+        <v>481.68</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>452.78</v>
+        <v>454.35</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>430.11</v>
+        <v>430.77</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>500.85</v>
+        <v>491.55</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>472.37</v>
+        <v>474.2</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>469.56</v>
+        <v>470.42</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>585.71</v>
+        <v>583.61</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 27-Apr-2026  17:53:31    |    Closing Price Date: 27-Apr-2026</t>
+          <t>Scan Run: 28-Apr-2026  19:12:31    |    Closing Price Date: 27-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>94</v>
+        <v>93.2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>86</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>47.6</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>27-Apr-2026  17:53:31</t>
+          <t>28-Apr-2026  19:12:31</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 94.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 93.2% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 86.0% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 85.6% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 235 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 233 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 215 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 214 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>435.55</v>
+        <v>449</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>433.34</v>
+        <v>434.83</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>433.19</v>
+        <v>433.81</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>455.26</v>
+        <v>455.2</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2494.6</v>
+        <v>2467.8</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2358.51</v>
+        <v>2368.92</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2235.63</v>
+        <v>2244.73</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1811.21</v>
+        <v>1817.75</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1044.95</v>
+        <v>1007.65</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1032.35</v>
+        <v>1030</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>987.33</v>
+        <v>988.13</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>962.95</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>963.4</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>14.05</v>
+        <v>14.15</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.71</v>
+        <v>14.65</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.17</v>
+        <v>15.13</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -2169,34 +2169,34 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>618.75</v>
+        <v>581.65</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>598.71</v>
+        <v>597.08</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>597.5</v>
+        <v>596.88</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>583.48</v>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>583.46</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1420.7</v>
+        <v>1439.2</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1324.52</v>
+        <v>1335.44</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1322.63</v>
+        <v>1327.2</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>337.35</v>
+        <v>331.3</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>304.37</v>
+        <v>306.93</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>289.83</v>
+        <v>291.46</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>274.37</v>
+        <v>274.94</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>662.5</v>
+        <v>680.05</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>620.28</v>
+        <v>625.97</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>613.48</v>
+        <v>616.09</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>701.61</v>
+        <v>701.39</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1231.9</v>
+        <v>1218.95</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1096.47</v>
+        <v>1108.14</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1045.78</v>
+        <v>1052.57</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1317.76</v>
+        <v>1316.78</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>507.9</v>
+        <v>498.65</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>487.4</v>
+        <v>488.48</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>490.56</v>
+        <v>490.88</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>535.11</v>
+        <v>534.75</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>662.65</v>
+        <v>680.75</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>621.84</v>
+        <v>627.45</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>641.08</v>
+        <v>642.63</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>749.9</v>
+        <v>749.21</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>320.08</v>
+        <v>322.54</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>300.02</v>
+        <v>302.16</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>299.93</v>
+        <v>300.82</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>305.83</v>
+        <v>306</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>58.95</v>
+        <v>58.77</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>51.88</v>
+        <v>52.54</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>49.36</v>
+        <v>49.73</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55.21</v>
+        <v>55.25</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>401.3</v>
+        <v>401.05</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>380.04</v>
+        <v>382.04</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>383.62</v>
+        <v>384.3</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>428.83</v>
+        <v>428.56</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>414</v>
+        <v>414.15</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>380.08</v>
+        <v>383.32</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>372.61</v>
+        <v>374.24</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>504.09</v>
+        <v>503.2</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>674.85</v>
+        <v>670.65</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>634.5</v>
+        <v>637.9400000000001</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>602.99</v>
+        <v>605.64</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>594.34</v>
+        <v>595.1</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>812</v>
+        <v>810.45</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>801.46</v>
+        <v>802.3099999999999</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>840.48</v>
+        <v>839.3</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1032.98</v>
+        <v>1030.77</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4646.1</v>
+        <v>4682.5</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4559.35</v>
+        <v>4571.08</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4452.39</v>
+        <v>4461.41</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4582.92</v>
+        <v>4583.91</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>412.9</v>
+        <v>406.1</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>392.74</v>
+        <v>394.01</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>396.77</v>
+        <v>397.13</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>482.3</v>
+        <v>481.54</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,17 +10265,17 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>114.86</v>
+        <v>117.27</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>110.31</v>
+        <v>110.97</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>108.64</v>
+        <v>108.97</v>
       </c>
       <c r="F218" s="11" t="n">
         <v>116.87</v>
@@ -10290,9 +10290,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I218" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I218" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J218" s="14" t="inlineStr">
@@ -11321,17 +11321,17 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>208.82</v>
+        <v>210.27</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>204.52</v>
+        <v>205.07</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>202.31</v>
+        <v>202.62</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1055.45</v>
+        <v>1059.35</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>984.59</v>
+        <v>991.71</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>933.11</v>
+        <v>938.0599999999999</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>962.46</v>
+        <v>963.4299999999999</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>260.47</v>
+        <v>254.89</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>247.83</v>
+        <v>248.5</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>250.53</v>
+        <v>250.7</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>317.79</v>
+        <v>317.17</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 28-Apr-2026  19:12:31    |    Closing Price Date: 27-Apr-2026</t>
+          <t>Scan Run: 30-Apr-2026  16:10:46    |    Closing Price Date: 30-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>93.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>85.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>47.6</v>
+        <v>46</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>28-Apr-2026  19:12:31</t>
+          <t>30-Apr-2026  16:10:46</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 93.2% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 82.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 85.6% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 79.2% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 47.6% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 233 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 206 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 214 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 198 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 119 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 115 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>564.9</v>
+        <v>634</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>546.8</v>
+        <v>572.75</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>560.0700000000001</v>
+        <v>569.96</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>692.0599999999999</v>
+        <v>689.67</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>449</v>
+        <v>439.95</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>434.83</v>
+        <v>435.57</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>433.81</v>
+        <v>434.2</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>455.2</v>
+        <v>454.48</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>381.8</v>
+        <v>376.3</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>361.81</v>
+        <v>365.56</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>363.36</v>
+        <v>364.83</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>403.41</v>
+        <v>402.55</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>712.75</v>
+        <v>740.25</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>683.28</v>
+        <v>693.1900000000001</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>689.6</v>
+        <v>693.14</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>742.62</v>
+        <v>741.23</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2467.8</v>
+        <v>2594.1</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2368.92</v>
+        <v>2401.87</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2244.73</v>
+        <v>2268.14</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1817.75</v>
+        <v>1832.22</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>330.55</v>
+        <v>347.7</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>296.55</v>
+        <v>308.51</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>292.66</v>
+        <v>298.3</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>302.33</v>
+        <v>303.48</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1154.5</v>
+        <v>1171.8</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1143.4</v>
+        <v>1150.32</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1082.94</v>
+        <v>1092.79</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.8200000000001</v>
+        <v>943.28</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>871.4</v>
+        <v>891</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>812.89</v>
+        <v>832.59</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>803.41</v>
+        <v>813.05</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>867.72</v>
+        <v>867.51</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>521.3</v>
+        <v>524.05</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>492.67</v>
+        <v>501.89</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>493.6</v>
+        <v>497.53</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>559.63</v>
+        <v>558.71</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1007.65</v>
+        <v>1038.15</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1030</v>
+        <v>1028.66</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>988.13</v>
+        <v>990.74</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>963.4</v>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>966.5</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.279999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>8.81</v>
+        <v>9</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.09</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17.82</v>
+        <v>17.54</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>554.55</v>
+        <v>531.8</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>512.51</v>
+        <v>520.2</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>494.34</v>
+        <v>499.77</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>501.18</v>
+        <v>502.02</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1334.5</v>
+        <v>1343.8</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1296.1</v>
+        <v>1301.6</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1278.85</v>
+        <v>1283.12</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1182.49</v>
+        <v>1186.48</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>123.49</v>
+        <v>121.73</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>117.97</v>
+        <v>119.4</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>118.55</v>
+        <v>119.12</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>135.06</v>
+        <v>134.55</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>601.9</v>
+        <v>607.3</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>596.76</v>
+        <v>600.8099999999999</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>585.03</v>
+        <v>588.12</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>589.05</v>
+        <v>589.71</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,29 +1421,29 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>452.65</v>
+        <v>443.15</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>451.88</v>
+        <v>449.67</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>447.65</v>
+        <v>447.17</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>470.98</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>469.92</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>390.7</v>
+        <v>398.55</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>378.83</v>
+        <v>383.04</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>364.14</v>
+        <v>367.62</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>343.8</v>
+        <v>344.87</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>136.79</v>
+        <v>134.25</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>128.84</v>
+        <v>130.49</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>131.27</v>
+        <v>131.72</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>164.2</v>
+        <v>163.13</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1138.35</v>
+        <v>1125.2</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1049.43</v>
+        <v>1065.37</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1000.73</v>
+        <v>1013.12</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>967.61</v>
+        <v>971.02</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>879.05</v>
+        <v>869.9</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>860.38</v>
+        <v>862.7</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>880.17</v>
+        <v>878.9400000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1074.34</v>
+        <v>1066.18</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1083.35</v>
+        <v>1057.25</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1038.18</v>
+        <v>1041.62</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>998.4</v>
+        <v>1004.35</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>949.5700000000001</v>
+        <v>950.1900000000001</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1426.2</v>
+        <v>1380.7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1371.51</v>
+        <v>1377</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1259.56</v>
+        <v>1274.69</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>978.38</v>
+        <v>990.16</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>14.15</v>
+        <v>13.74</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.65</v>
+        <v>14.5</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.13</v>
+        <v>15.03</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>350.05</v>
+        <v>351.42</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>325.73</v>
+        <v>332.74</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>328.19</v>
+        <v>330.98</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>454.76</v>
+        <v>451.54</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>2237.1</v>
+        <v>2164.9</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1833.66</v>
+        <v>1921.99</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1702.22</v>
+        <v>1755.68</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1627.43</v>
+        <v>1641.4</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>397.2</v>
+        <v>396.1</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>380.2</v>
+        <v>384.53</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>382.93</v>
+        <v>384.51</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>470.66</v>
+        <v>467.47</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1306.9</v>
+        <v>1333.65</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1147.83</v>
+        <v>1192.32</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1115.32</v>
+        <v>1138.37</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1244.59</v>
+        <v>1246.16</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>483.25</v>
+        <v>541.4</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>464.31</v>
+        <v>478.53</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>467.03</v>
+        <v>472.82</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>541.34</v>
+        <v>540.3200000000001</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1974,9 +1974,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J29" s="14" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>624.55</v>
+        <v>618.55</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>593.37</v>
+        <v>600.6900000000001</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>594.02</v>
+        <v>597.16</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>608.36</v>
+        <v>608.03</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>216.78</v>
+        <v>212.72</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>206.53</v>
+        <v>208.47</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>195</v>
+        <v>197.16</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>164.84</v>
+        <v>166.3</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3216.4</v>
+        <v>3096.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2677.7</v>
+        <v>2797.31</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2562.67</v>
+        <v>2628.03</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2739.32</v>
+        <v>2747.46</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,29 +2125,29 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>942.1</v>
+        <v>909.5</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>926.54</v>
+        <v>923.9299999999999</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>940.3200000000001</v>
+        <v>937.65</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1068.4</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1063.29</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>581.65</v>
+        <v>548.05</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>597.08</v>
+        <v>588.45</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>596.88</v>
+        <v>593.24</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>583.46</v>
+        <v>582.28</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>516.8</v>
+        <v>501.5</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>475.77</v>
+        <v>483.68</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>468.48</v>
+        <v>472.78</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>518.59</v>
+        <v>517.41</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1439.2</v>
+        <v>1390.6</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1335.44</v>
+        <v>1348.75</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1327.2</v>
+        <v>1333.52</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>483.8</v>
+        <v>473.75</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>468.12</v>
+        <v>469.39</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>455.92</v>
+        <v>457.84</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>432.48</v>
+        <v>433.38</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,24 +2345,24 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>304.2</v>
+        <v>290.35</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>302.78</v>
+        <v>300.5</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>304.24</v>
+        <v>303.11</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>351.05</v>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>349.28</v>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -2389,34 +2389,34 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>396.6</v>
+        <v>381.95</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>388.36</v>
+        <v>388.43</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>391.09</v>
+        <v>390.84</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>395.12</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>394.92</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1718.2</v>
+        <v>1623.4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1764.04</v>
+        <v>1732.57</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1890.93</v>
+        <v>1862.94</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2158.09</v>
+        <v>2140.03</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>331.3</v>
+        <v>338.6</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>306.93</v>
+        <v>312.64</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>291.46</v>
+        <v>295.07</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>274.94</v>
+        <v>276.08</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,24 +2521,24 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>428</v>
+        <v>417.5</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>420.93</v>
+        <v>420.34</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>434.94</v>
+        <v>433.1</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>516.72</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>513.49</v>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>680.05</v>
+        <v>815.25</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>625.97</v>
+        <v>648.6</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>616.09</v>
+        <v>626.29</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>701.39</v>
+        <v>702.3099999999999</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2590,9 +2590,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1187.8</v>
+        <v>1182.2</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1206.93</v>
+        <v>1201.74</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1259.25</v>
+        <v>1251.08</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1473.11</v>
+        <v>1461.44</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>400.1</v>
+        <v>393.1</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>339.2</v>
+        <v>353.3</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>334.35</v>
+        <v>341.05</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>394.11</v>
+        <v>393.91</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2678,9 +2678,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>190.92</v>
+        <v>186.76</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>185.76</v>
+        <v>186.78</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>182.06</v>
+        <v>182.93</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>165.42</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>166.11</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>722.65</v>
+        <v>732.8</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>715.49</v>
+        <v>717.21</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723.16</v>
+        <v>723</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>759.5599999999999</v>
+        <v>758.59</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1071.95</v>
+        <v>1079.65</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1019.64</v>
+        <v>1032.09</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1032.61</v>
+        <v>1036.54</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1219.41</v>
+        <v>1213.69</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>165.59</v>
+        <v>157.8</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>146.8</v>
+        <v>150.36</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>139.23</v>
+        <v>141.65</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>136.16</v>
+        <v>137.16</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>467.25</v>
+        <v>464.8</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>442</v>
+        <v>449.11</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>439.25</v>
+        <v>442.69</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>455.88</v>
+        <v>456.06</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>174.8</v>
+        <v>183.18</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>165.28</v>
+        <v>169.84</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>174.49</v>
+        <v>175.44</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>217.04</v>
+        <v>215.5</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1103.6</v>
+        <v>1099.9</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1070.03</v>
+        <v>1083.17</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1088.47</v>
+        <v>1092.22</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1176.73</v>
+        <v>1174.68</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>12417</v>
+        <v>11568</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>10631.51</v>
+        <v>10908.47</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>10048.54</v>
+        <v>10235.68</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8823.34</v>
+        <v>8896.15</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>229.34</v>
+        <v>226.13</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>222.78</v>
+        <v>223.66</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>214.82</v>
+        <v>216.1</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>212.15</v>
+        <v>212.44</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.92</v>
+        <v>7.86</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.55</v>
+        <v>7.63</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.43</v>
+        <v>7.48</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3137,24 +3137,24 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>123.07</v>
+        <v>114.25</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>115.71</v>
+        <v>116.93</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>112.98</v>
+        <v>113.85</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.98</v>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>110.14</v>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>110.51</v>
+        <v>124.34</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>102.12</v>
+        <v>108.01</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>99.84</v>
+        <v>102.66</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.19</v>
+        <v>114.28</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3206,9 +3206,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J57" s="14" t="inlineStr">
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>85.73999999999999</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>79.56</v>
+        <v>80.53</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>76.81</v>
+        <v>77.55</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.69</v>
+        <v>84.55</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3250,9 +3250,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I58" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
@@ -3282,7 +3282,7 @@
         <v>54.2</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>78.09</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1242.6</v>
+        <v>1216.4</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1221.3</v>
+        <v>1216.25</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1170.85</v>
+        <v>1174.31</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1154.63</v>
+        <v>1154.91</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>209.46</v>
+        <v>211.94</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>191.11</v>
+        <v>197.57</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>178.97</v>
+        <v>183.17</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>202.03</v>
+        <v>201.99</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1218.95</v>
+        <v>1215.65</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1108.14</v>
+        <v>1125.82</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1052.57</v>
+        <v>1064.31</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1316.78</v>
+        <v>1312.26</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>67.34</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>62.58</v>
+        <v>63.67</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>61.83</v>
+        <v>62.39</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>62.26</v>
+        <v>62.31</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,34 +3489,34 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2625.8</v>
+        <v>2401.8</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2456.52</v>
+        <v>2460.04</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2430.47</v>
+        <v>2435.36</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2591.16</v>
-      </c>
-      <c r="G64" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I64" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2585.84</v>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J64" s="14" t="inlineStr">
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
         <v>498.65</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>488.48</v>
+        <v>491.01</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>490.88</v>
+        <v>491.78</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>534.75</v>
+        <v>533.62</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>367.05</v>
+        <v>364.45</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>355.28</v>
+        <v>357.61</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>359.15</v>
+        <v>359.73</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>398.57</v>
+        <v>397.45</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2211.4</v>
+        <v>2182.7</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2173.25</v>
+        <v>2177.08</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2160.35</v>
+        <v>2163.5</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2069.95</v>
+        <v>2072.53</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,24 +3665,24 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4883.7</v>
+        <v>4628.1</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4703.35</v>
+        <v>4701.01</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4529.27</v>
+        <v>4548.2</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4480.48</v>
-      </c>
-      <c r="G68" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>4489.45</v>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
@@ -3709,29 +3709,29 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>881.4</v>
+        <v>937.2</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>873.3099999999999</v>
+        <v>885.51</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>899.61</v>
+        <v>901.9</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1034.66</v>
+        <v>1029.94</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H69" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I69" s="13" t="inlineStr">
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>513.35</v>
+        <v>506.8</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>487.35</v>
+        <v>493.73</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>487.61</v>
+        <v>490.38</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>545.75</v>
+        <v>544.51</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>915.15</v>
+        <v>905.55</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>901.24</v>
+        <v>901.74</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>918.0599999999999</v>
+        <v>916.38</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1037.39</v>
+        <v>1033.26</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>109.14</v>
+        <v>106.55</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>105.94</v>
+        <v>106.18</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>106.04</v>
+        <v>106.13</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.58</v>
+        <v>110.51</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>1013.5</v>
+        <v>1025.6</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>958.48</v>
+        <v>974.23</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>943.29</v>
+        <v>951.86</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>944.99</v>
+        <v>946.5</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>872.55</v>
+        <v>861.85</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>750.8099999999999</v>
+        <v>779.3099999999999</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>659.59</v>
+        <v>682.3200000000001</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>581.12</v>
+        <v>588.78</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>680.75</v>
+        <v>665.55</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>627.45</v>
+        <v>635.87</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>642.63</v>
+        <v>645.05</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>749.21</v>
+        <v>747.72</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1059.15</v>
+        <v>1049.55</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1004.37</v>
+        <v>1016</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>922.99</v>
+        <v>937.24</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1041.53</v>
+        <v>1040.52</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>4038</v>
+        <v>3999</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3901.03</v>
+        <v>3906.76</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3816.05</v>
+        <v>3828.03</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3656.5</v>
+        <v>3657.68</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,24 +4105,24 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>631.4</v>
+        <v>614.75</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>628.01</v>
+        <v>624.53</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>634.09</v>
+        <v>631.89</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>701.62</v>
-      </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>697.97</v>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>57.9</v>
+        <v>57.37</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>56.77</v>
+        <v>57</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>56.47</v>
+        <v>56.6</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.13</v>
+        <v>59.02</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>724.55</v>
+        <v>703.7</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>687.4</v>
+        <v>691.91</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>675.39</v>
+        <v>678.71</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>756.95</v>
+        <v>753.95</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>164.17</v>
+        <v>165.18</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>151.97</v>
+        <v>155.74</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>152.98</v>
+        <v>154.51</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>181.25</v>
+        <v>180.25</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>211.23</v>
+        <v>228.91</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>204.62</v>
+        <v>208.67</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>205.77</v>
+        <v>207.36</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>238.84</v>
+        <v>238.03</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>152.81</v>
+        <v>155.75</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>148.2</v>
+        <v>149.3</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>141.96</v>
+        <v>143.13</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>127.55</v>
+        <v>128.07</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>474.85</v>
+        <v>469.3</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>452.03</v>
+        <v>457.45</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>446.01</v>
+        <v>449.07</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>474.82</v>
+        <v>474.56</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4394,9 +4394,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I84" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
@@ -4413,20 +4413,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>157.61</v>
+        <v>156.05</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>155.12</v>
+        <v>155.63</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>159.21</v>
+        <v>158.97</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>162.08</v>
+        <v>161.78</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>174.9</v>
+        <v>170.39</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>166.8</v>
+        <v>168.17</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>165.89</v>
+        <v>166.6</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178.8</v>
+        <v>178.41</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,29 +4501,29 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>993</v>
+        <v>983.3</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>955.84</v>
+        <v>964.4299999999999</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>988.91</v>
+        <v>988.9400000000001</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1083.58</v>
+        <v>1079.66</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H87" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H87" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr">
@@ -4545,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>613.85</v>
+        <v>595</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>572.77</v>
+        <v>580.5</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>575.64</v>
+        <v>578.72</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>771.66</v>
+        <v>765.3099999999999</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>577.45</v>
+        <v>572.55</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>561.5700000000001</v>
+        <v>564.58</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>570.8</v>
+        <v>571.08</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>607.96</v>
+        <v>607.13</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,24 +4633,24 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>129.02</v>
+        <v>128.12</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>127.85</v>
+        <v>128.13</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.3</v>
+        <v>130.15</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>137.03</v>
-      </c>
-      <c r="G90" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>136.66</v>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>360.2</v>
+        <v>358.15</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>343.22</v>
+        <v>348.12</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>345.92</v>
+        <v>347.76</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>403.83</v>
+        <v>401.99</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,20 +4721,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>189.15</v>
+        <v>189.25</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>181.15</v>
+        <v>183.12</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>184.75</v>
+        <v>185.2</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>235.64</v>
+        <v>233.8</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>20.71</v>
+        <v>22.04</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>18.3</v>
+        <v>19.3</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>17.85</v>
+        <v>18.33</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.89</v>
+        <v>21.83</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4790,9 +4790,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I93" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J93" s="14" t="inlineStr">
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1189.4</v>
+        <v>1142.85</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1089.78</v>
+        <v>1107.72</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1112.97</v>
+        <v>1118.24</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1348.86</v>
+        <v>1342.98</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>322.54</v>
+        <v>312.33</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>302.16</v>
+        <v>304.15</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>300.82</v>
+        <v>301.77</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>306</v>
+        <v>305.2</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,24 +4897,24 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>47.7</v>
+        <v>45.48</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>45.9</v>
+        <v>45.85</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>45.26</v>
+        <v>45.31</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>51.19</v>
-      </c>
-      <c r="G96" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>50.93</v>
+      </c>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
@@ -4941,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>970.05</v>
+        <v>1042.05</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>935.1799999999999</v>
+        <v>955.66</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>919</v>
+        <v>929.58</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>905.17</v>
+        <v>907.04</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>819.8</v>
+        <v>809.6</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>784.11</v>
+        <v>791.87</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>767.1</v>
+        <v>772.42</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>798.83</v>
+        <v>798.6900000000001</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1521.9</v>
+        <v>1502.6</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1426.4</v>
+        <v>1469.28</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1348.28</v>
+        <v>1376.12</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1179.49</v>
+        <v>1190.25</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>869.7</v>
+        <v>860.2</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>833.65</v>
+        <v>842.33</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>871.85</v>
+        <v>871.33</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1024.69</v>
+        <v>1019.87</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>267.94</v>
+        <v>277.36</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>260.71</v>
+        <v>264.28</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>260.79</v>
+        <v>262.33</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>273.39</v>
+        <v>273</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5142,9 +5142,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4234.2</v>
+        <v>4417.7</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3985.68</v>
+        <v>4074.97</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3824.2</v>
+        <v>3881.01</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3709.17</v>
+        <v>3725.8</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>718.05</v>
+        <v>752.05</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>710.4400000000001</v>
+        <v>716.72</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>702.53</v>
+        <v>706.09</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>758.77</v>
+        <v>758.72</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>182.11</v>
+        <v>180.73</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>163.55</v>
+        <v>168.23</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>163.41</v>
+        <v>165.46</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>177.27</v>
+        <v>177.1</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>408.4</v>
+        <v>396.4</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>383.1</v>
+        <v>386.86</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>370.56</v>
+        <v>373.63</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>404.63</v>
+        <v>403.92</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5318,9 +5318,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I105" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1094.65</v>
+        <v>1088.95</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>1002.92</v>
+        <v>1024.27</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>939.67</v>
+        <v>956.14</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>940.22</v>
+        <v>943.29</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>516.6</v>
+        <v>519.9</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>497.5</v>
+        <v>502.74</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>507.15</v>
+        <v>508.33</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>578.3</v>
+        <v>575.72</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5425,29 +5425,29 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>657.6</v>
+        <v>645.1</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>639.14</v>
+        <v>643.08</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>656.88</v>
+        <v>656.64</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>751.15</v>
+        <v>748.17</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H108" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H108" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I108" s="13" t="inlineStr">
@@ -5469,24 +5469,24 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>374.15</v>
+        <v>360.25</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>359.54</v>
+        <v>360.7</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>349.57</v>
+        <v>351.22</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>356.97</v>
-      </c>
-      <c r="G109" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>356.59</v>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>78.16</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>67.84999999999999</v>
+        <v>71.08</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>66.42</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>82.73999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,20 +5557,20 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>33.06</v>
+        <v>32.52</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>32.14</v>
+        <v>32.31</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.33</v>
+        <v>33.27</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>43.07</v>
+        <v>42.65</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5601,24 +5601,24 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
+        <v>121.56</v>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>123.56</v>
+      </c>
+      <c r="E112" s="11" t="n">
         <v>124.51</v>
       </c>
-      <c r="D112" s="11" t="n">
-        <v>123.82</v>
-      </c>
-      <c r="E112" s="11" t="n">
-        <v>124.72</v>
-      </c>
       <c r="F112" s="11" t="n">
-        <v>114.55</v>
-      </c>
-      <c r="G112" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>114.83</v>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H112" s="13" t="inlineStr">
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>477.1</v>
+        <v>458.15</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>412.08</v>
+        <v>427.32</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>394.13</v>
+        <v>402.88</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>416.81</v>
+        <v>417.51</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>26.33</v>
+        <v>25.9</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>24.33</v>
+        <v>24.81</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>24.34</v>
+        <v>24.55</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>33.99</v>
+        <v>33.72</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>536.65</v>
+        <v>525.95</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>542.25</v>
+        <v>539.1900000000001</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>567.33</v>
+        <v>563.17</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>697.6799999999999</v>
+        <v>692.85</v>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>122.29</v>
+        <v>125.13</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>120.99</v>
+        <v>122.92</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>126.63</v>
+        <v>126.85</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>164.69</v>
+        <v>163.34</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>461.15</v>
+        <v>447.95</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>425.28</v>
+        <v>432.35</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>410.88</v>
+        <v>415.62</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>431.65</v>
+        <v>431.86</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>376.6</v>
+        <v>367.15</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>341.08</v>
+        <v>348.71</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>336.5</v>
+        <v>340.36</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>353.07</v>
+        <v>353.39</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1328.35</v>
+        <v>1295.35</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1112.15</v>
+        <v>1159.68</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>978.36</v>
+        <v>1014.24</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>856.78</v>
+        <v>870.53</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>799.8</v>
+        <v>849.7</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>726.67</v>
+        <v>752.14</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>710.63</v>
+        <v>723.46</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>760.28</v>
+        <v>760.96</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>201.29</v>
+        <v>197.19</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>193.49</v>
+        <v>194.67</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>195.3</v>
+        <v>195.62</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>219.21</v>
+        <v>218.65</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>254.32</v>
+        <v>268.61</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>240.07</v>
+        <v>247.06</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>226.49</v>
+        <v>231.07</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>202.29</v>
+        <v>204.16</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>927.05</v>
+        <v>965.35</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>898.91</v>
+        <v>910.3099999999999</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>873.03</v>
+        <v>880.85</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>959.27</v>
+        <v>959.51</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6110,9 +6110,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J123" s="14" t="inlineStr">
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1448.3</v>
+        <v>1503.3</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1255.57</v>
+        <v>1322.39</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1182.1</v>
+        <v>1219.59</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1162.76</v>
+        <v>1172.5</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>165.91</v>
+        <v>164.49</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>166.34</v>
+        <v>165.86</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>169.63</v>
+        <v>169.05</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>191.48</v>
+        <v>190.27</v>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14509</v>
+        <v>14562</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>13973.33</v>
+        <v>14169.92</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14134.77</v>
+        <v>14203.07</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14872.33</v>
+        <v>14865.54</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6261,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>148.79</v>
+        <v>144.34</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>134.2</v>
+        <v>137.54</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>133.67</v>
+        <v>135.2</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>162.81</v>
+        <v>162.24</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>169.59</v>
+        <v>168.08</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>173.64</v>
+        <v>172.46</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>182.15</v>
+        <v>180.68</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>209.71</v>
+        <v>208.36</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>58.77</v>
+        <v>57.77</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>52.54</v>
+        <v>53.49</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>49.73</v>
+        <v>50.35</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55.25</v>
+        <v>55.2</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>69.31</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>60.2</v>
+        <v>62.6</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>56.42</v>
+        <v>57.9</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.7</v>
+        <v>60.05</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6437,29 +6437,29 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1747.6</v>
+        <v>1621.4</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1721.94</v>
+        <v>1698.17</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1646.86</v>
+        <v>1645.08</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1378.43</v>
-      </c>
-      <c r="G131" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H131" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1385.09</v>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1657.2</v>
+        <v>1398.2</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1367.3</v>
+        <v>1391.06</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1173.4</v>
+        <v>1205.94</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1190.48</v>
+        <v>1194.07</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,24 +6525,24 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>324.15</v>
+        <v>310.9</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>311.06</v>
+        <v>314.62</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>308.12</v>
+        <v>310.05</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>326.36</v>
-      </c>
-      <c r="G133" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>325.76</v>
+      </c>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
@@ -6569,29 +6569,29 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>447.15</v>
+        <v>433.15</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>435.74</v>
+        <v>436.19</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>437.58</v>
+        <v>437.59</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>473.54</v>
-      </c>
-      <c r="G134" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H134" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>471.75</v>
+      </c>
+      <c r="G134" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H134" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I134" s="13" t="inlineStr">
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>5303</v>
+        <v>6457.1</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>4581.65</v>
+        <v>4908.27</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>3990.21</v>
+        <v>4196.86</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2866.24</v>
+        <v>2951.86</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,24 +6657,24 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>327.15</v>
+        <v>340.5</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>330.01</v>
+        <v>333.04</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>342.42</v>
+        <v>342.34</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>362.47</v>
-      </c>
-      <c r="G136" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>361.58</v>
+      </c>
+      <c r="G136" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>116.47</v>
+        <v>120.35</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>99.88</v>
+        <v>104.75</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>101.37</v>
+        <v>103.31</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>128.24</v>
+        <v>127.84</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1440.5</v>
+        <v>1509</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1360.96</v>
+        <v>1391.33</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1339.45</v>
+        <v>1354.98</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1332.08</v>
+        <v>1336.06</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>192.12</v>
+        <v>184.63</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>178.65</v>
+        <v>180.43</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>175.57</v>
+        <v>176.7</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>188.57</v>
+        <v>188.26</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6814,9 +6814,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I139" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J139" s="14" t="inlineStr">
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1735.7</v>
+        <v>1694.2</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1646.18</v>
+        <v>1657.36</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1672.84</v>
+        <v>1674.67</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1996.89</v>
+        <v>1984.81</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>401.05</v>
+        <v>391.3</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>382.04</v>
+        <v>384.45</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>384.3</v>
+        <v>385.16</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>428.56</v>
+        <v>427.05</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>899.95</v>
+        <v>872.15</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>869.92</v>
+        <v>871.5</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>850.99</v>
+        <v>853.83</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>826.39</v>
+        <v>828.15</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>382.15</v>
+        <v>389.9</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>351.93</v>
+        <v>362.81</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>341.55</v>
+        <v>347.48</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>349.53</v>
+        <v>350.35</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>199.29</v>
+        <v>196.21</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>194.44</v>
+        <v>195.06</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>199.66</v>
+        <v>199.34</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>235.73</v>
+        <v>234.47</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1654</v>
+        <v>1637.5</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1464.21</v>
+        <v>1512.63</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1378.14</v>
+        <v>1409.04</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1401.07</v>
+        <v>1404.77</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1216.5</v>
+        <v>1227.7</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1148.38</v>
+        <v>1166.09</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1133.79</v>
+        <v>1143.09</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1171.2</v>
+        <v>1172.31</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>76.91</v>
+        <v>77.91</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>74.8</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.42</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.25</v>
+        <v>84.02</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>270.67</v>
+        <v>263.56</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>259.06</v>
+        <v>260.84</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>256.23</v>
+        <v>257.34</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>266.47</v>
+        <v>266.02</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7210,9 +7210,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I148" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J148" s="14" t="inlineStr">
@@ -7229,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>35.37</v>
+        <v>34.43</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>33.92</v>
+        <v>34.13</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>34.37</v>
+        <v>34.41</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>41.99</v>
+        <v>41.7</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>413.75</v>
+        <v>415.8</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>383.86</v>
+        <v>392.96</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>387.47</v>
+        <v>391.04</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>483.12</v>
+        <v>479.88</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>585.25</v>
+        <v>625.75</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>553.95</v>
+        <v>568.3</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>580.55</v>
+        <v>583.71</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>728.5599999999999</v>
+        <v>720.47</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,29 +7361,29 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>148.01</v>
+        <v>143.8</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>141.96</v>
+        <v>143.11</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.75</v>
+        <v>145.83</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>190.99</v>
+        <v>189.64</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H152" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H152" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I152" s="13" t="inlineStr">
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>414.15</v>
+        <v>412.35</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>383.32</v>
+        <v>388.22</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>374.24</v>
+        <v>377.01</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>503.2</v>
+        <v>501.36</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>670.65</v>
+        <v>653.75</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>637.9400000000001</v>
+        <v>642.1</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>605.64</v>
+        <v>609.9</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>595.1</v>
+        <v>595.9</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.51</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>9.23</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.89</v>
+        <v>10.83</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>217.99</v>
+        <v>213.87</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>200.39</v>
+        <v>204.6</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>202.64</v>
+        <v>204.24</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>242.16</v>
+        <v>241.33</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>195.2</v>
+        <v>207.7</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>177.69</v>
+        <v>185</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>170.77</v>
+        <v>174.73</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>164.43</v>
+        <v>165.74</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>135.91</v>
+        <v>128.96</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>125.06</v>
+        <v>126.68</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>123.9</v>
+        <v>124.75</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.7</v>
+        <v>141.82</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>808.1</v>
+        <v>794.25</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>740.63</v>
+        <v>756.96</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>699.48</v>
+        <v>711.28</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>678.8099999999999</v>
+        <v>681.66</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>27.96</v>
+        <v>28.38</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>26.96</v>
+        <v>27.4</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>26.96</v>
+        <v>27.16</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.32</v>
+        <v>32.16</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,29 +7757,29 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1572.3</v>
+        <v>1535.8</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1552.87</v>
+        <v>1549.75</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1539.21</v>
+        <v>1539.44</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1488.22</v>
-      </c>
-      <c r="G161" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H161" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1489.78</v>
+      </c>
+      <c r="G161" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H161" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>915.95</v>
+        <v>946.2</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>861.13</v>
+        <v>883.8099999999999</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>847.22</v>
+        <v>858.67</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>929.51</v>
+        <v>928.36</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7826,9 +7826,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I162" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J162" s="14" t="inlineStr">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2497.8</v>
+        <v>2481.8</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2257.18</v>
+        <v>2313.34</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2164.43</v>
+        <v>2199.4</v>
       </c>
       <c r="F163" s="11" t="n">
         <v>2363.09</v>
@@ -7889,29 +7889,29 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>600</v>
+        <v>572.75</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>579.76</v>
+        <v>581.77</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>575.1</v>
+        <v>576.5599999999999</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>556.33</v>
-      </c>
-      <c r="G164" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H164" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>556.95</v>
+      </c>
+      <c r="G164" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H164" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I164" s="12" t="inlineStr">
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>274.18</v>
+        <v>259.39</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>250.25</v>
+        <v>253.59</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>247.91</v>
+        <v>249.65</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>277.25</v>
+        <v>276.67</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>133.9</v>
+        <v>133.84</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>128.58</v>
+        <v>129.74</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>127.46</v>
+        <v>128.09</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>134.91</v>
+        <v>134.75</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3261.4</v>
+        <v>3360.1</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>3060.74</v>
+        <v>3127.65</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>2975.7</v>
+        <v>3014.29</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2744.7</v>
+        <v>2758.68</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2857.4</v>
+        <v>2826.1</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2582.61</v>
+        <v>2647.59</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2483.42</v>
+        <v>2522.94</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2533.42</v>
+        <v>2537.62</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>218.32</v>
+        <v>214.37</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>207.12</v>
+        <v>209.34</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>207.07</v>
+        <v>208.05</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>238.76</v>
+        <v>237.35</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8153,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>198.76</v>
+        <v>197.68</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>190.74</v>
+        <v>193.17</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>191.91</v>
+        <v>192.84</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>246.2</v>
+        <v>244.43</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8197,29 +8197,29 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>131.04</v>
+        <v>126.2</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>125.76</v>
+        <v>126.77</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>127.53</v>
+        <v>127.78</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>134.06</v>
-      </c>
-      <c r="G171" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H171" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>133.79</v>
+      </c>
+      <c r="G171" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H171" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I171" s="13" t="inlineStr">
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>261.27</v>
+        <v>265.91</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>256.35</v>
+        <v>258.21</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>256.5</v>
+        <v>257.28</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>271.65</v>
+        <v>270.86</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>592.5</v>
+        <v>602.6</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>554.0700000000001</v>
+        <v>563.7</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>549.28</v>
+        <v>553.98</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>580.35</v>
+        <v>581.51</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2693.9</v>
+        <v>2645</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2410.24</v>
+        <v>2475.23</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2345.12</v>
+        <v>2380.89</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2404.08</v>
+        <v>2410.08</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>36.13</v>
+        <v>35.52</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>32.81</v>
+        <v>33.57</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>32.33</v>
+        <v>32.72</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.8</v>
+        <v>40.62</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8417,17 +8417,17 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>10.15</v>
+        <v>10.12</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>9.220000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>8.890000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F176" s="11" t="n">
         <v>9.92</v>
@@ -8461,24 +8461,24 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>810.45</v>
+        <v>794.2</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>802.3099999999999</v>
+        <v>801.85</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>839.3</v>
+        <v>836.27</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1030.77</v>
-      </c>
-      <c r="G177" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1022.66</v>
+      </c>
+      <c r="G177" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>256.32</v>
+        <v>263.86</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>235.75</v>
+        <v>243.44</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>231.49</v>
+        <v>235.33</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>296.27</v>
+        <v>295.17</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8549,24 +8549,24 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>308.29</v>
+        <v>298.09</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>297.29</v>
+        <v>298.5</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>311.91</v>
+        <v>310.8</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>384.02</v>
-      </c>
-      <c r="G179" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>381.44</v>
+      </c>
+      <c r="G179" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H179" s="13" t="inlineStr">
@@ -8593,24 +8593,24 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>223.01</v>
+        <v>221.64</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>221.91</v>
+        <v>222.56</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>223.99</v>
+        <v>224.05</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>237.05</v>
-      </c>
-      <c r="G180" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>236.2</v>
+      </c>
+      <c r="G180" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>64.14</v>
+        <v>65.36</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>62.58</v>
+        <v>63.25</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>62.67</v>
+        <v>62.95</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.70999999999999</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>531.6</v>
+        <v>527.15</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>495.86</v>
+        <v>504.44</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>510.41</v>
+        <v>512.52</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>679.13</v>
+        <v>674.6</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>422.4</v>
+        <v>453.9</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>393.18</v>
+        <v>407.97</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>368.56</v>
+        <v>377.76</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>342.86</v>
+        <v>345.24</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1472.1</v>
+        <v>1412.5</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1538.71</v>
+        <v>1511.42</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1652.52</v>
+        <v>1627.86</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1958.39</v>
+        <v>1944.15</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8813,29 +8813,29 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>163.93</v>
+        <v>156.27</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>157.5</v>
+        <v>157.73</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>158.27</v>
+        <v>158.29</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>177.02</v>
-      </c>
-      <c r="G185" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H185" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>176.41</v>
+      </c>
+      <c r="G185" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H185" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I185" s="13" t="inlineStr">
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>216.26</v>
+        <v>210.61</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>204.1</v>
+        <v>206.61</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>202.5</v>
+        <v>203.79</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>194.04</v>
+        <v>194.53</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4682.5</v>
+        <v>4763.9</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4571.08</v>
+        <v>4608.17</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4461.41</v>
+        <v>4485.59</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4583.91</v>
+        <v>4587.7</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3431.2</v>
+        <v>3407.2</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3446.95</v>
+        <v>3443.87</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3578.23</v>
+        <v>3562.18</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4251.91</v>
+        <v>4227.49</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2602.4</v>
+        <v>2513.6</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2352.37</v>
+        <v>2402.82</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2205.52</v>
+        <v>2244.27</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1809.51</v>
+        <v>1829.35</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,29 +9033,29 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>323.05</v>
+        <v>313.1</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>318.35</v>
+        <v>317.66</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>315.5</v>
+        <v>315.53</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>333.75</v>
-      </c>
-      <c r="G190" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H190" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>332.64</v>
+      </c>
+      <c r="G190" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H190" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I190" s="13" t="inlineStr">
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>2422.6</v>
+        <v>2532.6</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>2086.47</v>
+        <v>2198.38</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2080.2</v>
+        <v>2129.61</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2075.44</v>
+        <v>2087.19</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>565.05</v>
+        <v>564.3</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>534.8099999999999</v>
+        <v>542.5599999999999</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>547.35</v>
+        <v>549.3200000000001</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>690.4400000000001</v>
+        <v>689.09</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9165,24 +9165,24 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1124.7</v>
+        <v>1072.75</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1065.78</v>
+        <v>1081.3</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1035.6</v>
+        <v>1045.99</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>922.78</v>
-      </c>
-      <c r="G193" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>928.21</v>
+      </c>
+      <c r="G193" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr">
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>872.45</v>
+        <v>863.75</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>835.4400000000001</v>
+        <v>843.4299999999999</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>844.85</v>
+        <v>847.28</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>911.29</v>
+        <v>908.83</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,29 +9253,29 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>146.61</v>
+        <v>137.45</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>141.12</v>
+        <v>141</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>139.62</v>
+        <v>139.76</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>157.26</v>
-      </c>
-      <c r="G195" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H195" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>156.42</v>
+      </c>
+      <c r="G195" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H195" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I195" s="13" t="inlineStr">
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>525.35</v>
+        <v>509.05</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>530.74</v>
+        <v>526.24</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>535.9400000000001</v>
+        <v>533.41</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>608.4</v>
+        <v>605.22</v>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>415.2</v>
+        <v>406.65</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>396.22</v>
+        <v>398.79</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>366.52</v>
+        <v>371</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>360.38</v>
+        <v>360.97</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>28.03</v>
+        <v>29.21</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>27.44</v>
+        <v>27.7</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>26.41</v>
+        <v>26.63</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.78</v>
+        <v>27.8</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3569.2</v>
+        <v>3491.1</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3405.96</v>
+        <v>3423.01</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3215.99</v>
+        <v>3244.88</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2849.62</v>
+        <v>2867.02</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>477.75</v>
+        <v>478.45</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>415.16</v>
+        <v>433.1</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>392.89</v>
+        <v>403.26</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>429.26</v>
+        <v>430.24</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>39.91</v>
+        <v>39.46</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>38.56</v>
+        <v>38.84</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>38.7</v>
+        <v>38.81</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.24</v>
+        <v>36.29</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>235.18</v>
+        <v>230.29</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>221.14</v>
+        <v>223.36</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>216.96</v>
+        <v>218.4</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>224.02</v>
+        <v>224.37</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>216.01</v>
+        <v>208.34</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>194.66</v>
+        <v>198.91</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>190.34</v>
+        <v>192.7</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>224.98</v>
+        <v>224.7</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>279.77</v>
+        <v>294.8</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>241.2</v>
+        <v>254.64</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>201.46</v>
+        <v>211.79</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>143.44</v>
+        <v>147.76</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>1098.55</v>
+        <v>1036.8</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>998.86</v>
+        <v>1011.32</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>949.0599999999999</v>
+        <v>960.16</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>875.55</v>
+        <v>878.92</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2333.3</v>
+        <v>2260.9</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2133.78</v>
+        <v>2175.96</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>2038.9</v>
+        <v>2068.17</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2208.78</v>
+        <v>2209.06</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>779.1</v>
+        <v>778.55</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>747.89</v>
+        <v>756.27</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>750.77</v>
+        <v>754.11</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>805.4299999999999</v>
+        <v>804.89</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>884.4</v>
+        <v>914.35</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>843.17</v>
+        <v>858.51</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>852.97</v>
+        <v>858.52</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>998.6</v>
+        <v>995.73</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>146.72</v>
+        <v>143.04</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>138.48</v>
+        <v>140.44</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>133.34</v>
+        <v>134.79</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>138.08</v>
+        <v>138.19</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>296.05</v>
+        <v>292.61</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>261.18</v>
+        <v>269.51</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>248.25</v>
+        <v>253.35</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>254.94</v>
+        <v>255.77</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,29 +9957,29 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>355.35</v>
+        <v>340.25</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>333.82</v>
+        <v>337.69</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>346.17</v>
+        <v>346.49</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>391.71</v>
+        <v>390.49</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H211" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H211" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I211" s="13" t="inlineStr">
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>704.45</v>
+        <v>694.9</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>634.9400000000001</v>
+        <v>651.55</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>639.1</v>
+        <v>645.89</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>682.15</v>
+        <v>681.58</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>238.86</v>
+        <v>250.12</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>228.25</v>
+        <v>232.15</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>227.47</v>
+        <v>229.23</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.47</v>
+        <v>253.25</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,20 +10089,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>854.1</v>
+        <v>846.8</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>787.9299999999999</v>
+        <v>806.45</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>799.97</v>
+        <v>806.74</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>904.83</v>
+        <v>902.0700000000001</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10133,29 +10133,29 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>137.81</v>
+        <v>132.71</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>131.98</v>
+        <v>132.33</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>135.63</v>
+        <v>135.38</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>148.66</v>
+        <v>147.87</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H215" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H215" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I215" s="13" t="inlineStr">
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1089.8</v>
+        <v>1152.7</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>973.8099999999999</v>
+        <v>1019.12</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>895.08</v>
+        <v>923.72</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>724.1900000000001</v>
+        <v>736.26</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>406.1</v>
+        <v>402.95</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>394.01</v>
+        <v>395.93</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>397.13</v>
+        <v>397.71</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>481.54</v>
+        <v>480.02</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>117.27</v>
+        <v>114.51</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>110.97</v>
+        <v>111.66</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>108.97</v>
+        <v>109.42</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.87</v>
+        <v>116.73</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10290,9 +10290,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I218" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I218" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J218" s="14" t="inlineStr">
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>582.95</v>
+        <v>511.95</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>477.54</v>
+        <v>487.65</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>467.49</v>
+        <v>470.24</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>527.96</v>
+        <v>522.65</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10334,9 +10334,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I219" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I219" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J219" s="14" t="inlineStr">
@@ -10353,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1250</v>
+        <v>1232.3</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1215.29</v>
+        <v>1219.96</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1250.95</v>
+        <v>1248.98</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1562.5</v>
+        <v>1550.61</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10397,20 +10397,20 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1699.7</v>
+        <v>1663.4</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1708.83</v>
+        <v>1696.58</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1728.16</v>
+        <v>1720.65</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1769.53</v>
+        <v>1765.56</v>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
@@ -10441,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>107.15</v>
+        <v>105.47</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>100.08</v>
+        <v>101.59</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>102.47</v>
+        <v>102.86</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>124.79</v>
+        <v>123.83</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>3946.5</v>
+        <v>3955.8</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3908.32</v>
+        <v>3924.21</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3742.15</v>
+        <v>3767.9</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3084.61</v>
+        <v>3108.27</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2215.5</v>
+        <v>2062.2</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1946.29</v>
+        <v>1987.58</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1860.8</v>
+        <v>1888.72</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2153.57</v>
+        <v>2148.43</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10554,9 +10554,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I224" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I224" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J224" s="14" t="inlineStr">
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>99.2</v>
+        <v>93.55</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>101.83</v>
+        <v>100.2</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>105.41</v>
+        <v>104.31</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>130.77</v>
+        <v>129.45</v>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>412.45</v>
+        <v>400.3</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>389.55</v>
+        <v>393.18</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>392.6</v>
+        <v>393.85</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.47</v>
+        <v>396.42</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>462.35</v>
+        <v>464.1</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>449.8</v>
+        <v>452.52</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>444.48</v>
+        <v>446.26</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>436.5</v>
+        <v>436.82</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>186.68</v>
+        <v>193.01</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>183.31</v>
+        <v>184.43</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>181.05</v>
+        <v>181.78</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>193.1</v>
+        <v>192.55</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10730,9 +10730,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I228" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I228" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J228" s="14" t="inlineStr">
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>680.75</v>
+        <v>649.7</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>581.55</v>
+        <v>600.23</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>553.89</v>
+        <v>565.1900000000001</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>559.3</v>
+        <v>561.59</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>598.35</v>
+        <v>598.95</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>553.03</v>
+        <v>566.85</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>540.21</v>
+        <v>547.71</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>586.02</v>
+        <v>585.7</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10837,29 +10837,29 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>57.52</v>
+        <v>56.88</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>57.33</v>
+        <v>57.14</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>57.07</v>
+        <v>57.02</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="G231" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H231" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>52.95</v>
+      </c>
+      <c r="G231" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H231" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I231" s="12" t="inlineStr">
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>1023.95</v>
+        <v>1002.4</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>906.5599999999999</v>
+        <v>944.35</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>879.5599999999999</v>
+        <v>899.33</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>960.6799999999999</v>
+        <v>963.41</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>637.7</v>
+        <v>616.45</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>603.47</v>
+        <v>609.66</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>593.47</v>
+        <v>597.33</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>680.1</v>
+        <v>677.6900000000001</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>300</v>
+        <v>296.25</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>318.11</v>
+        <v>312.32</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>334.62</v>
+        <v>330.23</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>368.65</v>
+        <v>366.18</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11013,34 +11013,34 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>205.75</v>
+        <v>198.65</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>197.86</v>
+        <v>198.58</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>198.44</v>
+        <v>198.7</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>201.4</v>
+        <v>201.12</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H235" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I235" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H235" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I235" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J235" s="14" t="inlineStr">
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>258.9</v>
+        <v>258.37</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>242.29</v>
+        <v>246.68</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>235.4</v>
+        <v>238.1</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>250.86</v>
+        <v>250.89</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1500</v>
+        <v>1509.6</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1381.63</v>
+        <v>1412.69</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1312.44</v>
+        <v>1333.81</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1342</v>
+        <v>1344.95</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11145,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>220.67</v>
+        <v>217.18</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>213.95</v>
+        <v>215.23</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>215.77</v>
+        <v>216.13</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>228.06</v>
+        <v>227.5</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,29 +11189,29 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>521.35</v>
+        <v>533.8</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>515.3200000000001</v>
+        <v>517.51</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>523.9</v>
+        <v>523.84</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>556.78</v>
+        <v>554.96</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H239" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H239" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I239" s="13" t="inlineStr">
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>525.8</v>
+        <v>519.1</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>487.98</v>
+        <v>494.5</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>485.18</v>
+        <v>487.55</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>486.69</v>
+        <v>485.97</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,24 +11277,24 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1293.5</v>
+        <v>1322.3</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1303.06</v>
+        <v>1305.65</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1370.3</v>
+        <v>1363.77</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1544.42</v>
-      </c>
-      <c r="G241" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1539.41</v>
+      </c>
+      <c r="G241" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H241" s="13" t="inlineStr">
@@ -11321,24 +11321,24 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>210.27</v>
+        <v>203.74</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>205.07</v>
+        <v>205.13</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>202.62</v>
+        <v>202.84</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
       </c>
-      <c r="G242" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="G242" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H242" s="12" t="inlineStr">
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>11204</v>
+        <v>11742</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>9898.129999999999</v>
+        <v>10362.87</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>9121.389999999999</v>
+        <v>9411.379999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8290.549999999999</v>
+        <v>8382.280000000001</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1059.35</v>
+        <v>1017.6</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>991.71</v>
+        <v>998.4299999999999</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>938.0599999999999</v>
+        <v>945.0599999999999</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>963.4299999999999</v>
+        <v>964.73</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>116.39</v>
+        <v>110.66</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>88.45999999999999</v>
+        <v>95.59</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>79.68000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>97.29000000000001</v>
+        <v>97.84</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>523.35</v>
+        <v>523.25</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>476.2</v>
+        <v>489.41</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>472.73</v>
+        <v>478.87</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>496.14</v>
+        <v>496.45</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,29 +11541,29 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>469.3</v>
+        <v>475.85</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>465.79</v>
+        <v>469.05</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>475.47</v>
+        <v>475.81</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>562.8200000000001</v>
+        <v>559.9299999999999</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H247" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H247" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I247" s="13" t="inlineStr">
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>750.6</v>
+        <v>820</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>722.4400000000001</v>
+        <v>743.2</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>697.08</v>
+        <v>708.91</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>665.66</v>
+        <v>669.14</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,29 +11629,29 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>254.89</v>
+        <v>240.76</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>248.5</v>
+        <v>247.35</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>250.7</v>
+        <v>250.05</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>317.17</v>
-      </c>
-      <c r="G249" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H249" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>314.65</v>
+      </c>
+      <c r="G249" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H249" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I249" s="13" t="inlineStr">
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>492.75</v>
+        <v>508.55</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>481.68</v>
+        <v>486.46</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>454.35</v>
+        <v>459.48</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>430.77</v>
+        <v>432.65</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>491.55</v>
+        <v>489.4</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>474.2</v>
+        <v>478.44</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>470.42</v>
+        <v>472.71</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>583.61</v>
+        <v>581.3099999999999</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 30-Apr-2026  16:10:46    |    Closing Price Date: 30-Apr-2026</t>
+          <t>Scan Run: 01-May-2026  14:40:46    |    Closing Price Date: 30-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>79.2</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46</v>
+        <v>46.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>30-Apr-2026  16:10:46</t>
+          <t>01-May-2026  14:40:46</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 46.8% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 115 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 117 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>569.96</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>689.67</v>
+        <v>689.98</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>434.2</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>454.48</v>
+        <v>453.79</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>364.83</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>402.55</v>
+        <v>402.2</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>693.14</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>741.23</v>
+        <v>740.24</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -918,9 +918,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>298.3</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>303.48</v>
+        <v>303.33</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>1092.79</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>943.28</v>
+        <v>943.4</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>813.05</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>867.51</v>
+        <v>866.74</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>990.74</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>966.5</v>
+        <v>965.3200000000001</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>9.130000000000001</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17.54</v>
+        <v>17.5</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>499.77</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>502.02</v>
+        <v>501.74</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1283.12</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1186.48</v>
+        <v>1186.19</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>119.12</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>134.55</v>
+        <v>134.3</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>588.12</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>589.71</v>
+        <v>588.89</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>447.17</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>469.92</v>
+        <v>470.17</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>367.62</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>344.87</v>
+        <v>344.46</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131.72</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>163.13</v>
+        <v>162.71</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>1013.12</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>971.02</v>
+        <v>969.97</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>878.9400000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1066.18</v>
+        <v>1063.95</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>1004.35</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>950.1900000000001</v>
+        <v>948.42</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1274.69</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>990.16</v>
+        <v>991.26</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>330.98</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>451.54</v>
+        <v>450.59</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>1755.68</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1641.4</v>
+        <v>1640.07</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>384.51</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>467.47</v>
+        <v>466.46</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1138.37</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1246.16</v>
+        <v>1245.16</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>472.82</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>540.3200000000001</v>
+        <v>538.49</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>597.16</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>608.03</v>
+        <v>607.41</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>2628.03</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2747.46</v>
+        <v>2745.54</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>937.65</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1063.29</v>
+        <v>1062.65</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>593.24</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>582.28</v>
+        <v>581.49</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>472.78</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>517.41</v>
+        <v>517.6</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>457.84</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>433.38</v>
+        <v>433.28</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>303.11</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>349.28</v>
+        <v>348.86</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>390.84</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>394.92</v>
+        <v>394.76</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>1862.94</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2140.03</v>
+        <v>2136.09</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>295.07</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>276.08</v>
+        <v>275.87</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>433.1</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>513.49</v>
+        <v>512.8200000000001</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1251.08</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1461.44</v>
+        <v>1460.69</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>341.05</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>393.91</v>
+        <v>390.4</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2678,9 +2678,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
@@ -2710,7 +2710,7 @@
         <v>182.93</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>166.11</v>
+        <v>166.08</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>723</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>758.59</v>
+        <v>758.78</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>1036.54</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1213.69</v>
+        <v>1211.94</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>141.65</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>137.16</v>
+        <v>136.87</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>442.69</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>456.06</v>
+        <v>455.65</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>175.44</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>215.5</v>
+        <v>215.08</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>1092.22</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1174.68</v>
+        <v>1175.71</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>10235.68</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8896.15</v>
+        <v>8895.190000000001</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>216.1</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>212.44</v>
+        <v>212.33</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>7.48</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>113.85</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>110.14</v>
+        <v>110.01</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>102.66</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.28</v>
+        <v>114.38</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>77.55</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.55</v>
+        <v>84.44</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>54.2</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>78.15000000000001</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>1174.31</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1154.91</v>
+        <v>1154.52</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>183.17</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>201.99</v>
+        <v>201.65</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>1064.31</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1312.26</v>
+        <v>1311.34</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>62.39</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>62.31</v>
+        <v>62.34</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>2435.36</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2585.84</v>
+        <v>2579.71</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>491.78</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>533.62</v>
+        <v>533.21</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>359.73</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>397.45</v>
+        <v>397.02</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>2163.5</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2072.53</v>
+        <v>2071.55</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>4548.2</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4489.45</v>
+        <v>4487.37</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>901.9</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1029.94</v>
+        <v>1029.14</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>490.38</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>544.51</v>
+        <v>544.1900000000001</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>916.38</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1033.26</v>
+        <v>1032.98</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>106.13</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.51</v>
+        <v>110.46</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>951.86</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>946.5</v>
+        <v>945.6</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>682.3200000000001</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>588.78</v>
+        <v>588.63</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>937.24</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1040.52</v>
+        <v>1038.73</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>3828.03</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3657.68</v>
+        <v>3651.52</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>631.89</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>697.97</v>
+        <v>698.39</v>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>56.6</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>59.02</v>
+        <v>58.97</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>678.71</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>753.95</v>
+        <v>752.25</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>154.51</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>180.25</v>
+        <v>179.95</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>207.36</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>238.03</v>
+        <v>237.82</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>143.13</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>128.07</v>
+        <v>127.84</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>449.07</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>474.56</v>
+        <v>474.27</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>158.97</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>161.78</v>
+        <v>161.46</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>166.6</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178.41</v>
+        <v>178.48</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>988.9400000000001</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1079.66</v>
+        <v>1080.11</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>578.72</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>765.3099999999999</v>
+        <v>763.1</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>571.08</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>607.13</v>
+        <v>606.95</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>130.15</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>136.66</v>
+        <v>136.43</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>347.76</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>401.99</v>
+        <v>402.36</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>185.2</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>233.8</v>
+        <v>233.35</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>18.33</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.83</v>
+        <v>21.77</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>1118.24</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1342.98</v>
+        <v>1342.54</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>301.77</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>305.2</v>
+        <v>305.32</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>45.31</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>50.93</v>
+        <v>50.99</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>929.58</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>907.04</v>
+        <v>906.34</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>772.42</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>798.6900000000001</v>
+        <v>798.37</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>1376.12</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1190.25</v>
+        <v>1190.6</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>871.33</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1019.87</v>
+        <v>1019.93</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>262.33</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>273</v>
+        <v>272.92</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>3881.01</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3725.8</v>
+        <v>3725.43</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>706.09</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>758.72</v>
+        <v>757.29</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>165.46</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>177.1</v>
+        <v>177.06</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>373.63</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>403.92</v>
+        <v>403.35</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>956.14</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>943.29</v>
+        <v>940.4</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>508.33</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>575.72</v>
+        <v>575.59</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>656.64</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>748.17</v>
+        <v>747.61</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>351.22</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>356.59</v>
+        <v>356.53</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>67.98999999999999</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>82.28</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>33.27</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.65</v>
+        <v>42.5</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>124.51</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.83</v>
+        <v>114.71</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>402.88</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>417.51</v>
+        <v>420.62</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>563.17</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>692.85</v>
+        <v>692.96</v>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>126.85</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>163.34</v>
+        <v>162.99</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>415.62</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>431.86</v>
+        <v>430.98</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>340.36</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>353.39</v>
+        <v>353.15</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>1014.24</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>870.53</v>
+        <v>869.85</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>723.46</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>760.96</v>
+        <v>760.77</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>195.62</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>218.65</v>
+        <v>218.49</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>231.07</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>204.16</v>
+        <v>204.04</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>880.85</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>959.51</v>
+        <v>959.97</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>1219.59</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1172.5</v>
+        <v>1170.85</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>169.05</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>190.27</v>
+        <v>189.74</v>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>14203.07</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14865.54</v>
+        <v>14852.43</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>135.2</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>162.24</v>
+        <v>162.25</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>180.68</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>208.36</v>
+        <v>208.29</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>50.35</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55.2</v>
+        <v>55.19</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>57.9</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>60.05</v>
+        <v>60.16</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6447,10 +6447,10 @@
         <v>1698.17</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1645.08</v>
+        <v>1645.07</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1385.09</v>
+        <v>1384.41</v>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1205.94</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1194.07</v>
+        <v>1193.75</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>310.05</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>325.76</v>
+        <v>325.49</v>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>437.59</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>471.75</v>
+        <v>472.41</v>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>4196.86</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2951.86</v>
+        <v>2948.77</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>342.34</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>361.58</v>
+        <v>361.32</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>103.31</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>127.84</v>
+        <v>127.58</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>1354.98</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1336.06</v>
+        <v>1334.09</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>176.7</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>188.26</v>
+        <v>187.97</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>1674.67</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1984.81</v>
+        <v>1984.13</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>385.16</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>427.05</v>
+        <v>426.24</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>853.83</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>828.15</v>
+        <v>827.25</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>347.48</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>350.35</v>
+        <v>350.08</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>199.34</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>234.47</v>
+        <v>234.43</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>1409.04</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1404.77</v>
+        <v>1402.92</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>1143.09</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1172.31</v>
+        <v>1173.59</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>75.68000000000001</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>84.02</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>257.34</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>266.02</v>
+        <v>265.83</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>34.41</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>41.7</v>
+        <v>41.65</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>391.04</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>479.88</v>
+        <v>479.92</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>583.71</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>720.47</v>
+        <v>720.78</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>145.83</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>189.64</v>
+        <v>189.48</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>609.9</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>595.9</v>
+        <v>595.46</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>9.31</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.83</v>
+        <v>10.81</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>204.24</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>241.33</v>
+        <v>241.39</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>174.73</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>165.74</v>
+        <v>165.89</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>124.75</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.82</v>
+        <v>141.9</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>711.28</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>681.66</v>
+        <v>681.0599999999999</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>27.16</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.16</v>
+        <v>32.15</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>1539.44</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1489.78</v>
+        <v>1487.32</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>858.67</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>928.36</v>
+        <v>927.67</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>2199.4</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2363.09</v>
+        <v>2362.46</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>576.5599999999999</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>556.95</v>
+        <v>556.64</v>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>249.65</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>276.67</v>
+        <v>276.66</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>128.09</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>134.75</v>
+        <v>134.56</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>3014.29</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2758.68</v>
+        <v>2758.41</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>2522.94</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2537.62</v>
+        <v>2534.94</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>208.05</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>237.35</v>
+        <v>236.77</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>192.84</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>244.43</v>
+        <v>243.52</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>127.78</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>133.79</v>
+        <v>133.65</v>
       </c>
       <c r="G171" s="13" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>257.28</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>270.86</v>
+        <v>270.58</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>553.98</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>581.51</v>
+        <v>582.02</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>2380.89</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2410.08</v>
+        <v>2408.21</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>32.72</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.62</v>
+        <v>40.64</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>9.039999999999999</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>836.27</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1022.66</v>
+        <v>1019.44</v>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>235.33</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>295.17</v>
+        <v>294.79</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>310.8</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>381.44</v>
+        <v>381.08</v>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>224.05</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>236.2</v>
+        <v>235.78</v>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>62.95</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.56999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>512.52</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>674.6</v>
+        <v>672.5599999999999</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>377.76</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>345.24</v>
+        <v>345.59</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>1627.86</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1944.15</v>
+        <v>1942.32</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>158.29</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>176.41</v>
+        <v>176.34</v>
       </c>
       <c r="G185" s="13" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>4485.59</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4587.7</v>
+        <v>4587.28</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>3562.18</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4227.49</v>
+        <v>4227.5</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>2244.27</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1829.35</v>
+        <v>1828.28</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>315.53</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>332.64</v>
+        <v>331.38</v>
       </c>
       <c r="G190" s="13" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>2129.61</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2087.19</v>
+        <v>2087.56</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>549.3200000000001</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>689.09</v>
+        <v>690.05</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9175,10 +9175,10 @@
         <v>1081.3</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1045.99</v>
+        <v>1045.98</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>928.21</v>
+        <v>927.29</v>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>847.28</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>908.83</v>
+        <v>907.6799999999999</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>139.76</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>156.42</v>
+        <v>156.61</v>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>533.41</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>605.22</v>
+        <v>605.01</v>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>371</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>360.97</v>
+        <v>361</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>26.63</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.8</v>
+        <v>27.77</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>3244.88</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2867.02</v>
+        <v>2868.37</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>403.26</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>430.24</v>
+        <v>429.66</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>38.81</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.29</v>
+        <v>36.33</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>218.4</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>224.37</v>
+        <v>225.02</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>192.7</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>224.7</v>
+        <v>223.62</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>960.16</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>878.92</v>
+        <v>879.38</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>2068.17</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2209.06</v>
+        <v>2207.57</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>754.11</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>804.89</v>
+        <v>804.66</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>858.52</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>995.73</v>
+        <v>995.41</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>134.79</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>138.19</v>
+        <v>138.11</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>253.35</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>255.77</v>
+        <v>255.44</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>346.49</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>390.49</v>
+        <v>389.15</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>645.89</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>681.58</v>
+        <v>681.99</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>229.23</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.25</v>
+        <v>253.34</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>806.74</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>902.0700000000001</v>
+        <v>903.26</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>135.38</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>147.87</v>
+        <v>147.64</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>923.72</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>736.26</v>
+        <v>735.54</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>109.42</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.73</v>
+        <v>116.5</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>470.24</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>522.65</v>
+        <v>521.09</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>1248.98</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1550.61</v>
+        <v>1547.73</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>1720.65</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1765.56</v>
+        <v>1764.5</v>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>102.86</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>123.83</v>
+        <v>123.73</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>3767.9</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3108.27</v>
+        <v>3108.66</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>1888.72</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2148.43</v>
+        <v>2148.54</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>104.31</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>129.45</v>
+        <v>129.47</v>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>393.85</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.42</v>
+        <v>396.22</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>446.26</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>436.82</v>
+        <v>436.64</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>181.78</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>192.55</v>
+        <v>192.41</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>565.1900000000001</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>561.59</v>
+        <v>559.89</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>547.71</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>585.7</v>
+        <v>585.67</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>899.33</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>963.41</v>
+        <v>962.51</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>597.33</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>677.6900000000001</v>
+        <v>677.3099999999999</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>330.23</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>366.18</v>
+        <v>365.87</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>198.7</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>201.12</v>
+        <v>200.73</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>238.1</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>250.89</v>
+        <v>250.62</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>1333.81</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1344.95</v>
+        <v>1341.31</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>523.84</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>554.96</v>
+        <v>554.76</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>487.55</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>485.97</v>
+        <v>485.84</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>1363.77</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1539.41</v>
+        <v>1538.72</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>9411.379999999999</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8382.280000000001</v>
+        <v>8373.82</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>83.8</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>97.84</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>478.87</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>496.45</v>
+        <v>496.68</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>475.81</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>559.9299999999999</v>
+        <v>560.09</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>708.91</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>669.14</v>
+        <v>669.39</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>250.05</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>314.65</v>
+        <v>313.53</v>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>459.48</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>432.65</v>
+        <v>432.15</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>472.71</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>581.3099999999999</v>
+        <v>580.73</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 01-May-2026  14:40:46    |    Closing Price Date: 30-Apr-2026</t>
+          <t>Scan Run: 04-May-2026  17:16:37    |    Closing Price Date: 04-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>82.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>79.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46.8</v>
+        <v>52.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>01-May-2026  14:40:46</t>
+          <t>04-May-2026  17:16:37</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 82.4% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 85.2% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 79.2% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 84.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 46.8% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.8% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 206 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 213 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 198 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 211 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 117 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 132 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>634</v>
+        <v>632.6</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>572.75</v>
+        <v>578.45</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>569.96</v>
+        <v>572.42</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>689.98</v>
+        <v>687.8200000000001</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>439.95</v>
+        <v>461.05</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>435.57</v>
+        <v>437.99</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>434.2</v>
+        <v>435.25</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>453.79</v>
+        <v>453.09</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -830,9 +830,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J3" s="14" t="inlineStr">
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>376.3</v>
+        <v>395.85</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>365.56</v>
+        <v>368.45</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>364.83</v>
+        <v>366.05</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>402.2</v>
+        <v>401.45</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>740.25</v>
+        <v>806.1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>693.1900000000001</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>693.14</v>
+        <v>697.5700000000001</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>740.24</v>
+        <v>739.0700000000001</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2594.1</v>
+        <v>2676.4</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2401.87</v>
+        <v>2428.01</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2268.14</v>
+        <v>2284.15</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1832.22</v>
+        <v>1840.62</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>347.7</v>
+        <v>353.65</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>308.51</v>
+        <v>312.81</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>298.3</v>
+        <v>300.47</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>303.33</v>
+        <v>303.62</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1171.8</v>
+        <v>1252</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1150.32</v>
+        <v>1160</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1092.79</v>
+        <v>1099.04</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>943.4</v>
+        <v>944.71</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>891</v>
+        <v>875</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>832.59</v>
+        <v>836.63</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>813.05</v>
+        <v>815.48</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>866.74</v>
+        <v>866.12</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>524.05</v>
+        <v>530.8</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>501.89</v>
+        <v>504.64</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>497.53</v>
+        <v>498.83</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>558.71</v>
+        <v>558.4299999999999</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1038.15</v>
+        <v>1069.2</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1028.66</v>
+        <v>1032.52</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>990.74</v>
+        <v>993.8200000000001</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>965.3200000000001</v>
+        <v>969.64</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.68</v>
+        <v>9.66</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>9</v>
+        <v>9.06</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.130000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17.5</v>
+        <v>17.38</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>531.8</v>
+        <v>537.15</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>520.2</v>
+        <v>521.8099999999999</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>499.77</v>
+        <v>501.24</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>501.74</v>
+        <v>501.53</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1343.8</v>
+        <v>1348</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1301.6</v>
+        <v>1306.02</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1283.12</v>
+        <v>1285.66</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1186.19</v>
+        <v>1186.84</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>121.73</v>
+        <v>127.64</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>119.4</v>
+        <v>120.19</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>119.12</v>
+        <v>119.45</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>134.3</v>
+        <v>133.39</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>607.3</v>
+        <v>625.2</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>600.8099999999999</v>
+        <v>603.14</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>588.12</v>
+        <v>589.58</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>588.89</v>
+        <v>587.4</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>443.15</v>
+        <v>437.6</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>449.67</v>
+        <v>448.52</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>447.17</v>
+        <v>446.79</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>470.17</v>
+        <v>468.98</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>398.55</v>
+        <v>398.15</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>383.04</v>
+        <v>384.48</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>367.62</v>
+        <v>368.82</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>344.46</v>
+        <v>344.12</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>134.25</v>
+        <v>135.81</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>130.49</v>
+        <v>131</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>131.72</v>
+        <v>131.88</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>162.71</v>
+        <v>161.4</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1125.2</v>
+        <v>1110.7</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1065.37</v>
+        <v>1069.69</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1013.12</v>
+        <v>1016.95</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>969.97</v>
+        <v>970.09</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,24 +1597,24 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>869.9</v>
+        <v>859.15</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>862.7</v>
+        <v>862.36</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>878.9400000000001</v>
+        <v>878.17</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1063.95</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1058.95</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1057.25</v>
+        <v>1140</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1041.62</v>
+        <v>1050.99</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>1004.35</v>
+        <v>1009.67</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>948.42</v>
+        <v>946.1900000000001</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,24 +1685,24 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1380.7</v>
+        <v>1327.3</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1377</v>
+        <v>1372.27</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1274.69</v>
+        <v>1276.76</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>991.26</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>994.41</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>13.74</v>
+        <v>13.73</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.5</v>
+        <v>14.43</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.03</v>
+        <v>14.98</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>351.42</v>
+        <v>351.1</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>332.74</v>
+        <v>334.48</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>330.98</v>
+        <v>331.77</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>450.59</v>
+        <v>447.58</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>2164.9</v>
+        <v>2161.7</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1921.99</v>
+        <v>1944.82</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1755.68</v>
+        <v>1771.6</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1640.07</v>
+        <v>1637.36</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>396.1</v>
+        <v>398.3</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>384.53</v>
+        <v>385.84</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>384.51</v>
+        <v>385.05</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>466.46</v>
+        <v>466.48</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1333.65</v>
+        <v>1455.5</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1192.32</v>
+        <v>1217.38</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1138.37</v>
+        <v>1150.81</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1245.16</v>
+        <v>1243.43</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>541.4</v>
+        <v>561.1</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>478.53</v>
+        <v>486.39</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>472.82</v>
+        <v>476.28</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>538.49</v>
+        <v>535.65</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>618.55</v>
+        <v>623.7</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>600.6900000000001</v>
+        <v>602.88</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>597.16</v>
+        <v>598.2</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>607.41</v>
+        <v>606.35</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>212.72</v>
+        <v>215.74</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>208.47</v>
+        <v>209.17</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>197.16</v>
+        <v>197.88</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>166.3</v>
+        <v>166.79</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3096.8</v>
+        <v>3111.6</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2797.31</v>
+        <v>2827.24</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2628.03</v>
+        <v>2646.99</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2745.54</v>
+        <v>2740.95</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,29 +2125,29 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>909.5</v>
+        <v>959.85</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>923.9299999999999</v>
+        <v>927.35</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>937.65</v>
+        <v>938.52</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1062.65</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1061.25</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>548.05</v>
+        <v>566.55</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>588.45</v>
+        <v>586.37</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>593.24</v>
+        <v>592.1900000000001</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>581.49</v>
+        <v>578.88</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>501.5</v>
+        <v>524.9</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>483.68</v>
+        <v>487.61</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>472.78</v>
+        <v>474.82</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>517.6</v>
+        <v>515.1799999999999</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2238,9 +2238,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1390.6</v>
+        <v>1432.1</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1348.75</v>
+        <v>1356.69</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1333.52</v>
+        <v>1337.39</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>473.75</v>
+        <v>477.9</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>469.39</v>
+        <v>470.2</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>457.84</v>
+        <v>458.63</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>433.28</v>
+        <v>433.31</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>290.35</v>
+        <v>290.3</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>300.5</v>
+        <v>299.53</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>303.11</v>
+        <v>302.61</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>348.86</v>
+        <v>348.77</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2389,29 +2389,29 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>381.95</v>
+        <v>392.2</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>388.43</v>
+        <v>388.79</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>390.84</v>
+        <v>390.89</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>394.76</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>394.37</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1623.4</v>
+        <v>1651.7</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1732.57</v>
+        <v>1724.87</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1862.94</v>
+        <v>1854.66</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2136.09</v>
+        <v>2132.68</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>338.6</v>
+        <v>342.05</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>312.64</v>
+        <v>315.44</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>295.07</v>
+        <v>296.91</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>275.87</v>
+        <v>275.78</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>417.5</v>
+        <v>416.9</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>420.34</v>
+        <v>420.01</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>433.1</v>
+        <v>432.47</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>512.8200000000001</v>
+        <v>510.79</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>815.25</v>
+        <v>956.45</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>648.6</v>
+        <v>677.92</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>626.29</v>
+        <v>639.24</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>702.3099999999999</v>
+        <v>704.84</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1182.2</v>
+        <v>1146</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1201.74</v>
+        <v>1196.43</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1251.08</v>
+        <v>1246.96</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1460.69</v>
+        <v>1461.37</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>393.1</v>
+        <v>400.7</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>353.3</v>
+        <v>357.81</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>341.05</v>
+        <v>343.39</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>390.4</v>
+        <v>389.16</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>186.76</v>
+        <v>185.66</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>186.78</v>
+        <v>186.67</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>182.93</v>
+        <v>183.04</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>166.08</v>
+        <v>166.39</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>732.8</v>
+        <v>729.7</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>717.21</v>
+        <v>718.4</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723</v>
+        <v>723.26</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>758.78</v>
+        <v>756.54</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1079.65</v>
+        <v>1096.7</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1032.09</v>
+        <v>1038.24</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1036.54</v>
+        <v>1038.9</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1211.94</v>
+        <v>1207.49</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>157.8</v>
+        <v>166.02</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>150.36</v>
+        <v>151.85</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>141.65</v>
+        <v>142.6</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>136.87</v>
+        <v>136.72</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>464.8</v>
+        <v>474.9</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>449.11</v>
+        <v>451.57</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>442.69</v>
+        <v>443.95</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>455.65</v>
+        <v>454.18</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>183.18</v>
+        <v>186.36</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>169.84</v>
+        <v>171.41</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>175.44</v>
+        <v>175.86</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>215.08</v>
+        <v>213.78</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1099.9</v>
+        <v>1094.9</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1083.17</v>
+        <v>1084.28</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1092.22</v>
+        <v>1092.32</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1175.71</v>
+        <v>1170.78</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>11568</v>
+        <v>11481</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>10908.47</v>
+        <v>10963</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>10235.68</v>
+        <v>10284.51</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8895.190000000001</v>
+        <v>8898.83</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>226.13</v>
+        <v>224.99</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>223.66</v>
+        <v>223.78</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>216.1</v>
+        <v>216.45</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>212.33</v>
+        <v>211.85</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.86</v>
+        <v>7.82</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.63</v>
+        <v>7.65</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.48</v>
+        <v>7.49</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.32</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>114.25</v>
+        <v>116.79</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>116.93</v>
+        <v>116.91</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>113.85</v>
+        <v>113.96</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>110.01</v>
+        <v>109.92</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>124.34</v>
+        <v>120.3</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>108.01</v>
+        <v>109.18</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>102.66</v>
+        <v>103.35</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>114.38</v>
+        <v>113.86</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>81.98999999999999</v>
+        <v>88.62</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>80.53</v>
+        <v>81.3</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>77.55</v>
+        <v>77.98</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.44</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3250,9 +3250,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
@@ -3269,20 +3269,20 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>46.28</v>
+        <v>48.59</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>48.66</v>
+        <v>48.65</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>54.2</v>
+        <v>53.98</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>77.84999999999999</v>
+        <v>77.02</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1216.4</v>
+        <v>1233.4</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1216.25</v>
+        <v>1217.88</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1174.31</v>
+        <v>1176.62</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1154.52</v>
+        <v>1157.22</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>211.94</v>
+        <v>213.53</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>197.57</v>
+        <v>199.09</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>183.17</v>
+        <v>184.36</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>201.65</v>
+        <v>200.88</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1215.65</v>
+        <v>1328.7</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1125.82</v>
+        <v>1145.14</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1064.31</v>
+        <v>1074.68</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1311.34</v>
+        <v>1315.77</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3426,9 +3426,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I62" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J62" s="14" t="inlineStr">
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>66.84999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>63.67</v>
+        <v>64.36</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>62.39</v>
+        <v>62.72</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>62.34</v>
+        <v>62.1</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2401.8</v>
+        <v>2389.5</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2460.04</v>
+        <v>2453.32</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2435.36</v>
+        <v>2433.56</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2579.71</v>
+        <v>2574.72</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>498.65</v>
+        <v>506.5</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>491.01</v>
+        <v>492.49</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>491.78</v>
+        <v>492.35</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>533.21</v>
+        <v>531.99</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>364.45</v>
+        <v>371.85</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>357.61</v>
+        <v>358.97</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>359.73</v>
+        <v>360.2</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>397.02</v>
+        <v>397.15</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2182.7</v>
+        <v>2270.3</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2177.08</v>
+        <v>2185.96</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2163.5</v>
+        <v>2167.69</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2071.55</v>
+        <v>2070.97</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4628.1</v>
+        <v>4597.7</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4701.01</v>
+        <v>4691.17</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4548.2</v>
+        <v>4550.14</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4487.37</v>
+        <v>4482.37</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>937.2</v>
+        <v>945.25</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>885.51</v>
+        <v>891.2</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>901.9</v>
+        <v>903.6</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1029.14</v>
+        <v>1027.11</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>506.8</v>
+        <v>528.05</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>493.73</v>
+        <v>497</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>490.38</v>
+        <v>491.86</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>544.1900000000001</v>
+        <v>542.58</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>905.55</v>
+        <v>909.35</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>901.74</v>
+        <v>902.47</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>916.38</v>
+        <v>916.1</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1032.98</v>
+        <v>1029.02</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>106.55</v>
+        <v>107.75</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>106.18</v>
+        <v>106.33</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>106.13</v>
+        <v>106.2</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>110.46</v>
+        <v>109.92</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>1025.6</v>
+        <v>1028.7</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>974.23</v>
+        <v>979.42</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>951.86</v>
+        <v>954.88</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>945.6</v>
+        <v>946.16</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>861.85</v>
+        <v>872.5</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>779.3099999999999</v>
+        <v>788.1799999999999</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>682.3200000000001</v>
+        <v>689.78</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>588.63</v>
+        <v>591.1</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>665.55</v>
+        <v>658.45</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>635.87</v>
+        <v>638.02</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>645.05</v>
+        <v>645.58</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>747.72</v>
+        <v>746.84</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1049.55</v>
+        <v>1051.2</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1016</v>
+        <v>1019.36</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>937.24</v>
+        <v>941.71</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1038.73</v>
+        <v>1035.65</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>3999</v>
+        <v>4271.7</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3906.76</v>
+        <v>3941.52</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3828.03</v>
+        <v>3845.43</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3651.52</v>
+        <v>3639.26</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,29 +4105,29 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>614.75</v>
+        <v>634.65</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>624.53</v>
+        <v>625.5</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>631.89</v>
+        <v>631.99</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>698.39</v>
-      </c>
-      <c r="G78" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H78" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>696.61</v>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>57.37</v>
+        <v>59.33</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>57</v>
+        <v>57.22</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>56.6</v>
+        <v>56.71</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>58.97</v>
+        <v>58.86</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4174,9 +4174,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J79" s="14" t="inlineStr">
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>703.7</v>
+        <v>692.35</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>691.91</v>
+        <v>691.95</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>678.71</v>
+        <v>679.25</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>752.25</v>
+        <v>747.45</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>165.18</v>
+        <v>167.66</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>155.74</v>
+        <v>156.87</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>154.51</v>
+        <v>155.03</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>179.95</v>
+        <v>179.86</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>228.91</v>
+        <v>232.6</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>208.67</v>
+        <v>210.95</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>207.36</v>
+        <v>208.35</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>237.82</v>
+        <v>237.53</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>155.75</v>
+        <v>154.96</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>149.3</v>
+        <v>149.84</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>143.13</v>
+        <v>143.59</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>127.84</v>
+        <v>128.14</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>469.3</v>
+        <v>476.2</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>457.45</v>
+        <v>459.24</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>449.07</v>
+        <v>450.13</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>474.27</v>
+        <v>473.69</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4394,9 +4394,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I84" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
@@ -4413,20 +4413,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>156.05</v>
+        <v>158.97</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>155.63</v>
+        <v>155.95</v>
       </c>
       <c r="E85" s="11" t="n">
         <v>158.97</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>161.46</v>
+        <v>161.07</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>170.39</v>
+        <v>173.1</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>168.17</v>
+        <v>168.64</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>166.6</v>
+        <v>166.85</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>178.48</v>
+        <v>177.94</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>983.3</v>
+        <v>977.95</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>964.4299999999999</v>
+        <v>965.72</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>988.9400000000001</v>
+        <v>988.5</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1080.11</v>
+        <v>1076.26</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4545,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>595</v>
+        <v>598.8</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>580.5</v>
+        <v>582.24</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>578.72</v>
+        <v>579.51</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>763.1</v>
+        <v>758.29</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>572.55</v>
+        <v>605.85</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>564.58</v>
+        <v>568.51</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>571.08</v>
+        <v>572.4400000000001</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>606.95</v>
+        <v>606.24</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,29 +4633,29 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>128.12</v>
+        <v>135.25</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>128.13</v>
+        <v>128.81</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.15</v>
+        <v>130.35</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>136.43</v>
-      </c>
-      <c r="G90" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H90" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>135.91</v>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I90" s="13" t="inlineStr">
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>358.15</v>
+        <v>362</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>348.12</v>
+        <v>349.44</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>347.76</v>
+        <v>348.32</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>402.36</v>
+        <v>400.11</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,20 +4721,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>189.25</v>
+        <v>194.72</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>183.12</v>
+        <v>184.23</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>185.2</v>
+        <v>185.57</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>233.35</v>
+        <v>231.66</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>22.04</v>
+        <v>22.35</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>19.3</v>
+        <v>19.59</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>18.33</v>
+        <v>18.49</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.77</v>
+        <v>21.66</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1142.85</v>
+        <v>1217.7</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1107.72</v>
+        <v>1118.19</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1118.24</v>
+        <v>1122.14</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1342.54</v>
+        <v>1332.75</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>312.33</v>
+        <v>313.95</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>304.15</v>
+        <v>305.08</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>301.77</v>
+        <v>302.25</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>305.32</v>
+        <v>304.1</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>45.48</v>
+        <v>45.76</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>45.85</v>
+        <v>45.84</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>45.31</v>
+        <v>45.33</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>50.99</v>
+        <v>50.7</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -4941,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>1042.05</v>
+        <v>1037.9</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>955.66</v>
+        <v>963.49</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>929.58</v>
+        <v>933.83</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>906.34</v>
+        <v>905.16</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>809.6</v>
+        <v>824.15</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>791.87</v>
+        <v>794.9400000000001</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>772.42</v>
+        <v>774.45</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>798.37</v>
+        <v>798.54</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,24 +5029,24 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1502.6</v>
+        <v>1429.9</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1469.28</v>
+        <v>1465.53</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1376.12</v>
+        <v>1378.23</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1190.6</v>
-      </c>
-      <c r="G99" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1190.89</v>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>860.2</v>
+        <v>856.9</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>842.33</v>
+        <v>843.72</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>871.33</v>
+        <v>870.77</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1019.93</v>
+        <v>1015.97</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>277.36</v>
+        <v>295.4</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>264.28</v>
+        <v>267.25</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>262.33</v>
+        <v>263.63</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>272.92</v>
+        <v>272.42</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4417.7</v>
+        <v>4345.9</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>4074.97</v>
+        <v>4100.78</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3881.01</v>
+        <v>3899.24</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3725.43</v>
+        <v>3723.13</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>752.05</v>
+        <v>844.4</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>716.72</v>
+        <v>728.88</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>706.09</v>
+        <v>711.52</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>757.29</v>
+        <v>755.25</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5230,9 +5230,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J103" s="14" t="inlineStr">
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>180.73</v>
+        <v>188.98</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>168.23</v>
+        <v>170.2</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>165.46</v>
+        <v>166.39</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>177.06</v>
+        <v>176.38</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>396.4</v>
+        <v>411.65</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>386.86</v>
+        <v>389.22</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>373.63</v>
+        <v>375.12</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>403.35</v>
+        <v>400.65</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5318,9 +5318,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1088.95</v>
+        <v>1084.1</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>1024.27</v>
+        <v>1029.96</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>956.14</v>
+        <v>961.16</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>940.4</v>
+        <v>936.41</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>519.9</v>
+        <v>518.5</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>502.74</v>
+        <v>504.24</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>508.33</v>
+        <v>508.73</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>575.59</v>
+        <v>574.8099999999999</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5425,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>645.1</v>
+        <v>656.4</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>643.08</v>
+        <v>644.35</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>656.64</v>
+        <v>656.63</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>747.61</v>
+        <v>748.54</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5469,24 +5469,24 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>360.25</v>
+        <v>369.5</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>360.7</v>
+        <v>361.54</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>351.22</v>
+        <v>351.94</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>356.53</v>
-      </c>
-      <c r="G109" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>355.88</v>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>78.29000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>71.08</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>67.98999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>82.34999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5538,9 +5538,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J110" s="14" t="inlineStr">
@@ -5557,29 +5557,29 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>32.52</v>
+        <v>33.46</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>32.31</v>
+        <v>32.42</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.27</v>
+        <v>33.28</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.5</v>
+        <v>42.12</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H111" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H111" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I111" s="13" t="inlineStr">
@@ -5601,29 +5601,29 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>121.56</v>
+        <v>125.21</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>123.56</v>
+        <v>123.72</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.51</v>
+        <v>124.54</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.71</v>
-      </c>
-      <c r="G112" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H112" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>114.69</v>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I112" s="12" t="inlineStr">
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>458.15</v>
+        <v>446.65</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>427.32</v>
+        <v>429.16</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>402.88</v>
+        <v>404.59</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>420.62</v>
+        <v>419.38</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>25.9</v>
+        <v>26.22</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>24.81</v>
+        <v>24.95</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>24.55</v>
+        <v>24.62</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>33.72</v>
+        <v>33.76</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>525.95</v>
+        <v>526.45</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>539.1900000000001</v>
+        <v>537.97</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>563.17</v>
+        <v>561.73</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>692.96</v>
+        <v>687.48</v>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>125.13</v>
+        <v>125.51</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>122.92</v>
+        <v>123.17</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>126.85</v>
+        <v>126.8</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>162.99</v>
+        <v>161.96</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>447.95</v>
+        <v>459.05</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>432.35</v>
+        <v>434.9</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>415.62</v>
+        <v>417.32</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>430.98</v>
+        <v>428.84</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>367.15</v>
+        <v>371.3</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>348.71</v>
+        <v>350.86</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>340.36</v>
+        <v>341.57</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>353.15</v>
+        <v>352.91</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1295.35</v>
+        <v>1222.9</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1159.68</v>
+        <v>1165.71</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>1014.24</v>
+        <v>1022.43</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>869.85</v>
+        <v>869.24</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>849.7</v>
+        <v>885.85</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>752.14</v>
+        <v>764.87</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>723.46</v>
+        <v>729.83</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>760.77</v>
+        <v>758.04</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>197.19</v>
+        <v>196.69</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>194.67</v>
+        <v>194.86</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>195.62</v>
+        <v>195.66</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>218.49</v>
+        <v>218.08</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>268.61</v>
+        <v>274.4</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>247.06</v>
+        <v>249.67</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>231.07</v>
+        <v>232.76</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>204.04</v>
+        <v>204.46</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>965.35</v>
+        <v>972.75</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>910.3099999999999</v>
+        <v>916.25</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>880.85</v>
+        <v>884.45</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>959.97</v>
+        <v>958.58</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1503.3</v>
+        <v>1563</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1322.39</v>
+        <v>1345.3</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1219.59</v>
+        <v>1233.06</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1170.85</v>
+        <v>1172.24</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,24 +6173,24 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>164.49</v>
+        <v>167.83</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>165.86</v>
+        <v>166.05</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>169.05</v>
+        <v>169</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>189.74</v>
-      </c>
-      <c r="G125" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>188.19</v>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H125" s="13" t="inlineStr">
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14562</v>
+        <v>14466</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>14169.92</v>
+        <v>14198.12</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14203.07</v>
+        <v>14213.37</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14852.43</v>
+        <v>14798.86</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6261,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>144.34</v>
+        <v>145.49</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>137.54</v>
+        <v>138.3</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>135.2</v>
+        <v>135.61</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>162.25</v>
+        <v>161.39</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>168.08</v>
+        <v>169.68</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>172.46</v>
+        <v>172.19</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>180.68</v>
+        <v>180.24</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>208.29</v>
+        <v>207.66</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>57.77</v>
+        <v>58.42</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>53.49</v>
+        <v>53.96</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>50.35</v>
+        <v>50.66</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55.19</v>
+        <v>54.96</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>68.51000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>62.6</v>
+        <v>63.13</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>57.9</v>
+        <v>58.31</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>60.16</v>
+        <v>59.96</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1621.4</v>
+        <v>1568.3</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1698.17</v>
+        <v>1685.8</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1645.07</v>
+        <v>1642.06</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1384.41</v>
+        <v>1384.96</v>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1398.2</v>
+        <v>1457.5</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1391.06</v>
+        <v>1397.38</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1205.94</v>
+        <v>1215.8</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1193.75</v>
+        <v>1189.73</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>310.9</v>
+        <v>313.15</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>314.62</v>
+        <v>314.48</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>310.05</v>
+        <v>310.17</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>325.49</v>
+        <v>323.77</v>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
@@ -6569,29 +6569,29 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>433.15</v>
+        <v>442.8</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>436.19</v>
+        <v>436.82</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>437.59</v>
+        <v>437.8</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>472.41</v>
-      </c>
-      <c r="G134" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H134" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>469.5</v>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I134" s="13" t="inlineStr">
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>6457.1</v>
+        <v>6127.5</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>4908.27</v>
+        <v>5024.39</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>4196.86</v>
+        <v>4272.58</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2948.77</v>
+        <v>2976.95</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>340.5</v>
+        <v>335.85</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>333.04</v>
+        <v>333.31</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>342.34</v>
+        <v>342.08</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>361.32</v>
+        <v>360.29</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>120.35</v>
+        <v>123.64</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>104.75</v>
+        <v>106.55</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>103.31</v>
+        <v>104.11</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>127.58</v>
+        <v>126.35</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1509</v>
+        <v>1530.2</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1391.33</v>
+        <v>1404.56</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1354.98</v>
+        <v>1361.85</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1334.09</v>
+        <v>1332.62</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>184.63</v>
+        <v>189.29</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>180.43</v>
+        <v>181.27</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>176.7</v>
+        <v>177.19</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>187.97</v>
+        <v>187.11</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6814,9 +6814,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I139" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J139" s="14" t="inlineStr">
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1694.2</v>
+        <v>1675.6</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1657.36</v>
+        <v>1659.1</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1674.67</v>
+        <v>1674.71</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1984.13</v>
+        <v>1971.64</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>391.3</v>
+        <v>405.25</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>384.45</v>
+        <v>386.43</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>385.16</v>
+        <v>385.95</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>426.24</v>
+        <v>423.89</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,24 +6921,24 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>872.15</v>
+        <v>869.5</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>871.5</v>
+        <v>871.3099999999999</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>853.83</v>
+        <v>854.4400000000001</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>827.25</v>
-      </c>
-      <c r="G142" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>826.36</v>
+      </c>
+      <c r="G142" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>389.9</v>
+        <v>394.5</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>362.81</v>
+        <v>365.82</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>347.48</v>
+        <v>349.32</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>350.08</v>
+        <v>349.73</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>196.21</v>
+        <v>198.13</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>195.06</v>
+        <v>195.35</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>199.34</v>
+        <v>199.29</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>234.43</v>
+        <v>234.11</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1637.5</v>
+        <v>1686.8</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1512.63</v>
+        <v>1529.21</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1409.04</v>
+        <v>1419.93</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1402.92</v>
+        <v>1395.1</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1227.7</v>
+        <v>1285.3</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1166.09</v>
+        <v>1177.44</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1143.09</v>
+        <v>1148.67</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1173.59</v>
+        <v>1171.98</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>77.91</v>
+        <v>78.23</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>75.56999999999999</v>
+        <v>75.83</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.68000000000001</v>
+        <v>75.78</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>83.95999999999999</v>
+        <v>83.64</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>263.56</v>
+        <v>267.3</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>260.84</v>
+        <v>261.45</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>257.34</v>
+        <v>257.73</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>265.83</v>
+        <v>265.2</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7210,9 +7210,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I148" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I148" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J148" s="14" t="inlineStr">
@@ -7229,29 +7229,29 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>34.43</v>
+        <v>34.41</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>34.13</v>
+        <v>34.16</v>
       </c>
       <c r="E149" s="11" t="n">
         <v>34.41</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>41.65</v>
+        <v>41.4</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H149" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I149" s="13" t="inlineStr">
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>415.8</v>
+        <v>429.85</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>392.96</v>
+        <v>396.47</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>391.04</v>
+        <v>392.56</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>479.92</v>
+        <v>477.04</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>625.75</v>
+        <v>629.2</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>568.3</v>
+        <v>574.1</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>583.71</v>
+        <v>585.49</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>720.78</v>
+        <v>714.33</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,24 +7361,24 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>143.8</v>
+        <v>142.29</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>143.11</v>
+        <v>143.03</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.83</v>
+        <v>145.69</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>189.48</v>
-      </c>
-      <c r="G152" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>188.93</v>
+      </c>
+      <c r="G152" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>412.35</v>
+        <v>414.15</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>388.22</v>
+        <v>390.69</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>377.01</v>
+        <v>378.47</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>501.36</v>
+        <v>500.49</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>653.75</v>
+        <v>674.8</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>642.1</v>
+        <v>645.21</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>609.9</v>
+        <v>612.45</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>595.46</v>
+        <v>594.14</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.369999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>9.279999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E155" s="11" t="n">
         <v>9.31</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.81</v>
+        <v>10.77</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>213.87</v>
+        <v>215.34</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>204.6</v>
+        <v>205.63</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>204.24</v>
+        <v>204.67</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>241.39</v>
+        <v>240.56</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>207.7</v>
+        <v>217.09</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>185</v>
+        <v>188.05</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>174.73</v>
+        <v>176.39</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>165.89</v>
+        <v>166.03</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,24 +7625,24 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>128.96</v>
+        <v>126.33</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>126.68</v>
+        <v>126.65</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>124.75</v>
+        <v>124.81</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.9</v>
-      </c>
-      <c r="G158" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>141.1</v>
+      </c>
+      <c r="G158" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>794.25</v>
+        <v>782.35</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>756.96</v>
+        <v>759.37</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>711.28</v>
+        <v>714.0700000000001</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>681.0599999999999</v>
+        <v>681.6900000000001</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>28.38</v>
+        <v>28.73</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>27.4</v>
+        <v>27.53</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>27.16</v>
+        <v>27.22</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>32.15</v>
+        <v>31.94</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,29 +7757,29 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1535.8</v>
+        <v>1548.7</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1549.75</v>
+        <v>1549.65</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1539.44</v>
+        <v>1539.8</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1487.32</v>
+        <v>1485.27</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H161" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H161" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>946.2</v>
+        <v>940.65</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>883.8099999999999</v>
+        <v>889.22</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>858.67</v>
+        <v>861.89</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>927.67</v>
+        <v>922.52</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2481.8</v>
+        <v>2472.5</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2313.34</v>
+        <v>2328.5</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2199.4</v>
+        <v>2210.11</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2362.46</v>
+        <v>2356.79</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>572.75</v>
+        <v>576.4</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>581.77</v>
+        <v>581.26</v>
       </c>
       <c r="E164" s="11" t="n">
         <v>576.5599999999999</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>556.64</v>
+        <v>555</v>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>259.39</v>
+        <v>261.75</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>253.59</v>
+        <v>254.37</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>249.65</v>
+        <v>250.12</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>276.66</v>
+        <v>275.62</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>133.84</v>
+        <v>134.02</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>129.74</v>
+        <v>130.15</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>128.09</v>
+        <v>128.32</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>134.56</v>
+        <v>134.04</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3360.1</v>
+        <v>3362.8</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>3127.65</v>
+        <v>3150.05</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>3014.29</v>
+        <v>3027.96</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2758.41</v>
+        <v>2759.4</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2826.1</v>
+        <v>2855.3</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2647.59</v>
+        <v>2667.37</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2522.94</v>
+        <v>2535.97</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2534.94</v>
+        <v>2523.88</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>214.37</v>
+        <v>219.88</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>209.34</v>
+        <v>210.34</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>208.05</v>
+        <v>208.51</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>236.77</v>
+        <v>234.53</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8153,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>197.68</v>
+        <v>211.63</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>193.17</v>
+        <v>194.93</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>192.84</v>
+        <v>193.58</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>243.52</v>
+        <v>241.73</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8197,24 +8197,24 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>126.2</v>
+        <v>127.62</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>126.77</v>
+        <v>126.85</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>127.78</v>
+        <v>127.77</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>133.65</v>
-      </c>
-      <c r="G171" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>133.02</v>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr">
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>265.91</v>
+        <v>261.8</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>258.21</v>
+        <v>258.55</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>257.28</v>
+        <v>257.46</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>270.58</v>
+        <v>269.77</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>602.6</v>
+        <v>605.05</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>563.7</v>
+        <v>567.63</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>553.98</v>
+        <v>555.98</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>582.02</v>
+        <v>579.73</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2645</v>
+        <v>2710</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2475.23</v>
+        <v>2497.59</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2380.89</v>
+        <v>2393.8</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2408.21</v>
+        <v>2408.74</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>35.52</v>
+        <v>36.49</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>33.57</v>
+        <v>33.85</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>32.72</v>
+        <v>32.86</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.64</v>
+        <v>40.32</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8417,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>10.12</v>
+        <v>10.15</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.93</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>794.2</v>
+        <v>793.65</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>801.85</v>
+        <v>801.0700000000001</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>836.27</v>
+        <v>834.6</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1019.44</v>
+        <v>1011.65</v>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>263.86</v>
+        <v>260.6</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>243.44</v>
+        <v>245.07</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>235.33</v>
+        <v>236.33</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>294.79</v>
+        <v>295.61</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8549,24 +8549,24 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>298.09</v>
+        <v>301.05</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>298.5</v>
+        <v>298.75</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>310.8</v>
+        <v>310.42</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>381.08</v>
-      </c>
-      <c r="G179" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>379.42</v>
+      </c>
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H179" s="13" t="inlineStr">
@@ -8593,20 +8593,20 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>221.64</v>
+        <v>221.96</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>222.56</v>
+        <v>222.51</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>224.05</v>
+        <v>223.97</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>235.78</v>
+        <v>235.6</v>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>65.36</v>
+        <v>66.48</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>63.25</v>
+        <v>63.56</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>62.95</v>
+        <v>63.08</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>67.53</v>
+        <v>67.3</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>527.15</v>
+        <v>544.85</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>504.44</v>
+        <v>508.29</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>512.52</v>
+        <v>513.78</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>672.5599999999999</v>
+        <v>669.09</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>453.9</v>
+        <v>456.6</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>407.97</v>
+        <v>412.6</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>377.76</v>
+        <v>380.85</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>345.59</v>
+        <v>345.11</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1412.5</v>
+        <v>1418.9</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1511.42</v>
+        <v>1502.61</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1627.86</v>
+        <v>1619.66</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1942.32</v>
+        <v>1937.67</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8813,29 +8813,29 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>156.27</v>
+        <v>161.92</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>157.73</v>
+        <v>158.13</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>158.29</v>
+        <v>158.44</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>176.34</v>
-      </c>
-      <c r="G185" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H185" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>175.66</v>
+      </c>
+      <c r="G185" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H185" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I185" s="13" t="inlineStr">
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>210.61</v>
+        <v>210.63</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>206.61</v>
+        <v>206.99</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>203.79</v>
+        <v>204.06</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>194.53</v>
+        <v>194.54</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4763.9</v>
+        <v>4738</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4608.17</v>
+        <v>4620.54</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4485.59</v>
+        <v>4495.49</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4587.28</v>
+        <v>4585.78</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3407.2</v>
+        <v>3399.9</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3443.87</v>
+        <v>3439.68</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3562.18</v>
+        <v>3555.82</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4227.5</v>
+        <v>4215.45</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2513.6</v>
+        <v>2489.8</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2402.82</v>
+        <v>2411.1</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2244.27</v>
+        <v>2253.9</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1828.28</v>
+        <v>1831.98</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,34 +9033,34 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>313.1</v>
+        <v>335.3</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>317.66</v>
+        <v>319.34</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>315.53</v>
+        <v>316.31</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>331.38</v>
-      </c>
-      <c r="G190" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H190" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I190" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>330.29</v>
+      </c>
+      <c r="G190" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H190" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I190" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J190" s="14" t="inlineStr">
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>2532.6</v>
+        <v>2579</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>2198.38</v>
+        <v>2234.63</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2129.61</v>
+        <v>2147.23</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2087.56</v>
+        <v>2086.11</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>564.3</v>
+        <v>562.35</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>542.5599999999999</v>
+        <v>544.45</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>549.3200000000001</v>
+        <v>549.83</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>690.05</v>
+        <v>685.04</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9165,29 +9165,29 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1072.75</v>
+        <v>1039.7</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1081.3</v>
+        <v>1077.34</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1045.98</v>
+        <v>1045.74</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>927.29</v>
+        <v>926.1900000000001</v>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H193" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H193" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I193" s="12" t="inlineStr">
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>863.75</v>
+        <v>884.4</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>843.4299999999999</v>
+        <v>847.33</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>847.28</v>
+        <v>848.74</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>907.6799999999999</v>
+        <v>907.01</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,29 +9253,29 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>137.45</v>
+        <v>142.55</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>141</v>
+        <v>141.15</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>139.76</v>
+        <v>139.87</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>156.61</v>
-      </c>
-      <c r="G195" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H195" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>155.05</v>
+      </c>
+      <c r="G195" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H195" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I195" s="13" t="inlineStr">
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>509.05</v>
+        <v>522.05</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>526.24</v>
+        <v>525.84</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>533.41</v>
+        <v>532.96</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>605.01</v>
+        <v>603.6799999999999</v>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>406.65</v>
+        <v>418.7</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>398.79</v>
+        <v>400.69</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>371</v>
+        <v>372.87</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>361</v>
+        <v>359.67</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>29.21</v>
+        <v>29.14</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>27.7</v>
+        <v>27.84</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>26.63</v>
+        <v>26.73</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.77</v>
+        <v>27.68</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3491.1</v>
+        <v>3570.3</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3423.01</v>
+        <v>3437.04</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3244.88</v>
+        <v>3257.64</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2868.37</v>
+        <v>2872.41</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>478.45</v>
+        <v>490.7</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>433.1</v>
+        <v>438.58</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>403.26</v>
+        <v>406.69</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>429.66</v>
+        <v>428.06</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>39.46</v>
+        <v>41.06</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>38.84</v>
+        <v>39.05</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>38.81</v>
+        <v>38.9</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.33</v>
+        <v>36.28</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>230.29</v>
+        <v>238.25</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>223.36</v>
+        <v>224.78</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>218.4</v>
+        <v>219.18</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>225.02</v>
+        <v>224.49</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>208.34</v>
+        <v>212.07</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>198.91</v>
+        <v>200.16</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>192.7</v>
+        <v>193.46</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>223.62</v>
+        <v>221.66</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>294.8</v>
+        <v>309.35</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>254.64</v>
+        <v>259.85</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>211.79</v>
+        <v>215.62</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>147.76</v>
+        <v>149.08</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>1036.8</v>
+        <v>1031.5</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>1011.32</v>
+        <v>1013.24</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>960.16</v>
+        <v>962.95</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>879.38</v>
+        <v>880.6799999999999</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2260.9</v>
+        <v>2245.3</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2175.96</v>
+        <v>2182.56</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>2068.17</v>
+        <v>2075.12</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2207.57</v>
+        <v>2201.95</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>778.55</v>
+        <v>775.7</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>756.27</v>
+        <v>758.12</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>754.11</v>
+        <v>754.96</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>804.66</v>
+        <v>803.85</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>914.35</v>
+        <v>943</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>858.51</v>
+        <v>866.55</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>858.52</v>
+        <v>861.83</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>995.41</v>
+        <v>989.92</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9869,24 +9869,24 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>143.04</v>
+        <v>139.7</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>140.44</v>
+        <v>140.37</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>134.79</v>
+        <v>134.98</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>138.11</v>
-      </c>
-      <c r="G209" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>137.68</v>
+      </c>
+      <c r="G209" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H209" s="12" t="inlineStr">
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>292.61</v>
+        <v>321.15</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>269.51</v>
+        <v>274.43</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>253.35</v>
+        <v>256.01</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>255.44</v>
+        <v>255.13</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>340.25</v>
+        <v>339</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>337.69</v>
+        <v>337.82</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>346.49</v>
+        <v>346.2</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>389.15</v>
+        <v>388.55</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>694.9</v>
+        <v>691.2</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>651.55</v>
+        <v>655.3200000000001</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>645.89</v>
+        <v>647.67</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>681.99</v>
+        <v>679.84</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>250.12</v>
+        <v>267.9</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>232.15</v>
+        <v>235.55</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>229.23</v>
+        <v>230.74</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.34</v>
+        <v>253.69</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10070,9 +10070,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I213" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I213" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J213" s="14" t="inlineStr">
@@ -10089,20 +10089,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>846.8</v>
+        <v>824.55</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>806.45</v>
+        <v>808.1799999999999</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>806.74</v>
+        <v>807.4400000000001</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>903.26</v>
+        <v>901.92</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10133,29 +10133,29 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>132.71</v>
+        <v>138.19</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>132.33</v>
+        <v>132.89</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>135.38</v>
+        <v>135.49</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>147.64</v>
+        <v>146.99</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H215" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H215" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I215" s="13" t="inlineStr">
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1152.7</v>
+        <v>1162.5</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>1019.12</v>
+        <v>1032.77</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>923.72</v>
+        <v>933.08</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>735.54</v>
+        <v>739.38</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>402.95</v>
+        <v>414.2</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>395.93</v>
+        <v>397.67</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>397.71</v>
+        <v>398.36</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>480.02</v>
+        <v>479.36</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>114.51</v>
+        <v>116.98</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>111.66</v>
+        <v>112.17</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>109.42</v>
+        <v>109.72</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>116.5</v>
+        <v>115.97</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10290,9 +10290,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I218" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I218" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J218" s="14" t="inlineStr">
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>511.95</v>
+        <v>526.9</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>487.65</v>
+        <v>491.39</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>470.24</v>
+        <v>472.46</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>521.09</v>
+        <v>518.99</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10334,9 +10334,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I219" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I219" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J219" s="14" t="inlineStr">
@@ -10353,29 +10353,29 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1232.3</v>
+        <v>1271.3</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1219.96</v>
+        <v>1224.85</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1248.98</v>
+        <v>1249.85</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1547.73</v>
+        <v>1543.43</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H220" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H220" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I220" s="13" t="inlineStr">
@@ -10397,20 +10397,20 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1663.4</v>
+        <v>1659.2</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1696.58</v>
+        <v>1693.02</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1720.65</v>
+        <v>1718.24</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1764.5</v>
+        <v>1757</v>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
@@ -10441,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>105.47</v>
+        <v>107.94</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>101.59</v>
+        <v>102.19</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>102.86</v>
+        <v>103.06</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>123.73</v>
+        <v>122.87</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>3955.8</v>
+        <v>3989.7</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3924.21</v>
+        <v>3930.45</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3767.9</v>
+        <v>3776.6</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3108.66</v>
+        <v>3115.54</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2062.2</v>
+        <v>2077.5</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1987.58</v>
+        <v>1996.15</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1888.72</v>
+        <v>1896.12</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2148.54</v>
+        <v>2139.57</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>93.55</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>100.2</v>
+        <v>99.61</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>104.31</v>
+        <v>103.9</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>129.47</v>
+        <v>128.6</v>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>400.3</v>
+        <v>420.4</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>393.18</v>
+        <v>395.77</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>393.85</v>
+        <v>394.89</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.22</v>
+        <v>396.23</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>464.1</v>
+        <v>473</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>452.52</v>
+        <v>454.47</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>446.26</v>
+        <v>447.31</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>436.64</v>
+        <v>435.31</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>193.01</v>
+        <v>188.36</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>184.43</v>
+        <v>184.8</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>181.78</v>
+        <v>182.04</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>192.41</v>
+        <v>191.63</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10730,9 +10730,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I228" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I228" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J228" s="14" t="inlineStr">
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>649.7</v>
+        <v>645.5</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>600.23</v>
+        <v>604.54</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>565.1900000000001</v>
+        <v>568.34</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>559.89</v>
+        <v>560.08</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>598.95</v>
+        <v>602.15</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>566.85</v>
+        <v>570.21</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>547.71</v>
+        <v>549.85</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>585.67</v>
+        <v>582.8200000000001</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10837,29 +10837,29 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>56.88</v>
+        <v>61.37</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>57.14</v>
+        <v>57.55</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>57.02</v>
+        <v>57.19</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="G231" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H231" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>52.94</v>
+      </c>
+      <c r="G231" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H231" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I231" s="12" t="inlineStr">
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>1002.4</v>
+        <v>1031.4</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>944.35</v>
+        <v>952.64</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>899.33</v>
+        <v>904.51</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>962.51</v>
+        <v>961.33</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>616.45</v>
+        <v>635.7</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>609.66</v>
+        <v>612.14</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>597.33</v>
+        <v>598.83</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>677.3099999999999</v>
+        <v>675.59</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>296.25</v>
+        <v>296.05</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>312.32</v>
+        <v>310.77</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>330.23</v>
+        <v>328.89</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>365.87</v>
+        <v>364.35</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11013,34 +11013,34 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>198.65</v>
+        <v>203.36</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>198.58</v>
+        <v>199.03</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>198.7</v>
+        <v>198.88</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>200.73</v>
+        <v>201.21</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H235" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I235" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H235" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I235" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J235" s="14" t="inlineStr">
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>258.37</v>
+        <v>258.4</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>246.68</v>
+        <v>247.8</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>238.1</v>
+        <v>238.89</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>250.62</v>
+        <v>250.43</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1509.6</v>
+        <v>1510.4</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1412.69</v>
+        <v>1422</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1333.81</v>
+        <v>1340.74</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1341.31</v>
+        <v>1336.85</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11145,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>217.18</v>
+        <v>223.69</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>215.23</v>
+        <v>216.04</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>216.13</v>
+        <v>216.42</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>227.5</v>
+        <v>226.48</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>533.8</v>
+        <v>549.25</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>517.51</v>
+        <v>520.53</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>523.84</v>
+        <v>524.84</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>554.76</v>
+        <v>554.14</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>519.1</v>
+        <v>510.85</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>494.5</v>
+        <v>496.06</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>487.55</v>
+        <v>488.46</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>485.84</v>
+        <v>485.34</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1322.3</v>
+        <v>1335.1</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1305.65</v>
+        <v>1308.46</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1363.77</v>
+        <v>1362.65</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1538.72</v>
+        <v>1533.68</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11321,17 +11321,17 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>203.74</v>
+        <v>204.78</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>205.13</v>
+        <v>205.09</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>202.84</v>
+        <v>202.92</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>11742</v>
+        <v>12520</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>10362.87</v>
+        <v>10568.31</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>9411.379999999999</v>
+        <v>9533.280000000001</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8373.82</v>
+        <v>8386.07</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1017.6</v>
+        <v>1024</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>998.4299999999999</v>
+        <v>1000.87</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>945.0599999999999</v>
+        <v>948.16</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>964.73</v>
+        <v>965.3200000000001</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>110.66</v>
+        <v>116.19</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>95.59</v>
+        <v>97.55</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>83.8</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>97.48999999999999</v>
+        <v>96.69</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>523.25</v>
+        <v>527.4</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>489.41</v>
+        <v>493.03</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>478.87</v>
+        <v>480.77</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>496.68</v>
+        <v>496.88</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,20 +11541,20 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>475.85</v>
+        <v>481.2</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>469.05</v>
+        <v>470.21</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>475.81</v>
+        <v>476.02</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>560.09</v>
+        <v>558.36</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>820</v>
+        <v>821.85</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>743.2</v>
+        <v>750.6900000000001</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>708.91</v>
+        <v>713.34</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>669.39</v>
+        <v>670.55</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>240.76</v>
+        <v>245.76</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>247.35</v>
+        <v>247.2</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>250.05</v>
+        <v>249.88</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>313.53</v>
+        <v>310.96</v>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>508.55</v>
+        <v>509.5</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>486.46</v>
+        <v>488.66</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>459.48</v>
+        <v>461.44</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>432.15</v>
+        <v>432.55</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>489.4</v>
+        <v>497.7</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>478.44</v>
+        <v>480.28</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>472.71</v>
+        <v>473.69</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>580.73</v>
+        <v>578.14</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 04-May-2026  17:16:37    |    Closing Price Date: 04-May-2026</t>
+          <t>Scan Run: 05-May-2026  16:30:51    |    Closing Price Date: 05-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>85.2</v>
+        <v>80</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>52.8</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>04-May-2026  17:16:37</t>
+          <t>05-May-2026  16:30:51</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 85.2% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 80.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 84.4% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 79.6% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 52.8% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 213 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 200 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 211 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 199 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 132 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 130 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>632.6</v>
+        <v>621</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>578.45</v>
+        <v>582.5</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>572.42</v>
+        <v>574.33</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>687.8200000000001</v>
+        <v>687.15</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>461.05</v>
+        <v>458.8</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>437.99</v>
+        <v>439.98</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>435.25</v>
+        <v>436.17</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>453.09</v>
+        <v>453.14</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>395.85</v>
+        <v>391.35</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>368.45</v>
+        <v>371.46</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>366.05</v>
+        <v>367.45</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>401.45</v>
+        <v>401.1</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>806.1</v>
+        <v>767.45</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>703.9400000000001</v>
+        <v>709.99</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>697.5700000000001</v>
+        <v>700.3099999999999</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>739.0700000000001</v>
+        <v>739.35</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2676.4</v>
+        <v>2656.7</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2428.01</v>
+        <v>2449.79</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2284.15</v>
+        <v>2298.76</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1840.62</v>
+        <v>1848.74</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>353.65</v>
+        <v>357.65</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>312.81</v>
+        <v>317.08</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>300.47</v>
+        <v>302.71</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>303.62</v>
+        <v>304.16</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1252</v>
+        <v>1221.5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1160</v>
+        <v>1167.53</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1099.04</v>
+        <v>1106.7</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>944.71</v>
+        <v>949.71</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>875</v>
+        <v>877.75</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>836.63</v>
+        <v>840.54</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>815.48</v>
+        <v>817.92</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>866.12</v>
+        <v>866.24</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>530.8</v>
+        <v>533.4</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>504.64</v>
+        <v>507.38</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>498.83</v>
+        <v>500.19</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>558.4299999999999</v>
+        <v>558.1799999999999</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1069.2</v>
+        <v>1076.6</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1032.52</v>
+        <v>1036.72</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>993.8200000000001</v>
+        <v>997.0700000000001</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>969.64</v>
+        <v>970.7</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.66</v>
+        <v>9.6</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>9.06</v>
+        <v>9.16</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.16</v>
+        <v>9.19</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17.38</v>
+        <v>17.22</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>537.15</v>
+        <v>539.05</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>521.8099999999999</v>
+        <v>523.45</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>501.24</v>
+        <v>502.72</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>501.53</v>
+        <v>501.9</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1348</v>
+        <v>1359.3</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1306.02</v>
+        <v>1311.1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1285.66</v>
+        <v>1288.55</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1186.84</v>
+        <v>1188.56</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>127.64</v>
+        <v>127.78</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>120.19</v>
+        <v>120.91</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>119.45</v>
+        <v>119.78</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>133.39</v>
+        <v>133.33</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>625.2</v>
+        <v>621.6</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>603.14</v>
+        <v>604.89</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>589.58</v>
+        <v>590.83</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>587.4</v>
+        <v>587.74</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>437.6</v>
+        <v>436.3</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>448.52</v>
+        <v>446.85</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>446.79</v>
+        <v>446.24</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>468.98</v>
+        <v>468.4</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>398.15</v>
+        <v>394.1</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>384.48</v>
+        <v>386.6</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>368.82</v>
+        <v>370.93</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>344.12</v>
+        <v>345.15</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>135.81</v>
+        <v>134.42</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>131</v>
+        <v>131.32</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>131.88</v>
+        <v>131.98</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>161.4</v>
+        <v>161.13</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1110.7</v>
+        <v>1104.1</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1069.69</v>
+        <v>1072.96</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1016.95</v>
+        <v>1020.36</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>970.09</v>
+        <v>971.42</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>859.15</v>
+        <v>861.5</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>862.36</v>
+        <v>862.28</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>878.17</v>
+        <v>877.51</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1058.95</v>
+        <v>1056.99</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1140</v>
+        <v>1169.7</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1050.99</v>
+        <v>1063.51</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>1009.67</v>
+        <v>1017.86</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>946.1900000000001</v>
+        <v>949.52</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1327.3</v>
+        <v>1326.1</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1372.27</v>
+        <v>1368.16</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1276.76</v>
+        <v>1282.53</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>994.41</v>
+        <v>1001.51</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>13.73</v>
+        <v>13.78</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.43</v>
+        <v>14.37</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>14.98</v>
+        <v>14.93</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>351.1</v>
+        <v>359.05</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>334.48</v>
+        <v>336.82</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>331.77</v>
+        <v>332.84</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>447.58</v>
+        <v>446.7</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>2161.7</v>
+        <v>2153.8</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1944.82</v>
+        <v>1964.72</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1771.6</v>
+        <v>1786.59</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1637.36</v>
+        <v>1642.5</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>398.3</v>
+        <v>416.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>385.84</v>
+        <v>389.64</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>385.05</v>
+        <v>386.69</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>466.48</v>
+        <v>465.29</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1455.5</v>
+        <v>1462</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1217.38</v>
+        <v>1251.7</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1150.81</v>
+        <v>1170.08</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1243.43</v>
+        <v>1246.51</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>561.1</v>
+        <v>557.7</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>486.39</v>
+        <v>493.19</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>476.28</v>
+        <v>479.48</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>535.65</v>
+        <v>535.87</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>623.7</v>
+        <v>621.1</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>602.88</v>
+        <v>604.61</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>598.2</v>
+        <v>599.1</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>606.35</v>
+        <v>606.49</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>215.74</v>
+        <v>213.26</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>209.17</v>
+        <v>209.89</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>197.88</v>
+        <v>199.05</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>166.79</v>
+        <v>167.7</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3111.6</v>
+        <v>2939.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2827.24</v>
+        <v>2837.96</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2646.99</v>
+        <v>2658.47</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2740.95</v>
+        <v>2742.93</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>959.85</v>
+        <v>952.25</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>927.35</v>
+        <v>928.59</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>938.52</v>
+        <v>938.04</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1061.25</v>
+        <v>1058.68</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>566.55</v>
+        <v>555.7</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>586.37</v>
+        <v>583.45</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>592.1900000000001</v>
+        <v>590.76</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>578.88</v>
+        <v>578.65</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>524.9</v>
+        <v>518.1</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>487.61</v>
+        <v>490.51</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>474.82</v>
+        <v>476.52</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>515.1799999999999</v>
+        <v>515.21</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1432.1</v>
+        <v>1430.4</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1356.69</v>
+        <v>1363.71</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1337.39</v>
+        <v>1341.03</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>477.9</v>
+        <v>482.85</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>470.2</v>
+        <v>471.4</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>458.63</v>
+        <v>459.58</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>433.31</v>
+        <v>433.81</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>290.3</v>
+        <v>286.6</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>299.53</v>
+        <v>298.3</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>302.61</v>
+        <v>301.98</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>348.77</v>
+        <v>348.15</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2389,29 +2389,29 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>392.2</v>
+        <v>386.1</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>388.79</v>
+        <v>388.02</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>390.89</v>
+        <v>390.38</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>394.37</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>394.16</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1651.7</v>
+        <v>1645.6</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1724.87</v>
+        <v>1717.32</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1854.66</v>
+        <v>1846.46</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2132.68</v>
+        <v>2127.83</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>342.05</v>
+        <v>349.05</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>315.44</v>
+        <v>318.64</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>296.91</v>
+        <v>298.95</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>275.78</v>
+        <v>276.51</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>416.9</v>
+        <v>413.7</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>420.01</v>
+        <v>419.41</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>432.47</v>
+        <v>431.73</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>510.79</v>
+        <v>509.82</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>956.45</v>
+        <v>912.75</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>677.92</v>
+        <v>700.29</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>639.24</v>
+        <v>649.96</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>704.84</v>
+        <v>706.91</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1146</v>
+        <v>1160.7</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1196.43</v>
+        <v>1193.03</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1246.96</v>
+        <v>1243.58</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1461.37</v>
+        <v>1458.37</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>400.7</v>
+        <v>411.55</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>357.81</v>
+        <v>362.93</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>343.39</v>
+        <v>346.06</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>389.16</v>
+        <v>389.38</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,29 +2697,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>185.66</v>
+        <v>180.57</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>186.67</v>
+        <v>186.09</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>183.04</v>
+        <v>182.94</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>166.39</v>
+        <v>166.53</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>729.7</v>
+        <v>732.95</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>718.4</v>
+        <v>719.78</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723.26</v>
+        <v>723.64</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>756.54</v>
+        <v>756.3</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1096.7</v>
+        <v>1082.3</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1038.24</v>
+        <v>1042.44</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1038.9</v>
+        <v>1040.6</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1207.49</v>
+        <v>1206.24</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>166.02</v>
+        <v>167.32</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>151.85</v>
+        <v>153.9</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>142.6</v>
+        <v>144.16</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>136.72</v>
+        <v>137.23</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>474.9</v>
+        <v>469.55</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>451.57</v>
+        <v>453.28</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>443.95</v>
+        <v>444.95</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>454.18</v>
+        <v>454.33</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>186.36</v>
+        <v>186.14</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>171.41</v>
+        <v>172.82</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>175.86</v>
+        <v>176.27</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>213.78</v>
+        <v>213.51</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,29 +2961,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1094.9</v>
+        <v>1073.7</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1084.28</v>
+        <v>1083.28</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1092.32</v>
+        <v>1091.59</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1170.78</v>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H52" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1169.82</v>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>11481</v>
+        <v>12222</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>10963</v>
+        <v>11082.9</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>10284.51</v>
+        <v>10360.49</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8898.83</v>
+        <v>8931.889999999999</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3049,24 +3049,24 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>224.99</v>
+        <v>220.64</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>223.78</v>
+        <v>223.49</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>216.45</v>
+        <v>216.61</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>211.85</v>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>211.94</v>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.82</v>
+        <v>7.79</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.65</v>
+        <v>7.66</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.49</v>
+        <v>7.5</v>
       </c>
       <c r="F55" s="11" t="n">
         <v>8.289999999999999</v>
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>116.79</v>
+        <v>114.73</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>116.91</v>
+        <v>116.5</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>113.96</v>
+        <v>114.01</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>109.92</v>
+        <v>110.01</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>120.3</v>
+        <v>121.76</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>109.18</v>
+        <v>110.37</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>103.35</v>
+        <v>104.07</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>113.86</v>
+        <v>113.94</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>88.62</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>81.3</v>
+        <v>82.56</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>77.98</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.18000000000001</v>
+        <v>84.25</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3313,24 +3313,24 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1233.4</v>
+        <v>1207.1</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1217.88</v>
+        <v>1216.86</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1176.62</v>
+        <v>1177.82</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1157.22</v>
-      </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1157.72</v>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>213.53</v>
+        <v>211.51</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>199.09</v>
+        <v>200.27</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>184.36</v>
+        <v>185.43</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>200.88</v>
+        <v>200.98</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1328.7</v>
+        <v>1349.1</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1145.14</v>
+        <v>1164.57</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1074.68</v>
+        <v>1085.44</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1315.77</v>
+        <v>1316.11</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>70.90000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>64.36</v>
+        <v>65.2</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>62.72</v>
+        <v>63.19</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>62.1</v>
+        <v>62.23</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2389.5</v>
+        <v>2362</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2453.32</v>
+        <v>2444.62</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2433.56</v>
+        <v>2430.76</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2574.72</v>
+        <v>2572.6</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>506.5</v>
+        <v>505.75</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>492.49</v>
+        <v>493.75</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>492.35</v>
+        <v>492.88</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>531.99</v>
+        <v>531.73</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>371.85</v>
+        <v>368.3</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>358.97</v>
+        <v>359.86</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>360.2</v>
+        <v>360.52</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>397.15</v>
+        <v>396.86</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2270.3</v>
+        <v>2244.1</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2185.96</v>
+        <v>2191.49</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2167.69</v>
+        <v>2170.68</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2070.97</v>
+        <v>2072.69</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4597.7</v>
+        <v>4575.1</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4691.17</v>
+        <v>4680.11</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4550.14</v>
+        <v>4551.12</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4482.37</v>
+        <v>4483.29</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>945.25</v>
+        <v>952.75</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>891.2</v>
+        <v>897.0599999999999</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>903.6</v>
+        <v>905.52</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1027.11</v>
+        <v>1026.37</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>528.05</v>
+        <v>521.55</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>497</v>
+        <v>499.34</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>491.86</v>
+        <v>493.02</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>542.58</v>
+        <v>542.37</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,24 +3797,24 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>909.35</v>
+        <v>899.1</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>902.47</v>
+        <v>902.15</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>916.1</v>
+        <v>915.4400000000001</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1029.02</v>
-      </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1027.73</v>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>107.75</v>
+        <v>108.24</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>106.33</v>
+        <v>106.54</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>106.2</v>
+        <v>106.29</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>109.92</v>
+        <v>109.87</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>1028.7</v>
+        <v>1081.8</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>979.42</v>
+        <v>989.17</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>954.88</v>
+        <v>959.85</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>946.16</v>
+        <v>947.51</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>872.5</v>
+        <v>877.15</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>788.1799999999999</v>
+        <v>803.09</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>689.78</v>
+        <v>703.62</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>591.1</v>
+        <v>596.61</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>658.45</v>
+        <v>656.45</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>638.02</v>
+        <v>639.77</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>645.58</v>
+        <v>646</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>746.84</v>
+        <v>745.9400000000001</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1051.2</v>
+        <v>1057.9</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1019.36</v>
+        <v>1025.64</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>941.71</v>
+        <v>950.33</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1035.65</v>
+        <v>1036.01</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>4271.7</v>
+        <v>4477.3</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3941.52</v>
+        <v>3992.54</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3845.43</v>
+        <v>3870.21</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3639.26</v>
+        <v>3647.6</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,29 +4105,29 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>634.65</v>
+        <v>624.45</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>625.5</v>
+        <v>625.4</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>631.99</v>
+        <v>631.7</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>696.61</v>
-      </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H78" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>695.89</v>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>59.33</v>
+        <v>59.45</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>57.22</v>
+        <v>57.46</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>56.71</v>
+        <v>56.85</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>58.86</v>
+        <v>58.85</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4193,24 +4193,24 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>692.35</v>
+        <v>680.6</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>691.95</v>
+        <v>691.79</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>679.25</v>
+        <v>680.2</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>747.45</v>
-      </c>
-      <c r="G80" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>746.35</v>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>167.66</v>
+        <v>168.43</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>156.87</v>
+        <v>158.71</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>155.03</v>
+        <v>155.94</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>179.86</v>
+        <v>179.6</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>232.6</v>
+        <v>233.28</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>210.95</v>
+        <v>213.08</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>208.35</v>
+        <v>209.32</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>237.53</v>
+        <v>237.49</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>154.96</v>
+        <v>157.86</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>149.84</v>
+        <v>150.6</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>143.59</v>
+        <v>144.15</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>128.14</v>
+        <v>128.44</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>476.2</v>
+        <v>483.2</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>459.24</v>
+        <v>461.52</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>450.13</v>
+        <v>451.43</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>473.69</v>
+        <v>473.79</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4413,20 +4413,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>158.97</v>
+        <v>157.83</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>155.95</v>
+        <v>156.16</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>158.97</v>
+        <v>158.82</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>161.07</v>
+        <v>160.98</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>173.1</v>
+        <v>173.5</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>168.64</v>
+        <v>169.27</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>166.85</v>
+        <v>167.25</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>177.94</v>
+        <v>177.82</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,24 +4501,24 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>977.95</v>
+        <v>958.85</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>965.72</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>988.5</v>
+        <v>987.34</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1076.26</v>
-      </c>
-      <c r="G87" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1075.09</v>
+      </c>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4545,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>598.8</v>
+        <v>611.55</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>582.24</v>
+        <v>585.03</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>579.51</v>
+        <v>580.76</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>758.29</v>
+        <v>756.83</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>605.85</v>
+        <v>618.35</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>568.51</v>
+        <v>573.26</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>572.4400000000001</v>
+        <v>574.24</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>606.24</v>
+        <v>606.36</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4614,9 +4614,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I89" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J89" s="14" t="inlineStr">
@@ -4633,20 +4633,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>135.25</v>
+        <v>141.59</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>128.81</v>
+        <v>130.03</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.35</v>
+        <v>130.79</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>135.91</v>
+        <v>135.97</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4658,9 +4658,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I90" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>362</v>
+        <v>355.35</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>349.44</v>
+        <v>350</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>348.32</v>
+        <v>348.6</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>400.11</v>
+        <v>399.66</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,20 +4721,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>194.72</v>
+        <v>197.05</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>184.23</v>
+        <v>185.93</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>185.57</v>
+        <v>186.17</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>231.66</v>
+        <v>230.9</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>22.35</v>
+        <v>23.58</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>19.59</v>
+        <v>20.18</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>18.49</v>
+        <v>18.83</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.66</v>
+        <v>21.69</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1217.7</v>
+        <v>1226.4</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1118.19</v>
+        <v>1128.5</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1122.14</v>
+        <v>1126.23</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1332.75</v>
+        <v>1331.7</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>313.95</v>
+        <v>326.85</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>305.08</v>
+        <v>307.16</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>302.25</v>
+        <v>303.21</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>304.1</v>
+        <v>304.32</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,24 +4897,24 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>45.76</v>
+        <v>46.67</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>45.84</v>
+        <v>45.92</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>45.33</v>
+        <v>45.38</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="G96" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>50.66</v>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
@@ -4941,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>1037.9</v>
+        <v>1033.5</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>963.49</v>
+        <v>976.9</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>933.83</v>
+        <v>941.8099999999999</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>905.16</v>
+        <v>907.79</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>824.15</v>
+        <v>835.9</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>794.9400000000001</v>
+        <v>798.84</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>774.45</v>
+        <v>776.86</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>798.54</v>
+        <v>798.91</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1429.9</v>
+        <v>1421.9</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1465.53</v>
+        <v>1461.38</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1378.23</v>
+        <v>1379.94</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1190.89</v>
+        <v>1193.19</v>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>856.9</v>
+        <v>863</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>843.72</v>
+        <v>845.5599999999999</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>870.77</v>
+        <v>870.46</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1015.97</v>
+        <v>1014.45</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>295.4</v>
+        <v>290.75</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>267.25</v>
+        <v>269.49</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>263.63</v>
+        <v>264.69</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>272.42</v>
+        <v>272.6</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4345.9</v>
+        <v>4297.4</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>4100.78</v>
+        <v>4146.22</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3899.24</v>
+        <v>3934.28</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3723.13</v>
+        <v>3735.68</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>844.4</v>
+        <v>871.05</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>728.88</v>
+        <v>742.42</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>711.52</v>
+        <v>717.77</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>755.25</v>
+        <v>756.4</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>188.98</v>
+        <v>190.09</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>170.2</v>
+        <v>172.1</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>166.39</v>
+        <v>167.32</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.38</v>
+        <v>176.51</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>411.65</v>
+        <v>421.25</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>389.22</v>
+        <v>393.01</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>375.12</v>
+        <v>377.75</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>400.65</v>
+        <v>400.81</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1084.1</v>
+        <v>1082.4</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>1029.96</v>
+        <v>1034.96</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>961.16</v>
+        <v>965.91</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>936.41</v>
+        <v>937.86</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,29 +5381,29 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>518.5</v>
+        <v>507.25</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>504.24</v>
+        <v>504.53</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>508.73</v>
+        <v>508.67</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>574.8099999999999</v>
+        <v>574.14</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H107" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr">
@@ -5425,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>656.4</v>
+        <v>650.4</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>644.35</v>
+        <v>645.08</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>656.63</v>
+        <v>655.97</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>748.54</v>
+        <v>746.54</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5469,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>369.5</v>
+        <v>370.5</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>361.54</v>
+        <v>362.39</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>351.94</v>
+        <v>352.67</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>355.88</v>
+        <v>356.03</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>82.59999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>72.18000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>68.56999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>81.69</v>
+        <v>81.66</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,29 +5557,29 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>33.46</v>
+        <v>32.87</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>32.42</v>
+        <v>32.46</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.28</v>
+        <v>33.26</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.12</v>
+        <v>42.03</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H111" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I111" s="13" t="inlineStr">
@@ -5601,29 +5601,29 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>125.21</v>
+        <v>123.41</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>123.72</v>
+        <v>123.53</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.54</v>
+        <v>124.39</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.69</v>
-      </c>
-      <c r="G112" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H112" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>114.85</v>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H112" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I112" s="12" t="inlineStr">
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>446.65</v>
+        <v>447.85</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>429.16</v>
+        <v>430.94</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>404.59</v>
+        <v>406.29</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>419.38</v>
+        <v>419.66</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>26.22</v>
+        <v>25.93</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>24.95</v>
+        <v>25.12</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>24.62</v>
+        <v>24.72</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>33.76</v>
+        <v>33.6</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>526.45</v>
+        <v>530.45</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>537.97</v>
+        <v>537.26</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>561.73</v>
+        <v>560.51</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>687.48</v>
+        <v>685.92</v>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>125.51</v>
+        <v>125.35</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>123.17</v>
+        <v>123.55</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>126.8</v>
+        <v>126.68</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>161.96</v>
+        <v>161.23</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>459.05</v>
+        <v>455.85</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>434.9</v>
+        <v>436.89</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>417.32</v>
+        <v>418.83</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>428.84</v>
+        <v>429.11</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>371.3</v>
+        <v>372.4</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>350.86</v>
+        <v>352.91</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>341.57</v>
+        <v>342.78</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>352.91</v>
+        <v>353.11</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1222.9</v>
+        <v>1204.9</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1165.71</v>
+        <v>1169.44</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>1022.43</v>
+        <v>1029.58</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>869.24</v>
+        <v>872.58</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>885.85</v>
+        <v>895.35</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>764.87</v>
+        <v>784.9</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>729.83</v>
+        <v>740.89</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>758.04</v>
+        <v>760.3099999999999</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,29 +5997,29 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>196.69</v>
+        <v>194.13</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>194.86</v>
+        <v>194.79</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>195.66</v>
+        <v>195.6</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>218.08</v>
-      </c>
-      <c r="G121" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>217.84</v>
+      </c>
+      <c r="G121" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H121" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I121" s="13" t="inlineStr">
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>274.4</v>
+        <v>269.6</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>249.67</v>
+        <v>253.24</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>232.76</v>
+        <v>235.57</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>204.46</v>
+        <v>205.75</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>972.75</v>
+        <v>977.3</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>916.25</v>
+        <v>922.0700000000001</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>884.45</v>
+        <v>888.09</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>958.58</v>
+        <v>958.77</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1563</v>
+        <v>1524.3</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1345.3</v>
+        <v>1362.35</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1233.06</v>
+        <v>1244.48</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1172.24</v>
+        <v>1175.74</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,29 +6173,29 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>167.83</v>
+        <v>170.09</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>166.05</v>
+        <v>166.43</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>169</v>
+        <v>169.04</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>188.19</v>
+        <v>188.01</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H125" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I125" s="13" t="inlineStr">
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14466</v>
+        <v>14583</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>14198.12</v>
+        <v>14234.77</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14213.37</v>
+        <v>14227.87</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14798.86</v>
+        <v>14796.72</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6261,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>145.49</v>
+        <v>144.41</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>138.3</v>
+        <v>138.88</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>135.61</v>
+        <v>135.95</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>161.39</v>
+        <v>161.22</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>169.68</v>
+        <v>164.51</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>172.19</v>
+        <v>171.12</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>180.24</v>
+        <v>179.17</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>207.66</v>
+        <v>206.84</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>58.42</v>
+        <v>59.54</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>53.96</v>
+        <v>54.49</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>50.66</v>
+        <v>51.01</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>54.96</v>
+        <v>55</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>68.18000000000001</v>
+        <v>67.69</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>63.13</v>
+        <v>63.57</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>58.31</v>
+        <v>58.67</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>59.96</v>
+        <v>60.03</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1568.3</v>
+        <v>1561.7</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1685.8</v>
+        <v>1668</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1642.06</v>
+        <v>1638.06</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1384.96</v>
+        <v>1389.04</v>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1457.5</v>
+        <v>1416.7</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1397.38</v>
+        <v>1399.22</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1215.8</v>
+        <v>1223.68</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1189.73</v>
+        <v>1191.99</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,29 +6525,29 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>313.15</v>
+        <v>309.05</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>314.48</v>
+        <v>313.96</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>310.17</v>
+        <v>310.13</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>323.77</v>
+        <v>323.62</v>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H133" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I133" s="13" t="inlineStr">
@@ -6569,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>442.8</v>
+        <v>439.95</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>436.82</v>
+        <v>437.12</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>437.8</v>
+        <v>437.88</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>469.5</v>
+        <v>469.2</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>6127.5</v>
+        <v>6266</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>5024.39</v>
+        <v>5263.38</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>4272.58</v>
+        <v>4432.57</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2976.95</v>
+        <v>3043.92</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,24 +6657,24 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>335.85</v>
+        <v>327.25</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>333.31</v>
+        <v>332.73</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>342.08</v>
+        <v>341.5</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>360.29</v>
-      </c>
-      <c r="G136" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>359.96</v>
+      </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>123.64</v>
+        <v>125.49</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>106.55</v>
+        <v>108.36</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>104.11</v>
+        <v>104.95</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>126.35</v>
+        <v>126.34</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1530.2</v>
+        <v>1594.5</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1404.56</v>
+        <v>1431.82</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1361.85</v>
+        <v>1376.55</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1332.62</v>
+        <v>1336.96</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>189.29</v>
+        <v>186.92</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>181.27</v>
+        <v>182.14</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>177.19</v>
+        <v>177.86</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>187.11</v>
+        <v>187.09</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6814,9 +6814,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I139" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J139" s="14" t="inlineStr">
@@ -6833,29 +6833,29 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1675.6</v>
+        <v>1659</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1659.1</v>
+        <v>1661.96</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1674.71</v>
+        <v>1674.8</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1971.64</v>
-      </c>
-      <c r="G140" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H140" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1965.79</v>
+      </c>
+      <c r="G140" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H140" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I140" s="13" t="inlineStr">
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>405.25</v>
+        <v>404.9</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>386.43</v>
+        <v>388.19</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>385.95</v>
+        <v>386.69</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>423.89</v>
+        <v>423.7</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>869.5</v>
+        <v>858.9</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>871.3099999999999</v>
+        <v>870.13</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>854.4400000000001</v>
+        <v>854.62</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>826.36</v>
+        <v>826.6799999999999</v>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>394.5</v>
+        <v>396.85</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>365.82</v>
+        <v>370.89</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>349.32</v>
+        <v>352.72</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>349.73</v>
+        <v>350.59</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7009,29 +7009,29 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>198.13</v>
+        <v>199.68</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>195.35</v>
+        <v>195.76</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>199.29</v>
+        <v>199.31</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>234.11</v>
+        <v>233.77</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H144" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I144" s="13" t="inlineStr">
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1686.8</v>
+        <v>1708.7</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1529.21</v>
+        <v>1546.31</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1419.93</v>
+        <v>1431.25</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1395.1</v>
+        <v>1398.22</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1285.3</v>
+        <v>1308.4</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1177.44</v>
+        <v>1189.91</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1148.67</v>
+        <v>1154.93</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1171.98</v>
+        <v>1173.33</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>78.23</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>75.83</v>
+        <v>76.22</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.78</v>
+        <v>75.95</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>83.64</v>
+        <v>83.52</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>267.3</v>
+        <v>265.75</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>261.45</v>
+        <v>262.07</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>257.73</v>
+        <v>258.27</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>265.2</v>
+        <v>265.18</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7229,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>34.41</v>
+        <v>34.27</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>34.16</v>
+        <v>34.19</v>
       </c>
       <c r="E149" s="11" t="n">
         <v>34.41</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>41.4</v>
+        <v>41.26</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>429.85</v>
+        <v>434.7</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>396.47</v>
+        <v>400.11</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>392.56</v>
+        <v>394.21</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>477.04</v>
+        <v>476.62</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>629.2</v>
+        <v>627.35</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>574.1</v>
+        <v>583.65</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>585.49</v>
+        <v>588.66</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>714.33</v>
+        <v>712.59</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,20 +7361,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>142.29</v>
+        <v>140.43</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>143.03</v>
+        <v>142.78</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.69</v>
+        <v>145.49</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>188.93</v>
+        <v>188.45</v>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>414.15</v>
+        <v>410.25</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>390.69</v>
+        <v>392.55</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>378.47</v>
+        <v>379.72</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>500.49</v>
+        <v>499.59</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>674.8</v>
+        <v>689.2</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>645.21</v>
+        <v>649.4</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>612.45</v>
+        <v>615.46</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>594.14</v>
+        <v>595.09</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.44</v>
+        <v>9.41</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>9.31</v>
+        <v>9.32</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.77</v>
+        <v>10.74</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>215.34</v>
+        <v>215.87</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>205.63</v>
+        <v>207.32</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>204.67</v>
+        <v>205.46</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>240.56</v>
+        <v>240.05</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>217.09</v>
+        <v>215.9</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>188.05</v>
+        <v>192.48</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>176.39</v>
+        <v>179.14</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>166.03</v>
+        <v>166.94</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,29 +7625,29 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>126.33</v>
+        <v>123.24</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>126.65</v>
+        <v>126.5</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>124.81</v>
+        <v>124.9</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>141.1</v>
+        <v>140.8</v>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H158" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H158" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I158" s="13" t="inlineStr">
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>782.35</v>
+        <v>794.55</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>759.37</v>
+        <v>765.63</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>714.0700000000001</v>
+        <v>720.23</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>681.6900000000001</v>
+        <v>683.92</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>28.73</v>
+        <v>28.66</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>27.53</v>
+        <v>27.71</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>27.22</v>
+        <v>27.32</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>31.94</v>
+        <v>31.87</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,29 +7757,29 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1548.7</v>
+        <v>1535.6</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1549.65</v>
+        <v>1548.32</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1539.8</v>
+        <v>1539.64</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1485.27</v>
+        <v>1485.77</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H161" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H161" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>940.65</v>
+        <v>927.3</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>889.22</v>
+        <v>892.85</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>861.89</v>
+        <v>864.45</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>922.52</v>
+        <v>922.5700000000001</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2472.5</v>
+        <v>2593.9</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2328.5</v>
+        <v>2366.91</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2210.11</v>
+        <v>2235.38</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2356.79</v>
+        <v>2360.38</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,29 +7889,29 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>576.4</v>
+        <v>585.05</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>581.26</v>
+        <v>581.62</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>576.5599999999999</v>
+        <v>576.89</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>555</v>
-      </c>
-      <c r="G164" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H164" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>555.3</v>
+      </c>
+      <c r="G164" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H164" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I164" s="12" t="inlineStr">
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>261.75</v>
+        <v>262.2</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>254.37</v>
+        <v>255.11</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>250.12</v>
+        <v>250.59</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>275.62</v>
+        <v>275.49</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
+        <v>132.33</v>
+      </c>
+      <c r="D166" s="11" t="n">
+        <v>130.36</v>
+      </c>
+      <c r="E166" s="11" t="n">
+        <v>128.48</v>
+      </c>
+      <c r="F166" s="11" t="n">
         <v>134.02</v>
-      </c>
-      <c r="D166" s="11" t="n">
-        <v>130.15</v>
-      </c>
-      <c r="E166" s="11" t="n">
-        <v>128.32</v>
-      </c>
-      <c r="F166" s="11" t="n">
-        <v>134.04</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3362.8</v>
+        <v>3375.2</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>3150.05</v>
+        <v>3171.49</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>3027.96</v>
+        <v>3041.57</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2759.4</v>
+        <v>2765.52</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2855.3</v>
+        <v>2900.2</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2667.37</v>
+        <v>2689.55</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2535.97</v>
+        <v>2550.26</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2523.88</v>
+        <v>2527.63</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>219.88</v>
+        <v>218.7</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>210.34</v>
+        <v>211.14</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>208.51</v>
+        <v>208.91</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>234.53</v>
+        <v>234.38</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8153,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>211.63</v>
+        <v>223.41</v>
       </c>
       <c r="D170" s="11" t="n">
+        <v>197.99</v>
+      </c>
+      <c r="E170" s="11" t="n">
         <v>194.93</v>
       </c>
-      <c r="E170" s="11" t="n">
-        <v>193.58</v>
-      </c>
       <c r="F170" s="11" t="n">
-        <v>241.73</v>
+        <v>241.12</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8197,24 +8197,24 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>127.62</v>
+        <v>126</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>126.85</v>
+        <v>126.77</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>127.77</v>
+        <v>127.7</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>133.02</v>
-      </c>
-      <c r="G171" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>132.95</v>
+      </c>
+      <c r="G171" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr">
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>261.8</v>
+        <v>265</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>258.55</v>
+        <v>259.76</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>257.46</v>
+        <v>258.06</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>269.77</v>
+        <v>269.68</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>605.05</v>
+        <v>604.9</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>567.63</v>
+        <v>574.22</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>555.98</v>
+        <v>559.66</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>579.73</v>
+        <v>580.21</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2710</v>
+        <v>2742.1</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2497.59</v>
+        <v>2520.87</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2393.8</v>
+        <v>2407.45</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2408.74</v>
+        <v>2412.06</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>36.49</v>
+        <v>36.08</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>33.85</v>
+        <v>34.06</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>32.86</v>
+        <v>32.99</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.32</v>
+        <v>40.28</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8417,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>10.15</v>
+        <v>10.08</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>9.529999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>9.08</v>
+        <v>9.16</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>793.65</v>
+        <v>791.15</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>801.0700000000001</v>
+        <v>800.12</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>834.6</v>
+        <v>832.9</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1011.65</v>
+        <v>1009.46</v>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>260.6</v>
+        <v>255.95</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>245.07</v>
+        <v>246.11</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>236.33</v>
+        <v>237.1</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>295.61</v>
+        <v>295.22</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>301.05</v>
+        <v>299.65</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>298.75</v>
+        <v>298.83</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>310.42</v>
+        <v>309.99</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>379.42</v>
+        <v>378.63</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8593,24 +8593,24 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>221.96</v>
+        <v>222.55</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>222.51</v>
+        <v>222.44</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>223.97</v>
+        <v>223.83</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>235.6</v>
-      </c>
-      <c r="G180" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>235.33</v>
+      </c>
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -8637,17 +8637,17 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>66.48</v>
+        <v>67.23</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>63.56</v>
+        <v>63.91</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>63.08</v>
+        <v>63.25</v>
       </c>
       <c r="F181" s="11" t="n">
         <v>67.3</v>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>544.85</v>
+        <v>559.2</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>508.29</v>
+        <v>514.91</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>513.78</v>
+        <v>516.09</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>669.09</v>
+        <v>666.6</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>456.6</v>
+        <v>456.35</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>412.6</v>
+        <v>416.77</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>380.85</v>
+        <v>383.81</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>345.11</v>
+        <v>346.21</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1418.9</v>
+        <v>1367.6</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1502.61</v>
+        <v>1489.75</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1619.66</v>
+        <v>1609.78</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1937.67</v>
+        <v>1931.99</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8813,29 +8813,29 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>161.92</v>
+        <v>157.87</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>158.13</v>
+        <v>157.99</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>158.44</v>
+        <v>158.34</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>175.66</v>
-      </c>
-      <c r="G185" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H185" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>175.29</v>
+      </c>
+      <c r="G185" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H185" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I185" s="13" t="inlineStr">
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>210.63</v>
+        <v>207.8</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>206.99</v>
+        <v>207.38</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>204.06</v>
+        <v>204.45</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>194.54</v>
+        <v>194.83</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,24 +8901,24 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4738</v>
+        <v>4581.6</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4620.54</v>
+        <v>4616.83</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4495.49</v>
+        <v>4498.87</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4585.78</v>
-      </c>
-      <c r="G187" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>4585.74</v>
+      </c>
+      <c r="G187" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr">
@@ -8926,9 +8926,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I187" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J187" s="14" t="inlineStr">
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3399.9</v>
+        <v>3403.8</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3439.68</v>
+        <v>3436.26</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3555.82</v>
+        <v>3549.86</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4215.45</v>
+        <v>4207.37</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2489.8</v>
+        <v>2526.6</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2411.1</v>
+        <v>2430.74</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2253.9</v>
+        <v>2274.35</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1831.98</v>
+        <v>1845.61</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>335.3</v>
+        <v>345.7</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>319.34</v>
+        <v>321.5</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>316.31</v>
+        <v>317.37</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>330.29</v>
+        <v>330.28</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>2579</v>
+        <v>2603.1</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>2234.63</v>
+        <v>2295.78</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2147.23</v>
+        <v>2179.7</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2086.11</v>
+        <v>2095.66</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9121,29 +9121,29 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>562.35</v>
+        <v>547.9</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>544.45</v>
+        <v>546.47</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>549.83</v>
+        <v>550.3</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>685.04</v>
+        <v>682.49</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H192" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H192" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I192" s="13" t="inlineStr">
@@ -9165,29 +9165,29 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1039.7</v>
+        <v>1081.5</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1077.34</v>
+        <v>1077.73</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1045.74</v>
+        <v>1047.14</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>926.1900000000001</v>
-      </c>
-      <c r="G193" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H193" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>927.74</v>
+      </c>
+      <c r="G193" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H193" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I193" s="12" t="inlineStr">
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>884.4</v>
+        <v>879.25</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>847.33</v>
+        <v>850.37</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>848.74</v>
+        <v>849.9299999999999</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>907.01</v>
+        <v>906.73</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>142.55</v>
+        <v>142.81</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>141.15</v>
+        <v>141.31</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>139.87</v>
+        <v>139.98</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>155.05</v>
+        <v>154.93</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9297,24 +9297,24 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>522.05</v>
+        <v>525.9</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>525.84</v>
+        <v>525.85</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>532.96</v>
+        <v>532.6799999999999</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>603.6799999999999</v>
-      </c>
-      <c r="G196" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>602.91</v>
+      </c>
+      <c r="G196" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr">
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>418.7</v>
+        <v>424.4</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>400.69</v>
+        <v>403.56</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>372.87</v>
+        <v>376.18</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>359.67</v>
+        <v>360.78</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>29.14</v>
+        <v>29.48</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>27.84</v>
+        <v>28.11</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>26.73</v>
+        <v>26.93</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.68</v>
+        <v>27.71</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3570.3</v>
+        <v>3535.5</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3437.04</v>
+        <v>3446.41</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3257.64</v>
+        <v>3268.53</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2872.41</v>
+        <v>2879.01</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>490.7</v>
+        <v>483.9</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>438.58</v>
+        <v>442.9</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>406.69</v>
+        <v>409.71</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>428.06</v>
+        <v>428.62</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>41.06</v>
+        <v>40.95</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>39.05</v>
+        <v>39.28</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.28</v>
+        <v>36.36</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>238.25</v>
+        <v>234.35</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>224.78</v>
+        <v>225.69</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>219.18</v>
+        <v>219.78</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>224.49</v>
+        <v>224.59</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>212.07</v>
+        <v>210.5</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>200.16</v>
+        <v>201.88</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>193.46</v>
+        <v>194.69</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>221.66</v>
+        <v>221.42</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>309.35</v>
+        <v>324.8</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>259.85</v>
+        <v>269.17</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>215.62</v>
+        <v>222.9</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>149.08</v>
+        <v>152.27</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>1031.5</v>
+        <v>1052.1</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>1013.24</v>
+        <v>1016.94</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>962.95</v>
+        <v>966.45</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>880.6799999999999</v>
+        <v>882.39</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2245.3</v>
+        <v>2226.2</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2182.56</v>
+        <v>2186.72</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>2075.12</v>
+        <v>2081.04</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2201.95</v>
+        <v>2202.19</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>775.7</v>
+        <v>768.2</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>758.12</v>
+        <v>760.8200000000001</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>754.96</v>
+        <v>756.36</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>803.85</v>
+        <v>803.25</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>943</v>
+        <v>938.7</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>866.55</v>
+        <v>873.42</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>861.83</v>
+        <v>864.85</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>989.92</v>
+        <v>989.41</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>139.7</v>
+        <v>140</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>140.37</v>
+        <v>140.33</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>134.98</v>
+        <v>135.18</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.68</v>
+        <v>137.71</v>
       </c>
       <c r="G209" s="13" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>321.15</v>
+        <v>350.8</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>274.43</v>
+        <v>281.71</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>256.01</v>
+        <v>259.73</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>255.13</v>
+        <v>256.09</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,24 +9957,24 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>339</v>
+        <v>335.7</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>337.82</v>
+        <v>337.81</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>346.2</v>
+        <v>345.56</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>388.55</v>
-      </c>
-      <c r="G211" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>387.55</v>
+      </c>
+      <c r="G211" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H211" s="13" t="inlineStr">
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>691.2</v>
+        <v>690.75</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>655.3200000000001</v>
+        <v>658.7</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>647.67</v>
+        <v>649.36</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>679.84</v>
+        <v>679.95</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>267.9</v>
+        <v>275.8</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>235.55</v>
+        <v>239.38</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>230.74</v>
+        <v>232.51</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>253.69</v>
+        <v>253.91</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,29 +10089,29 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>824.55</v>
+        <v>805.65</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>808.1799999999999</v>
+        <v>807.9400000000001</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>807.4400000000001</v>
+        <v>807.37</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>901.92</v>
-      </c>
-      <c r="G214" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H214" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>900.96</v>
+      </c>
+      <c r="G214" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H214" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I214" s="13" t="inlineStr">
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>138.19</v>
+        <v>137.97</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>132.89</v>
+        <v>133.37</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>135.49</v>
+        <v>135.58</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>146.99</v>
+        <v>146.9</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1162.5</v>
+        <v>1176.8</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>1032.77</v>
+        <v>1046.49</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>933.08</v>
+        <v>942.64</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>739.38</v>
+        <v>743.73</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>414.2</v>
+        <v>414.5</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>397.67</v>
+        <v>399.28</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>398.36</v>
+        <v>398.99</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>479.36</v>
+        <v>478.72</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>116.98</v>
+        <v>114.02</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>112.17</v>
+        <v>112.35</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>109.72</v>
+        <v>109.89</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>115.97</v>
+        <v>115.95</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10290,9 +10290,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I218" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I218" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J218" s="14" t="inlineStr">
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>526.9</v>
+        <v>538</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>491.39</v>
+        <v>497.72</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>472.46</v>
+        <v>476.54</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>518.99</v>
+        <v>519.11</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10353,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>1271.3</v>
+        <v>1306.8</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>1224.85</v>
+        <v>1232.65</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>1249.85</v>
+        <v>1252.09</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1543.43</v>
+        <v>1541.08</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10397,20 +10397,20 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1659.2</v>
+        <v>1618.2</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1693.02</v>
+        <v>1685.89</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1718.24</v>
+        <v>1714.32</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1757</v>
+        <v>1755.62</v>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
@@ -10441,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>107.94</v>
+        <v>113.28</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>102.19</v>
+        <v>103.55</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>103.06</v>
+        <v>103.56</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>122.87</v>
+        <v>122.61</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>3989.7</v>
+        <v>3970.7</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>3930.45</v>
+        <v>3934.28</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3776.6</v>
+        <v>3784.21</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>3115.54</v>
+        <v>3124.05</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>2077.5</v>
+        <v>2072.2</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>1996.15</v>
+        <v>2003.39</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1896.12</v>
+        <v>1903.02</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2139.57</v>
+        <v>2138.9</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>93.93000000000001</v>
+        <v>91.94</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>99.61</v>
+        <v>98.36</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>103.9</v>
+        <v>103.04</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>128.6</v>
+        <v>127.89</v>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>420.4</v>
+        <v>431.2</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>395.77</v>
+        <v>399.14</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>394.89</v>
+        <v>396.32</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>396.23</v>
+        <v>396.57</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>473</v>
+        <v>462.05</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>454.47</v>
+        <v>455.19</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>447.31</v>
+        <v>447.89</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>435.31</v>
+        <v>435.58</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>188.36</v>
+        <v>186.13</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>184.8</v>
+        <v>185.6</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>182.04</v>
+        <v>182.6</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>191.63</v>
+        <v>191.59</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>645.5</v>
+        <v>645.65</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>604.54</v>
+        <v>608.46</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>568.34</v>
+        <v>571.37</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>560.08</v>
+        <v>560.9299999999999</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>602.15</v>
+        <v>587.9</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>570.21</v>
+        <v>571.89</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>549.85</v>
+        <v>551.34</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>582.8200000000001</v>
+        <v>582.87</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10837,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>61.37</v>
+        <v>61.75</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>57.55</v>
+        <v>57.93</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>57.19</v>
+        <v>57.36</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>52.94</v>
+        <v>53.07</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>1031.4</v>
+        <v>1023.7</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>952.64</v>
+        <v>959.41</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>904.51</v>
+        <v>909.1799999999999</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>961.33</v>
+        <v>961.95</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>635.7</v>
+        <v>623.75</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>612.14</v>
+        <v>613.25</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>598.83</v>
+        <v>599.8099999999999</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>675.59</v>
+        <v>675.08</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>296.05</v>
+        <v>295.05</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>310.77</v>
+        <v>308.02</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>328.89</v>
+        <v>326.33</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>364.35</v>
+        <v>362.99</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>203.36</v>
+        <v>200.79</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>199.03</v>
+        <v>199.2</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>198.88</v>
+        <v>198.95</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>201.21</v>
+        <v>201.2</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11038,9 +11038,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I235" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I235" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J235" s="14" t="inlineStr">
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>258.4</v>
+        <v>256.9</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>247.8</v>
+        <v>248.66</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>238.89</v>
+        <v>239.6</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>250.43</v>
+        <v>250.5</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>1510.4</v>
+        <v>1480.4</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>1422</v>
+        <v>1427.56</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1340.74</v>
+        <v>1346.21</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>1336.85</v>
+        <v>1338.28</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11145,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>223.69</v>
+        <v>221.5</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>216.04</v>
+        <v>216.56</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>216.42</v>
+        <v>216.62</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>226.48</v>
+        <v>226.43</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>549.25</v>
+        <v>538.25</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>520.53</v>
+        <v>522.22</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>524.84</v>
+        <v>525.36</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>554.14</v>
+        <v>553.98</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>510.85</v>
+        <v>523.05</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>496.06</v>
+        <v>498.63</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>488.46</v>
+        <v>489.82</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>485.34</v>
+        <v>485.71</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>1335.1</v>
+        <v>1337.3</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>1308.46</v>
+        <v>1311.2</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>1362.65</v>
+        <v>1361.66</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>1533.68</v>
+        <v>1531.72</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11321,17 +11321,17 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>204.78</v>
+        <v>200.57</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>205.09</v>
+        <v>204.66</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>202.92</v>
+        <v>202.82</v>
       </c>
       <c r="F242" s="11" t="n">
         <v/>
@@ -11341,9 +11341,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H242" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H242" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I242" s="13" t="inlineStr">
@@ -11365,24 +11365,24 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>12520</v>
+        <v>10082</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>10568.31</v>
+        <v>10629.51</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>9533.280000000001</v>
+        <v>9639.17</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>8386.07</v>
-      </c>
-      <c r="G243" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>8436.08</v>
+      </c>
+      <c r="G243" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H243" s="12" t="inlineStr">
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>1024</v>
+        <v>1016.3</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>1000.87</v>
+        <v>1002.34</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>948.16</v>
+        <v>950.83</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>965.3200000000001</v>
+        <v>965.83</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>116.19</v>
+        <v>121.85</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>97.55</v>
+        <v>99.86</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>85.06999999999999</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>96.69</v>
+        <v>96.94</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>527.4</v>
+        <v>522.2</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>493.03</v>
+        <v>495.81</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>480.77</v>
+        <v>482.4</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>496.88</v>
+        <v>497.13</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,20 +11541,20 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>481.2</v>
+        <v>487.1</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>470.21</v>
+        <v>471.82</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>476.02</v>
+        <v>476.45</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>558.36</v>
+        <v>557.65</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>821.85</v>
+        <v>821.3</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>750.6900000000001</v>
+        <v>757.42</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>713.34</v>
+        <v>717.5700000000001</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>670.55</v>
+        <v>672.05</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>245.76</v>
+        <v>241.02</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>247.2</v>
+        <v>246.61</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>249.88</v>
+        <v>249.53</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>310.96</v>
+        <v>310.26</v>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>509.5</v>
+        <v>503.8</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>488.66</v>
+        <v>490.1</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>461.44</v>
+        <v>463.1</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>432.55</v>
+        <v>433.26</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>497.7</v>
+        <v>497</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>480.28</v>
+        <v>481.87</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>473.69</v>
+        <v>474.6</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>578.14</v>
+        <v>577.33</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 05-May-2026  16:30:51    |    Closing Price Date: 05-May-2026</t>
+          <t>Scan Run: 06-May-2026  16:25:35    |    Closing Price Date: 06-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>80</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>79.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>52</v>
+        <v>55.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>05-May-2026  16:30:51</t>
+          <t>06-May-2026  16:25:35</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 80.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 91.6% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 79.6% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 92.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 55.6% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 200 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 229 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 199 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 231 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 130 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 139 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>621</v>
+        <v>638.25</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>582.5</v>
+        <v>587.8099999999999</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>574.33</v>
+        <v>576.83</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>687.15</v>
+        <v>686.67</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>458.8</v>
+        <v>460.05</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>439.98</v>
+        <v>441.89</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>436.17</v>
+        <v>437.11</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>453.14</v>
+        <v>453.21</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>391.35</v>
+        <v>400.45</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>371.46</v>
+        <v>374.22</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>367.45</v>
+        <v>368.75</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>401.1</v>
+        <v>401.09</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>767.45</v>
+        <v>788.45</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>709.99</v>
+        <v>720.78</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>700.3099999999999</v>
+        <v>705.4</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>739.35</v>
+        <v>739.85</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2656.7</v>
+        <v>2685.8</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2449.79</v>
+        <v>2472.27</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2298.76</v>
+        <v>2313.94</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1848.74</v>
+        <v>1857.07</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>357.65</v>
+        <v>355.95</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>317.08</v>
+        <v>320.78</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>302.71</v>
+        <v>304.8</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>304.16</v>
+        <v>304.67</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1221.5</v>
+        <v>1232.7</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1167.53</v>
+        <v>1173.74</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1106.7</v>
+        <v>1111.64</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>949.71</v>
+        <v>952.52</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>877.75</v>
+        <v>852.65</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>840.54</v>
+        <v>841.7</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>817.92</v>
+        <v>819.29</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>866.24</v>
+        <v>866.1</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1094,9 +1094,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>533.4</v>
+        <v>542.15</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>507.38</v>
+        <v>510.69</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>500.19</v>
+        <v>501.83</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>558.1799999999999</v>
+        <v>558.02</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1076.6</v>
+        <v>1125</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1036.72</v>
+        <v>1045.13</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>997.0700000000001</v>
+        <v>1002.08</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>970.7</v>
+        <v>972.24</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.6</v>
+        <v>9.73</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>9.16</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>9.19</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17.22</v>
+        <v>17.15</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>539.05</v>
+        <v>544.8</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>523.45</v>
+        <v>525.49</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>502.72</v>
+        <v>504.37</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>501.9</v>
+        <v>502.33</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1359.3</v>
+        <v>1360.4</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1311.1</v>
+        <v>1315.79</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1288.55</v>
+        <v>1291.37</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1188.56</v>
+        <v>1190.27</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>127.78</v>
+        <v>132.06</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>120.91</v>
+        <v>121.97</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>119.78</v>
+        <v>120.26</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>133.33</v>
+        <v>133.32</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>621.6</v>
+        <v>621.25</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>604.89</v>
+        <v>606.45</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>590.83</v>
+        <v>592.03</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>587.74</v>
+        <v>588.08</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,34 +1421,34 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>436.3</v>
+        <v>480</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>446.85</v>
+        <v>450.01</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>446.24</v>
+        <v>447.56</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>468.4</v>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>468.52</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J17" s="14" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>394.1</v>
+        <v>389.7</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>386.6</v>
+        <v>386.9</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>370.93</v>
+        <v>371.67</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>345.15</v>
+        <v>345.59</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>134.42</v>
+        <v>138.02</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>131.32</v>
+        <v>132.23</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>131.98</v>
+        <v>132.3</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>161.13</v>
+        <v>160.63</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1104.1</v>
+        <v>1088.2</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1072.96</v>
+        <v>1074.41</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1020.36</v>
+        <v>1023.02</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>971.42</v>
+        <v>972.58</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,29 +1597,29 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>861.5</v>
+        <v>880.4</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>862.28</v>
+        <v>864</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>877.51</v>
+        <v>877.63</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1056.99</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1055.23</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1169.7</v>
+        <v>1150.8</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1063.51</v>
+        <v>1071.82</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>1017.86</v>
+        <v>1023.08</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>949.52</v>
+        <v>951.52</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1326.1</v>
+        <v>1348.4</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1368.16</v>
+        <v>1366.28</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1282.53</v>
+        <v>1285.11</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1001.51</v>
+        <v>1004.96</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>13.78</v>
+        <v>14.08</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.37</v>
+        <v>14.34</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>14.93</v>
+        <v>14.9</v>
       </c>
       <c r="F24" s="11" t="n">
         <v/>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>359.05</v>
+        <v>364.4</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>336.82</v>
+        <v>339.45</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>332.84</v>
+        <v>334.07</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>446.7</v>
+        <v>445.88</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>2153.8</v>
+        <v>2194.3</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>1964.72</v>
+        <v>1986.59</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1786.59</v>
+        <v>1802.58</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1642.5</v>
+        <v>1647.99</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>416.2</v>
+        <v>418.15</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>389.64</v>
+        <v>392.35</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>386.69</v>
+        <v>387.92</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>465.29</v>
+        <v>464.82</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1462</v>
+        <v>1492.4</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1251.7</v>
+        <v>1274.62</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1170.08</v>
+        <v>1182.72</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1246.51</v>
+        <v>1248.95</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>557.7</v>
+        <v>559</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>493.19</v>
+        <v>503.89</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>479.48</v>
+        <v>484.98</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>535.87</v>
+        <v>536.15</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>621.1</v>
+        <v>635.6</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>604.61</v>
+        <v>607.5599999999999</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>599.1</v>
+        <v>600.53</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>606.49</v>
+        <v>606.78</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>213.26</v>
+        <v>222.12</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>209.89</v>
+        <v>211.05</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>199.05</v>
+        <v>199.96</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>167.7</v>
+        <v>168.25</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,24 +2081,24 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2939.8</v>
+        <v>2773.3</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2837.96</v>
+        <v>2852.93</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2658.47</v>
+        <v>2679.28</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2742.93</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2746.7</v>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>952.25</v>
+        <v>976</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>928.59</v>
+        <v>933.11</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>938.04</v>
+        <v>939.53</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1058.68</v>
+        <v>1057.86</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>555.7</v>
+        <v>560.1</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>583.45</v>
+        <v>581.22</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>590.76</v>
+        <v>589.5599999999999</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>578.65</v>
+        <v>578.47</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>518.1</v>
+        <v>544.85</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>490.51</v>
+        <v>496.94</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>476.52</v>
+        <v>480.2</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>515.21</v>
+        <v>515.37</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1430.4</v>
+        <v>1443.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1363.71</v>
+        <v>1371.31</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1341.03</v>
+        <v>1345.05</v>
       </c>
       <c r="F36" s="11" t="n">
         <v/>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>482.85</v>
+        <v>477.6</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>471.4</v>
+        <v>471.99</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>459.58</v>
+        <v>460.28</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>433.81</v>
+        <v>434.24</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>286.6</v>
+        <v>291.15</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>298.3</v>
+        <v>296.9</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>301.98</v>
+        <v>301.11</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>348.15</v>
+        <v>347.01</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>386.1</v>
+        <v>371.95</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>388.02</v>
+        <v>386.49</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>390.38</v>
+        <v>389.66</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>394.16</v>
+        <v>393.94</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2433,24 +2433,24 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1645.6</v>
+        <v>1807.3</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1717.32</v>
+        <v>1718.19</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1846.46</v>
+        <v>1836.59</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2127.83</v>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2119.68</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>349.05</v>
+        <v>345</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>318.64</v>
+        <v>321.15</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>298.95</v>
+        <v>300.76</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>276.51</v>
+        <v>277.19</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,24 +2521,24 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>413.7</v>
+        <v>425.75</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>419.41</v>
+        <v>420.01</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>431.73</v>
+        <v>431.5</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>509.82</v>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>508.99</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>912.75</v>
+        <v>944.1</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>700.29</v>
+        <v>723.51</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>649.96</v>
+        <v>661.5</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>706.91</v>
+        <v>709.27</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,29 +2609,29 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1160.7</v>
+        <v>1274.7</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1193.03</v>
+        <v>1200.81</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1243.58</v>
+        <v>1244.8</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1458.37</v>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1456.55</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>411.55</v>
+        <v>415.9</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>362.93</v>
+        <v>367.97</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>346.06</v>
+        <v>348.8</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>389.38</v>
+        <v>389.64</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,29 +2697,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>180.57</v>
+        <v>189.78</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>186.09</v>
+        <v>186.44</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>182.94</v>
+        <v>183.21</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>166.53</v>
-      </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>166.76</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>732.95</v>
+        <v>779</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>719.78</v>
+        <v>725.42</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>723.64</v>
+        <v>725.8099999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>756.3</v>
+        <v>756.53</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2766,9 +2766,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1082.3</v>
+        <v>1089.7</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1042.44</v>
+        <v>1046.94</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1040.6</v>
+        <v>1042.53</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1206.24</v>
+        <v>1205.09</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>167.32</v>
+        <v>177.13</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>153.9</v>
+        <v>156.11</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>144.16</v>
+        <v>145.45</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>137.23</v>
+        <v>137.63</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>469.55</v>
+        <v>479.95</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>453.28</v>
+        <v>455.82</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>444.95</v>
+        <v>446.33</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>454.33</v>
+        <v>454.58</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>186.14</v>
+        <v>189.04</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>172.82</v>
+        <v>174.36</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>176.27</v>
+        <v>176.77</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>213.51</v>
+        <v>213.26</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,29 +2961,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1073.7</v>
+        <v>1096.5</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>1083.28</v>
+        <v>1084.54</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1091.59</v>
+        <v>1091.78</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1169.82</v>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1169.09</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>12222</v>
+        <v>12383</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>11082.9</v>
+        <v>11206.72</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>10360.49</v>
+        <v>10439.81</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8931.889999999999</v>
+        <v>8966.23</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3049,24 +3049,24 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>220.64</v>
+        <v>228.79</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>223.49</v>
+        <v>224.16</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>216.61</v>
+        <v>217.44</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>211.94</v>
-      </c>
-      <c r="G54" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>212.25</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7.79</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>7.66</v>
+        <v>7.71</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>7.5</v>
+        <v>7.54</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8.289999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3137,24 +3137,24 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>114.73</v>
+        <v>120.08</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>116.5</v>
+        <v>116.84</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>114.01</v>
+        <v>114.24</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>110.01</v>
-      </c>
-      <c r="G56" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>110.11</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>121.76</v>
+        <v>120.87</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>110.37</v>
+        <v>111.37</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>104.07</v>
+        <v>104.73</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>113.94</v>
+        <v>114</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>93.29000000000001</v>
+        <v>93.61</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>82.56</v>
+        <v>83.61</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>78.73999999999999</v>
+        <v>79.33</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>84.25</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3269,29 +3269,29 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>48.59</v>
+        <v>58.3</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>48.65</v>
+        <v>49.57</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>53.98</v>
+        <v>54.15</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>77.02</v>
-      </c>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H59" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>76.84</v>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I59" s="13" t="inlineStr">
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1207.1</v>
+        <v>1210.8</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1216.86</v>
+        <v>1216.28</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1177.82</v>
+        <v>1179.11</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1157.72</v>
+        <v>1158.24</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>211.51</v>
+        <v>211.39</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>200.27</v>
+        <v>202.35</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>185.43</v>
+        <v>187.44</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>200.98</v>
+        <v>201.19</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>1349.1</v>
+        <v>1364</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1164.57</v>
+        <v>1183.56</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1085.44</v>
+        <v>1096.37</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1316.11</v>
+        <v>1316.58</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>70.55</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>65.2</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>63.19</v>
+        <v>63.6</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>62.23</v>
+        <v>62.34</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2362</v>
+        <v>2391.6</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2444.62</v>
+        <v>2439.57</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2430.76</v>
+        <v>2429.22</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2572.6</v>
+        <v>2570.8</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>505.75</v>
+        <v>520.95</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>493.75</v>
+        <v>496.34</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>492.88</v>
+        <v>493.98</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>531.73</v>
+        <v>531.63</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>368.3</v>
+        <v>371.45</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>359.86</v>
+        <v>360.96</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>360.52</v>
+        <v>360.95</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>396.86</v>
+        <v>396.61</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>2244.1</v>
+        <v>2256.4</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2191.49</v>
+        <v>2197.68</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2170.68</v>
+        <v>2174.04</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2072.69</v>
+        <v>2074.52</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>4575.1</v>
+        <v>4658.8</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>4680.11</v>
+        <v>4678.08</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4551.12</v>
+        <v>4555.34</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4483.29</v>
+        <v>4485.04</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>952.75</v>
+        <v>983.8</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>897.0599999999999</v>
+        <v>905.3200000000001</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>905.52</v>
+        <v>908.59</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1026.37</v>
+        <v>1025.94</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>521.55</v>
+        <v>517.4</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>499.34</v>
+        <v>501.06</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>493.02</v>
+        <v>493.98</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>542.37</v>
+        <v>542.12</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,24 +3797,24 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>899.1</v>
+        <v>914.8</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>902.15</v>
+        <v>903.62</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>915.4400000000001</v>
+        <v>915.03</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1027.73</v>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1025.4</v>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>108.24</v>
+        <v>110.81</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>106.54</v>
+        <v>106.94</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>106.29</v>
+        <v>106.47</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>109.87</v>
+        <v>109.88</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3866,9 +3866,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J72" s="14" t="inlineStr">
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>1081.8</v>
+        <v>1085</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>989.17</v>
+        <v>1001.92</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>959.85</v>
+        <v>967.33</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>947.51</v>
+        <v>949.65</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>877.15</v>
+        <v>843.5</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>803.09</v>
+        <v>806.9400000000001</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>703.62</v>
+        <v>709.11</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>596.61</v>
+        <v>599.0700000000001</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>656.45</v>
+        <v>679.55</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>639.77</v>
+        <v>643.5599999999999</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>646</v>
+        <v>647.3200000000001</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>745.9400000000001</v>
+        <v>745.28</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1057.9</v>
+        <v>1033.9</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1025.64</v>
+        <v>1026.43</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>950.33</v>
+        <v>953.61</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1036.01</v>
+        <v>1035.98</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4042,9 +4042,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>4477.3</v>
+        <v>5044</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>3992.54</v>
+        <v>4099.19</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>3870.21</v>
+        <v>3922.18</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3647.6</v>
+        <v>3665.03</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,29 +4105,29 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>624.45</v>
+        <v>666.7</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>625.4</v>
+        <v>629.33</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>631.7</v>
+        <v>633.0700000000001</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>695.89</v>
-      </c>
-      <c r="G78" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H78" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>695.6</v>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>59.45</v>
+        <v>60.38</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>57.46</v>
+        <v>57.74</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>56.85</v>
+        <v>56.98</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>58.85</v>
+        <v>58.87</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>680.6</v>
+        <v>684.35</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>691.79</v>
+        <v>691.08</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>680.2</v>
+        <v>680.37</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>746.35</v>
+        <v>745.73</v>
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>168.43</v>
+        <v>173.17</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>158.71</v>
+        <v>160.09</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>155.94</v>
+        <v>156.62</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>179.6</v>
+        <v>179.54</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>233.28</v>
+        <v>231.46</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>213.08</v>
+        <v>214.83</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>209.32</v>
+        <v>210.19</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>237.49</v>
+        <v>237.43</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>157.86</v>
+        <v>156.63</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>150.6</v>
+        <v>151.18</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>144.15</v>
+        <v>144.64</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>128.44</v>
+        <v>128.72</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>483.2</v>
+        <v>498.35</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>461.52</v>
+        <v>465.86</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>451.43</v>
+        <v>453.97</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>473.79</v>
+        <v>473.99</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4413,29 +4413,29 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>157.83</v>
+        <v>158.99</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>156.16</v>
+        <v>156.43</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>158.82</v>
+        <v>158.83</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>160.98</v>
+        <v>160.96</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H85" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
@@ -4457,17 +4457,17 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>173.5</v>
+        <v>177.92</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>169.27</v>
+        <v>170.1</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>167.25</v>
+        <v>167.67</v>
       </c>
       <c r="F86" s="11" t="n">
         <v>177.82</v>
@@ -4482,9 +4482,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I86" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
@@ -4501,29 +4501,29 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>958.85</v>
+        <v>1011.7</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>965.0700000000001</v>
+        <v>970.84</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>987.34</v>
+        <v>988.1</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1075.09</v>
-      </c>
-      <c r="G87" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H87" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1073.55</v>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr">
@@ -4545,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>611.55</v>
+        <v>627.9</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>585.03</v>
+        <v>590.14</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>580.76</v>
+        <v>583.1799999999999</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>756.83</v>
+        <v>753.95</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>618.35</v>
+        <v>620.6</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>573.26</v>
+        <v>578.33</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>574.24</v>
+        <v>576.11</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>606.36</v>
+        <v>606.17</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,20 +4633,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>141.59</v>
+        <v>140.43</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>130.03</v>
+        <v>131.02</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>130.79</v>
+        <v>131.17</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>135.97</v>
+        <v>136.01</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>355.35</v>
+        <v>359.85</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>350</v>
+        <v>350.94</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>348.6</v>
+        <v>349.04</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>399.66</v>
+        <v>399.26</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,20 +4721,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>197.05</v>
+        <v>211.34</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>185.93</v>
+        <v>188.35</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>186.17</v>
+        <v>187.16</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>230.9</v>
+        <v>230.7</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>23.58</v>
+        <v>24.15</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>20.18</v>
+        <v>20.56</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>18.83</v>
+        <v>19.03</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>21.69</v>
+        <v>21.71</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1226.4</v>
+        <v>1223.4</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1128.5</v>
+        <v>1137.54</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1126.23</v>
+        <v>1130.04</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1331.7</v>
+        <v>1330.62</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>326.85</v>
+        <v>332.5</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>307.16</v>
+        <v>309.57</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>303.21</v>
+        <v>304.36</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>304.32</v>
+        <v>304.6</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>46.67</v>
+        <v>47.11</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>45.92</v>
+        <v>46.03</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>45.38</v>
+        <v>45.45</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>50.66</v>
+        <v>50.62</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>1033.5</v>
+        <v>1092.9</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>976.9</v>
+        <v>987.9400000000001</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>941.8099999999999</v>
+        <v>947.73</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>907.79</v>
+        <v>909.63</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>835.9</v>
+        <v>839.9</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>798.84</v>
+        <v>802.75</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>776.86</v>
+        <v>779.33</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>798.91</v>
+        <v>799.3200000000001</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1421.9</v>
+        <v>1447.9</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1461.38</v>
+        <v>1460.09</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1379.94</v>
+        <v>1382.6</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1193.19</v>
+        <v>1195.73</v>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
@@ -5073,29 +5073,29 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>863</v>
+        <v>897.25</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>845.5599999999999</v>
+        <v>850.48</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>870.46</v>
+        <v>871.51</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1014.45</v>
+        <v>1013.29</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H100" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I100" s="13" t="inlineStr">
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>290.75</v>
+        <v>290.35</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>269.49</v>
+        <v>272.4</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>264.69</v>
+        <v>266.22</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>272.6</v>
+        <v>272.83</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>4297.4</v>
+        <v>4394.9</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>4146.22</v>
+        <v>4169.91</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3934.28</v>
+        <v>3952.35</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3735.68</v>
+        <v>3742.24</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>871.05</v>
+        <v>872.75</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>742.42</v>
+        <v>754.83</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>717.77</v>
+        <v>723.85</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>756.4</v>
+        <v>757.5599999999999</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>190.09</v>
+        <v>194.18</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>172.1</v>
+        <v>174.2</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>167.32</v>
+        <v>168.37</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>176.51</v>
+        <v>176.69</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>421.25</v>
+        <v>416.4</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>393.01</v>
+        <v>395.24</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>377.75</v>
+        <v>379.27</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>400.81</v>
+        <v>400.97</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1082.4</v>
+        <v>1075.6</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>1034.96</v>
+        <v>1038.83</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>965.91</v>
+        <v>970.21</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>937.86</v>
+        <v>939.23</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,29 +5381,29 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>507.25</v>
+        <v>513.9</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>504.53</v>
+        <v>505.42</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>508.67</v>
+        <v>508.88</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>574.14</v>
+        <v>573.54</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H107" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H107" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr">
@@ -5425,29 +5425,29 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>650.4</v>
+        <v>663.6</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>645.08</v>
+        <v>646.85</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>655.97</v>
+        <v>656.26</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>746.54</v>
+        <v>745.72</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H108" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H108" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I108" s="13" t="inlineStr">
@@ -5469,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>370.5</v>
+        <v>376.2</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>362.39</v>
+        <v>363.71</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>352.67</v>
+        <v>353.59</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>356.03</v>
+        <v>356.23</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>82.18000000000001</v>
+        <v>83.97</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>73.69</v>
+        <v>74.67</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>69.47</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>81.66</v>
+        <v>81.69</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,29 +5557,29 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>32.87</v>
+        <v>34.07</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>32.46</v>
+        <v>32.61</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>33.26</v>
+        <v>33.29</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>42.03</v>
+        <v>41.95</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H111" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H111" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I111" s="13" t="inlineStr">
@@ -5601,29 +5601,29 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>123.41</v>
+        <v>124.84</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>123.53</v>
+        <v>123.66</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>124.39</v>
+        <v>124.41</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>114.85</v>
-      </c>
-      <c r="G112" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H112" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>114.95</v>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I112" s="12" t="inlineStr">
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>447.85</v>
+        <v>459.4</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>430.94</v>
+        <v>435.82</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>406.29</v>
+        <v>410.29</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>419.66</v>
+        <v>420.43</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>25.93</v>
+        <v>26.5</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>25.12</v>
+        <v>25.25</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>24.72</v>
+        <v>24.79</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>33.6</v>
+        <v>33.53</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,24 +5733,24 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>530.45</v>
+        <v>539.45</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>537.26</v>
+        <v>537.47</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>560.51</v>
+        <v>559.6799999999999</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>685.92</v>
-      </c>
-      <c r="G115" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>684.46</v>
+      </c>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
@@ -5777,29 +5777,29 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>125.35</v>
+        <v>132.37</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>123.55</v>
+        <v>124.39</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>126.68</v>
+        <v>126.9</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>161.23</v>
+        <v>160.95</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H116" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H116" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I116" s="13" t="inlineStr">
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>455.85</v>
+        <v>482.35</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>436.89</v>
+        <v>441.22</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>418.83</v>
+        <v>421.32</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>429.11</v>
+        <v>429.64</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>372.4</v>
+        <v>376.85</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>352.91</v>
+        <v>355.19</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>342.78</v>
+        <v>344.12</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>353.11</v>
+        <v>353.34</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1204.9</v>
+        <v>1290.5</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1169.44</v>
+        <v>1180.97</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>1029.58</v>
+        <v>1039.81</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>872.58</v>
+        <v>876.74</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>895.35</v>
+        <v>893.9</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>784.9</v>
+        <v>795.28</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>740.89</v>
+        <v>746.89</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>760.3099999999999</v>
+        <v>761.64</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,29 +5997,29 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>194.13</v>
+        <v>201.43</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>194.79</v>
+        <v>195.42</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>195.6</v>
+        <v>195.83</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>217.84</v>
-      </c>
-      <c r="G121" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H121" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>217.68</v>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I121" s="13" t="inlineStr">
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>269.6</v>
+        <v>266.4</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>253.24</v>
+        <v>254.5</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>235.57</v>
+        <v>236.78</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>205.75</v>
+        <v>206.35</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>977.3</v>
+        <v>994.95</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>922.0700000000001</v>
+        <v>929.01</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>888.09</v>
+        <v>892.28</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>958.77</v>
+        <v>959.13</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1524.3</v>
+        <v>1547.4</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1362.35</v>
+        <v>1379.97</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1244.48</v>
+        <v>1256.36</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1175.74</v>
+        <v>1179.44</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>170.09</v>
+        <v>170.52</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>166.43</v>
+        <v>166.73</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>169.04</v>
+        <v>168.94</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>188.01</v>
+        <v>187.6</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>14583</v>
+        <v>14881</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>14234.77</v>
+        <v>14296.32</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>14227.87</v>
+        <v>14253.48</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>14796.72</v>
+        <v>14797.56</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6242,9 +6242,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I126" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J126" s="14" t="inlineStr">
@@ -6261,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>144.41</v>
+        <v>154.55</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>138.88</v>
+        <v>140.37</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>135.95</v>
+        <v>136.68</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>161.22</v>
+        <v>161.16</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>164.51</v>
+        <v>169.72</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>171.12</v>
+        <v>170.99</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>179.17</v>
+        <v>178.8</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>206.84</v>
+        <v>206.47</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>59.54</v>
+        <v>57.97</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>54.49</v>
+        <v>54.83</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>51.01</v>
+        <v>51.29</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>55</v>
+        <v>55.03</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>67.69</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>63.57</v>
+        <v>63.97</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>58.67</v>
+        <v>59.03</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>60.03</v>
+        <v>60.11</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6437,29 +6437,29 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1561.7</v>
+        <v>1644.2</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1668</v>
+        <v>1665.73</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>1638.06</v>
+        <v>1638.3</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1389.04</v>
+        <v>1391.58</v>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H131" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>1416.7</v>
+        <v>1437.1</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1399.22</v>
+        <v>1402.83</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1223.68</v>
+        <v>1232.05</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1191.99</v>
+        <v>1194.43</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,29 +6525,29 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>309.05</v>
+        <v>313.4</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>313.96</v>
+        <v>313.91</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>310.13</v>
+        <v>310.26</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>323.62</v>
+        <v>323.52</v>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H133" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H133" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I133" s="13" t="inlineStr">
@@ -6569,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>439.95</v>
+        <v>446.05</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>437.12</v>
+        <v>437.75</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>437.88</v>
+        <v>438.05</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>469.2</v>
+        <v>468.62</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>6266</v>
+        <v>6286.5</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>5263.38</v>
+        <v>5360.82</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>4432.57</v>
+        <v>4505.27</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>3043.92</v>
+        <v>3076.19</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,24 +6657,24 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>327.25</v>
+        <v>337.6</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>332.73</v>
+        <v>333.2</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>341.5</v>
+        <v>341.35</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>359.96</v>
-      </c>
-      <c r="G136" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>359.73</v>
+      </c>
+      <c r="G136" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>125.49</v>
+        <v>127.51</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>108.36</v>
+        <v>110.18</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>104.95</v>
+        <v>105.83</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>126.34</v>
+        <v>126.35</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6726,9 +6726,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I137" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J137" s="14" t="inlineStr">
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1594.5</v>
+        <v>1602.7</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1431.82</v>
+        <v>1448.1</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1376.55</v>
+        <v>1385.42</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1336.96</v>
+        <v>1339.61</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>186.92</v>
+        <v>196.2</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>182.14</v>
+        <v>183.48</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>177.86</v>
+        <v>178.58</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>187.09</v>
+        <v>187.18</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6814,9 +6814,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I139" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J139" s="14" t="inlineStr">
@@ -6833,29 +6833,29 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1659</v>
+        <v>1692.7</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1661.96</v>
+        <v>1664.89</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1674.8</v>
+        <v>1675.5</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1965.79</v>
-      </c>
-      <c r="G140" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H140" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1963.08</v>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I140" s="13" t="inlineStr">
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>404.9</v>
+        <v>413.75</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>388.19</v>
+        <v>390.62</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>386.69</v>
+        <v>387.75</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>423.7</v>
+        <v>423.6</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,24 +6921,24 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>858.9</v>
+        <v>882.55</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>870.13</v>
+        <v>871.3099999999999</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>854.62</v>
+        <v>855.71</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>826.6799999999999</v>
-      </c>
-      <c r="G142" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>827.24</v>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>396.85</v>
+        <v>397</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>370.89</v>
+        <v>373.38</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>352.72</v>
+        <v>354.46</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>350.59</v>
+        <v>351.05</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>199.68</v>
+        <v>203.79</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>195.76</v>
+        <v>196.61</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>199.31</v>
+        <v>199.38</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>233.77</v>
+        <v>233.1</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1708.7</v>
+        <v>1697.6</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1546.31</v>
+        <v>1560.72</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1431.25</v>
+        <v>1441.7</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1398.22</v>
+        <v>1401.2</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1308.4</v>
+        <v>1279.6</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>1189.91</v>
+        <v>1198.46</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1154.93</v>
+        <v>1159.82</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1173.33</v>
+        <v>1174.39</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>78.06999999999999</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>76.22</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>75.95</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>83.52</v>
+        <v>83.48</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>265.75</v>
+        <v>271.8</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>262.07</v>
+        <v>263</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>258.27</v>
+        <v>258.8</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>265.18</v>
+        <v>265.25</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7229,29 +7229,29 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>34.27</v>
+        <v>34.76</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>34.19</v>
+        <v>34.25</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>34.41</v>
+        <v>34.42</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>41.26</v>
+        <v>41.19</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H149" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H149" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I149" s="13" t="inlineStr">
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>434.7</v>
+        <v>447.95</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>400.11</v>
+        <v>404.67</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>394.21</v>
+        <v>396.32</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>476.62</v>
+        <v>476.34</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>627.35</v>
+        <v>661.55</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>583.65</v>
+        <v>591.0700000000001</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>588.66</v>
+        <v>591.51</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>712.59</v>
+        <v>712.08</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,24 +7361,24 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>140.43</v>
+        <v>142.95</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>142.78</v>
+        <v>142.8</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>145.49</v>
+        <v>145.39</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>188.45</v>
-      </c>
-      <c r="G152" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>187.99</v>
+      </c>
+      <c r="G152" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>410.25</v>
+        <v>422.45</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>392.55</v>
+        <v>395.4</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>379.72</v>
+        <v>381.39</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>499.59</v>
+        <v>498.82</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>689.2</v>
+        <v>697.5</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>649.4</v>
+        <v>653.98</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>615.46</v>
+        <v>618.67</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>595.09</v>
+        <v>596.11</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>9.41</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>9.32</v>
+        <v>9.33</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>10.74</v>
+        <v>10.73</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>215.87</v>
+        <v>219.25</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>207.32</v>
+        <v>208.46</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>205.46</v>
+        <v>206</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>240.05</v>
+        <v>239.85</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>215.9</v>
+        <v>218.46</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>192.48</v>
+        <v>194.95</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>179.14</v>
+        <v>180.68</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>166.94</v>
+        <v>167.45</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,29 +7625,29 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>123.24</v>
+        <v>126.41</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>126.5</v>
+        <v>126.49</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>124.9</v>
+        <v>124.96</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>140.8</v>
+        <v>140.66</v>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H158" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H158" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I158" s="13" t="inlineStr">
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>794.55</v>
+        <v>805.1</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>765.63</v>
+        <v>769.39</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>720.23</v>
+        <v>723.5599999999999</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>683.92</v>
+        <v>685.12</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>28.66</v>
+        <v>28.99</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>27.71</v>
+        <v>27.84</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>27.32</v>
+        <v>27.38</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>31.87</v>
+        <v>31.84</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,29 +7757,29 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1535.6</v>
+        <v>1565.6</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1548.32</v>
+        <v>1549.96</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1539.64</v>
+        <v>1540.66</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1485.77</v>
-      </c>
-      <c r="G161" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H161" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1486.57</v>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H161" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>927.3</v>
+        <v>949.5</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>892.85</v>
+        <v>898.25</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>864.45</v>
+        <v>867.79</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>922.5700000000001</v>
+        <v>922.84</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>2593.9</v>
+        <v>2565.3</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>2366.91</v>
+        <v>2385.81</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>2235.38</v>
+        <v>2248.32</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2360.38</v>
+        <v>2362.42</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>585.05</v>
+        <v>585.9</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>581.62</v>
+        <v>582.03</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>576.89</v>
+        <v>577.24</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>555.3</v>
+        <v>555.6</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>262.2</v>
+        <v>261.95</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>255.11</v>
+        <v>255.76</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>250.59</v>
+        <v>251.04</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>275.49</v>
+        <v>275.35</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>132.33</v>
+        <v>133.22</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>130.36</v>
+        <v>130.63</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>128.48</v>
+        <v>128.66</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>134.02</v>
+        <v>134.01</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>3375.2</v>
+        <v>3388.3</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>3171.49</v>
+        <v>3192.14</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>3041.57</v>
+        <v>3055.17</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>2765.52</v>
+        <v>2771.72</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>2900.2</v>
+        <v>2908</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2689.55</v>
+        <v>2710.35</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2550.26</v>
+        <v>2564.28</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>2527.63</v>
+        <v>2531.41</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>218.7</v>
+        <v>221.98</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>211.14</v>
+        <v>212.17</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>208.91</v>
+        <v>209.42</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>234.38</v>
+        <v>234.25</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8153,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>223.41</v>
+        <v>222.82</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>197.99</v>
+        <v>200.36</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>194.93</v>
+        <v>196.02</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>241.12</v>
+        <v>240.93</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8197,29 +8197,29 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>126</v>
+        <v>130.9</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>126.77</v>
+        <v>127.12</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>127.7</v>
+        <v>127.77</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>132.95</v>
-      </c>
-      <c r="G171" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H171" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>132.87</v>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I171" s="13" t="inlineStr">
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>265</v>
+        <v>263.95</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>259.76</v>
+        <v>260.16</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>258.06</v>
+        <v>258.29</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>269.68</v>
+        <v>269.62</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>604.9</v>
+        <v>637.85</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>574.22</v>
+        <v>580.28</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>559.66</v>
+        <v>562.73</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>580.21</v>
+        <v>580.78</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>2742.1</v>
+        <v>2737</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2520.87</v>
+        <v>2541.46</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2407.45</v>
+        <v>2420.38</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2412.06</v>
+        <v>2415.29</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>36.08</v>
+        <v>36.81</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>34.06</v>
+        <v>34.46</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>32.99</v>
+        <v>33.24</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>40.28</v>
+        <v>40.2</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8417,17 +8417,17 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>10.08</v>
+        <v>10.18</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>9.630000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>9.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F176" s="11" t="n">
         <v>9.869999999999999</v>
@@ -8461,24 +8461,24 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>791.15</v>
+        <v>828.4</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>800.12</v>
+        <v>802.8099999999999</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>832.9</v>
+        <v>832.72</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1009.46</v>
-      </c>
-      <c r="G177" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1007.66</v>
+      </c>
+      <c r="G177" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>255.95</v>
+        <v>255.9</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>246.11</v>
+        <v>247.04</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>237.1</v>
+        <v>237.83</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>295.22</v>
+        <v>294.82</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>299.65</v>
+        <v>301.85</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>298.83</v>
+        <v>299.12</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>309.99</v>
+        <v>309.67</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>378.63</v>
+        <v>377.87</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8593,29 +8593,29 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>222.55</v>
+        <v>223.94</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>222.44</v>
+        <v>222.58</v>
       </c>
       <c r="E180" s="11" t="n">
         <v>223.83</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>235.33</v>
+        <v>235.22</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H180" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H180" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I180" s="13" t="inlineStr">
@@ -8637,17 +8637,17 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>67.23</v>
+        <v>67.48</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>63.91</v>
+        <v>64.25</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>63.25</v>
+        <v>63.41</v>
       </c>
       <c r="F181" s="11" t="n">
         <v>67.3</v>
@@ -8662,9 +8662,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I181" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I181" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J181" s="14" t="inlineStr">
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>559.2</v>
+        <v>560.9</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>514.91</v>
+        <v>519.29</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>516.09</v>
+        <v>517.85</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>666.6</v>
+        <v>665.55</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>456.35</v>
+        <v>479</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>416.77</v>
+        <v>425.93</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>383.81</v>
+        <v>390.19</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>346.21</v>
+        <v>348.6</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1367.6</v>
+        <v>1478.7</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1489.75</v>
+        <v>1488.7</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1609.78</v>
+        <v>1604.64</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1931.99</v>
+        <v>1927.48</v>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
@@ -8813,29 +8813,29 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>157.87</v>
+        <v>160.2</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>157.99</v>
+        <v>158.2</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>158.34</v>
+        <v>158.41</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>175.29</v>
-      </c>
-      <c r="G185" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H185" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>175.14</v>
+      </c>
+      <c r="G185" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H185" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I185" s="13" t="inlineStr">
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>207.8</v>
+        <v>213.93</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>207.38</v>
+        <v>208</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>204.45</v>
+        <v>204.82</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>194.83</v>
+        <v>195.02</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,24 +8901,24 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>4581.6</v>
+        <v>4663.8</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>4616.83</v>
+        <v>4621.3</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>4498.87</v>
+        <v>4505.34</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>4585.74</v>
-      </c>
-      <c r="G187" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>4586.52</v>
+      </c>
+      <c r="G187" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr">
@@ -8926,9 +8926,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I187" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I187" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J187" s="14" t="inlineStr">
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>3403.8</v>
+        <v>3398.7</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>3436.26</v>
+        <v>3432.69</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>3549.86</v>
+        <v>3543.93</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>4207.37</v>
+        <v>4199.33</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>2526.6</v>
+        <v>2506.6</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>2430.74</v>
+        <v>2437.97</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>2274.35</v>
+        <v>2283.45</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1845.61</v>
+        <v>1852.18</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>345.7</v>
+        <v>344.5</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>321.5</v>
+        <v>323.69</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>317.37</v>
+        <v>318.44</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>330.28</v>
+        <v>330.42</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>2603.1</v>
+        <v>2631.2</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>2295.78</v>
+        <v>2327.72</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2179.7</v>
+        <v>2197.41</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>2095.66</v>
+        <v>2100.99</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9121,29 +9121,29 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>547.9</v>
+        <v>573.05</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>546.47</v>
+        <v>549</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>550.3</v>
+        <v>551.1900000000001</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>682.49</v>
+        <v>681.4</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H192" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H192" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I192" s="13" t="inlineStr">
@@ -9165,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1081.5</v>
+        <v>1119.6</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>1077.73</v>
+        <v>1081.72</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1047.14</v>
+        <v>1049.98</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>927.74</v>
+        <v>929.65</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>879.25</v>
+        <v>904.05</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>850.37</v>
+        <v>855.48</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>849.9299999999999</v>
+        <v>852.0599999999999</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>906.73</v>
+        <v>906.71</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>142.81</v>
+        <v>146.53</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>141.31</v>
+        <v>141.81</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>139.98</v>
+        <v>140.24</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>154.93</v>
+        <v>154.85</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9297,29 +9297,29 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>525.9</v>
+        <v>544.25</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>525.85</v>
+        <v>527.6</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>532.6799999999999</v>
+        <v>533.14</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>602.91</v>
+        <v>602.33</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H196" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H196" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I196" s="13" t="inlineStr">
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>424.4</v>
+        <v>441.9</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>403.56</v>
+        <v>407.21</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>376.18</v>
+        <v>378.76</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>360.78</v>
+        <v>361.58</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>29.48</v>
+        <v>29.14</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>28.11</v>
+        <v>28.21</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>26.93</v>
+        <v>27.02</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>27.71</v>
+        <v>27.72</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>3535.5</v>
+        <v>3562.5</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>3446.41</v>
+        <v>3457.47</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>3268.53</v>
+        <v>3280.06</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>2879.01</v>
+        <v>2885.81</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>483.9</v>
+        <v>490.3</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>442.9</v>
+        <v>447.41</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>409.71</v>
+        <v>412.87</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>428.62</v>
+        <v>429.23</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>40.95</v>
+        <v>42.54</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>39.28</v>
+        <v>39.59</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>39</v>
+        <v>39.14</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>36.36</v>
+        <v>36.42</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>234.35</v>
+        <v>234.39</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>225.69</v>
+        <v>227.01</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>219.78</v>
+        <v>220.76</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>224.59</v>
+        <v>224.74</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>210.5</v>
+        <v>215.79</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>201.88</v>
+        <v>203.21</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>194.69</v>
+        <v>195.52</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>221.42</v>
+        <v>221.36</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>324.8</v>
+        <v>341</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>269.17</v>
+        <v>276.01</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>222.9</v>
+        <v>227.53</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>152.27</v>
+        <v>154.15</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>1052.1</v>
+        <v>1098</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>1016.94</v>
+        <v>1024.66</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>966.45</v>
+        <v>971.61</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>882.39</v>
+        <v>884.53</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>2226.2</v>
+        <v>2327.6</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2186.72</v>
+        <v>2206.13</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>2081.04</v>
+        <v>2097.42</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>2202.19</v>
+        <v>2204.01</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>768.2</v>
+        <v>783.3</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>760.8200000000001</v>
+        <v>762.96</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>756.36</v>
+        <v>757.42</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>803.25</v>
+        <v>803.05</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>938.7</v>
+        <v>945.5</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>873.42</v>
+        <v>880.29</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>864.85</v>
+        <v>868.01</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>989.41</v>
+        <v>988.97</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9869,24 +9869,24 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>140</v>
+        <v>157.08</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>140.33</v>
+        <v>141.93</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>135.18</v>
+        <v>136.03</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>137.71</v>
-      </c>
-      <c r="G209" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>137.9</v>
+      </c>
+      <c r="G209" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H209" s="12" t="inlineStr">
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>350.8</v>
+        <v>396.65</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>281.71</v>
+        <v>292.65</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>259.73</v>
+        <v>265.1</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>256.09</v>
+        <v>257.48</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,29 +9957,29 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>335.7</v>
+        <v>351.3</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>337.81</v>
+        <v>339.1</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>345.56</v>
+        <v>345.79</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="G211" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H211" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>387.19</v>
+      </c>
+      <c r="G211" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H211" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I211" s="13" t="inlineStr">
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>690.75</